--- a/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3AB06DBF-E792-462F-BDF6-2291D7B42BE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{670F2B53-8660-46C7-8D85-E7E457F7D74F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{4CCE5B53-B51A-41F6-B066-2F3EAC5F6A72}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{A8DFADBD-D290-4AB4-8530-B1621B1DD8C5}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1406" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1510" uniqueCount="483">
   <si>
     <t>~tradelinks_dins</t>
   </si>
@@ -72,364 +72,406 @@
     <t>ELC</t>
   </si>
   <si>
-    <t>e_PL15-400_POL</t>
-  </si>
-  <si>
-    <t>e_PL36-400_POL</t>
-  </si>
-  <si>
-    <t>g_PL15-400_POL-PL36-400_POL</t>
+    <t>e_BielskoBiala_POL</t>
+  </si>
+  <si>
+    <t>e_Katowice_POL</t>
+  </si>
+  <si>
+    <t>g_BielskoBiala_POL-Katowice_POL</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
-    <t>e_PL7-400_POL</t>
-  </si>
-  <si>
-    <t>g_PL15-400_POL-PL7-400_POL</t>
-  </si>
-  <si>
-    <t>e_w112614319-400_POL</t>
-  </si>
-  <si>
-    <t>g_PL15-400_POL-w112614319-400_POL</t>
-  </si>
-  <si>
-    <t>e_w178838661-220_POL</t>
-  </si>
-  <si>
-    <t>g_PL15-400_POL-w178838661-220_POL</t>
-  </si>
-  <si>
-    <t>e_w245964556-220_POL</t>
-  </si>
-  <si>
-    <t>g_PL15-400_POL-w245964556-220_POL</t>
-  </si>
-  <si>
-    <t>e_w46092396-400_POL</t>
-  </si>
-  <si>
-    <t>g_PL15-400_POL-w46092396-400_POL</t>
-  </si>
-  <si>
-    <t>e_w658600169-400_POL</t>
-  </si>
-  <si>
-    <t>g_PL15-400_POL-w658600169-400_POL</t>
-  </si>
-  <si>
-    <t>e_PL18-400_POL</t>
-  </si>
-  <si>
-    <t>e_w158232924-220_POL</t>
-  </si>
-  <si>
-    <t>g_PL18-400_POL-w158232924-220_POL</t>
-  </si>
-  <si>
-    <t>e_PL34-400_POL</t>
-  </si>
-  <si>
-    <t>g_PL34-400_POL-PL36-400_POL</t>
-  </si>
-  <si>
-    <t>e_PL46-220_POL</t>
-  </si>
-  <si>
-    <t>g_PL34-400_POL-PL46-220_POL</t>
-  </si>
-  <si>
-    <t>e_w180535363-220_POL</t>
-  </si>
-  <si>
-    <t>g_PL34-400_POL-w180535363-220_POL</t>
-  </si>
-  <si>
-    <t>g_PL36-400_POL-PL46-220_POL</t>
-  </si>
-  <si>
-    <t>e_w170316833-220_POL</t>
-  </si>
-  <si>
-    <t>g_PL36-400_POL-w170316833-220_POL</t>
-  </si>
-  <si>
-    <t>e_w171917072-400_POL</t>
-  </si>
-  <si>
-    <t>g_PL36-400_POL-w171917072-400_POL</t>
-  </si>
-  <si>
-    <t>e_w216060722-220_POL</t>
-  </si>
-  <si>
-    <t>g_PL36-400_POL-w216060722-220_POL</t>
-  </si>
-  <si>
-    <t>e_w336990960-220_POL</t>
-  </si>
-  <si>
-    <t>g_PL46-220_POL-w336990960-220_POL</t>
-  </si>
-  <si>
-    <t>g_PL7-400_POL-w245964556-220_POL</t>
-  </si>
-  <si>
-    <t>g_PL7-400_POL-w46092396-400_POL</t>
-  </si>
-  <si>
-    <t>e_w111615226-380_POL</t>
-  </si>
-  <si>
-    <t>g_w111615226-380_POL-PL34-400_POL</t>
-  </si>
-  <si>
-    <t>g_w111615226-380_POL-w158232924-220_POL</t>
-  </si>
-  <si>
-    <t>g_w111615226-380_POL-w180535363-220_POL</t>
-  </si>
-  <si>
-    <t>e_w101915790-220_POL</t>
-  </si>
-  <si>
-    <t>g_w112614319-400_POL-w101915790-220_POL</t>
-  </si>
-  <si>
-    <t>g_w112614319-400_POL-w46092396-400_POL</t>
-  </si>
-  <si>
-    <t>e_w121656686-220_POL</t>
-  </si>
-  <si>
-    <t>g_w121656686-220_POL-w101915790-220_POL</t>
-  </si>
-  <si>
-    <t>e_w170259740-220_POL</t>
-  </si>
-  <si>
-    <t>g_w121656686-220_POL-w170259740-220_POL</t>
-  </si>
-  <si>
-    <t>e_w303870256-400_POL</t>
-  </si>
-  <si>
-    <t>g_w121656686-220_POL-w303870256-400_POL</t>
-  </si>
-  <si>
-    <t>g_w158232924-220_POL-w180535363-220_POL</t>
-  </si>
-  <si>
-    <t>e_w165763717-220_POL</t>
-  </si>
-  <si>
-    <t>g_w165763717-220_POL-w178838661-220_POL</t>
-  </si>
-  <si>
-    <t>e_w166838338-400_POL</t>
-  </si>
-  <si>
-    <t>e_w215282393-400_POL</t>
-  </si>
-  <si>
-    <t>g_w166838338-400_POL-w215282393-400_POL</t>
-  </si>
-  <si>
-    <t>g_w170316833-220_POL-w658600169-400_POL</t>
-  </si>
-  <si>
-    <t>g_w171917072-400_POL-w170316833-220_POL</t>
-  </si>
-  <si>
-    <t>g_w171917072-400_POL-w216060722-220_POL</t>
-  </si>
-  <si>
-    <t>e_w173613665-220_POL</t>
-  </si>
-  <si>
-    <t>e_w194903381-400_POL</t>
-  </si>
-  <si>
-    <t>g_w173613665-220_POL-w194903381-400_POL</t>
-  </si>
-  <si>
-    <t>g_w178838661-220_POL-w112614319-400_POL</t>
-  </si>
-  <si>
-    <t>g_w178838661-220_POL-w180535363-220_POL</t>
-  </si>
-  <si>
-    <t>e_w255314292_POL</t>
-  </si>
-  <si>
-    <t>g_w178838661-220_POL-w255314292_POL</t>
-  </si>
-  <si>
-    <t>g_w180535363-220_POL-PL15-400_POL</t>
-  </si>
-  <si>
-    <t>g_w180535363-220_POL-PL18-400_POL</t>
-  </si>
-  <si>
-    <t>e_w183945016-220_POL</t>
-  </si>
-  <si>
-    <t>e_w293489607-400_POL</t>
-  </si>
-  <si>
-    <t>g_w183945016-220_POL-w293489607-400_POL</t>
-  </si>
-  <si>
-    <t>e_w40946790-220_POL</t>
-  </si>
-  <si>
-    <t>g_w183945016-220_POL-w40946790-220_POL</t>
-  </si>
-  <si>
-    <t>e_w44389929-220_POL</t>
-  </si>
-  <si>
-    <t>g_w183945016-220_POL-w44389929-220_POL</t>
-  </si>
-  <si>
-    <t>e_w191038569-220_POL</t>
-  </si>
-  <si>
-    <t>g_w191038569-220_POL-w166838338-400_POL</t>
-  </si>
-  <si>
-    <t>e_w199098053-220_POL</t>
-  </si>
-  <si>
-    <t>g_w191038569-220_POL-w199098053-220_POL</t>
-  </si>
-  <si>
-    <t>g_w191038569-220_POL-w215282393-400_POL</t>
-  </si>
-  <si>
-    <t>e_w199098050-220_POL</t>
-  </si>
-  <si>
-    <t>g_w199098050-220_POL-w199098053-220_POL</t>
-  </si>
-  <si>
-    <t>e_w254235846-400_POL</t>
-  </si>
-  <si>
-    <t>g_w199098050-220_POL-w254235846-400_POL</t>
-  </si>
-  <si>
-    <t>e_w198635989-220_POL</t>
-  </si>
-  <si>
-    <t>g_w199098053-220_POL-w198635989-220_POL</t>
-  </si>
-  <si>
-    <t>g_w199098053-220_POL-w254235846-400_POL</t>
-  </si>
-  <si>
-    <t>g_w215282393-400_POL-w199098053-220_POL</t>
-  </si>
-  <si>
-    <t>e_w88544449-220_POL</t>
-  </si>
-  <si>
-    <t>g_w215282393-400_POL-w88544449-220_POL</t>
-  </si>
-  <si>
-    <t>g_w216060722-220_POL-w170316833-220_POL</t>
-  </si>
-  <si>
-    <t>g_w216060722-220_POL-w199098050-220_POL</t>
-  </si>
-  <si>
-    <t>g_w245964556-220_POL-w101915790-220_POL</t>
-  </si>
-  <si>
-    <t>g_w245964556-220_POL-w170316833-220_POL</t>
-  </si>
-  <si>
-    <t>g_w245964556-220_POL-w658600169-400_POL</t>
-  </si>
-  <si>
-    <t>g_w254235846-400_POL-w88544449-220_POL</t>
-  </si>
-  <si>
-    <t>e_w255277953-400_POL</t>
-  </si>
-  <si>
-    <t>g_w255277953-400_POL-PL36-400_POL</t>
-  </si>
-  <si>
-    <t>g_w255277953-400_POL-PL46-220_POL</t>
-  </si>
-  <si>
-    <t>g_w255277953-400_POL-w183945016-220_POL</t>
-  </si>
-  <si>
-    <t>g_w255314292_POL-w112614319-400_POL</t>
-  </si>
-  <si>
-    <t>g_w293489607-400_POL-w40946790-220_POL</t>
-  </si>
-  <si>
-    <t>g_w303870256-400_POL-w170259740-220_POL</t>
-  </si>
-  <si>
-    <t>g_w336990960-220_POL-w183945016-220_POL</t>
-  </si>
-  <si>
-    <t>e_w39428977-400_POL</t>
-  </si>
-  <si>
-    <t>g_w39428977-400_POL-PL18-400_POL</t>
-  </si>
-  <si>
-    <t>g_w39428977-400_POL-w165763717-220_POL</t>
-  </si>
-  <si>
-    <t>g_w39428977-400_POL-w180535363-220_POL</t>
-  </si>
-  <si>
-    <t>g_w40946790-220_POL-w183945016-220_POL</t>
-  </si>
-  <si>
-    <t>g_w40946790-220_POL-w199098050-220_POL</t>
-  </si>
-  <si>
-    <t>g_w40946790-220_POL-w216060722-220_POL</t>
-  </si>
-  <si>
-    <t>e_w87667718-220_POL</t>
-  </si>
-  <si>
-    <t>g_w40946790-220_POL-w87667718-220_POL</t>
-  </si>
-  <si>
-    <t>g_w44389929-220_POL-w40946790-220_POL</t>
-  </si>
-  <si>
-    <t>g_w46092396-400_POL-w658600169-400_POL</t>
-  </si>
-  <si>
-    <t>g_w658600169-400_POL-w121656686-220_POL</t>
-  </si>
-  <si>
-    <t>g_w87667718-220_POL-w191038569-220_POL</t>
-  </si>
-  <si>
-    <t>g_w87667718-220_POL-w215282393-400_POL</t>
-  </si>
-  <si>
-    <t>g_w88544449-220_POL-w121656686-220_POL</t>
-  </si>
-  <si>
-    <t>g_w88544449-220_POL-w173613665-220_POL</t>
-  </si>
-  <si>
-    <t>g_w88544449-220_POL-w194903381-400_POL</t>
+    <t>e_Boleslawiec_POL</t>
+  </si>
+  <si>
+    <t>e_Legnica_POL</t>
+  </si>
+  <si>
+    <t>g_Boleslawiec_POL-Legnica_POL</t>
+  </si>
+  <si>
+    <t>e_Lubin_POL</t>
+  </si>
+  <si>
+    <t>g_Boleslawiec_POL-Lubin_POL</t>
+  </si>
+  <si>
+    <t>e_ZielonaGora_POL</t>
+  </si>
+  <si>
+    <t>g_Boleslawiec_POL-ZielonaGora_POL</t>
+  </si>
+  <si>
+    <t>e_Bydgoszcz_POL</t>
+  </si>
+  <si>
+    <t>e_Gdansk_POL</t>
+  </si>
+  <si>
+    <t>g_Bydgoszcz_POL-Gdansk_POL</t>
+  </si>
+  <si>
+    <t>e_Grudziadz_POL</t>
+  </si>
+  <si>
+    <t>g_Bydgoszcz_POL-Grudziadz_POL</t>
+  </si>
+  <si>
+    <t>e_Kwidzyn_POL</t>
+  </si>
+  <si>
+    <t>g_Bydgoszcz_POL-Kwidzyn_POL</t>
+  </si>
+  <si>
+    <t>e_Poznan_POL</t>
+  </si>
+  <si>
+    <t>g_Bydgoszcz_POL-Poznan_POL</t>
+  </si>
+  <si>
+    <t>e_Czestochowa_POL</t>
+  </si>
+  <si>
+    <t>e_Kielce_POL</t>
+  </si>
+  <si>
+    <t>g_Czestochowa_POL-Kielce_POL</t>
+  </si>
+  <si>
+    <t>e_PiotrkowTrybunalsk_POL</t>
+  </si>
+  <si>
+    <t>g_Czestochowa_POL-PiotrkowTrybunalsk_POL</t>
+  </si>
+  <si>
+    <t>e_Gdynia_POL</t>
+  </si>
+  <si>
+    <t>g_Gdansk_POL-Gdynia_POL</t>
+  </si>
+  <si>
+    <t>g_Gdansk_POL-Grudziadz_POL</t>
+  </si>
+  <si>
+    <t>e_Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>g_Gdansk_POL-Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>e_Gliwice_POL</t>
+  </si>
+  <si>
+    <t>g_Gliwice_POL-Katowice_POL</t>
+  </si>
+  <si>
+    <t>e_GorzowWielkopolski_POL</t>
+  </si>
+  <si>
+    <t>g_GorzowWielkopolski_POL-ZielonaGora_POL</t>
+  </si>
+  <si>
+    <t>e_Plock_POL</t>
+  </si>
+  <si>
+    <t>g_Grudziadz_POL-Plock_POL</t>
+  </si>
+  <si>
+    <t>g_Katowice_POL-Czestochowa_POL</t>
+  </si>
+  <si>
+    <t>g_Katowice_POL-Kielce_POL</t>
+  </si>
+  <si>
+    <t>e_Krakow_POL</t>
+  </si>
+  <si>
+    <t>g_Katowice_POL-Krakow_POL</t>
+  </si>
+  <si>
+    <t>e_Sosnowiec_POL</t>
+  </si>
+  <si>
+    <t>g_Katowice_POL-Sosnowiec_POL</t>
+  </si>
+  <si>
+    <t>e_KedzierzynKozle_POL</t>
+  </si>
+  <si>
+    <t>g_KedzierzynKozle_POL-Sosnowiec_POL</t>
+  </si>
+  <si>
+    <t>e_Mielec_POL</t>
+  </si>
+  <si>
+    <t>g_Kielce_POL-Mielec_POL</t>
+  </si>
+  <si>
+    <t>e_OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>g_Kielce_POL-OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>e_Konin_POL</t>
+  </si>
+  <si>
+    <t>g_Konin_POL-Bydgoszcz_POL</t>
+  </si>
+  <si>
+    <t>g_Konin_POL-PiotrkowTrybunalsk_POL</t>
+  </si>
+  <si>
+    <t>g_Konin_POL-Plock_POL</t>
+  </si>
+  <si>
+    <t>e_Warsaw_POL</t>
+  </si>
+  <si>
+    <t>g_Konin_POL-Warsaw_POL</t>
+  </si>
+  <si>
+    <t>e_Wloclawek_POL</t>
+  </si>
+  <si>
+    <t>g_Konin_POL-Wloclawek_POL</t>
+  </si>
+  <si>
+    <t>e_Koszalin_POL</t>
+  </si>
+  <si>
+    <t>g_Koszalin_POL-Gdansk_POL</t>
+  </si>
+  <si>
+    <t>e_Slupsk_POL</t>
+  </si>
+  <si>
+    <t>g_Koszalin_POL-Slupsk_POL</t>
+  </si>
+  <si>
+    <t>e_Rzeszow_POL</t>
+  </si>
+  <si>
+    <t>g_Krakow_POL-Rzeszow_POL</t>
+  </si>
+  <si>
+    <t>e_Tarnow_POL</t>
+  </si>
+  <si>
+    <t>g_Krakow_POL-Tarnow_POL</t>
+  </si>
+  <si>
+    <t>e_Krosno_POL</t>
+  </si>
+  <si>
+    <t>g_Krosno_POL-Rzeszow_POL</t>
+  </si>
+  <si>
+    <t>g_Kwidzyn_POL-Grudziadz_POL</t>
+  </si>
+  <si>
+    <t>g_Kwidzyn_POL-Wloclawek_POL</t>
+  </si>
+  <si>
+    <t>g_Legnica_POL-Lubin_POL</t>
+  </si>
+  <si>
+    <t>e_Swidnica_POL</t>
+  </si>
+  <si>
+    <t>g_Legnica_POL-Swidnica_POL</t>
+  </si>
+  <si>
+    <t>e_Wroclaw_POL</t>
+  </si>
+  <si>
+    <t>g_Legnica_POL-Wroclaw_POL</t>
+  </si>
+  <si>
+    <t>e_Lomza_POL</t>
+  </si>
+  <si>
+    <t>e_Bialystok_POL</t>
+  </si>
+  <si>
+    <t>g_Lomza_POL-Bialystok_POL</t>
+  </si>
+  <si>
+    <t>e_Elk_POL</t>
+  </si>
+  <si>
+    <t>g_Lomza_POL-Elk_POL</t>
+  </si>
+  <si>
+    <t>e_Grajewo_POL</t>
+  </si>
+  <si>
+    <t>g_Lomza_POL-Grajewo_POL</t>
+  </si>
+  <si>
+    <t>g_Lomza_POL-Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>g_Lomza_POL-Warsaw_POL</t>
+  </si>
+  <si>
+    <t>g_Lubin_POL-Poznan_POL</t>
+  </si>
+  <si>
+    <t>e_Debica_POL</t>
+  </si>
+  <si>
+    <t>g_Mielec_POL-Debica_POL</t>
+  </si>
+  <si>
+    <t>g_Mielec_POL-OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>e_Olesnica_POL</t>
+  </si>
+  <si>
+    <t>g_Olesnica_POL-Czestochowa_POL</t>
+  </si>
+  <si>
+    <t>g_Olesnica_POL-PiotrkowTrybunalsk_POL</t>
+  </si>
+  <si>
+    <t>e_Radomsko_POL</t>
+  </si>
+  <si>
+    <t>g_Olesnica_POL-Radomsko_POL</t>
+  </si>
+  <si>
+    <t>e_Opole_POL</t>
+  </si>
+  <si>
+    <t>g_Opole_POL-Olesnica_POL</t>
+  </si>
+  <si>
+    <t>g_Opole_POL-Sosnowiec_POL</t>
+  </si>
+  <si>
+    <t>g_Opole_POL-Wroclaw_POL</t>
+  </si>
+  <si>
+    <t>e_Pulawy_POL</t>
+  </si>
+  <si>
+    <t>g_OstrowiecSwietokrz_POL-Pulawy_POL</t>
+  </si>
+  <si>
+    <t>g_PiotrkowTrybunalsk_POL-Plock_POL</t>
+  </si>
+  <si>
+    <t>g_PiotrkowTrybunalsk_POL-Warsaw_POL</t>
+  </si>
+  <si>
+    <t>g_Plock_POL-Warsaw_POL</t>
+  </si>
+  <si>
+    <t>e_Police_POL</t>
+  </si>
+  <si>
+    <t>g_Police_POL-Koszalin_POL</t>
+  </si>
+  <si>
+    <t>g_Poznan_POL-GorzowWielkopolski_POL</t>
+  </si>
+  <si>
+    <t>g_Poznan_POL-Konin_POL</t>
+  </si>
+  <si>
+    <t>g_Poznan_POL-Koszalin_POL</t>
+  </si>
+  <si>
+    <t>g_Poznan_POL-Olesnica_POL</t>
+  </si>
+  <si>
+    <t>e_Chelm_POL</t>
+  </si>
+  <si>
+    <t>g_Pulawy_POL-Chelm_POL</t>
+  </si>
+  <si>
+    <t>g_Pulawy_POL-Lomza_POL</t>
+  </si>
+  <si>
+    <t>g_Pulawy_POL-Warsaw_POL</t>
+  </si>
+  <si>
+    <t>e_Zamosc_POL</t>
+  </si>
+  <si>
+    <t>g_Pulawy_POL-Zamosc_POL</t>
+  </si>
+  <si>
+    <t>g_Radomsko_POL-Czestochowa_POL</t>
+  </si>
+  <si>
+    <t>g_Radomsko_POL-PiotrkowTrybunalsk_POL</t>
+  </si>
+  <si>
+    <t>g_Rzeszow_POL-Mielec_POL</t>
+  </si>
+  <si>
+    <t>g_Rzeszow_POL-Pulawy_POL</t>
+  </si>
+  <si>
+    <t>g_Slupsk_POL-Gdynia_POL</t>
+  </si>
+  <si>
+    <t>e_Ustka_POL</t>
+  </si>
+  <si>
+    <t>g_Slupsk_POL-Ustka_POL</t>
+  </si>
+  <si>
+    <t>g_Sosnowiec_POL-BielskoBiala_POL</t>
+  </si>
+  <si>
+    <t>g_Sosnowiec_POL-Gliwice_POL</t>
+  </si>
+  <si>
+    <t>g_Sosnowiec_POL-Katowice_POL</t>
+  </si>
+  <si>
+    <t>g_Swidnica_POL-KedzierzynKozle_POL</t>
+  </si>
+  <si>
+    <t>e_Szczecin_POL</t>
+  </si>
+  <si>
+    <t>g_Szczecin_POL-GorzowWielkopolski_POL</t>
+  </si>
+  <si>
+    <t>g_Szczecin_POL-Police_POL</t>
+  </si>
+  <si>
+    <t>g_Szczecin_POL-Poznan_POL</t>
+  </si>
+  <si>
+    <t>g_Tarnow_POL-Krosno_POL</t>
+  </si>
+  <si>
+    <t>g_Tarnow_POL-Mielec_POL</t>
+  </si>
+  <si>
+    <t>g_Tarnow_POL-Rzeszow_POL</t>
+  </si>
+  <si>
+    <t>g_Wloclawek_POL-Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>g_Wroclaw_POL-Olesnica_POL</t>
+  </si>
+  <si>
+    <t>g_Zamosc_POL-Chelm_POL</t>
+  </si>
+  <si>
+    <t>g_ZielonaGora_POL-Lubin_POL</t>
   </si>
   <si>
     <t>~tradelinks_desc</t>
@@ -441,40 +483,145 @@
     <t>description</t>
   </si>
   <si>
-    <t>grid link -113.0 km- PL15-400;PL36-400</t>
+    <t>grid link -49.0 km- way/40946790-220;way/44389929-220</t>
+  </si>
+  <si>
+    <t>grid link -98.0 km- PL34-400;way/111615226-220</t>
+  </si>
+  <si>
+    <t>grid link -89.0 km- way/111615226-220;way/180535363-220</t>
+  </si>
+  <si>
+    <t>grid link -107.0 km- way/111615226-220;way/158232924-220</t>
+  </si>
+  <si>
+    <t>grid link -106.0 km- PL15-400;way/112614319-400</t>
+  </si>
+  <si>
+    <t>grid link -74.0 km- PL15-400;way/46092396-400</t>
   </si>
   <si>
     <t>grid link -70.0 km- PL15-400;PL7-400</t>
   </si>
   <si>
-    <t>grid link -106.0 km- PL15-400;way/112614319-400</t>
-  </si>
-  <si>
-    <t>grid link -83.0 km- PL15-400;way/178838661-220</t>
-  </si>
-  <si>
-    <t>grid link -30.0 km- PL15-400;way/245964556-220</t>
-  </si>
-  <si>
-    <t>grid link -74.0 km- PL15-400;way/46092396-400</t>
-  </si>
-  <si>
-    <t>grid link -108.0 km- PL15-400;way/658600169-400</t>
+    <t>grid link -83.0 km- PL15-400;way/32036484-220</t>
+  </si>
+  <si>
+    <t>grid link -82.0 km- way/199098050-220;way/216060722-220</t>
+  </si>
+  <si>
+    <t>grid link -78.0 km- way/170316833-220;way/216060722-220</t>
+  </si>
+  <si>
+    <t>grid link -53.0 km- way/112614319-400;way/86494356-400</t>
+  </si>
+  <si>
+    <t>grid link -90.0 km- way/112614319-400;way/46092396-400</t>
+  </si>
+  <si>
+    <t>grid link -137.0 km- way/101915790-220;way/112614319-400</t>
+  </si>
+  <si>
+    <t>grid link -34.0 km- way/293489607-400;way/40946790-220</t>
   </si>
   <si>
     <t>grid link -91.0 km- PL18-400;way/158232924-220</t>
   </si>
   <si>
-    <t>grid link -52.0 km- PL34-400;PL36-400</t>
+    <t>grid link -120.0 km- way/46092396-400;way/658600169-400</t>
+  </si>
+  <si>
+    <t>grid link -43.0 km- way/216060722-220;way/40946790-220</t>
+  </si>
+  <si>
+    <t>grid link -92.0 km- way/199098050-220;way/40946790-220</t>
+  </si>
+  <si>
+    <t>grid link -85.0 km- way/40946790-220;way/87667718-220</t>
+  </si>
+  <si>
+    <t>grid link -15.0 km- way/183945016-220;way/40946790-220</t>
+  </si>
+  <si>
+    <t>grid link -49.0 km- way/183945016-220;way/336990960-220</t>
+  </si>
+  <si>
+    <t>grid link -110.0 km- way/199098050-220;way/199098053-220</t>
+  </si>
+  <si>
+    <t>grid link -72.0 km- way/199098050-220;way/254235846-400</t>
+  </si>
+  <si>
+    <t>grid link -94.0 km- PL15-400;way/255284259-220</t>
+  </si>
+  <si>
+    <t>grid link -78.0 km- way/170316833-220;way/255284259-220</t>
+  </si>
+  <si>
+    <t>grid link -108.0 km- way/255284259-220;way/658600169-400</t>
+  </si>
+  <si>
+    <t>grid link -146.0 km- way/255284259-220;way/29115701-220</t>
+  </si>
+  <si>
+    <t>grid link -81.0 km- way/245964556-220;way/255284259-220</t>
+  </si>
+  <si>
+    <t>grid link -122.0 km- way/112614319-400;way/178838661-220</t>
+  </si>
+  <si>
+    <t>grid link -65.0 km- relation/18085709-400;way/178838661-220</t>
+  </si>
+  <si>
+    <t>grid link -188.0 km- way/215282393-400;way/87667718-220</t>
+  </si>
+  <si>
+    <t>grid link -99.0 km- way/191038569-220;way/87667718-220</t>
+  </si>
+  <si>
+    <t>grid link -59.0 km- way/166838338-400;way/215282393-400</t>
+  </si>
+  <si>
+    <t>grid link -4.0 km- PL7-400;way/46092396-400</t>
+  </si>
+  <si>
+    <t>grid link -64.0 km- PL7-400;way/245964556-220</t>
+  </si>
+  <si>
+    <t>grid link -23.0 km- PL34-400;way/180535363-220</t>
   </si>
   <si>
     <t>grid link -43.0 km- PL34-400;PL46-220</t>
   </si>
   <si>
-    <t>grid link -23.0 km- PL34-400;way/180535363-220</t>
-  </si>
-  <si>
-    <t>grid link -34.0 km- PL36-400;PL46-220</t>
+    <t>grid link -49.0 km- PL34-400;way/79033485-400</t>
+  </si>
+  <si>
+    <t>grid link -90.0 km- PL17-400;way/121656686-220</t>
+  </si>
+  <si>
+    <t>grid link -83.0 km- way/121656686-220;way/303870256-400</t>
+  </si>
+  <si>
+    <t>grid link -92.0 km- way/121656686-220;way/170259740-220</t>
+  </si>
+  <si>
+    <t>grid link -133.0 km- way/101915790-220;way/121656686-220</t>
+  </si>
+  <si>
+    <t>grid link -35.0 km- way/121656686-220;way/29115701-220</t>
+  </si>
+  <si>
+    <t>grid link -90.0 km- way/180535363-220;way/32036484-220</t>
+  </si>
+  <si>
+    <t>grid link -68.0 km- way/198635989-220;way/199098053-220</t>
+  </si>
+  <si>
+    <t>grid link -61.0 km- way/199098053-220;way/254235846-400</t>
+  </si>
+  <si>
+    <t>grid link -94.0 km- PL36-400;way/216060722-220</t>
   </si>
   <si>
     <t>grid link -125.0 km- PL36-400;way/170316833-220</t>
@@ -483,198 +630,114 @@
     <t>grid link -130.0 km- PL36-400;way/171917072-400</t>
   </si>
   <si>
-    <t>grid link -94.0 km- PL36-400;way/216060722-220</t>
+    <t>grid link -54.0 km- PL36-400;way/255277953-400</t>
+  </si>
+  <si>
+    <t>grid link -121.0 km- way/183945016-220;way/255277953-400</t>
+  </si>
+  <si>
+    <t>grid link -78.0 km- way/255277953-400;way/79033485-400</t>
+  </si>
+  <si>
+    <t>grid link -78.0 km- way/254235846-400;way/88544449-220</t>
+  </si>
+  <si>
+    <t>grid link -204.0 km- way/170316833-220;way/658600169-400</t>
+  </si>
+  <si>
+    <t>grid link -180.0 km- way/170316833-220;way/29115701-220</t>
+  </si>
+  <si>
+    <t>grid link -94.0 km- way/29115701-220;way/658600169-400</t>
+  </si>
+  <si>
+    <t>grid link -128.0 km- way/165763717-220;way/178838661-220</t>
+  </si>
+  <si>
+    <t>grid link -140.0 km- PL18-400;way/32036484-220</t>
+  </si>
+  <si>
+    <t>grid link -81.0 km- way/255284259-220;way/32036484-220</t>
+  </si>
+  <si>
+    <t>grid link -113.0 km- way/178838661-220;way/32036484-220</t>
+  </si>
+  <si>
+    <t>grid link -113.0 km- PL36-400;way/32036484-220</t>
+  </si>
+  <si>
+    <t>grid link -66.0 km- way/194903381-400;way/88544449-220</t>
+  </si>
+  <si>
+    <t>grid link -13.0 km- way/121656686-220;way/88544449-220</t>
+  </si>
+  <si>
+    <t>grid link -38.0 km- way/29115701-220;way/88544449-220</t>
+  </si>
+  <si>
+    <t>grid link -79.0 km- way/173613665-220;way/88544449-220</t>
+  </si>
+  <si>
+    <t>grid link -27.0 km- way/171917072-400;way/216060722-220</t>
+  </si>
+  <si>
+    <t>grid link -44.0 km- way/170316833-220;way/171917072-400</t>
+  </si>
+  <si>
+    <t>grid link -52.0 km- way/199098053-220;way/215282393-400</t>
+  </si>
+  <si>
+    <t>grid link -86.0 km- way/215282393-400;way/88544449-220</t>
+  </si>
+  <si>
+    <t>grid link -88.0 km- relation/18085709-400;way/86494356-400</t>
+  </si>
+  <si>
+    <t>grid link -0.0 km- relation/18085709-400;way/255314292</t>
+  </si>
+  <si>
+    <t>grid link -48.0 km- way/183945016-220;way/44389929-220</t>
+  </si>
+  <si>
+    <t>grid link -52.0 km- way/183945016-220;way/293489607-400</t>
+  </si>
+  <si>
+    <t>grid link -66.0 km- way/183945016-220;way/40946790-220</t>
   </si>
   <si>
     <t>grid link -93.0 km- PL46-220;way/336990960-220</t>
   </si>
   <si>
-    <t>grid link -64.0 km- PL7-400;way/245964556-220</t>
-  </si>
-  <si>
-    <t>grid link -4.0 km- PL7-400;way/46092396-400</t>
-  </si>
-  <si>
-    <t>grid link -94.0 km- PL34-400;way/111615226-380</t>
-  </si>
-  <si>
-    <t>grid link -107.0 km- way/111615226-380;way/158232924-220</t>
-  </si>
-  <si>
-    <t>grid link -89.0 km- way/111615226-380;way/180535363-220</t>
-  </si>
-  <si>
-    <t>grid link -137.0 km- way/101915790-220;way/112614319-400</t>
-  </si>
-  <si>
-    <t>grid link -90.0 km- way/112614319-400;way/46092396-400</t>
-  </si>
-  <si>
-    <t>grid link -133.0 km- way/101915790-220;way/121656686-220</t>
-  </si>
-  <si>
-    <t>grid link -92.0 km- way/121656686-220;way/170259740-220</t>
-  </si>
-  <si>
-    <t>grid link -87.0 km- way/121656686-220;way/303870256-400</t>
+    <t>grid link -92.0 km- PL18-400;way/39428977-400</t>
+  </si>
+  <si>
+    <t>grid link -45.0 km- way/165763717-220;way/39428977-400</t>
+  </si>
+  <si>
+    <t>grid link -208.0 km- way/32036484-220;way/39428977-400</t>
+  </si>
+  <si>
+    <t>grid link -82.0 km- way/166838338-400;way/191038569-220</t>
+  </si>
+  <si>
+    <t>grid link -96.0 km- way/191038569-220;way/199098053-220</t>
+  </si>
+  <si>
+    <t>grid link -86.0 km- way/191038569-220;way/215282393-400</t>
+  </si>
+  <si>
+    <t>grid link -182.0 km- way/101915790-220;way/245964556-220</t>
+  </si>
+  <si>
+    <t>grid link -61.0 km- PL36-400;way/79033485-400</t>
+  </si>
+  <si>
+    <t>grid link -60.0 km- way/173613665-220;way/194903381-400</t>
   </si>
   <si>
     <t>grid link -66.0 km- way/158232924-220;way/180535363-220</t>
   </si>
   <si>
-    <t>grid link -128.0 km- way/165763717-220;way/178838661-220</t>
-  </si>
-  <si>
-    <t>grid link -59.0 km- way/166838338-400;way/215282393-400</t>
-  </si>
-  <si>
-    <t>grid link -181.0 km- way/170316833-220;way/658600169-400</t>
-  </si>
-  <si>
-    <t>grid link -43.0 km- way/170316833-220;way/171917072-400</t>
-  </si>
-  <si>
-    <t>grid link -27.0 km- way/171917072-400;way/216060722-220</t>
-  </si>
-  <si>
-    <t>grid link -60.0 km- way/173613665-220;way/194903381-400</t>
-  </si>
-  <si>
-    <t>grid link -122.0 km- way/112614319-400;way/178838661-220</t>
-  </si>
-  <si>
-    <t>grid link -93.0 km- way/178838661-220;way/180535363-220</t>
-  </si>
-  <si>
-    <t>grid link -65.0 km- way/178838661-220;way/255314292</t>
-  </si>
-  <si>
-    <t>grid link -31.0 km- PL15-400;way/180535363-220</t>
-  </si>
-  <si>
-    <t>grid link -140.0 km- PL18-400;way/180535363-220</t>
-  </si>
-  <si>
-    <t>grid link -52.0 km- way/183945016-220;way/293489607-400</t>
-  </si>
-  <si>
-    <t>grid link -66.0 km- way/183945016-220;way/40946790-220</t>
-  </si>
-  <si>
-    <t>grid link -48.0 km- way/183945016-220;way/44389929-220</t>
-  </si>
-  <si>
-    <t>grid link -82.0 km- way/166838338-400;way/191038569-220</t>
-  </si>
-  <si>
-    <t>grid link -85.0 km- way/191038569-220;way/199098053-220</t>
-  </si>
-  <si>
-    <t>grid link -86.0 km- way/191038569-220;way/215282393-400</t>
-  </si>
-  <si>
-    <t>grid link -110.0 km- way/199098050-220;way/199098053-220</t>
-  </si>
-  <si>
-    <t>grid link -72.0 km- way/199098050-220;way/254235846-400</t>
-  </si>
-  <si>
-    <t>grid link -68.0 km- way/198635989-220;way/199098053-220</t>
-  </si>
-  <si>
-    <t>grid link -61.0 km- way/199098053-220;way/254235846-400</t>
-  </si>
-  <si>
-    <t>grid link -52.0 km- way/199098053-220;way/215282393-400</t>
-  </si>
-  <si>
-    <t>grid link -86.0 km- way/215282393-400;way/88544449-220</t>
-  </si>
-  <si>
-    <t>grid link -68.0 km- way/170316833-220;way/216060722-220</t>
-  </si>
-  <si>
-    <t>grid link -82.0 km- way/199098050-220;way/216060722-220</t>
-  </si>
-  <si>
-    <t>grid link -182.0 km- way/101915790-220;way/245964556-220</t>
-  </si>
-  <si>
-    <t>grid link -75.0 km- way/170316833-220;way/245964556-220</t>
-  </si>
-  <si>
-    <t>grid link -146.0 km- way/245964556-220;way/658600169-400</t>
-  </si>
-  <si>
-    <t>grid link -78.0 km- way/254235846-400;way/88544449-220</t>
-  </si>
-  <si>
-    <t>grid link -54.0 km- PL36-400;way/255277953-400</t>
-  </si>
-  <si>
-    <t>grid link -78.0 km- PL46-220;way/255277953-400</t>
-  </si>
-  <si>
-    <t>grid link -121.0 km- way/183945016-220;way/255277953-400</t>
-  </si>
-  <si>
-    <t>grid link -88.0 km- way/112614319-400;way/255314292</t>
-  </si>
-  <si>
-    <t>grid link -34.0 km- way/293489607-400;way/40946790-220</t>
-  </si>
-  <si>
-    <t>grid link -13.0 km- way/170259740-220;way/303870256-400</t>
-  </si>
-  <si>
-    <t>grid link -49.0 km- way/183945016-220;way/336990960-220</t>
-  </si>
-  <si>
-    <t>grid link -74.0 km- PL18-400;way/39428977-400</t>
-  </si>
-  <si>
-    <t>grid link -40.0 km- way/165763717-220;way/39428977-400</t>
-  </si>
-  <si>
-    <t>grid link -208.0 km- way/180535363-220;way/39428977-400</t>
-  </si>
-  <si>
-    <t>grid link -15.0 km- way/183945016-220;way/40946790-220</t>
-  </si>
-  <si>
-    <t>grid link -92.0 km- way/199098050-220;way/40946790-220</t>
-  </si>
-  <si>
-    <t>grid link -43.0 km- way/216060722-220;way/40946790-220</t>
-  </si>
-  <si>
-    <t>grid link -63.0 km- way/40946790-220;way/87667718-220</t>
-  </si>
-  <si>
-    <t>grid link -32.0 km- way/40946790-220;way/44389929-220</t>
-  </si>
-  <si>
-    <t>grid link -120.0 km- way/46092396-400;way/658600169-400</t>
-  </si>
-  <si>
-    <t>grid link -43.0 km- way/121656686-220;way/658600169-400</t>
-  </si>
-  <si>
-    <t>grid link -89.0 km- way/191038569-220;way/87667718-220</t>
-  </si>
-  <si>
-    <t>grid link -188.0 km- way/215282393-400;way/87667718-220</t>
-  </si>
-  <si>
-    <t>grid link -26.0 km- way/121656686-220;way/88544449-220</t>
-  </si>
-  <si>
-    <t>grid link -79.0 km- way/173613665-220;way/88544449-220</t>
-  </si>
-  <si>
-    <t>grid link -66.0 km- way/194903381-400;way/88544449-220</t>
-  </si>
-  <si>
     <t>~commodity_geo</t>
   </si>
   <si>
@@ -843,390 +906,423 @@
     <t>co2</t>
   </si>
   <si>
-    <t>co2_PL15-400_POL</t>
+    <t>co2_Bydgoszcz_POL</t>
   </si>
   <si>
     <t>co2s_ogci11090_POL</t>
   </si>
   <si>
-    <t>p_co2_PL15-400_POL-ogci11090</t>
+    <t>p_co2_Bydgoszcz_POL-ogci11090</t>
   </si>
   <si>
     <t>U</t>
   </si>
   <si>
-    <t>co2_PL18-400_POL</t>
+    <t>co2_Bialystok_POL</t>
+  </si>
+  <si>
+    <t>co2s_T6_POL</t>
+  </si>
+  <si>
+    <t>p_co2_Bialystok_POL-T6</t>
+  </si>
+  <si>
+    <t>co2_GorzowWielkopolski_POL</t>
   </si>
   <si>
     <t>co2s_ogci11086_POL</t>
   </si>
   <si>
-    <t>p_co2_PL18-400_POL-ogci11086</t>
-  </si>
-  <si>
-    <t>co2_PL34-400_POL</t>
+    <t>p_co2_GorzowWielkopolski_POL-ogci11086</t>
+  </si>
+  <si>
+    <t>co2_Legnica_POL</t>
   </si>
   <si>
     <t>co2s_T4_POL</t>
   </si>
   <si>
-    <t>p_co2_PL34-400_POL-T4</t>
-  </si>
-  <si>
-    <t>co2_PL36-400_POL</t>
+    <t>p_co2_Legnica_POL-T4</t>
+  </si>
+  <si>
+    <t>co2_Olesnica_POL</t>
   </si>
   <si>
     <t>co2s_T3_POL</t>
   </si>
   <si>
-    <t>p_co2_PL36-400_POL-T3</t>
-  </si>
-  <si>
-    <t>co2_PL46-220_POL</t>
+    <t>p_co2_Olesnica_POL-T3</t>
+  </si>
+  <si>
+    <t>co2_Swidnica_POL</t>
   </si>
   <si>
     <t>co2s_T5_POL</t>
   </si>
   <si>
-    <t>p_co2_PL46-220_POL-T5</t>
-  </si>
-  <si>
-    <t>co2_PL7-400_POL</t>
-  </si>
-  <si>
-    <t>p_co2_PL7-400_POL-ogci11090</t>
-  </si>
-  <si>
-    <t>co2_w101915790-220_POL</t>
+    <t>p_co2_Swidnica_POL-T5</t>
+  </si>
+  <si>
+    <t>co2_Kwidzyn_POL</t>
+  </si>
+  <si>
+    <t>p_co2_Kwidzyn_POL-ogci11090</t>
+  </si>
+  <si>
+    <t>co2_Slupsk_POL</t>
+  </si>
+  <si>
+    <t>co2s_ogci11088_POL</t>
+  </si>
+  <si>
+    <t>p_co2_Slupsk_POL-ogci11088</t>
+  </si>
+  <si>
+    <t>co2_Olsztyn_POL</t>
   </si>
   <si>
     <t>co2s_T8_POL</t>
   </si>
   <si>
-    <t>p_co2_w101915790-220_POL-T8</t>
-  </si>
-  <si>
-    <t>co2_w111615226-380_POL</t>
-  </si>
-  <si>
-    <t>p_co2_w111615226-380_POL-T4</t>
-  </si>
-  <si>
-    <t>co2_w112614319-400_POL</t>
-  </si>
-  <si>
-    <t>p_co2_w112614319-400_POL-T8</t>
-  </si>
-  <si>
-    <t>co2_w121656686-220_POL</t>
-  </si>
-  <si>
-    <t>co2s_T6_POL</t>
-  </si>
-  <si>
-    <t>p_co2_w121656686-220_POL-T6</t>
-  </si>
-  <si>
-    <t>co2_w158232924-220_POL</t>
-  </si>
-  <si>
-    <t>p_co2_w158232924-220_POL-T4</t>
-  </si>
-  <si>
-    <t>co2_w165763717-220_POL</t>
+    <t>p_co2_Olsztyn_POL-T8</t>
+  </si>
+  <si>
+    <t>co2_Boleslawiec_POL</t>
+  </si>
+  <si>
+    <t>p_co2_Boleslawiec_POL-T4</t>
+  </si>
+  <si>
+    <t>co2_Gdansk_POL</t>
+  </si>
+  <si>
+    <t>p_co2_Gdansk_POL-T8</t>
+  </si>
+  <si>
+    <t>co2_Lomza_POL</t>
+  </si>
+  <si>
+    <t>p_co2_Lomza_POL-T6</t>
+  </si>
+  <si>
+    <t>co2_ZielonaGora_POL</t>
+  </si>
+  <si>
+    <t>p_co2_ZielonaGora_POL-T4</t>
+  </si>
+  <si>
+    <t>co2_Police_POL</t>
   </si>
   <si>
     <t>co2s_ogci11091_POL</t>
   </si>
   <si>
-    <t>p_co2_w165763717-220_POL-ogci11091</t>
-  </si>
-  <si>
-    <t>co2_w166838338-400_POL</t>
+    <t>p_co2_Police_POL-ogci11091</t>
+  </si>
+  <si>
+    <t>co2_Krosno_POL</t>
   </si>
   <si>
     <t>co2s_ogci11083_POL</t>
   </si>
   <si>
-    <t>p_co2_w166838338-400_POL-ogci11083</t>
-  </si>
-  <si>
-    <t>co2_w170259740-220_POL</t>
-  </si>
-  <si>
-    <t>p_co2_w170259740-220_POL-T8</t>
-  </si>
-  <si>
-    <t>co2_w170316833-220_POL</t>
+    <t>p_co2_Krosno_POL-ogci11083</t>
+  </si>
+  <si>
+    <t>co2_Grajewo_POL</t>
+  </si>
+  <si>
+    <t>p_co2_Grajewo_POL-T8</t>
+  </si>
+  <si>
+    <t>co2_PiotrkowTrybunalsk_POL</t>
   </si>
   <si>
     <t>co2s_ogci11082_POL</t>
   </si>
   <si>
-    <t>p_co2_w170316833-220_POL-ogci11082</t>
-  </si>
-  <si>
-    <t>co2_w171917072-400_POL</t>
+    <t>p_co2_PiotrkowTrybunalsk_POL-ogci11082</t>
+  </si>
+  <si>
+    <t>co2_Radomsko_POL</t>
   </si>
   <si>
     <t>co2s_ogci11093_POL</t>
   </si>
   <si>
-    <t>p_co2_w171917072-400_POL-ogci11093</t>
-  </si>
-  <si>
-    <t>co2_w173613665-220_POL</t>
-  </si>
-  <si>
-    <t>p_co2_w173613665-220_POL-ogci11083</t>
-  </si>
-  <si>
-    <t>co2_w178838661-220_POL</t>
+    <t>p_co2_Radomsko_POL-ogci11093</t>
+  </si>
+  <si>
+    <t>co2_Zamosc_POL</t>
+  </si>
+  <si>
+    <t>p_co2_Zamosc_POL-ogci11083</t>
+  </si>
+  <si>
+    <t>co2_Koszalin_POL</t>
   </si>
   <si>
     <t>co2s_ogci11077_POL</t>
   </si>
   <si>
-    <t>p_co2_w178838661-220_POL-ogci11077</t>
-  </si>
-  <si>
-    <t>co2_w180535363-220_POL</t>
-  </si>
-  <si>
-    <t>p_co2_w180535363-220_POL-T4</t>
-  </si>
-  <si>
-    <t>co2_w183945016-220_POL</t>
+    <t>p_co2_Koszalin_POL-ogci11077</t>
+  </si>
+  <si>
+    <t>co2_Lubin_POL</t>
+  </si>
+  <si>
+    <t>p_co2_Lubin_POL-T4</t>
+  </si>
+  <si>
+    <t>co2_Sosnowiec_POL</t>
   </si>
   <si>
     <t>co2s_T1_POL</t>
   </si>
   <si>
-    <t>p_co2_w183945016-220_POL-T1</t>
-  </si>
-  <si>
-    <t>co2_w191038569-220_POL</t>
-  </si>
-  <si>
-    <t>p_co2_w191038569-220_POL-T1</t>
-  </si>
-  <si>
-    <t>co2_w194903381-400_POL</t>
-  </si>
-  <si>
-    <t>p_co2_w194903381-400_POL-ogci11083</t>
-  </si>
-  <si>
-    <t>co2_w198635989-220_POL</t>
-  </si>
-  <si>
-    <t>p_co2_w198635989-220_POL-ogci11083</t>
-  </si>
-  <si>
-    <t>co2_w199098050-220_POL</t>
-  </si>
-  <si>
-    <t>p_co2_w199098050-220_POL-ogci11082</t>
-  </si>
-  <si>
-    <t>co2_w199098053-220_POL</t>
-  </si>
-  <si>
-    <t>p_co2_w199098053-220_POL-ogci11083</t>
-  </si>
-  <si>
-    <t>co2_w215282393-400_POL</t>
-  </si>
-  <si>
-    <t>p_co2_w215282393-400_POL-ogci11083</t>
-  </si>
-  <si>
-    <t>co2_w216060722-220_POL</t>
-  </si>
-  <si>
-    <t>p_co2_w216060722-220_POL-ogci11093</t>
-  </si>
-  <si>
-    <t>co2_w245964556-220_POL</t>
+    <t>p_co2_Sosnowiec_POL-T1</t>
+  </si>
+  <si>
+    <t>co2_Tarnow_POL</t>
+  </si>
+  <si>
+    <t>p_co2_Tarnow_POL-T1</t>
+  </si>
+  <si>
+    <t>co2_Chelm_POL</t>
+  </si>
+  <si>
+    <t>p_co2_Chelm_POL-ogci11083</t>
+  </si>
+  <si>
+    <t>co2_Debica_POL</t>
+  </si>
+  <si>
+    <t>p_co2_Debica_POL-ogci11083</t>
+  </si>
+  <si>
+    <t>co2_Kielce_POL</t>
+  </si>
+  <si>
+    <t>p_co2_Kielce_POL-ogci11082</t>
+  </si>
+  <si>
+    <t>co2_Mielec_POL</t>
+  </si>
+  <si>
+    <t>p_co2_Mielec_POL-ogci11083</t>
+  </si>
+  <si>
+    <t>co2_Rzeszow_POL</t>
+  </si>
+  <si>
+    <t>p_co2_Rzeszow_POL-ogci11083</t>
+  </si>
+  <si>
+    <t>co2_Czestochowa_POL</t>
+  </si>
+  <si>
+    <t>p_co2_Czestochowa_POL-ogci11093</t>
+  </si>
+  <si>
+    <t>co2_Wloclawek_POL</t>
   </si>
   <si>
     <t>co2s_ogci11078_POL</t>
   </si>
   <si>
-    <t>p_co2_w245964556-220_POL-ogci11078</t>
-  </si>
-  <si>
-    <t>co2_w254235846-400_POL</t>
-  </si>
-  <si>
-    <t>p_co2_w254235846-400_POL-ogci11083</t>
-  </si>
-  <si>
-    <t>co2_w255277953-400_POL</t>
-  </si>
-  <si>
-    <t>p_co2_w255277953-400_POL-T3</t>
-  </si>
-  <si>
-    <t>co2_w255314292_POL</t>
-  </si>
-  <si>
-    <t>co2s_ogci11088_POL</t>
-  </si>
-  <si>
-    <t>p_co2_w255314292_POL-ogci11088</t>
-  </si>
-  <si>
-    <t>co2_w293489607-400_POL</t>
-  </si>
-  <si>
-    <t>p_co2_w293489607-400_POL-T1</t>
-  </si>
-  <si>
-    <t>co2_w303870256-400_POL</t>
-  </si>
-  <si>
-    <t>p_co2_w303870256-400_POL-T8</t>
-  </si>
-  <si>
-    <t>co2_w336990960-220_POL</t>
-  </si>
-  <si>
-    <t>p_co2_w336990960-220_POL-T1</t>
-  </si>
-  <si>
-    <t>co2_w39428977-400_POL</t>
-  </si>
-  <si>
-    <t>p_co2_w39428977-400_POL-ogci11091</t>
-  </si>
-  <si>
-    <t>co2_w40946790-220_POL</t>
-  </si>
-  <si>
-    <t>p_co2_w40946790-220_POL-T1</t>
-  </si>
-  <si>
-    <t>co2_w44389929-220_POL</t>
-  </si>
-  <si>
-    <t>p_co2_w44389929-220_POL-T1</t>
-  </si>
-  <si>
-    <t>co2_w46092396-400_POL</t>
-  </si>
-  <si>
-    <t>p_co2_w46092396-400_POL-ogci11090</t>
-  </si>
-  <si>
-    <t>co2_w658600169-400_POL</t>
+    <t>p_co2_Wloclawek_POL-ogci11078</t>
+  </si>
+  <si>
+    <t>co2_OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>p_co2_OstrowiecSwietokrz_POL-ogci11083</t>
+  </si>
+  <si>
+    <t>co2_Opole_POL</t>
+  </si>
+  <si>
+    <t>p_co2_Opole_POL-T3</t>
+  </si>
+  <si>
+    <t>co2_Konin_POL</t>
+  </si>
+  <si>
+    <t>co2s_ogci11080_POL</t>
+  </si>
+  <si>
+    <t>p_co2_Konin_POL-ogci11080</t>
+  </si>
+  <si>
+    <t>co2_Ustka_POL</t>
+  </si>
+  <si>
+    <t>p_co2_Ustka_POL-ogci11088</t>
+  </si>
+  <si>
+    <t>co2_Warsaw_POL</t>
+  </si>
+  <si>
+    <t>p_co2_Warsaw_POL-ogci11083</t>
+  </si>
+  <si>
+    <t>co2_Gliwice_POL</t>
+  </si>
+  <si>
+    <t>p_co2_Gliwice_POL-T1</t>
+  </si>
+  <si>
+    <t>co2_Elk_POL</t>
+  </si>
+  <si>
+    <t>p_co2_Elk_POL-T8</t>
+  </si>
+  <si>
+    <t>co2_Poznan_POL</t>
+  </si>
+  <si>
+    <t>co2s_ogci11094_POL</t>
+  </si>
+  <si>
+    <t>p_co2_Poznan_POL-ogci11094</t>
+  </si>
+  <si>
+    <t>co2_KedzierzynKozle_POL</t>
+  </si>
+  <si>
+    <t>p_co2_KedzierzynKozle_POL-T1</t>
+  </si>
+  <si>
+    <t>co2_Szczecin_POL</t>
+  </si>
+  <si>
+    <t>p_co2_Szczecin_POL-ogci11091</t>
+  </si>
+  <si>
+    <t>co2_Katowice_POL</t>
+  </si>
+  <si>
+    <t>p_co2_Katowice_POL-T1</t>
+  </si>
+  <si>
+    <t>co2_BielskoBiala_POL</t>
+  </si>
+  <si>
+    <t>p_co2_BielskoBiala_POL-T1</t>
+  </si>
+  <si>
+    <t>co2_Grudziadz_POL</t>
+  </si>
+  <si>
+    <t>p_co2_Grudziadz_POL-ogci11090</t>
+  </si>
+  <si>
+    <t>co2_Plock_POL</t>
   </si>
   <si>
     <t>co2s_ogci11075_POL</t>
   </si>
   <si>
-    <t>p_co2_w658600169-400_POL-ogci11075</t>
-  </si>
-  <si>
-    <t>co2_w87667718-220_POL</t>
-  </si>
-  <si>
-    <t>p_co2_w87667718-220_POL-T1</t>
-  </si>
-  <si>
-    <t>co2_w88544449-220_POL</t>
-  </si>
-  <si>
-    <t>p_co2_w88544449-220_POL-ogci11083</t>
+    <t>p_co2_Plock_POL-ogci11075</t>
+  </si>
+  <si>
+    <t>co2_Wroclaw_POL</t>
+  </si>
+  <si>
+    <t>co2s_T2_POL</t>
+  </si>
+  <si>
+    <t>p_co2_Wroclaw_POL-T2</t>
+  </si>
+  <si>
+    <t>co2_Gdynia_POL</t>
+  </si>
+  <si>
+    <t>co2s_ogci11092_POL</t>
+  </si>
+  <si>
+    <t>p_co2_Gdynia_POL-ogci11092</t>
+  </si>
+  <si>
+    <t>co2_Krakow_POL</t>
+  </si>
+  <si>
+    <t>p_co2_Krakow_POL-T1</t>
+  </si>
+  <si>
+    <t>co2_Pulawy_POL</t>
+  </si>
+  <si>
+    <t>p_co2_Pulawy_POL-ogci11083</t>
   </si>
   <si>
     <t>co2s_ogci11072_POL</t>
   </si>
   <si>
-    <t>p_co2_w658600169-400_POL-ogci11072</t>
+    <t>p_co2_Plock_POL-ogci11072</t>
   </si>
   <si>
     <t>co2s_ogci11074_POL</t>
   </si>
   <si>
-    <t>p_co2_w658600169-400_POL-ogci11074</t>
+    <t>p_co2_Plock_POL-ogci11074</t>
   </si>
   <si>
     <t>co2s_ogci11076_POL</t>
   </si>
   <si>
-    <t>p_co2_w658600169-400_POL-ogci11076</t>
+    <t>p_co2_Plock_POL-ogci11076</t>
   </si>
   <si>
     <t>co2s_ogci11079_POL</t>
   </si>
   <si>
-    <t>p_co2_w245964556-220_POL-ogci11079</t>
-  </si>
-  <si>
-    <t>co2s_ogci11080_POL</t>
-  </si>
-  <si>
-    <t>p_co2_w245964556-220_POL-ogci11080</t>
+    <t>p_co2_Wloclawek_POL-ogci11079</t>
   </si>
   <si>
     <t>co2s_ogci11081_POL</t>
   </si>
   <si>
-    <t>p_co2_w245964556-220_POL-ogci11081</t>
+    <t>p_co2_Konin_POL-ogci11081</t>
   </si>
   <si>
     <t>co2s_ogci11084_POL</t>
   </si>
   <si>
-    <t>p_co2_w165763717-220_POL-ogci11084</t>
+    <t>p_co2_Police_POL-ogci11084</t>
   </si>
   <si>
     <t>co2s_ogci11085_POL</t>
   </si>
   <si>
-    <t>p_co2_w165763717-220_POL-ogci11085</t>
+    <t>p_co2_Police_POL-ogci11085</t>
   </si>
   <si>
     <t>co2s_ogci11087_POL</t>
   </si>
   <si>
-    <t>p_co2_w170316833-220_POL-ogci11087</t>
+    <t>p_co2_PiotrkowTrybunalsk_POL-ogci11087</t>
   </si>
   <si>
     <t>co2s_ogci11089_POL</t>
   </si>
   <si>
-    <t>p_co2_w165763717-220_POL-ogci11089</t>
-  </si>
-  <si>
-    <t>co2s_ogci11092_POL</t>
-  </si>
-  <si>
-    <t>p_co2_PL15-400_POL-ogci11092</t>
-  </si>
-  <si>
-    <t>co2s_ogci11094_POL</t>
-  </si>
-  <si>
-    <t>p_co2_PL15-400_POL-ogci11094</t>
-  </si>
-  <si>
-    <t>co2s_T2_POL</t>
-  </si>
-  <si>
-    <t>p_co2_PL36-400_POL-T2</t>
+    <t>p_co2_Police_POL-ogci11089</t>
   </si>
   <si>
     <t>co2s_T7_POL</t>
   </si>
   <si>
-    <t>p_co2_w658600169-400_POL-T7</t>
+    <t>p_co2_Warsaw_POL-T7</t>
   </si>
   <si>
     <t>co2 pipeline -20 km- PL15-400 to ogci_11090.0</t>
   </si>
   <si>
+    <t>co2 pipeline -106 km- PL17-400 to T6</t>
+  </si>
+  <si>
     <t>co2 pipeline -104 km- PL18-400 to ogci_11086.0</t>
   </si>
   <si>
@@ -1242,10 +1338,13 @@
     <t>co2 pipeline -83 km- PL7-400 to ogci_11090.0</t>
   </si>
   <si>
+    <t>co2 pipeline -150 km- relation/18085709-400 to ogci_11088.0</t>
+  </si>
+  <si>
     <t>co2 pipeline -40 km- way/101915790-220 to T8</t>
   </si>
   <si>
-    <t>co2 pipeline -132 km- way/111615226-380 to T4</t>
+    <t>co2 pipeline -132 km- way/111615226-220 to T4</t>
   </si>
   <si>
     <t>co2 pipeline -183 km- way/112614319-400 to T8</t>
@@ -1314,15 +1413,24 @@
     <t>co2 pipeline -50 km- way/255277953-400 to T3</t>
   </si>
   <si>
+    <t>co2 pipeline -27 km- way/255284259-220 to ogci_11080.0</t>
+  </si>
+  <si>
     <t>co2 pipeline -150 km- way/255314292 to ogci_11088.0</t>
   </si>
   <si>
+    <t>co2 pipeline -45 km- way/29115701-220 to ogci_11083.0</t>
+  </si>
+  <si>
     <t>co2 pipeline -44 km- way/293489607-400 to T1</t>
   </si>
   <si>
     <t>co2 pipeline -143 km- way/303870256-400 to T8</t>
   </si>
   <si>
+    <t>co2 pipeline -24 km- way/32036484-220 to ogci_11094.0</t>
+  </si>
+  <si>
     <t>co2 pipeline -40 km- way/336990960-220 to T1</t>
   </si>
   <si>
@@ -1341,6 +1449,12 @@
     <t>co2 pipeline -26 km- way/658600169-400 to ogci_11075.0</t>
   </si>
   <si>
+    <t>co2 pipeline -4 km- way/79033485-400 to T2</t>
+  </si>
+  <si>
+    <t>co2 pipeline -230 km- way/86494356-400 to ogci_11092.0</t>
+  </si>
+  <si>
     <t>co2 pipeline -162 km- way/87667718-220 to T1</t>
   </si>
   <si>
@@ -1359,10 +1473,7 @@
     <t>co2 pipeline -44 km- way/245964556-220 to ogci_11079.0</t>
   </si>
   <si>
-    <t>co2 pipeline -62 km- way/245964556-220 to ogci_11080.0</t>
-  </si>
-  <si>
-    <t>co2 pipeline -91 km- way/245964556-220 to ogci_11081.0</t>
+    <t>co2 pipeline -42 km- way/255284259-220 to ogci_11081.0</t>
   </si>
   <si>
     <t>co2 pipeline -42 km- way/165763717-220 to ogci_11084.0</t>
@@ -1377,16 +1488,7 @@
     <t>co2 pipeline -85 km- way/165763717-220 to ogci_11089.0</t>
   </si>
   <si>
-    <t>co2 pipeline -35 km- PL15-400 to ogci_11092.0</t>
-  </si>
-  <si>
-    <t>co2 pipeline -123 km- PL15-400 to ogci_11094.0</t>
-  </si>
-  <si>
-    <t>co2 pipeline -48 km- PL36-400 to T2</t>
-  </si>
-  <si>
-    <t>co2 pipeline -88 km- way/658600169-400 to T7</t>
+    <t>co2 pipeline -46 km- way/29115701-220 to T7</t>
   </si>
 </sst>
 </file>
@@ -1757,8 +1859,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{852D2E7C-A81B-4B3E-AA03-FA44BCF063B5}">
-  <dimension ref="B3:R95"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C481C62A-DF29-4320-A519-031B17D83434}">
+  <dimension ref="B3:R102"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="3" spans="2:18" x14ac:dyDescent="0.45">
@@ -1766,10 +1868,10 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="O3" t="s">
-        <v>211</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4" spans="2:18" x14ac:dyDescent="0.45">
@@ -1795,22 +1897,22 @@
         <v>7</v>
       </c>
       <c r="K4" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="L4" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="O4" t="s">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="P4" t="s">
-        <v>213</v>
+        <v>234</v>
       </c>
       <c r="Q4" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
       <c r="R4" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.45">
@@ -1839,19 +1941,19 @@
         <v>12</v>
       </c>
       <c r="L5" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="O5" t="s">
-        <v>10</v>
+        <v>84</v>
       </c>
       <c r="P5" t="s">
         <v>8</v>
       </c>
       <c r="Q5">
-        <v>18.136420151493411</v>
+        <v>22.9435906</v>
       </c>
       <c r="R5">
-        <v>53.09476020715347</v>
+        <v>52.934591495109792</v>
       </c>
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.45">
@@ -1865,34 +1967,34 @@
         <v>9</v>
       </c>
       <c r="E6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" t="s">
+        <v>13</v>
+      </c>
+      <c r="K6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L6" t="s">
+        <v>148</v>
+      </c>
+      <c r="O6" t="s">
         <v>10</v>
       </c>
-      <c r="F6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H6" t="s">
-        <v>13</v>
-      </c>
-      <c r="K6" t="s">
-        <v>15</v>
-      </c>
-      <c r="L6" t="s">
-        <v>134</v>
-      </c>
-      <c r="O6" t="s">
-        <v>26</v>
-      </c>
       <c r="P6" t="s">
         <v>8</v>
       </c>
       <c r="Q6">
-        <v>15.036772099999991</v>
+        <v>19.212740275249061</v>
       </c>
       <c r="R6">
-        <v>52.764178895043841</v>
+        <v>49.84240724566758</v>
       </c>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.45">
@@ -1906,34 +2008,34 @@
         <v>9</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H7" t="s">
         <v>13</v>
       </c>
       <c r="K7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L7" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="O7" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="P7" t="s">
         <v>8</v>
       </c>
       <c r="Q7">
-        <v>16.425764160923386</v>
+        <v>15.114048637999945</v>
       </c>
       <c r="R7">
-        <v>51.187765701036277</v>
+        <v>51.092587962369954</v>
       </c>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.45">
@@ -1947,34 +2049,34 @@
         <v>9</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H8" t="s">
         <v>13</v>
       </c>
       <c r="K8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L8" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="O8" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="P8" t="s">
         <v>8</v>
       </c>
       <c r="Q8">
-        <v>17.694280600000003</v>
+        <v>18.136420151493411</v>
       </c>
       <c r="R8">
-        <v>51.108497194339172</v>
+        <v>53.09476020715347</v>
       </c>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.45">
@@ -1988,34 +2090,34 @@
         <v>9</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H9" t="s">
         <v>13</v>
       </c>
       <c r="K9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L9" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="O9" t="s">
-        <v>31</v>
+        <v>116</v>
       </c>
       <c r="P9" t="s">
         <v>8</v>
       </c>
       <c r="Q9">
-        <v>16.803664099999992</v>
+        <v>23.439530165761369</v>
       </c>
       <c r="R9">
-        <v>50.605684994101473</v>
+        <v>51.15840073090456</v>
       </c>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.45">
@@ -2029,34 +2131,34 @@
         <v>9</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H10" t="s">
         <v>13</v>
       </c>
       <c r="K10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L10" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="O10" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="P10" t="s">
         <v>8</v>
       </c>
       <c r="Q10">
-        <v>18.807259299999998</v>
+        <v>19.142315791015029</v>
       </c>
       <c r="R10">
-        <v>53.420298595291477</v>
+        <v>50.832052960395522</v>
       </c>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.45">
@@ -2070,34 +2172,34 @@
         <v>9</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F11" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H11" t="s">
         <v>13</v>
       </c>
       <c r="K11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L11" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="O11" t="s">
-        <v>50</v>
+        <v>93</v>
       </c>
       <c r="P11" t="s">
         <v>8</v>
       </c>
       <c r="Q11">
-        <v>20.529140970063281</v>
+        <v>21.932877434209747</v>
       </c>
       <c r="R11">
-        <v>53.802992196846674</v>
+        <v>49.994080927127975</v>
       </c>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.45">
@@ -2111,34 +2213,34 @@
         <v>9</v>
       </c>
       <c r="E12" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H12" t="s">
         <v>13</v>
       </c>
       <c r="K12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L12" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="O12" t="s">
-        <v>46</v>
+        <v>86</v>
       </c>
       <c r="P12" t="s">
         <v>8</v>
       </c>
       <c r="Q12">
-        <v>15.114292070099101</v>
+        <v>22.30185788377095</v>
       </c>
       <c r="R12">
-        <v>51.092411755272451</v>
+        <v>53.757586946292747</v>
       </c>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.45">
@@ -2152,25 +2254,25 @@
         <v>9</v>
       </c>
       <c r="E13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F13" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="G13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H13" t="s">
         <v>13</v>
       </c>
       <c r="K13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L13" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="O13" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="P13" t="s">
         <v>8</v>
@@ -2193,34 +2295,34 @@
         <v>9</v>
       </c>
       <c r="E14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H14" t="s">
         <v>13</v>
       </c>
       <c r="K14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L14" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="O14" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="P14" t="s">
         <v>8</v>
       </c>
       <c r="Q14">
-        <v>21.622064197413163</v>
+        <v>18.109334026299528</v>
       </c>
       <c r="R14">
-        <v>53.106985778887129</v>
+        <v>54.718832956325642</v>
       </c>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.45">
@@ -2234,34 +2336,34 @@
         <v>9</v>
       </c>
       <c r="E15" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F15" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H15" t="s">
         <v>13</v>
       </c>
       <c r="K15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L15" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="O15" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="P15" t="s">
         <v>8</v>
       </c>
       <c r="Q15">
-        <v>15.292621647189277</v>
+        <v>18.772002420791907</v>
       </c>
       <c r="R15">
-        <v>51.988382273984612</v>
+        <v>50.365380141626972</v>
       </c>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.45">
@@ -2275,34 +2377,34 @@
         <v>9</v>
       </c>
       <c r="E16" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F16" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="G16" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H16" t="s">
         <v>13</v>
       </c>
       <c r="K16" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L16" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="O16" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="P16" t="s">
         <v>8</v>
       </c>
       <c r="Q16">
-        <v>14.521960541156195</v>
+        <v>15.036772099999991</v>
       </c>
       <c r="R16">
-        <v>53.564351149135263</v>
+        <v>52.764178895043841</v>
       </c>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.45">
@@ -2316,34 +2418,34 @@
         <v>9</v>
       </c>
       <c r="E17" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F17" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G17" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H17" t="s">
         <v>13</v>
       </c>
       <c r="K17" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L17" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="O17" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="P17" t="s">
         <v>8</v>
       </c>
       <c r="Q17">
-        <v>21.852623292646182</v>
+        <v>22.32320624934065</v>
       </c>
       <c r="R17">
-        <v>49.688226064614483</v>
+        <v>53.773833315299122</v>
       </c>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.45">
@@ -2357,34 +2459,34 @@
         <v>9</v>
       </c>
       <c r="E18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F18" t="s">
         <v>11</v>
       </c>
-      <c r="F18" t="s">
-        <v>38</v>
-      </c>
       <c r="G18" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H18" t="s">
         <v>13</v>
       </c>
       <c r="K18" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L18" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="O18" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="P18" t="s">
         <v>8</v>
       </c>
       <c r="Q18">
-        <v>22.32320624934065</v>
+        <v>18.80413943487487</v>
       </c>
       <c r="R18">
-        <v>53.773833315299122</v>
+        <v>53.446973465922014</v>
       </c>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.45">
@@ -2398,34 +2500,34 @@
         <v>9</v>
       </c>
       <c r="E19" t="s">
+        <v>42</v>
+      </c>
+      <c r="F19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G19" t="s">
+        <v>43</v>
+      </c>
+      <c r="H19" t="s">
+        <v>13</v>
+      </c>
+      <c r="K19" t="s">
+        <v>43</v>
+      </c>
+      <c r="L19" t="s">
+        <v>161</v>
+      </c>
+      <c r="O19" t="s">
         <v>11</v>
       </c>
-      <c r="F19" t="s">
-        <v>40</v>
-      </c>
-      <c r="G19" t="s">
-        <v>41</v>
-      </c>
-      <c r="H19" t="s">
-        <v>13</v>
-      </c>
-      <c r="K19" t="s">
-        <v>41</v>
-      </c>
-      <c r="L19" t="s">
-        <v>147</v>
-      </c>
-      <c r="O19" t="s">
-        <v>36</v>
-      </c>
       <c r="P19" t="s">
         <v>8</v>
       </c>
       <c r="Q19">
-        <v>19.683344241421601</v>
+        <v>19.26958678998464</v>
       </c>
       <c r="R19">
-        <v>51.428225694344057</v>
+        <v>50.325695616526026</v>
       </c>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.45">
@@ -2439,34 +2541,34 @@
         <v>9</v>
       </c>
       <c r="E20" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F20" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G20" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H20" t="s">
         <v>13</v>
       </c>
       <c r="K20" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L20" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="O20" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="P20" t="s">
         <v>8</v>
       </c>
       <c r="Q20">
-        <v>18.907832339956155</v>
+        <v>17.971461740692011</v>
       </c>
       <c r="R20">
-        <v>51.14274257049226</v>
+        <v>50.613417792273673</v>
       </c>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.45">
@@ -2480,34 +2582,34 @@
         <v>9</v>
       </c>
       <c r="E21" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F21" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G21" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H21" t="s">
         <v>13</v>
       </c>
       <c r="K21" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L21" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="O21" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="P21" t="s">
         <v>8</v>
       </c>
       <c r="Q21">
-        <v>23.292570654205857</v>
+        <v>20.414702726123267</v>
       </c>
       <c r="R21">
-        <v>50.716735959213132</v>
+        <v>50.89970891903441</v>
       </c>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.45">
@@ -2521,34 +2623,34 @@
         <v>9</v>
       </c>
       <c r="E22" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F22" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="G22" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H22" t="s">
         <v>13</v>
       </c>
       <c r="K22" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L22" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="O22" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="P22" t="s">
         <v>8</v>
       </c>
       <c r="Q22">
-        <v>16.710076017737201</v>
+        <v>18.23382697092811</v>
       </c>
       <c r="R22">
-        <v>54.024054311061576</v>
+        <v>52.305225562416602</v>
       </c>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.45">
@@ -2562,34 +2664,34 @@
         <v>9</v>
       </c>
       <c r="E23" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="F23" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="G23" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H23" t="s">
         <v>13</v>
       </c>
       <c r="K23" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L23" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="O23" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="P23" t="s">
         <v>8</v>
       </c>
       <c r="Q23">
-        <v>16.005965049711531</v>
+        <v>16.710076017737201</v>
       </c>
       <c r="R23">
-        <v>51.662137784346321</v>
+        <v>54.024054311061576</v>
       </c>
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.45">
@@ -2603,34 +2705,34 @@
         <v>9</v>
       </c>
       <c r="E24" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="F24" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="G24" t="s">
+        <v>51</v>
+      </c>
+      <c r="H24" t="s">
+        <v>13</v>
+      </c>
+      <c r="K24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L24" t="s">
+        <v>166</v>
+      </c>
+      <c r="O24" t="s">
         <v>48</v>
       </c>
-      <c r="H24" t="s">
-        <v>13</v>
-      </c>
-      <c r="K24" t="s">
-        <v>48</v>
-      </c>
-      <c r="L24" t="s">
-        <v>152</v>
-      </c>
-      <c r="O24" t="s">
-        <v>77</v>
-      </c>
       <c r="P24" t="s">
         <v>8</v>
       </c>
       <c r="Q24">
-        <v>18.849567300984408</v>
+        <v>20.098449471876847</v>
       </c>
       <c r="R24">
-        <v>50.130601442155474</v>
+        <v>50.096013088752883</v>
       </c>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.45">
@@ -2644,34 +2746,34 @@
         <v>9</v>
       </c>
       <c r="E25" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="F25" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="G25" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="H25" t="s">
         <v>13</v>
       </c>
       <c r="K25" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="L25" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="O25" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="P25" t="s">
         <v>8</v>
       </c>
       <c r="Q25">
-        <v>20.926415095548208</v>
+        <v>21.852623292646182</v>
       </c>
       <c r="R25">
-        <v>50.022590448951917</v>
+        <v>49.688226064614483</v>
       </c>
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.45">
@@ -2685,34 +2787,34 @@
         <v>9</v>
       </c>
       <c r="E26" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F26" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G26" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="H26" t="s">
         <v>13</v>
       </c>
       <c r="K26" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="L26" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="O26" t="s">
-        <v>69</v>
+        <v>26</v>
       </c>
       <c r="P26" t="s">
         <v>8</v>
       </c>
       <c r="Q26">
-        <v>23.439530165761369</v>
+        <v>18.807259299999998</v>
       </c>
       <c r="R26">
-        <v>51.15840073090456</v>
+        <v>53.420298595291477</v>
       </c>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.45">
@@ -2726,34 +2828,34 @@
         <v>9</v>
       </c>
       <c r="E27" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F27" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="G27" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="H27" t="s">
         <v>13</v>
       </c>
       <c r="K27" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="L27" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="O27" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="P27" t="s">
         <v>8</v>
       </c>
       <c r="Q27">
-        <v>21.932877434209747</v>
+        <v>16.425764160923386</v>
       </c>
       <c r="R27">
-        <v>49.994080927127975</v>
+        <v>51.187765701036277</v>
       </c>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.45">
@@ -2767,34 +2869,34 @@
         <v>9</v>
       </c>
       <c r="E28" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F28" t="s">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="G28" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="H28" t="s">
         <v>13</v>
       </c>
       <c r="K28" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="L28" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="O28" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="P28" t="s">
         <v>8</v>
       </c>
       <c r="Q28">
-        <v>20.414702726123267</v>
+        <v>21.622064197413163</v>
       </c>
       <c r="R28">
-        <v>50.89970891903441</v>
+        <v>53.106985778887129</v>
       </c>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.45">
@@ -2808,34 +2910,34 @@
         <v>9</v>
       </c>
       <c r="E29" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F29" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="G29" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H29" t="s">
         <v>13</v>
       </c>
       <c r="K29" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="L29" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="O29" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="P29" t="s">
         <v>8</v>
       </c>
       <c r="Q29">
-        <v>21.329216800872093</v>
+        <v>16.005965049711531</v>
       </c>
       <c r="R29">
-        <v>50.441384740226297</v>
+        <v>51.662137784346321</v>
       </c>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.45">
@@ -2849,34 +2951,34 @@
         <v>9</v>
       </c>
       <c r="E30" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F30" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="G30" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H30" t="s">
         <v>13</v>
       </c>
       <c r="K30" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="L30" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="O30" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="P30" t="s">
         <v>8</v>
       </c>
       <c r="Q30">
-        <v>21.87079962455832</v>
+        <v>21.329216800872093</v>
       </c>
       <c r="R30">
-        <v>50.190926527507919</v>
+        <v>50.441384740226297</v>
       </c>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.45">
@@ -2890,34 +2992,34 @@
         <v>9</v>
       </c>
       <c r="E31" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="F31" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="G31" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H31" t="s">
         <v>13</v>
       </c>
       <c r="K31" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="L31" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="O31" t="s">
-        <v>40</v>
+        <v>96</v>
       </c>
       <c r="P31" t="s">
         <v>8</v>
       </c>
       <c r="Q31">
-        <v>19.142315791015029</v>
+        <v>17.694280600000003</v>
       </c>
       <c r="R31">
-        <v>50.832052960395522</v>
+        <v>51.108497194339172</v>
       </c>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.45">
@@ -2931,34 +3033,34 @@
         <v>9</v>
       </c>
       <c r="E32" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F32" t="s">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="G32" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="H32" t="s">
         <v>13</v>
       </c>
       <c r="K32" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="L32" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="O32" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="P32" t="s">
         <v>8</v>
       </c>
       <c r="Q32">
-        <v>18.956064538096921</v>
+        <v>20.529140970063281</v>
       </c>
       <c r="R32">
-        <v>52.714665383017554</v>
+        <v>53.802992196846674</v>
       </c>
     </row>
     <row r="33" spans="2:18" x14ac:dyDescent="0.45">
@@ -2972,34 +3074,34 @@
         <v>9</v>
       </c>
       <c r="E33" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F33" t="s">
-        <v>63</v>
+        <v>22</v>
       </c>
       <c r="G33" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H33" t="s">
         <v>13</v>
       </c>
       <c r="K33" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="L33" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="O33" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="P33" t="s">
         <v>8</v>
       </c>
       <c r="Q33">
-        <v>21.451867596848331</v>
+        <v>17.872695321486159</v>
       </c>
       <c r="R33">
-        <v>50.938934166502882</v>
+        <v>50.746544696597532</v>
       </c>
     </row>
     <row r="34" spans="2:18" x14ac:dyDescent="0.45">
@@ -3013,34 +3115,34 @@
         <v>9</v>
       </c>
       <c r="E34" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="F34" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="G34" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="H34" t="s">
         <v>13</v>
       </c>
       <c r="K34" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="L34" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="O34" t="s">
-        <v>105</v>
+        <v>56</v>
       </c>
       <c r="P34" t="s">
         <v>8</v>
       </c>
       <c r="Q34">
-        <v>17.872695321486159</v>
+        <v>21.451867596848331</v>
       </c>
       <c r="R34">
-        <v>50.746544696597532</v>
+        <v>50.938934166502882</v>
       </c>
     </row>
     <row r="35" spans="2:18" x14ac:dyDescent="0.45">
@@ -3054,34 +3156,34 @@
         <v>9</v>
       </c>
       <c r="E35" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F35" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="G35" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H35" t="s">
         <v>13</v>
       </c>
       <c r="K35" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="L35" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="O35" t="s">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="P35" t="s">
         <v>8</v>
       </c>
       <c r="Q35">
-        <v>16.89038355962467</v>
+        <v>19.683344241421601</v>
       </c>
       <c r="R35">
-        <v>54.50215260847132</v>
+        <v>51.428225694344057</v>
       </c>
     </row>
     <row r="36" spans="2:18" x14ac:dyDescent="0.45">
@@ -3095,34 +3197,34 @@
         <v>9</v>
       </c>
       <c r="E36" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F36" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="G36" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="H36" t="s">
         <v>13</v>
       </c>
       <c r="K36" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="L36" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="O36" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="P36" t="s">
         <v>8</v>
       </c>
       <c r="Q36">
-        <v>18.772002420791907</v>
+        <v>19.702975226287894</v>
       </c>
       <c r="R36">
-        <v>50.365380141626972</v>
+        <v>52.585421539045129</v>
       </c>
     </row>
     <row r="37" spans="2:18" x14ac:dyDescent="0.45">
@@ -3136,34 +3238,34 @@
         <v>9</v>
       </c>
       <c r="E37" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F37" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G37" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H37" t="s">
         <v>13</v>
       </c>
       <c r="K37" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="L37" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="O37" t="s">
-        <v>57</v>
+        <v>110</v>
       </c>
       <c r="P37" t="s">
         <v>8</v>
       </c>
       <c r="Q37">
-        <v>22.30185788377095</v>
+        <v>14.521960541156195</v>
       </c>
       <c r="R37">
-        <v>53.757586946292747</v>
+        <v>53.564351149135263</v>
       </c>
     </row>
     <row r="38" spans="2:18" x14ac:dyDescent="0.45">
@@ -3177,34 +3279,34 @@
         <v>9</v>
       </c>
       <c r="E38" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F38" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G38" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="H38" t="s">
         <v>13</v>
       </c>
       <c r="K38" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="L38" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="O38" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="P38" t="s">
         <v>8</v>
       </c>
       <c r="Q38">
-        <v>17.971461740692011</v>
+        <v>16.779042268819836</v>
       </c>
       <c r="R38">
-        <v>50.613417792273673</v>
+        <v>52.367785611218373</v>
       </c>
     </row>
     <row r="39" spans="2:18" x14ac:dyDescent="0.45">
@@ -3218,34 +3320,34 @@
         <v>9</v>
       </c>
       <c r="E39" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F39" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="G39" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="H39" t="s">
         <v>13</v>
       </c>
       <c r="K39" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="L39" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="O39" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="P39" t="s">
         <v>8</v>
       </c>
       <c r="Q39">
-        <v>14.476073038134764</v>
+        <v>21.989289035599807</v>
       </c>
       <c r="R39">
-        <v>53.19612477284646</v>
+        <v>51.453800109559978</v>
       </c>
     </row>
     <row r="40" spans="2:18" x14ac:dyDescent="0.45">
@@ -3259,34 +3361,34 @@
         <v>9</v>
       </c>
       <c r="E40" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F40" t="s">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="G40" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H40" t="s">
         <v>13</v>
       </c>
       <c r="K40" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="L40" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="O40" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="P40" t="s">
         <v>8</v>
       </c>
       <c r="Q40">
-        <v>19.26958678998464</v>
+        <v>18.907832339956155</v>
       </c>
       <c r="R40">
-        <v>50.325695616526026</v>
+        <v>51.14274257049226</v>
       </c>
     </row>
     <row r="41" spans="2:18" x14ac:dyDescent="0.45">
@@ -3300,34 +3402,34 @@
         <v>9</v>
       </c>
       <c r="E41" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F41" t="s">
-        <v>10</v>
+        <v>79</v>
       </c>
       <c r="G41" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H41" t="s">
         <v>13</v>
       </c>
       <c r="K41" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="L41" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="O41" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="P41" t="s">
         <v>8</v>
       </c>
       <c r="Q41">
-        <v>19.212740275249061</v>
+        <v>21.87079962455832</v>
       </c>
       <c r="R41">
-        <v>49.84240724566758</v>
+        <v>50.190926527507919</v>
       </c>
     </row>
     <row r="42" spans="2:18" x14ac:dyDescent="0.45">
@@ -3341,34 +3443,34 @@
         <v>9</v>
       </c>
       <c r="E42" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F42" t="s">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="G42" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H42" t="s">
         <v>13</v>
       </c>
       <c r="K42" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="L42" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="O42" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="P42" t="s">
         <v>8</v>
       </c>
       <c r="Q42">
-        <v>18.80413943487487</v>
+        <v>16.891209385550301</v>
       </c>
       <c r="R42">
-        <v>53.446973465922014</v>
+        <v>54.501380892532538</v>
       </c>
     </row>
     <row r="43" spans="2:18" x14ac:dyDescent="0.45">
@@ -3382,34 +3484,34 @@
         <v>9</v>
       </c>
       <c r="E43" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F43" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G43" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="H43" t="s">
         <v>13</v>
       </c>
       <c r="K43" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="L43" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="O43" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="P43" t="s">
         <v>8</v>
       </c>
       <c r="Q43">
-        <v>19.702975226287894</v>
+        <v>18.849567300984408</v>
       </c>
       <c r="R43">
-        <v>52.585421539045129</v>
+        <v>50.130601442155474</v>
       </c>
     </row>
     <row r="44" spans="2:18" x14ac:dyDescent="0.45">
@@ -3423,34 +3525,34 @@
         <v>9</v>
       </c>
       <c r="E44" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F44" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G44" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="H44" t="s">
         <v>13</v>
       </c>
       <c r="K44" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="L44" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="O44" t="s">
-        <v>120</v>
+        <v>79</v>
       </c>
       <c r="P44" t="s">
         <v>8</v>
       </c>
       <c r="Q44">
-        <v>20.098449471876847</v>
+        <v>16.803664099999992</v>
       </c>
       <c r="R44">
-        <v>50.096013088752883</v>
+        <v>50.605684994101473</v>
       </c>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.45">
@@ -3464,34 +3566,34 @@
         <v>9</v>
       </c>
       <c r="E45" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F45" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="G45" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="H45" t="s">
         <v>13</v>
       </c>
       <c r="K45" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="L45" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="O45" t="s">
-        <v>97</v>
+        <v>133</v>
       </c>
       <c r="P45" t="s">
         <v>8</v>
       </c>
       <c r="Q45">
-        <v>21.989289035599807</v>
+        <v>14.476073038134764</v>
       </c>
       <c r="R45">
-        <v>51.453800109559978</v>
+        <v>53.19612477284646</v>
       </c>
     </row>
     <row r="46" spans="2:18" x14ac:dyDescent="0.45">
@@ -3505,34 +3607,34 @@
         <v>9</v>
       </c>
       <c r="E46" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F46" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="G46" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="H46" t="s">
         <v>13</v>
       </c>
       <c r="K46" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="L46" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="O46" t="s">
-        <v>216</v>
+        <v>72</v>
       </c>
       <c r="P46" t="s">
         <v>8</v>
       </c>
       <c r="Q46">
-        <v>14.918750384776654</v>
+        <v>20.926415095548208</v>
       </c>
       <c r="R46">
-        <v>51.583436367597201</v>
+        <v>50.022590448951917</v>
       </c>
     </row>
     <row r="47" spans="2:18" x14ac:dyDescent="0.45">
@@ -3546,34 +3648,34 @@
         <v>9</v>
       </c>
       <c r="E47" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F47" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="G47" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="H47" t="s">
         <v>13</v>
       </c>
       <c r="K47" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="L47" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="O47" t="s">
-        <v>217</v>
+        <v>127</v>
       </c>
       <c r="P47" t="s">
         <v>8</v>
       </c>
       <c r="Q47">
-        <v>17.419694531519191</v>
+        <v>16.89038355962467</v>
       </c>
       <c r="R47">
-        <v>50.345189363482064</v>
+        <v>54.50215260847132</v>
       </c>
     </row>
     <row r="48" spans="2:18" x14ac:dyDescent="0.45">
@@ -3587,34 +3689,34 @@
         <v>9</v>
       </c>
       <c r="E48" t="s">
-        <v>84</v>
+        <v>17</v>
       </c>
       <c r="F48" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="G48" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H48" t="s">
         <v>13</v>
       </c>
       <c r="K48" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="L48" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="O48" t="s">
-        <v>218</v>
+        <v>62</v>
       </c>
       <c r="P48" t="s">
         <v>8</v>
       </c>
       <c r="Q48">
-        <v>16.751959330113646</v>
+        <v>20.877296701170323</v>
       </c>
       <c r="R48">
-        <v>51.394042753969877</v>
+        <v>52.214439540966467</v>
       </c>
     </row>
     <row r="49" spans="2:18" x14ac:dyDescent="0.45">
@@ -3628,34 +3730,34 @@
         <v>9</v>
       </c>
       <c r="E49" t="s">
-        <v>89</v>
+        <v>54</v>
       </c>
       <c r="F49" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="G49" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="H49" t="s">
         <v>13</v>
       </c>
       <c r="K49" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="L49" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="O49" t="s">
-        <v>219</v>
+        <v>64</v>
       </c>
       <c r="P49" t="s">
         <v>8</v>
       </c>
       <c r="Q49">
-        <v>14.990153475277031</v>
+        <v>18.956064538096921</v>
       </c>
       <c r="R49">
-        <v>52.622736475773067</v>
+        <v>52.714665383017554</v>
       </c>
     </row>
     <row r="50" spans="2:18" x14ac:dyDescent="0.45">
@@ -3669,34 +3771,34 @@
         <v>9</v>
       </c>
       <c r="E50" t="s">
-        <v>89</v>
+        <v>54</v>
       </c>
       <c r="F50" t="s">
-        <v>91</v>
+        <v>56</v>
       </c>
       <c r="G50" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="H50" t="s">
         <v>13</v>
       </c>
       <c r="K50" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="L50" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="O50" t="s">
-        <v>220</v>
+        <v>81</v>
       </c>
       <c r="P50" t="s">
         <v>8</v>
       </c>
       <c r="Q50">
-        <v>16.824637442608388</v>
+        <v>17.119120438571215</v>
       </c>
       <c r="R50">
-        <v>52.928251230696389</v>
+        <v>51.213751122843391</v>
       </c>
     </row>
     <row r="51" spans="2:18" x14ac:dyDescent="0.45">
@@ -3710,34 +3812,34 @@
         <v>9</v>
       </c>
       <c r="E51" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="F51" t="s">
-        <v>93</v>
+        <v>30</v>
       </c>
       <c r="G51" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="H51" t="s">
         <v>13</v>
       </c>
       <c r="K51" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="L51" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="O51" t="s">
-        <v>221</v>
+        <v>120</v>
       </c>
       <c r="P51" t="s">
         <v>8</v>
       </c>
       <c r="Q51">
-        <v>20.643266624036407</v>
+        <v>23.292570654205857</v>
       </c>
       <c r="R51">
-        <v>54.059169587861376</v>
+        <v>50.716735959213132</v>
       </c>
     </row>
     <row r="52" spans="2:18" x14ac:dyDescent="0.45">
@@ -3751,34 +3853,34 @@
         <v>9</v>
       </c>
       <c r="E52" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="F52" t="s">
-        <v>91</v>
+        <v>33</v>
       </c>
       <c r="G52" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="H52" t="s">
         <v>13</v>
       </c>
       <c r="K52" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="L52" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="O52" t="s">
-        <v>222</v>
+        <v>19</v>
       </c>
       <c r="P52" t="s">
         <v>8</v>
       </c>
       <c r="Q52">
-        <v>16.92764152265681</v>
+        <v>15.292621647189277</v>
       </c>
       <c r="R52">
-        <v>54.160621229584443</v>
+        <v>51.988382273984612</v>
       </c>
     </row>
     <row r="53" spans="2:18" x14ac:dyDescent="0.45">
@@ -3792,34 +3894,34 @@
         <v>9</v>
       </c>
       <c r="E53" t="s">
-        <v>63</v>
+        <v>96</v>
       </c>
       <c r="F53" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="G53" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="H53" t="s">
         <v>13</v>
       </c>
       <c r="K53" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L53" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="O53" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="P53" t="s">
         <v>8</v>
       </c>
       <c r="Q53">
-        <v>19.007446557812909</v>
+        <v>14.802766317314759</v>
       </c>
       <c r="R53">
-        <v>53.850966420117743</v>
+        <v>51.535218780041816</v>
       </c>
     </row>
     <row r="54" spans="2:18" x14ac:dyDescent="0.45">
@@ -3833,34 +3935,34 @@
         <v>9</v>
       </c>
       <c r="E54" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="F54" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G54" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="H54" t="s">
         <v>13</v>
       </c>
       <c r="K54" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="L54" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="O54" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="P54" t="s">
         <v>8</v>
       </c>
       <c r="Q54">
-        <v>23.043264145360411</v>
+        <v>17.419694531519191</v>
       </c>
       <c r="R54">
-        <v>52.430848156657824</v>
+        <v>50.345189363482064</v>
       </c>
     </row>
     <row r="55" spans="2:18" x14ac:dyDescent="0.45">
@@ -3874,34 +3976,34 @@
         <v>9</v>
       </c>
       <c r="E55" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="F55" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="G55" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H55" t="s">
         <v>13</v>
       </c>
       <c r="K55" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="L55" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="O55" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="P55" t="s">
         <v>8</v>
       </c>
       <c r="Q55">
-        <v>22.2025648456056</v>
+        <v>17.419694531519191</v>
       </c>
       <c r="R55">
-        <v>54.306478182754368</v>
+        <v>51.113688192174173</v>
       </c>
     </row>
     <row r="56" spans="2:18" x14ac:dyDescent="0.45">
@@ -3915,34 +4017,34 @@
         <v>9</v>
       </c>
       <c r="E56" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="F56" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="G56" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="H56" t="s">
         <v>13</v>
       </c>
       <c r="K56" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="L56" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="O56" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="P56" t="s">
         <v>8</v>
       </c>
       <c r="Q56">
-        <v>22.619231503504921</v>
+        <v>14.879031900155717</v>
       </c>
       <c r="R56">
-        <v>53.408286508261966</v>
+        <v>52.593490272793417</v>
       </c>
     </row>
     <row r="57" spans="2:18" x14ac:dyDescent="0.45">
@@ -3956,34 +4058,34 @@
         <v>9</v>
       </c>
       <c r="E57" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="F57" t="s">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="G57" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="H57" t="s">
         <v>13</v>
       </c>
       <c r="K57" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="L57" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="O57" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="P57" t="s">
         <v>8</v>
       </c>
       <c r="Q57">
-        <v>22.73628524706481</v>
+        <v>16.921576298661556</v>
       </c>
       <c r="R57">
-        <v>49.725566374889411</v>
+        <v>53.043150454655688</v>
       </c>
     </row>
     <row r="58" spans="2:18" x14ac:dyDescent="0.45">
@@ -3997,34 +4099,34 @@
         <v>9</v>
       </c>
       <c r="E58" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F58" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G58" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="H58" t="s">
         <v>13</v>
       </c>
       <c r="K58" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="L58" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="O58" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="P58" t="s">
         <v>8</v>
       </c>
       <c r="Q58">
-        <v>23.511924325985657</v>
+        <v>20.701782962343003</v>
       </c>
       <c r="R58">
-        <v>50.329104893700588</v>
+        <v>54.18832903488137</v>
       </c>
     </row>
     <row r="59" spans="2:18" x14ac:dyDescent="0.45">
@@ -4038,34 +4140,34 @@
         <v>9</v>
       </c>
       <c r="E59" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F59" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="G59" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="H59" t="s">
         <v>13</v>
       </c>
       <c r="K59" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="L59" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="O59" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="P59" t="s">
         <v>8</v>
       </c>
       <c r="Q59">
-        <v>19.974964350935519</v>
+        <v>17.019284902403875</v>
       </c>
       <c r="R59">
-        <v>49.925997532530509</v>
+        <v>54.223922873901166</v>
       </c>
     </row>
     <row r="60" spans="2:18" x14ac:dyDescent="0.45">
@@ -4079,34 +4181,34 @@
         <v>9</v>
       </c>
       <c r="E60" t="s">
-        <v>91</v>
+        <v>44</v>
       </c>
       <c r="F60" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="G60" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="H60" t="s">
         <v>13</v>
       </c>
       <c r="K60" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="L60" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="O60" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="P60" t="s">
         <v>8</v>
       </c>
       <c r="Q60">
-        <v>18.855198827926174</v>
+        <v>19.124890801214669</v>
       </c>
       <c r="R60">
-        <v>50.373976316407479</v>
+        <v>53.942470818380237</v>
       </c>
     </row>
     <row r="61" spans="2:18" x14ac:dyDescent="0.45">
@@ -4120,34 +4222,34 @@
         <v>9</v>
       </c>
       <c r="E61" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F61" t="s">
-        <v>11</v>
+        <v>66</v>
       </c>
       <c r="G61" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H61" t="s">
         <v>13</v>
       </c>
       <c r="K61" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="L61" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="O61" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="P61" t="s">
         <v>8</v>
       </c>
       <c r="Q61">
-        <v>18.49109582272952</v>
+        <v>22.958991065199903</v>
       </c>
       <c r="R61">
-        <v>51.996387905088739</v>
+        <v>52.452026740518932</v>
       </c>
     </row>
     <row r="62" spans="2:18" x14ac:dyDescent="0.45">
@@ -4161,34 +4263,34 @@
         <v>9</v>
       </c>
       <c r="E62" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="F62" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G62" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="H62" t="s">
         <v>13</v>
       </c>
       <c r="K62" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="L62" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="O62" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="P62" t="s">
         <v>8</v>
       </c>
       <c r="Q62">
-        <v>18.672302969332311</v>
+        <v>22.192834290615568</v>
       </c>
       <c r="R62">
-        <v>52.848851245773041</v>
+        <v>54.314299403909786</v>
       </c>
     </row>
     <row r="63" spans="2:18" x14ac:dyDescent="0.45">
@@ -4202,34 +4304,34 @@
         <v>9</v>
       </c>
       <c r="E63" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="F63" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="G63" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="H63" t="s">
         <v>13</v>
       </c>
       <c r="K63" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="L63" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="O63" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="P63" t="s">
         <v>8</v>
       </c>
       <c r="Q63">
-        <v>21.103293415309576</v>
+        <v>22.648597650181891</v>
       </c>
       <c r="R63">
-        <v>52.463652089533532</v>
+        <v>53.434480489186768</v>
       </c>
     </row>
     <row r="64" spans="2:18" x14ac:dyDescent="0.45">
@@ -4243,34 +4345,34 @@
         <v>9</v>
       </c>
       <c r="E64" t="s">
-        <v>73</v>
+        <v>28</v>
       </c>
       <c r="F64" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="G64" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="H64" t="s">
         <v>13</v>
       </c>
       <c r="K64" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="L64" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="O64" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="P64" t="s">
         <v>8</v>
       </c>
       <c r="Q64">
-        <v>20.661910967063164</v>
+        <v>22.769487912886849</v>
       </c>
       <c r="R64">
-        <v>51.291433003066999</v>
+        <v>49.699254968261187</v>
       </c>
     </row>
     <row r="65" spans="2:18" x14ac:dyDescent="0.45">
@@ -4284,34 +4386,34 @@
         <v>9</v>
       </c>
       <c r="E65" t="s">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="F65" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="G65" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="H65" t="s">
         <v>13</v>
       </c>
       <c r="K65" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="L65" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="O65" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="P65" t="s">
         <v>8</v>
       </c>
       <c r="Q65">
-        <v>21.901398412958557</v>
+        <v>23.518797665713208</v>
       </c>
       <c r="R65">
-        <v>51.935870244934229</v>
+        <v>50.281517317209371</v>
       </c>
     </row>
     <row r="66" spans="2:18" x14ac:dyDescent="0.45">
@@ -4325,34 +4427,34 @@
         <v>9</v>
       </c>
       <c r="E66" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="F66" t="s">
-        <v>55</v>
+        <v>116</v>
       </c>
       <c r="G66" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="H66" t="s">
         <v>13</v>
       </c>
       <c r="K66" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="L66" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="O66" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="P66" t="s">
         <v>8</v>
       </c>
       <c r="Q66">
-        <v>19.270472330221128</v>
+        <v>19.808895899423351</v>
       </c>
       <c r="R66">
-        <v>54.260443399297102</v>
+        <v>49.877840849428637</v>
       </c>
     </row>
     <row r="67" spans="2:18" x14ac:dyDescent="0.45">
@@ -4366,34 +4468,34 @@
         <v>9</v>
       </c>
       <c r="E67" t="s">
-        <v>42</v>
+        <v>105</v>
       </c>
       <c r="F67" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="G67" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="H67" t="s">
         <v>13</v>
       </c>
       <c r="K67" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="L67" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="O67" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="P67" t="s">
         <v>8</v>
       </c>
       <c r="Q67">
-        <v>19.132260930767764</v>
+        <v>18.832255867717425</v>
       </c>
       <c r="R67">
-        <v>55.159763763021651</v>
+        <v>50.208161047601962</v>
       </c>
     </row>
     <row r="68" spans="2:18" x14ac:dyDescent="0.45">
@@ -4407,34 +4509,34 @@
         <v>9</v>
       </c>
       <c r="E68" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="F68" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="G68" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="H68" t="s">
         <v>13</v>
       </c>
       <c r="K68" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="L68" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="O68" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="P68" t="s">
         <v>8</v>
       </c>
       <c r="Q68">
-        <v>19.209642059320888</v>
+        <v>18.264969048585325</v>
       </c>
       <c r="R68">
-        <v>54.710103581159373</v>
+        <v>52.039365767049581</v>
       </c>
     </row>
     <row r="69" spans="2:18" x14ac:dyDescent="0.45">
@@ -4448,34 +4550,34 @@
         <v>9</v>
       </c>
       <c r="E69" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="F69" t="s">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="G69" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="H69" t="s">
         <v>13</v>
       </c>
       <c r="K69" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="L69" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="O69" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="P69" t="s">
         <v>8</v>
       </c>
       <c r="Q69">
-        <v>16.941424009640372</v>
+        <v>18.420682874609959</v>
       </c>
       <c r="R69">
-        <v>55.609423944883922</v>
+        <v>53.000181755301838</v>
       </c>
     </row>
     <row r="70" spans="2:18" x14ac:dyDescent="0.45">
@@ -4489,34 +4591,34 @@
         <v>9</v>
       </c>
       <c r="E70" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="F70" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G70" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="H70" t="s">
         <v>13</v>
       </c>
       <c r="K70" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="L70" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="O70" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="P70" t="s">
         <v>8</v>
       </c>
       <c r="Q70">
-        <v>18.450609737767209</v>
+        <v>21.248115859694053</v>
       </c>
       <c r="R70">
-        <v>55.609423944883922</v>
+        <v>52.500354971622542</v>
       </c>
     </row>
     <row r="71" spans="2:18" x14ac:dyDescent="0.45">
@@ -4530,34 +4632,34 @@
         <v>9</v>
       </c>
       <c r="E71" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="F71" t="s">
-        <v>77</v>
+        <v>33</v>
       </c>
       <c r="G71" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="H71" t="s">
         <v>13</v>
       </c>
       <c r="K71" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="L71" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="O71" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="P71" t="s">
         <v>8</v>
       </c>
       <c r="Q71">
-        <v>17.878339404336558</v>
+        <v>20.515250703668858</v>
       </c>
       <c r="R71">
-        <v>55.159763763021651</v>
+        <v>51.474217933303869</v>
       </c>
     </row>
     <row r="72" spans="2:18" x14ac:dyDescent="0.45">
@@ -4571,34 +4673,34 @@
         <v>9</v>
       </c>
       <c r="E72" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F72" t="s">
-        <v>89</v>
+        <v>54</v>
       </c>
       <c r="G72" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="H72" t="s">
         <v>13</v>
       </c>
       <c r="K72" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="L72" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="O72" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="P72" t="s">
         <v>8</v>
       </c>
       <c r="Q72">
-        <v>15.473861680498253</v>
+        <v>21.857841551631548</v>
       </c>
       <c r="R72">
-        <v>54.260443399297102</v>
+        <v>51.981070871811788</v>
       </c>
     </row>
     <row r="73" spans="2:18" x14ac:dyDescent="0.45">
@@ -4612,34 +4714,34 @@
         <v>9</v>
       </c>
       <c r="E73" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F73" t="s">
-        <v>40</v>
+        <v>105</v>
       </c>
       <c r="G73" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="H73" t="s">
         <v>13</v>
       </c>
       <c r="K73" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="L73" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="O73" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="P73" t="s">
         <v>8</v>
       </c>
       <c r="Q73">
-        <v>15.288202232632583</v>
+        <v>19.270410803611803</v>
       </c>
       <c r="R73">
-        <v>54.71010358115938</v>
+        <v>54.260516439232255</v>
       </c>
     </row>
     <row r="74" spans="2:18" x14ac:dyDescent="0.45">
@@ -4653,34 +4755,34 @@
         <v>9</v>
       </c>
       <c r="E74" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="F74" t="s">
-        <v>120</v>
+        <v>35</v>
       </c>
       <c r="G74" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H74" t="s">
         <v>13</v>
       </c>
       <c r="K74" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="L74" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="O74" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="P74" t="s">
         <v>8</v>
       </c>
       <c r="Q74">
-        <v>16.268434622192224</v>
+        <v>19.132199145306835</v>
       </c>
       <c r="R74">
-        <v>55.159763763021651</v>
+        <v>55.159813342891759</v>
       </c>
     </row>
     <row r="75" spans="2:18" x14ac:dyDescent="0.45">
@@ -4694,34 +4796,34 @@
         <v>9</v>
       </c>
       <c r="E75" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="F75" t="s">
-        <v>80</v>
+        <v>127</v>
       </c>
       <c r="G75" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="H75" t="s">
         <v>13</v>
       </c>
       <c r="K75" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="L75" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="O75" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="P75" t="s">
         <v>8</v>
       </c>
       <c r="Q75">
-        <v>16.047850156734548</v>
+        <v>19.209580353300481</v>
       </c>
       <c r="R75">
-        <v>54.710103581159373</v>
+        <v>54.710164987068232</v>
       </c>
     </row>
     <row r="76" spans="2:18" x14ac:dyDescent="0.45">
@@ -4735,34 +4837,34 @@
         <v>9</v>
       </c>
       <c r="E76" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="F76" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G76" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="H76" t="s">
         <v>13</v>
       </c>
       <c r="K76" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="L76" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="O76" t="s">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="P76" t="s">
         <v>8</v>
       </c>
       <c r="Q76">
-        <v>20.569491805687608</v>
+        <v>16.941376551896891</v>
       </c>
       <c r="R76">
-        <v>51.945619106835984</v>
+        <v>55.60946078087305</v>
       </c>
     </row>
     <row r="77" spans="2:18" x14ac:dyDescent="0.45">
@@ -4776,34 +4878,34 @@
         <v>9</v>
       </c>
       <c r="E77" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="F77" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="G77" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="H77" t="s">
         <v>13</v>
       </c>
       <c r="K77" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="L77" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="O77" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="P77" t="s">
         <v>8</v>
       </c>
       <c r="Q77">
-        <v>21.215073317961568</v>
+        <v>18.450551982707839</v>
       </c>
       <c r="R77">
-        <v>50.551911719897767</v>
+        <v>55.609461280132123</v>
       </c>
     </row>
     <row r="78" spans="2:18" x14ac:dyDescent="0.45">
@@ -4817,34 +4919,34 @@
         <v>9</v>
       </c>
       <c r="E78" t="s">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="F78" t="s">
-        <v>84</v>
+        <v>11</v>
       </c>
       <c r="G78" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="H78" t="s">
         <v>13</v>
       </c>
       <c r="K78" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="L78" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="O78" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="P78" t="s">
         <v>8</v>
       </c>
       <c r="Q78">
-        <v>22.221541482666314</v>
+        <v>17.878286085105412</v>
       </c>
       <c r="R78">
-        <v>52.402780027123931</v>
+        <v>55.159812876695007</v>
       </c>
     </row>
     <row r="79" spans="2:18" x14ac:dyDescent="0.45">
@@ -4858,34 +4960,34 @@
         <v>9</v>
       </c>
       <c r="E79" t="s">
-        <v>120</v>
+        <v>79</v>
       </c>
       <c r="F79" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G79" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="H79" t="s">
         <v>13</v>
       </c>
       <c r="K79" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="L79" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="O79" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="P79" t="s">
         <v>8</v>
       </c>
       <c r="Q79">
-        <v>23.413558137569936</v>
+        <v>15.47382532166216</v>
       </c>
       <c r="R79">
-        <v>50.221928080120989</v>
+        <v>54.260515174922851</v>
       </c>
     </row>
     <row r="80" spans="2:18" x14ac:dyDescent="0.45">
@@ -4899,34 +5001,34 @@
         <v>9</v>
       </c>
       <c r="E80" t="s">
-        <v>97</v>
+        <v>133</v>
       </c>
       <c r="F80" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="G80" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="H80" t="s">
         <v>13</v>
       </c>
       <c r="K80" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="L80" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="O80" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="P80" t="s">
         <v>8</v>
       </c>
       <c r="Q80">
-        <v>22.593353600809184</v>
+        <v>15.28816677077992</v>
       </c>
       <c r="R80">
-        <v>53.760902274894448</v>
+        <v>54.710163723178738</v>
       </c>
     </row>
     <row r="81" spans="2:18" x14ac:dyDescent="0.45">
@@ -4940,34 +5042,34 @@
         <v>9</v>
       </c>
       <c r="E81" t="s">
-        <v>97</v>
+        <v>133</v>
       </c>
       <c r="F81" t="s">
-        <v>68</v>
+        <v>110</v>
       </c>
       <c r="G81" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="H81" t="s">
         <v>13</v>
       </c>
       <c r="K81" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="L81" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="O81" t="s">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="P81" t="s">
         <v>8</v>
       </c>
       <c r="Q81">
-        <v>18.692082563317275</v>
+        <v>16.268392183867956</v>
       </c>
       <c r="R81">
-        <v>52.378757098306828</v>
+        <v>55.159812379291822</v>
       </c>
     </row>
     <row r="82" spans="2:18" x14ac:dyDescent="0.45">
@@ -4981,215 +5083,502 @@
         <v>9</v>
       </c>
       <c r="E82" t="s">
-        <v>97</v>
+        <v>133</v>
       </c>
       <c r="F82" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="G82" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="H82" t="s">
         <v>13</v>
       </c>
       <c r="K82" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="L82" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="O82" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="P82" t="s">
         <v>8</v>
       </c>
       <c r="Q82">
+        <v>16.047809605897839</v>
+      </c>
+      <c r="R82">
+        <v>54.710163913347117</v>
+      </c>
+    </row>
+    <row r="83" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B83" t="s">
+        <v>8</v>
+      </c>
+      <c r="C83" t="s">
+        <v>8</v>
+      </c>
+      <c r="D83" t="s">
+        <v>9</v>
+      </c>
+      <c r="E83" t="s">
+        <v>72</v>
+      </c>
+      <c r="F83" t="s">
+        <v>74</v>
+      </c>
+      <c r="G83" t="s">
+        <v>137</v>
+      </c>
+      <c r="H83" t="s">
+        <v>13</v>
+      </c>
+      <c r="K83" t="s">
+        <v>137</v>
+      </c>
+      <c r="L83" t="s">
+        <v>225</v>
+      </c>
+      <c r="O83" t="s">
+        <v>267</v>
+      </c>
+      <c r="P83" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q83">
+        <v>20.569491805687608</v>
+      </c>
+      <c r="R83">
+        <v>51.945619106835984</v>
+      </c>
+    </row>
+    <row r="84" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B84" t="s">
+        <v>8</v>
+      </c>
+      <c r="C84" t="s">
+        <v>8</v>
+      </c>
+      <c r="D84" t="s">
+        <v>9</v>
+      </c>
+      <c r="E84" t="s">
+        <v>72</v>
+      </c>
+      <c r="F84" t="s">
+        <v>54</v>
+      </c>
+      <c r="G84" t="s">
+        <v>138</v>
+      </c>
+      <c r="H84" t="s">
+        <v>13</v>
+      </c>
+      <c r="K84" t="s">
+        <v>138</v>
+      </c>
+      <c r="L84" t="s">
+        <v>226</v>
+      </c>
+      <c r="O84" t="s">
+        <v>268</v>
+      </c>
+      <c r="P84" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q84">
+        <v>21.251508341202094</v>
+      </c>
+      <c r="R84">
+        <v>50.572503835555374</v>
+      </c>
+    </row>
+    <row r="85" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B85" t="s">
+        <v>8</v>
+      </c>
+      <c r="C85" t="s">
+        <v>8</v>
+      </c>
+      <c r="D85" t="s">
+        <v>9</v>
+      </c>
+      <c r="E85" t="s">
+        <v>72</v>
+      </c>
+      <c r="F85" t="s">
+        <v>70</v>
+      </c>
+      <c r="G85" t="s">
+        <v>139</v>
+      </c>
+      <c r="H85" t="s">
+        <v>13</v>
+      </c>
+      <c r="K85" t="s">
+        <v>139</v>
+      </c>
+      <c r="L85" t="s">
+        <v>227</v>
+      </c>
+      <c r="O85" t="s">
+        <v>269</v>
+      </c>
+      <c r="P85" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q85">
+        <v>22.221541482666314</v>
+      </c>
+      <c r="R85">
+        <v>52.402780027123931</v>
+      </c>
+    </row>
+    <row r="86" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B86" t="s">
+        <v>8</v>
+      </c>
+      <c r="C86" t="s">
+        <v>8</v>
+      </c>
+      <c r="D86" t="s">
+        <v>9</v>
+      </c>
+      <c r="E86" t="s">
+        <v>64</v>
+      </c>
+      <c r="F86" t="s">
+        <v>38</v>
+      </c>
+      <c r="G86" t="s">
+        <v>140</v>
+      </c>
+      <c r="H86" t="s">
+        <v>13</v>
+      </c>
+      <c r="K86" t="s">
+        <v>140</v>
+      </c>
+      <c r="L86" t="s">
+        <v>228</v>
+      </c>
+      <c r="O86" t="s">
+        <v>270</v>
+      </c>
+      <c r="P86" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q86">
+        <v>23.413558137569936</v>
+      </c>
+      <c r="R86">
+        <v>50.221928080120989</v>
+      </c>
+    </row>
+    <row r="87" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B87" t="s">
+        <v>8</v>
+      </c>
+      <c r="C87" t="s">
+        <v>8</v>
+      </c>
+      <c r="D87" t="s">
+        <v>9</v>
+      </c>
+      <c r="E87" t="s">
+        <v>81</v>
+      </c>
+      <c r="F87" t="s">
+        <v>96</v>
+      </c>
+      <c r="G87" t="s">
+        <v>141</v>
+      </c>
+      <c r="H87" t="s">
+        <v>13</v>
+      </c>
+      <c r="K87" t="s">
+        <v>141</v>
+      </c>
+      <c r="L87" t="s">
+        <v>229</v>
+      </c>
+      <c r="O87" t="s">
+        <v>271</v>
+      </c>
+      <c r="P87" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q87">
+        <v>22.593353600809184</v>
+      </c>
+      <c r="R87">
+        <v>53.760902274894448</v>
+      </c>
+    </row>
+    <row r="88" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B88" t="s">
+        <v>8</v>
+      </c>
+      <c r="C88" t="s">
+        <v>8</v>
+      </c>
+      <c r="D88" t="s">
+        <v>9</v>
+      </c>
+      <c r="E88" t="s">
+        <v>120</v>
+      </c>
+      <c r="F88" t="s">
+        <v>116</v>
+      </c>
+      <c r="G88" t="s">
+        <v>142</v>
+      </c>
+      <c r="H88" t="s">
+        <v>13</v>
+      </c>
+      <c r="K88" t="s">
+        <v>142</v>
+      </c>
+      <c r="L88" t="s">
+        <v>230</v>
+      </c>
+      <c r="O88" t="s">
+        <v>272</v>
+      </c>
+      <c r="P88" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q88">
+        <v>18.684196405805043</v>
+      </c>
+      <c r="R88">
+        <v>52.397385084500648</v>
+      </c>
+    </row>
+    <row r="89" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B89" t="s">
+        <v>8</v>
+      </c>
+      <c r="C89" t="s">
+        <v>8</v>
+      </c>
+      <c r="D89" t="s">
+        <v>9</v>
+      </c>
+      <c r="E89" t="s">
+        <v>19</v>
+      </c>
+      <c r="F89" t="s">
+        <v>17</v>
+      </c>
+      <c r="G89" t="s">
+        <v>143</v>
+      </c>
+      <c r="H89" t="s">
+        <v>13</v>
+      </c>
+      <c r="K89" t="s">
+        <v>143</v>
+      </c>
+      <c r="L89" t="s">
+        <v>231</v>
+      </c>
+      <c r="O89" t="s">
+        <v>273</v>
+      </c>
+      <c r="P89" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q89">
         <v>20.68150354863176</v>
       </c>
-      <c r="R82">
+      <c r="R89">
         <v>53.14080843144523</v>
-      </c>
-    </row>
-    <row r="83" spans="2:18" x14ac:dyDescent="0.45">
-      <c r="O83" t="s">
-        <v>253</v>
-      </c>
-      <c r="P83" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q83">
-        <v>21.103188435801304</v>
-      </c>
-      <c r="R83">
-        <v>54.312441674352527</v>
-      </c>
-    </row>
-    <row r="84" spans="2:18" x14ac:dyDescent="0.45">
-      <c r="O84" t="s">
-        <v>254</v>
-      </c>
-      <c r="P84" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q84">
-        <v>19.258540287803484</v>
-      </c>
-      <c r="R84">
-        <v>53.94247081838023</v>
-      </c>
-    </row>
-    <row r="85" spans="2:18" x14ac:dyDescent="0.45">
-      <c r="O85" t="s">
-        <v>255</v>
-      </c>
-      <c r="P85" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q85">
-        <v>16.903251720257263</v>
-      </c>
-      <c r="R85">
-        <v>54.161619422062977</v>
-      </c>
-    </row>
-    <row r="86" spans="2:18" x14ac:dyDescent="0.45">
-      <c r="O86" t="s">
-        <v>256</v>
-      </c>
-      <c r="P86" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q86">
-        <v>15.361927969342226</v>
-      </c>
-      <c r="R86">
-        <v>51.244509727206612</v>
-      </c>
-    </row>
-    <row r="87" spans="2:18" x14ac:dyDescent="0.45">
-      <c r="O87" t="s">
-        <v>257</v>
-      </c>
-      <c r="P87" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q87">
-        <v>15.026892107180988</v>
-      </c>
-      <c r="R87">
-        <v>52.383060462397033</v>
-      </c>
-    </row>
-    <row r="88" spans="2:18" x14ac:dyDescent="0.45">
-      <c r="O88" t="s">
-        <v>258</v>
-      </c>
-      <c r="P88" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q88">
-        <v>16.375814143056594</v>
-      </c>
-      <c r="R88">
-        <v>51.541179017177562</v>
-      </c>
-    </row>
-    <row r="89" spans="2:18" x14ac:dyDescent="0.45">
-      <c r="O89" t="s">
-        <v>259</v>
-      </c>
-      <c r="P89" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q89">
-        <v>16.859888285978002</v>
-      </c>
-      <c r="R89">
-        <v>52.951863842623695</v>
       </c>
     </row>
     <row r="90" spans="2:18" x14ac:dyDescent="0.45">
       <c r="O90" t="s">
-        <v>260</v>
+        <v>274</v>
       </c>
       <c r="P90" t="s">
         <v>8</v>
       </c>
       <c r="Q90">
-        <v>19.826467717110425</v>
+        <v>21.103188435801304</v>
       </c>
       <c r="R90">
-        <v>49.445868999757508</v>
+        <v>54.312441674352527</v>
       </c>
     </row>
     <row r="91" spans="2:18" x14ac:dyDescent="0.45">
       <c r="O91" t="s">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="P91" t="s">
         <v>8</v>
       </c>
       <c r="Q91">
-        <v>22.221149843265444</v>
+        <v>19.258540287803484</v>
       </c>
       <c r="R91">
-        <v>49.445868999757522</v>
+        <v>53.94247081838023</v>
       </c>
     </row>
     <row r="92" spans="2:18" x14ac:dyDescent="0.45">
       <c r="O92" t="s">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="P92" t="s">
         <v>8</v>
       </c>
       <c r="Q92">
-        <v>21.136931470305012</v>
+        <v>16.903251720257263</v>
       </c>
       <c r="R92">
-        <v>49.735591777639613</v>
+        <v>54.161619422062977</v>
       </c>
     </row>
     <row r="93" spans="2:18" x14ac:dyDescent="0.45">
       <c r="O93" t="s">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="P93" t="s">
         <v>8</v>
       </c>
       <c r="Q93">
-        <v>16.733772344126869</v>
+        <v>15.361927969342226</v>
       </c>
       <c r="R93">
-        <v>50.345189363482064</v>
+        <v>51.244509727206612</v>
       </c>
     </row>
     <row r="94" spans="2:18" x14ac:dyDescent="0.45">
       <c r="O94" t="s">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="P94" t="s">
         <v>8</v>
       </c>
       <c r="Q94">
-        <v>19.682335745634312</v>
+        <v>15.026892107180988</v>
       </c>
       <c r="R94">
-        <v>50.203591507323402</v>
+        <v>52.383060462397033</v>
       </c>
     </row>
     <row r="95" spans="2:18" x14ac:dyDescent="0.45">
       <c r="O95" t="s">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="P95" t="s">
         <v>8</v>
       </c>
       <c r="Q95">
+        <v>16.375814143056594</v>
+      </c>
+      <c r="R95">
+        <v>51.541179017177562</v>
+      </c>
+    </row>
+    <row r="96" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="O96" t="s">
+        <v>280</v>
+      </c>
+      <c r="P96" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q96">
+        <v>16.859888285978002</v>
+      </c>
+      <c r="R96">
+        <v>52.951863842623695</v>
+      </c>
+    </row>
+    <row r="97" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O97" t="s">
+        <v>281</v>
+      </c>
+      <c r="P97" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q97">
+        <v>19.826467717110425</v>
+      </c>
+      <c r="R97">
+        <v>49.445868999757508</v>
+      </c>
+    </row>
+    <row r="98" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O98" t="s">
+        <v>282</v>
+      </c>
+      <c r="P98" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q98">
+        <v>22.221149843265444</v>
+      </c>
+      <c r="R98">
+        <v>49.445868999757522</v>
+      </c>
+    </row>
+    <row r="99" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O99" t="s">
+        <v>283</v>
+      </c>
+      <c r="P99" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q99">
+        <v>21.136931470305012</v>
+      </c>
+      <c r="R99">
+        <v>49.735591777639613</v>
+      </c>
+    </row>
+    <row r="100" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O100" t="s">
+        <v>284</v>
+      </c>
+      <c r="P100" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q100">
+        <v>16.733772344126869</v>
+      </c>
+      <c r="R100">
+        <v>50.345189363482064</v>
+      </c>
+    </row>
+    <row r="101" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O101" t="s">
+        <v>285</v>
+      </c>
+      <c r="P101" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q101">
+        <v>19.691296586567169</v>
+      </c>
+      <c r="R101">
+        <v>50.177730966847243</v>
+      </c>
+    </row>
+    <row r="102" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O102" t="s">
+        <v>286</v>
+      </c>
+      <c r="P102" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q102">
         <v>18.59892442917592</v>
       </c>
-      <c r="R95">
+      <c r="R102">
         <v>49.960030388543707</v>
       </c>
     </row>
@@ -5199,8 +5588,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{729E777C-5BE6-441E-92E2-884D91B082A7}">
-  <dimension ref="B3:L59"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8F86D84-A9C0-439F-AFAE-4257FED65682}">
+  <dimension ref="B3:L62"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="3" spans="2:12" x14ac:dyDescent="0.45">
@@ -5208,7 +5597,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.45">
@@ -5234,10 +5623,10 @@
         <v>7</v>
       </c>
       <c r="K4" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="L4" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.45">
@@ -5248,25 +5637,25 @@
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E5" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="F5" t="s">
-        <v>268</v>
+        <v>289</v>
       </c>
       <c r="G5" t="s">
-        <v>269</v>
+        <v>290</v>
       </c>
       <c r="H5" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K5" t="s">
-        <v>269</v>
+        <v>290</v>
       </c>
       <c r="L5" t="s">
-        <v>394</v>
+        <v>425</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.45">
@@ -5277,25 +5666,25 @@
         <v>8</v>
       </c>
       <c r="D6" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E6" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="F6" t="s">
-        <v>272</v>
+        <v>293</v>
       </c>
       <c r="G6" t="s">
-        <v>273</v>
+        <v>294</v>
       </c>
       <c r="H6" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K6" t="s">
-        <v>273</v>
+        <v>294</v>
       </c>
       <c r="L6" t="s">
-        <v>395</v>
+        <v>426</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.45">
@@ -5306,25 +5695,25 @@
         <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E7" t="s">
-        <v>274</v>
+        <v>295</v>
       </c>
       <c r="F7" t="s">
-        <v>275</v>
+        <v>296</v>
       </c>
       <c r="G7" t="s">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="H7" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K7" t="s">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="L7" t="s">
-        <v>396</v>
+        <v>427</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.45">
@@ -5335,25 +5724,25 @@
         <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E8" t="s">
-        <v>277</v>
+        <v>298</v>
       </c>
       <c r="F8" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="G8" t="s">
-        <v>279</v>
+        <v>300</v>
       </c>
       <c r="H8" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K8" t="s">
-        <v>279</v>
+        <v>300</v>
       </c>
       <c r="L8" t="s">
-        <v>397</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.45">
@@ -5364,25 +5753,25 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E9" t="s">
-        <v>280</v>
+        <v>301</v>
       </c>
       <c r="F9" t="s">
-        <v>281</v>
+        <v>302</v>
       </c>
       <c r="G9" t="s">
-        <v>282</v>
+        <v>303</v>
       </c>
       <c r="H9" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K9" t="s">
-        <v>282</v>
+        <v>303</v>
       </c>
       <c r="L9" t="s">
-        <v>398</v>
+        <v>429</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.45">
@@ -5393,25 +5782,25 @@
         <v>8</v>
       </c>
       <c r="D10" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E10" t="s">
-        <v>283</v>
+        <v>304</v>
       </c>
       <c r="F10" t="s">
-        <v>268</v>
+        <v>305</v>
       </c>
       <c r="G10" t="s">
-        <v>284</v>
+        <v>306</v>
       </c>
       <c r="H10" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K10" t="s">
-        <v>284</v>
+        <v>306</v>
       </c>
       <c r="L10" t="s">
-        <v>399</v>
+        <v>430</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.45">
@@ -5422,25 +5811,25 @@
         <v>8</v>
       </c>
       <c r="D11" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E11" t="s">
-        <v>285</v>
+        <v>307</v>
       </c>
       <c r="F11" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="G11" t="s">
-        <v>287</v>
+        <v>308</v>
       </c>
       <c r="H11" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K11" t="s">
-        <v>287</v>
+        <v>308</v>
       </c>
       <c r="L11" t="s">
-        <v>400</v>
+        <v>431</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.45">
@@ -5451,25 +5840,25 @@
         <v>8</v>
       </c>
       <c r="D12" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E12" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F12" t="s">
-        <v>275</v>
+        <v>310</v>
       </c>
       <c r="G12" t="s">
-        <v>289</v>
+        <v>311</v>
       </c>
       <c r="H12" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K12" t="s">
-        <v>289</v>
+        <v>311</v>
       </c>
       <c r="L12" t="s">
-        <v>401</v>
+        <v>432</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.45">
@@ -5480,25 +5869,25 @@
         <v>8</v>
       </c>
       <c r="D13" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E13" t="s">
-        <v>290</v>
+        <v>312</v>
       </c>
       <c r="F13" t="s">
-        <v>286</v>
+        <v>313</v>
       </c>
       <c r="G13" t="s">
+        <v>314</v>
+      </c>
+      <c r="H13" t="s">
         <v>291</v>
       </c>
-      <c r="H13" t="s">
-        <v>270</v>
-      </c>
       <c r="K13" t="s">
-        <v>291</v>
+        <v>314</v>
       </c>
       <c r="L13" t="s">
-        <v>402</v>
+        <v>433</v>
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.45">
@@ -5509,25 +5898,25 @@
         <v>8</v>
       </c>
       <c r="D14" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E14" t="s">
-        <v>292</v>
+        <v>315</v>
       </c>
       <c r="F14" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="G14" t="s">
-        <v>294</v>
+        <v>316</v>
       </c>
       <c r="H14" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K14" t="s">
-        <v>294</v>
+        <v>316</v>
       </c>
       <c r="L14" t="s">
-        <v>403</v>
+        <v>434</v>
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.45">
@@ -5538,25 +5927,25 @@
         <v>8</v>
       </c>
       <c r="D15" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E15" t="s">
-        <v>295</v>
+        <v>317</v>
       </c>
       <c r="F15" t="s">
-        <v>275</v>
+        <v>313</v>
       </c>
       <c r="G15" t="s">
-        <v>296</v>
+        <v>318</v>
       </c>
       <c r="H15" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K15" t="s">
-        <v>296</v>
+        <v>318</v>
       </c>
       <c r="L15" t="s">
-        <v>404</v>
+        <v>435</v>
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.45">
@@ -5567,25 +5956,25 @@
         <v>8</v>
       </c>
       <c r="D16" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E16" t="s">
-        <v>297</v>
+        <v>319</v>
       </c>
       <c r="F16" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="G16" t="s">
-        <v>299</v>
+        <v>320</v>
       </c>
       <c r="H16" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K16" t="s">
-        <v>299</v>
+        <v>320</v>
       </c>
       <c r="L16" t="s">
-        <v>405</v>
+        <v>436</v>
       </c>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.45">
@@ -5596,25 +5985,25 @@
         <v>8</v>
       </c>
       <c r="D17" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E17" t="s">
-        <v>300</v>
+        <v>321</v>
       </c>
       <c r="F17" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="G17" t="s">
-        <v>302</v>
+        <v>322</v>
       </c>
       <c r="H17" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K17" t="s">
-        <v>302</v>
+        <v>322</v>
       </c>
       <c r="L17" t="s">
-        <v>406</v>
+        <v>437</v>
       </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.45">
@@ -5625,25 +6014,25 @@
         <v>8</v>
       </c>
       <c r="D18" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E18" t="s">
-        <v>303</v>
+        <v>323</v>
       </c>
       <c r="F18" t="s">
-        <v>286</v>
+        <v>324</v>
       </c>
       <c r="G18" t="s">
-        <v>304</v>
+        <v>325</v>
       </c>
       <c r="H18" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K18" t="s">
-        <v>304</v>
+        <v>325</v>
       </c>
       <c r="L18" t="s">
-        <v>407</v>
+        <v>438</v>
       </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.45">
@@ -5654,25 +6043,25 @@
         <v>8</v>
       </c>
       <c r="D19" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E19" t="s">
-        <v>305</v>
+        <v>326</v>
       </c>
       <c r="F19" t="s">
-        <v>306</v>
+        <v>327</v>
       </c>
       <c r="G19" t="s">
-        <v>307</v>
+        <v>328</v>
       </c>
       <c r="H19" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K19" t="s">
-        <v>307</v>
+        <v>328</v>
       </c>
       <c r="L19" t="s">
-        <v>408</v>
+        <v>439</v>
       </c>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.45">
@@ -5683,25 +6072,25 @@
         <v>8</v>
       </c>
       <c r="D20" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E20" t="s">
-        <v>308</v>
+        <v>329</v>
       </c>
       <c r="F20" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="G20" t="s">
-        <v>310</v>
+        <v>330</v>
       </c>
       <c r="H20" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K20" t="s">
-        <v>310</v>
+        <v>330</v>
       </c>
       <c r="L20" t="s">
-        <v>409</v>
+        <v>440</v>
       </c>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.45">
@@ -5712,25 +6101,25 @@
         <v>8</v>
       </c>
       <c r="D21" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E21" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
       <c r="F21" t="s">
-        <v>301</v>
+        <v>332</v>
       </c>
       <c r="G21" t="s">
-        <v>312</v>
+        <v>333</v>
       </c>
       <c r="H21" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K21" t="s">
-        <v>312</v>
+        <v>333</v>
       </c>
       <c r="L21" t="s">
-        <v>410</v>
+        <v>441</v>
       </c>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.45">
@@ -5741,25 +6130,25 @@
         <v>8</v>
       </c>
       <c r="D22" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E22" t="s">
-        <v>313</v>
+        <v>334</v>
       </c>
       <c r="F22" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="G22" t="s">
-        <v>315</v>
+        <v>336</v>
       </c>
       <c r="H22" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K22" t="s">
-        <v>315</v>
+        <v>336</v>
       </c>
       <c r="L22" t="s">
-        <v>411</v>
+        <v>442</v>
       </c>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.45">
@@ -5770,25 +6159,25 @@
         <v>8</v>
       </c>
       <c r="D23" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E23" t="s">
-        <v>316</v>
+        <v>337</v>
       </c>
       <c r="F23" t="s">
-        <v>275</v>
+        <v>327</v>
       </c>
       <c r="G23" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="H23" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K23" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="L23" t="s">
-        <v>412</v>
+        <v>443</v>
       </c>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.45">
@@ -5799,25 +6188,25 @@
         <v>8</v>
       </c>
       <c r="D24" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E24" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="F24" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="G24" t="s">
-        <v>320</v>
+        <v>341</v>
       </c>
       <c r="H24" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K24" t="s">
-        <v>320</v>
+        <v>341</v>
       </c>
       <c r="L24" t="s">
-        <v>413</v>
+        <v>444</v>
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.45">
@@ -5828,25 +6217,25 @@
         <v>8</v>
       </c>
       <c r="D25" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E25" t="s">
-        <v>321</v>
+        <v>342</v>
       </c>
       <c r="F25" t="s">
-        <v>319</v>
+        <v>299</v>
       </c>
       <c r="G25" t="s">
-        <v>322</v>
+        <v>343</v>
       </c>
       <c r="H25" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K25" t="s">
-        <v>322</v>
+        <v>343</v>
       </c>
       <c r="L25" t="s">
-        <v>414</v>
+        <v>445</v>
       </c>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.45">
@@ -5857,25 +6246,25 @@
         <v>8</v>
       </c>
       <c r="D26" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E26" t="s">
-        <v>323</v>
+        <v>344</v>
       </c>
       <c r="F26" t="s">
-        <v>301</v>
+        <v>345</v>
       </c>
       <c r="G26" t="s">
-        <v>324</v>
+        <v>346</v>
       </c>
       <c r="H26" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K26" t="s">
-        <v>324</v>
+        <v>346</v>
       </c>
       <c r="L26" t="s">
-        <v>415</v>
+        <v>446</v>
       </c>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.45">
@@ -5886,25 +6275,25 @@
         <v>8</v>
       </c>
       <c r="D27" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E27" t="s">
-        <v>325</v>
+        <v>347</v>
       </c>
       <c r="F27" t="s">
-        <v>301</v>
+        <v>345</v>
       </c>
       <c r="G27" t="s">
-        <v>326</v>
+        <v>348</v>
       </c>
       <c r="H27" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K27" t="s">
-        <v>326</v>
+        <v>348</v>
       </c>
       <c r="L27" t="s">
-        <v>416</v>
+        <v>447</v>
       </c>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.45">
@@ -5915,25 +6304,25 @@
         <v>8</v>
       </c>
       <c r="D28" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E28" t="s">
+        <v>349</v>
+      </c>
+      <c r="F28" t="s">
         <v>327</v>
       </c>
-      <c r="F28" t="s">
-        <v>306</v>
-      </c>
       <c r="G28" t="s">
-        <v>328</v>
+        <v>350</v>
       </c>
       <c r="H28" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K28" t="s">
-        <v>328</v>
+        <v>350</v>
       </c>
       <c r="L28" t="s">
-        <v>417</v>
+        <v>448</v>
       </c>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.45">
@@ -5944,25 +6333,25 @@
         <v>8</v>
       </c>
       <c r="D29" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E29" t="s">
-        <v>329</v>
+        <v>351</v>
       </c>
       <c r="F29" t="s">
-        <v>301</v>
+        <v>327</v>
       </c>
       <c r="G29" t="s">
-        <v>330</v>
+        <v>352</v>
       </c>
       <c r="H29" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K29" t="s">
-        <v>330</v>
+        <v>352</v>
       </c>
       <c r="L29" t="s">
-        <v>418</v>
+        <v>449</v>
       </c>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.45">
@@ -5973,25 +6362,25 @@
         <v>8</v>
       </c>
       <c r="D30" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E30" t="s">
-        <v>331</v>
+        <v>353</v>
       </c>
       <c r="F30" t="s">
-        <v>301</v>
+        <v>332</v>
       </c>
       <c r="G30" t="s">
-        <v>332</v>
+        <v>354</v>
       </c>
       <c r="H30" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K30" t="s">
-        <v>332</v>
+        <v>354</v>
       </c>
       <c r="L30" t="s">
-        <v>419</v>
+        <v>450</v>
       </c>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.45">
@@ -6002,25 +6391,25 @@
         <v>8</v>
       </c>
       <c r="D31" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E31" t="s">
-        <v>333</v>
+        <v>355</v>
       </c>
       <c r="F31" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="G31" t="s">
-        <v>334</v>
+        <v>356</v>
       </c>
       <c r="H31" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K31" t="s">
-        <v>334</v>
+        <v>356</v>
       </c>
       <c r="L31" t="s">
-        <v>420</v>
+        <v>451</v>
       </c>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.45">
@@ -6031,25 +6420,25 @@
         <v>8</v>
       </c>
       <c r="D32" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E32" t="s">
-        <v>335</v>
+        <v>357</v>
       </c>
       <c r="F32" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="G32" t="s">
-        <v>337</v>
+        <v>358</v>
       </c>
       <c r="H32" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K32" t="s">
-        <v>337</v>
+        <v>358</v>
       </c>
       <c r="L32" t="s">
-        <v>421</v>
+        <v>452</v>
       </c>
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.45">
@@ -6060,25 +6449,25 @@
         <v>8</v>
       </c>
       <c r="D33" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E33" t="s">
-        <v>338</v>
+        <v>359</v>
       </c>
       <c r="F33" t="s">
-        <v>301</v>
+        <v>335</v>
       </c>
       <c r="G33" t="s">
-        <v>339</v>
+        <v>360</v>
       </c>
       <c r="H33" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K33" t="s">
-        <v>339</v>
+        <v>360</v>
       </c>
       <c r="L33" t="s">
-        <v>422</v>
+        <v>453</v>
       </c>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.45">
@@ -6089,25 +6478,25 @@
         <v>8</v>
       </c>
       <c r="D34" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E34" t="s">
-        <v>340</v>
+        <v>361</v>
       </c>
       <c r="F34" t="s">
-        <v>278</v>
+        <v>362</v>
       </c>
       <c r="G34" t="s">
-        <v>341</v>
+        <v>363</v>
       </c>
       <c r="H34" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K34" t="s">
-        <v>341</v>
+        <v>363</v>
       </c>
       <c r="L34" t="s">
-        <v>423</v>
+        <v>454</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.45">
@@ -6118,25 +6507,25 @@
         <v>8</v>
       </c>
       <c r="D35" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E35" t="s">
-        <v>342</v>
+        <v>364</v>
       </c>
       <c r="F35" t="s">
-        <v>343</v>
+        <v>327</v>
       </c>
       <c r="G35" t="s">
-        <v>344</v>
+        <v>365</v>
       </c>
       <c r="H35" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K35" t="s">
-        <v>344</v>
+        <v>365</v>
       </c>
       <c r="L35" t="s">
-        <v>424</v>
+        <v>455</v>
       </c>
     </row>
     <row r="36" spans="2:12" x14ac:dyDescent="0.45">
@@ -6147,25 +6536,25 @@
         <v>8</v>
       </c>
       <c r="D36" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E36" t="s">
-        <v>345</v>
+        <v>366</v>
       </c>
       <c r="F36" t="s">
-        <v>319</v>
+        <v>302</v>
       </c>
       <c r="G36" t="s">
-        <v>346</v>
+        <v>367</v>
       </c>
       <c r="H36" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K36" t="s">
-        <v>346</v>
+        <v>367</v>
       </c>
       <c r="L36" t="s">
-        <v>425</v>
+        <v>456</v>
       </c>
     </row>
     <row r="37" spans="2:12" x14ac:dyDescent="0.45">
@@ -6176,25 +6565,25 @@
         <v>8</v>
       </c>
       <c r="D37" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E37" t="s">
-        <v>347</v>
+        <v>368</v>
       </c>
       <c r="F37" t="s">
-        <v>286</v>
+        <v>369</v>
       </c>
       <c r="G37" t="s">
-        <v>348</v>
+        <v>370</v>
       </c>
       <c r="H37" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K37" t="s">
-        <v>348</v>
+        <v>370</v>
       </c>
       <c r="L37" t="s">
-        <v>426</v>
+        <v>457</v>
       </c>
     </row>
     <row r="38" spans="2:12" x14ac:dyDescent="0.45">
@@ -6205,25 +6594,25 @@
         <v>8</v>
       </c>
       <c r="D38" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E38" t="s">
-        <v>349</v>
+        <v>371</v>
       </c>
       <c r="F38" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="G38" t="s">
-        <v>350</v>
+        <v>372</v>
       </c>
       <c r="H38" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K38" t="s">
-        <v>350</v>
+        <v>372</v>
       </c>
       <c r="L38" t="s">
-        <v>427</v>
+        <v>458</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.45">
@@ -6234,25 +6623,25 @@
         <v>8</v>
       </c>
       <c r="D39" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E39" t="s">
-        <v>351</v>
+        <v>373</v>
       </c>
       <c r="F39" t="s">
-        <v>298</v>
+        <v>327</v>
       </c>
       <c r="G39" t="s">
-        <v>352</v>
+        <v>374</v>
       </c>
       <c r="H39" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K39" t="s">
-        <v>352</v>
+        <v>374</v>
       </c>
       <c r="L39" t="s">
-        <v>428</v>
+        <v>459</v>
       </c>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.45">
@@ -6263,25 +6652,25 @@
         <v>8</v>
       </c>
       <c r="D40" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E40" t="s">
-        <v>353</v>
+        <v>375</v>
       </c>
       <c r="F40" t="s">
-        <v>319</v>
+        <v>345</v>
       </c>
       <c r="G40" t="s">
-        <v>354</v>
+        <v>376</v>
       </c>
       <c r="H40" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K40" t="s">
-        <v>354</v>
+        <v>376</v>
       </c>
       <c r="L40" t="s">
-        <v>429</v>
+        <v>460</v>
       </c>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.45">
@@ -6292,25 +6681,25 @@
         <v>8</v>
       </c>
       <c r="D41" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E41" t="s">
-        <v>355</v>
+        <v>377</v>
       </c>
       <c r="F41" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="G41" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="H41" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K41" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="L41" t="s">
-        <v>430</v>
+        <v>461</v>
       </c>
     </row>
     <row r="42" spans="2:12" x14ac:dyDescent="0.45">
@@ -6321,25 +6710,25 @@
         <v>8</v>
       </c>
       <c r="D42" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E42" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="F42" t="s">
-        <v>268</v>
+        <v>380</v>
       </c>
       <c r="G42" t="s">
-        <v>358</v>
+        <v>381</v>
       </c>
       <c r="H42" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K42" t="s">
-        <v>358</v>
+        <v>381</v>
       </c>
       <c r="L42" t="s">
-        <v>431</v>
+        <v>462</v>
       </c>
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.45">
@@ -6350,25 +6739,25 @@
         <v>8</v>
       </c>
       <c r="D43" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E43" t="s">
-        <v>359</v>
+        <v>382</v>
       </c>
       <c r="F43" t="s">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="G43" t="s">
-        <v>361</v>
+        <v>383</v>
       </c>
       <c r="H43" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K43" t="s">
-        <v>361</v>
+        <v>383</v>
       </c>
       <c r="L43" t="s">
-        <v>432</v>
+        <v>463</v>
       </c>
     </row>
     <row r="44" spans="2:12" x14ac:dyDescent="0.45">
@@ -6379,25 +6768,25 @@
         <v>8</v>
       </c>
       <c r="D44" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E44" t="s">
-        <v>362</v>
+        <v>384</v>
       </c>
       <c r="F44" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="G44" t="s">
-        <v>363</v>
+        <v>385</v>
       </c>
       <c r="H44" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K44" t="s">
-        <v>363</v>
+        <v>385</v>
       </c>
       <c r="L44" t="s">
-        <v>433</v>
+        <v>464</v>
       </c>
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.45">
@@ -6408,25 +6797,25 @@
         <v>8</v>
       </c>
       <c r="D45" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E45" t="s">
-        <v>364</v>
+        <v>386</v>
       </c>
       <c r="F45" t="s">
-        <v>301</v>
+        <v>345</v>
       </c>
       <c r="G45" t="s">
-        <v>365</v>
+        <v>387</v>
       </c>
       <c r="H45" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K45" t="s">
-        <v>365</v>
+        <v>387</v>
       </c>
       <c r="L45" t="s">
-        <v>434</v>
+        <v>465</v>
       </c>
     </row>
     <row r="46" spans="2:12" x14ac:dyDescent="0.45">
@@ -6437,25 +6826,25 @@
         <v>8</v>
       </c>
       <c r="D46" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E46" t="s">
-        <v>359</v>
+        <v>388</v>
       </c>
       <c r="F46" t="s">
-        <v>366</v>
+        <v>345</v>
       </c>
       <c r="G46" t="s">
-        <v>367</v>
+        <v>389</v>
       </c>
       <c r="H46" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K46" t="s">
-        <v>367</v>
+        <v>389</v>
       </c>
       <c r="L46" t="s">
-        <v>435</v>
+        <v>466</v>
       </c>
     </row>
     <row r="47" spans="2:12" x14ac:dyDescent="0.45">
@@ -6466,25 +6855,25 @@
         <v>8</v>
       </c>
       <c r="D47" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E47" t="s">
-        <v>359</v>
+        <v>390</v>
       </c>
       <c r="F47" t="s">
-        <v>368</v>
+        <v>289</v>
       </c>
       <c r="G47" t="s">
-        <v>369</v>
+        <v>391</v>
       </c>
       <c r="H47" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K47" t="s">
-        <v>369</v>
+        <v>391</v>
       </c>
       <c r="L47" t="s">
-        <v>436</v>
+        <v>467</v>
       </c>
     </row>
     <row r="48" spans="2:12" x14ac:dyDescent="0.45">
@@ -6495,25 +6884,25 @@
         <v>8</v>
       </c>
       <c r="D48" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E48" t="s">
-        <v>359</v>
+        <v>392</v>
       </c>
       <c r="F48" t="s">
-        <v>370</v>
+        <v>393</v>
       </c>
       <c r="G48" t="s">
-        <v>371</v>
+        <v>394</v>
       </c>
       <c r="H48" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K48" t="s">
-        <v>371</v>
+        <v>394</v>
       </c>
       <c r="L48" t="s">
-        <v>437</v>
+        <v>468</v>
       </c>
     </row>
     <row r="49" spans="2:12" x14ac:dyDescent="0.45">
@@ -6524,25 +6913,25 @@
         <v>8</v>
       </c>
       <c r="D49" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E49" t="s">
-        <v>335</v>
+        <v>395</v>
       </c>
       <c r="F49" t="s">
-        <v>372</v>
+        <v>396</v>
       </c>
       <c r="G49" t="s">
-        <v>373</v>
+        <v>397</v>
       </c>
       <c r="H49" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K49" t="s">
-        <v>373</v>
+        <v>397</v>
       </c>
       <c r="L49" t="s">
-        <v>438</v>
+        <v>469</v>
       </c>
     </row>
     <row r="50" spans="2:12" x14ac:dyDescent="0.45">
@@ -6553,25 +6942,25 @@
         <v>8</v>
       </c>
       <c r="D50" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E50" t="s">
-        <v>335</v>
+        <v>398</v>
       </c>
       <c r="F50" t="s">
-        <v>374</v>
+        <v>399</v>
       </c>
       <c r="G50" t="s">
-        <v>375</v>
+        <v>400</v>
       </c>
       <c r="H50" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K50" t="s">
-        <v>375</v>
+        <v>400</v>
       </c>
       <c r="L50" t="s">
-        <v>439</v>
+        <v>470</v>
       </c>
     </row>
     <row r="51" spans="2:12" x14ac:dyDescent="0.45">
@@ -6582,25 +6971,25 @@
         <v>8</v>
       </c>
       <c r="D51" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E51" t="s">
-        <v>335</v>
+        <v>401</v>
       </c>
       <c r="F51" t="s">
-        <v>376</v>
+        <v>345</v>
       </c>
       <c r="G51" t="s">
-        <v>377</v>
+        <v>402</v>
       </c>
       <c r="H51" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K51" t="s">
-        <v>377</v>
+        <v>402</v>
       </c>
       <c r="L51" t="s">
-        <v>440</v>
+        <v>471</v>
       </c>
     </row>
     <row r="52" spans="2:12" x14ac:dyDescent="0.45">
@@ -6611,25 +7000,25 @@
         <v>8</v>
       </c>
       <c r="D52" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E52" t="s">
-        <v>297</v>
+        <v>403</v>
       </c>
       <c r="F52" t="s">
-        <v>378</v>
+        <v>327</v>
       </c>
       <c r="G52" t="s">
-        <v>379</v>
+        <v>404</v>
       </c>
       <c r="H52" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K52" t="s">
-        <v>379</v>
+        <v>404</v>
       </c>
       <c r="L52" t="s">
-        <v>441</v>
+        <v>472</v>
       </c>
     </row>
     <row r="53" spans="2:12" x14ac:dyDescent="0.45">
@@ -6640,25 +7029,25 @@
         <v>8</v>
       </c>
       <c r="D53" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E53" t="s">
-        <v>297</v>
+        <v>392</v>
       </c>
       <c r="F53" t="s">
-        <v>380</v>
+        <v>405</v>
       </c>
       <c r="G53" t="s">
-        <v>381</v>
+        <v>406</v>
       </c>
       <c r="H53" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K53" t="s">
-        <v>381</v>
+        <v>406</v>
       </c>
       <c r="L53" t="s">
-        <v>442</v>
+        <v>473</v>
       </c>
     </row>
     <row r="54" spans="2:12" x14ac:dyDescent="0.45">
@@ -6669,25 +7058,25 @@
         <v>8</v>
       </c>
       <c r="D54" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E54" t="s">
-        <v>305</v>
+        <v>392</v>
       </c>
       <c r="F54" t="s">
-        <v>382</v>
+        <v>407</v>
       </c>
       <c r="G54" t="s">
-        <v>383</v>
+        <v>408</v>
       </c>
       <c r="H54" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K54" t="s">
-        <v>383</v>
+        <v>408</v>
       </c>
       <c r="L54" t="s">
-        <v>443</v>
+        <v>474</v>
       </c>
     </row>
     <row r="55" spans="2:12" x14ac:dyDescent="0.45">
@@ -6698,25 +7087,25 @@
         <v>8</v>
       </c>
       <c r="D55" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E55" t="s">
-        <v>297</v>
+        <v>392</v>
       </c>
       <c r="F55" t="s">
-        <v>384</v>
+        <v>409</v>
       </c>
       <c r="G55" t="s">
-        <v>385</v>
+        <v>410</v>
       </c>
       <c r="H55" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K55" t="s">
-        <v>385</v>
+        <v>410</v>
       </c>
       <c r="L55" t="s">
-        <v>444</v>
+        <v>475</v>
       </c>
     </row>
     <row r="56" spans="2:12" x14ac:dyDescent="0.45">
@@ -6727,25 +7116,25 @@
         <v>8</v>
       </c>
       <c r="D56" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E56" t="s">
-        <v>267</v>
+        <v>361</v>
       </c>
       <c r="F56" t="s">
-        <v>386</v>
+        <v>411</v>
       </c>
       <c r="G56" t="s">
-        <v>387</v>
+        <v>412</v>
       </c>
       <c r="H56" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K56" t="s">
-        <v>387</v>
+        <v>412</v>
       </c>
       <c r="L56" t="s">
-        <v>445</v>
+        <v>476</v>
       </c>
     </row>
     <row r="57" spans="2:12" x14ac:dyDescent="0.45">
@@ -6756,25 +7145,25 @@
         <v>8</v>
       </c>
       <c r="D57" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E57" t="s">
-        <v>267</v>
+        <v>368</v>
       </c>
       <c r="F57" t="s">
-        <v>388</v>
+        <v>413</v>
       </c>
       <c r="G57" t="s">
-        <v>389</v>
+        <v>414</v>
       </c>
       <c r="H57" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K57" t="s">
-        <v>389</v>
+        <v>414</v>
       </c>
       <c r="L57" t="s">
-        <v>446</v>
+        <v>477</v>
       </c>
     </row>
     <row r="58" spans="2:12" x14ac:dyDescent="0.45">
@@ -6785,25 +7174,25 @@
         <v>8</v>
       </c>
       <c r="D58" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E58" t="s">
-        <v>277</v>
+        <v>323</v>
       </c>
       <c r="F58" t="s">
-        <v>390</v>
+        <v>415</v>
       </c>
       <c r="G58" t="s">
-        <v>391</v>
+        <v>416</v>
       </c>
       <c r="H58" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K58" t="s">
-        <v>391</v>
+        <v>416</v>
       </c>
       <c r="L58" t="s">
-        <v>447</v>
+        <v>478</v>
       </c>
     </row>
     <row r="59" spans="2:12" x14ac:dyDescent="0.45">
@@ -6814,25 +7203,112 @@
         <v>8</v>
       </c>
       <c r="D59" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="E59" t="s">
-        <v>359</v>
+        <v>323</v>
       </c>
       <c r="F59" t="s">
-        <v>392</v>
+        <v>417</v>
       </c>
       <c r="G59" t="s">
-        <v>393</v>
+        <v>418</v>
       </c>
       <c r="H59" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="K59" t="s">
-        <v>393</v>
+        <v>418</v>
       </c>
       <c r="L59" t="s">
-        <v>448</v>
+        <v>479</v>
+      </c>
+    </row>
+    <row r="60" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B60" t="s">
+        <v>8</v>
+      </c>
+      <c r="C60" t="s">
+        <v>8</v>
+      </c>
+      <c r="D60" t="s">
+        <v>287</v>
+      </c>
+      <c r="E60" t="s">
+        <v>331</v>
+      </c>
+      <c r="F60" t="s">
+        <v>419</v>
+      </c>
+      <c r="G60" t="s">
+        <v>420</v>
+      </c>
+      <c r="H60" t="s">
+        <v>291</v>
+      </c>
+      <c r="K60" t="s">
+        <v>420</v>
+      </c>
+      <c r="L60" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="61" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B61" t="s">
+        <v>8</v>
+      </c>
+      <c r="C61" t="s">
+        <v>8</v>
+      </c>
+      <c r="D61" t="s">
+        <v>287</v>
+      </c>
+      <c r="E61" t="s">
+        <v>323</v>
+      </c>
+      <c r="F61" t="s">
+        <v>421</v>
+      </c>
+      <c r="G61" t="s">
+        <v>422</v>
+      </c>
+      <c r="H61" t="s">
+        <v>291</v>
+      </c>
+      <c r="K61" t="s">
+        <v>422</v>
+      </c>
+      <c r="L61" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="62" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B62" t="s">
+        <v>8</v>
+      </c>
+      <c r="C62" t="s">
+        <v>8</v>
+      </c>
+      <c r="D62" t="s">
+        <v>287</v>
+      </c>
+      <c r="E62" t="s">
+        <v>373</v>
+      </c>
+      <c r="F62" t="s">
+        <v>423</v>
+      </c>
+      <c r="G62" t="s">
+        <v>424</v>
+      </c>
+      <c r="H62" t="s">
+        <v>291</v>
+      </c>
+      <c r="K62" t="s">
+        <v>424</v>
+      </c>
+      <c r="L62" t="s">
+        <v>482</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{670F2B53-8660-46C7-8D85-E7E457F7D74F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{95D6A5E3-F38D-4ED8-872C-745D81C6538E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{A8DFADBD-D290-4AB4-8530-B1621B1DD8C5}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{871E8455-AEF4-4FA2-8A82-047E86C38BFC}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1859,7 +1859,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C481C62A-DF29-4320-A519-031B17D83434}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{373AFBFD-0EED-4A3A-95B5-89CF70283BA6}">
   <dimension ref="B3:R102"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5588,7 +5588,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8F86D84-A9C0-439F-AFAE-4257FED65682}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71C98B48-6419-42BA-A6CC-98CA2EB6638D}">
   <dimension ref="B3:L62"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{95D6A5E3-F38D-4ED8-872C-745D81C6538E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{89D76FC4-B127-42B9-ACA1-0789FCB622B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{871E8455-AEF4-4FA2-8A82-047E86C38BFC}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{F3E95831-E935-493D-9DDA-E4A22E0B6BCC}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1859,7 +1859,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{373AFBFD-0EED-4A3A-95B5-89CF70283BA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE247E11-D640-49CA-95A1-B47B7DE15DFA}">
   <dimension ref="B3:R102"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5588,7 +5588,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71C98B48-6419-42BA-A6CC-98CA2EB6638D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{355DE110-9A50-40DC-A4CC-0B8AC88299B9}">
   <dimension ref="B3:L62"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{89D76FC4-B127-42B9-ACA1-0789FCB622B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F5EF525C-1793-43A6-A4BB-0EB005427486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{F3E95831-E935-493D-9DDA-E4A22E0B6BCC}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{C7089C44-57FE-455C-81EC-49AD1D9F27FF}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1859,7 +1859,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE247E11-D640-49CA-95A1-B47B7DE15DFA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10D3C11F-0E06-40C2-B9C7-A1F720CF77E3}">
   <dimension ref="B3:R102"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5588,7 +5588,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{355DE110-9A50-40DC-A4CC-0B8AC88299B9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28EF66D0-6174-4F16-B25B-E0FC42A6BCD2}">
   <dimension ref="B3:L62"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F5EF525C-1793-43A6-A4BB-0EB005427486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E6D73DC8-8060-47C4-94B4-5ED6BC142576}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{C7089C44-57FE-455C-81EC-49AD1D9F27FF}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{CE9F9559-AE8F-484B-9D3B-EC99FC30C6F5}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1859,7 +1859,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10D3C11F-0E06-40C2-B9C7-A1F720CF77E3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BDCA1AB-D49E-4B88-B8B6-9A148499982C}">
   <dimension ref="B3:R102"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5588,7 +5588,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28EF66D0-6174-4F16-B25B-E0FC42A6BCD2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97EA4332-0844-4D7C-B00D-3E86B15E3BD9}">
   <dimension ref="B3:L62"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E6D73DC8-8060-47C4-94B4-5ED6BC142576}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F899FCD4-D6E4-4156-B3DF-A13C4B32C0F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{CE9F9559-AE8F-484B-9D3B-EC99FC30C6F5}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{AD3ED68E-F768-4517-A4F6-C08ED8FE6CD8}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1859,7 +1859,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BDCA1AB-D49E-4B88-B8B6-9A148499982C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DBE8F98-A936-46C2-A86E-61E75712BD48}">
   <dimension ref="B3:R102"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5588,7 +5588,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97EA4332-0844-4D7C-B00D-3E86B15E3BD9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5CFE25B-29F9-480C-9FAA-369FB5CF27BB}">
   <dimension ref="B3:L62"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F899FCD4-D6E4-4156-B3DF-A13C4B32C0F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{950F751E-0D9D-41B7-B789-E2A46D828E8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{AD3ED68E-F768-4517-A4F6-C08ED8FE6CD8}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{0A8FE5BB-0076-4BA9-90EC-C6E913A1F9F7}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1859,7 +1859,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DBE8F98-A936-46C2-A86E-61E75712BD48}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{760CA62B-53D9-4005-AB87-6DD5A5EF2AA0}">
   <dimension ref="B3:R102"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5588,7 +5588,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5CFE25B-29F9-480C-9FAA-369FB5CF27BB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18E7D5E0-0847-40C4-A827-EC29C5551B24}">
   <dimension ref="B3:L62"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{950F751E-0D9D-41B7-B789-E2A46D828E8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E704A69D-AD2D-43A3-A8AD-9273376B6EF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{0A8FE5BB-0076-4BA9-90EC-C6E913A1F9F7}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{930E420A-B68C-401B-9E45-081B68150F6A}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1859,7 +1859,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{760CA62B-53D9-4005-AB87-6DD5A5EF2AA0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{119E4FDD-81F5-484E-93EC-297D09D114BD}">
   <dimension ref="B3:R102"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5588,7 +5588,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18E7D5E0-0847-40C4-A827-EC29C5551B24}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45A43BA6-10D2-4546-B03B-F1661C43A4E1}">
   <dimension ref="B3:L62"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E704A69D-AD2D-43A3-A8AD-9273376B6EF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{15E8E54C-BD28-4AFA-B915-AADE32F5D42B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{930E420A-B68C-401B-9E45-081B68150F6A}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{F940C910-E4E9-44BF-9193-71AEACF3F93C}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1859,7 +1859,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{119E4FDD-81F5-484E-93EC-297D09D114BD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{850B27E4-5C17-46F5-A8EE-BC51301CE7F5}">
   <dimension ref="B3:R102"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5588,7 +5588,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45A43BA6-10D2-4546-B03B-F1661C43A4E1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDD5A010-5AB2-45A4-8FD4-56F34429DCEA}">
   <dimension ref="B3:L62"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{15E8E54C-BD28-4AFA-B915-AADE32F5D42B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{17D54C4C-16A1-4436-9664-6E054688AE9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{F940C910-E4E9-44BF-9193-71AEACF3F93C}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{F9A85825-F185-48D9-9630-123A38D08E52}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1859,7 +1859,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{850B27E4-5C17-46F5-A8EE-BC51301CE7F5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{700CACBC-EFE4-4E7A-9C21-A1E7E07CA2DA}">
   <dimension ref="B3:R102"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5588,7 +5588,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDD5A010-5AB2-45A4-8FD4-56F34429DCEA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFB74A8A-D030-4FA8-B87E-DE4B6444AECA}">
   <dimension ref="B3:L62"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{17D54C4C-16A1-4436-9664-6E054688AE9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9A006272-12BD-4B01-9326-9B59762B4B29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{F9A85825-F185-48D9-9630-123A38D08E52}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{CC3BD2DA-523D-4A2B-A40A-6B46A844E049}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1859,7 +1859,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{700CACBC-EFE4-4E7A-9C21-A1E7E07CA2DA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04A9E722-1521-46E6-AE1F-75AF796516AF}">
   <dimension ref="B3:R102"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5588,7 +5588,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFB74A8A-D030-4FA8-B87E-DE4B6444AECA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{746E0B5A-BC12-416B-B3C0-3B1400335A17}">
   <dimension ref="B3:L62"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9A006272-12BD-4B01-9326-9B59762B4B29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5186AEF9-E7DD-430F-A3EF-13F960ED80A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{CC3BD2DA-523D-4A2B-A40A-6B46A844E049}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{8C4ADE14-7A6A-42F0-83C4-4EE93DF9CD76}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -483,259 +483,259 @@
     <t>description</t>
   </si>
   <si>
-    <t>grid link -49.0 km- way/40946790-220;way/44389929-220</t>
-  </si>
-  <si>
-    <t>grid link -98.0 km- PL34-400;way/111615226-220</t>
-  </si>
-  <si>
-    <t>grid link -89.0 km- way/111615226-220;way/180535363-220</t>
-  </si>
-  <si>
-    <t>grid link -107.0 km- way/111615226-220;way/158232924-220</t>
-  </si>
-  <si>
-    <t>grid link -106.0 km- PL15-400;way/112614319-400</t>
-  </si>
-  <si>
-    <t>grid link -74.0 km- PL15-400;way/46092396-400</t>
-  </si>
-  <si>
-    <t>grid link -70.0 km- PL15-400;PL7-400</t>
-  </si>
-  <si>
-    <t>grid link -83.0 km- PL15-400;way/32036484-220</t>
-  </si>
-  <si>
-    <t>grid link -82.0 km- way/199098050-220;way/216060722-220</t>
-  </si>
-  <si>
-    <t>grid link -78.0 km- way/170316833-220;way/216060722-220</t>
-  </si>
-  <si>
-    <t>grid link -53.0 km- way/112614319-400;way/86494356-400</t>
-  </si>
-  <si>
-    <t>grid link -90.0 km- way/112614319-400;way/46092396-400</t>
-  </si>
-  <si>
-    <t>grid link -137.0 km- way/101915790-220;way/112614319-400</t>
-  </si>
-  <si>
-    <t>grid link -34.0 km- way/293489607-400;way/40946790-220</t>
-  </si>
-  <si>
-    <t>grid link -91.0 km- PL18-400;way/158232924-220</t>
-  </si>
-  <si>
-    <t>grid link -120.0 km- way/46092396-400;way/658600169-400</t>
-  </si>
-  <si>
-    <t>grid link -43.0 km- way/216060722-220;way/40946790-220</t>
-  </si>
-  <si>
-    <t>grid link -92.0 km- way/199098050-220;way/40946790-220</t>
-  </si>
-  <si>
-    <t>grid link -85.0 km- way/40946790-220;way/87667718-220</t>
-  </si>
-  <si>
-    <t>grid link -15.0 km- way/183945016-220;way/40946790-220</t>
-  </si>
-  <si>
-    <t>grid link -49.0 km- way/183945016-220;way/336990960-220</t>
-  </si>
-  <si>
-    <t>grid link -110.0 km- way/199098050-220;way/199098053-220</t>
-  </si>
-  <si>
-    <t>grid link -72.0 km- way/199098050-220;way/254235846-400</t>
-  </si>
-  <si>
-    <t>grid link -94.0 km- PL15-400;way/255284259-220</t>
-  </si>
-  <si>
-    <t>grid link -78.0 km- way/170316833-220;way/255284259-220</t>
-  </si>
-  <si>
-    <t>grid link -108.0 km- way/255284259-220;way/658600169-400</t>
-  </si>
-  <si>
-    <t>grid link -146.0 km- way/255284259-220;way/29115701-220</t>
-  </si>
-  <si>
-    <t>grid link -81.0 km- way/245964556-220;way/255284259-220</t>
-  </si>
-  <si>
-    <t>grid link -122.0 km- way/112614319-400;way/178838661-220</t>
-  </si>
-  <si>
-    <t>grid link -65.0 km- relation/18085709-400;way/178838661-220</t>
-  </si>
-  <si>
-    <t>grid link -188.0 km- way/215282393-400;way/87667718-220</t>
-  </si>
-  <si>
-    <t>grid link -99.0 km- way/191038569-220;way/87667718-220</t>
-  </si>
-  <si>
-    <t>grid link -59.0 km- way/166838338-400;way/215282393-400</t>
-  </si>
-  <si>
-    <t>grid link -4.0 km- PL7-400;way/46092396-400</t>
-  </si>
-  <si>
-    <t>grid link -64.0 km- PL7-400;way/245964556-220</t>
-  </si>
-  <si>
-    <t>grid link -23.0 km- PL34-400;way/180535363-220</t>
-  </si>
-  <si>
-    <t>grid link -43.0 km- PL34-400;PL46-220</t>
-  </si>
-  <si>
-    <t>grid link -49.0 km- PL34-400;way/79033485-400</t>
-  </si>
-  <si>
-    <t>grid link -90.0 km- PL17-400;way/121656686-220</t>
-  </si>
-  <si>
-    <t>grid link -83.0 km- way/121656686-220;way/303870256-400</t>
-  </si>
-  <si>
-    <t>grid link -92.0 km- way/121656686-220;way/170259740-220</t>
-  </si>
-  <si>
-    <t>grid link -133.0 km- way/101915790-220;way/121656686-220</t>
-  </si>
-  <si>
-    <t>grid link -35.0 km- way/121656686-220;way/29115701-220</t>
-  </si>
-  <si>
-    <t>grid link -90.0 km- way/180535363-220;way/32036484-220</t>
-  </si>
-  <si>
-    <t>grid link -68.0 km- way/198635989-220;way/199098053-220</t>
-  </si>
-  <si>
-    <t>grid link -61.0 km- way/199098053-220;way/254235846-400</t>
-  </si>
-  <si>
-    <t>grid link -94.0 km- PL36-400;way/216060722-220</t>
-  </si>
-  <si>
-    <t>grid link -125.0 km- PL36-400;way/170316833-220</t>
-  </si>
-  <si>
-    <t>grid link -130.0 km- PL36-400;way/171917072-400</t>
-  </si>
-  <si>
-    <t>grid link -54.0 km- PL36-400;way/255277953-400</t>
-  </si>
-  <si>
-    <t>grid link -121.0 km- way/183945016-220;way/255277953-400</t>
-  </si>
-  <si>
-    <t>grid link -78.0 km- way/255277953-400;way/79033485-400</t>
-  </si>
-  <si>
-    <t>grid link -78.0 km- way/254235846-400;way/88544449-220</t>
-  </si>
-  <si>
-    <t>grid link -204.0 km- way/170316833-220;way/658600169-400</t>
-  </si>
-  <si>
-    <t>grid link -180.0 km- way/170316833-220;way/29115701-220</t>
-  </si>
-  <si>
-    <t>grid link -94.0 km- way/29115701-220;way/658600169-400</t>
-  </si>
-  <si>
-    <t>grid link -128.0 km- way/165763717-220;way/178838661-220</t>
-  </si>
-  <si>
-    <t>grid link -140.0 km- PL18-400;way/32036484-220</t>
-  </si>
-  <si>
-    <t>grid link -81.0 km- way/255284259-220;way/32036484-220</t>
-  </si>
-  <si>
-    <t>grid link -113.0 km- way/178838661-220;way/32036484-220</t>
-  </si>
-  <si>
-    <t>grid link -113.0 km- PL36-400;way/32036484-220</t>
-  </si>
-  <si>
-    <t>grid link -66.0 km- way/194903381-400;way/88544449-220</t>
-  </si>
-  <si>
-    <t>grid link -13.0 km- way/121656686-220;way/88544449-220</t>
-  </si>
-  <si>
-    <t>grid link -38.0 km- way/29115701-220;way/88544449-220</t>
-  </si>
-  <si>
-    <t>grid link -79.0 km- way/173613665-220;way/88544449-220</t>
-  </si>
-  <si>
-    <t>grid link -27.0 km- way/171917072-400;way/216060722-220</t>
-  </si>
-  <si>
-    <t>grid link -44.0 km- way/170316833-220;way/171917072-400</t>
-  </si>
-  <si>
-    <t>grid link -52.0 km- way/199098053-220;way/215282393-400</t>
-  </si>
-  <si>
-    <t>grid link -86.0 km- way/215282393-400;way/88544449-220</t>
-  </si>
-  <si>
-    <t>grid link -88.0 km- relation/18085709-400;way/86494356-400</t>
-  </si>
-  <si>
-    <t>grid link -0.0 km- relation/18085709-400;way/255314292</t>
-  </si>
-  <si>
-    <t>grid link -48.0 km- way/183945016-220;way/44389929-220</t>
-  </si>
-  <si>
-    <t>grid link -52.0 km- way/183945016-220;way/293489607-400</t>
-  </si>
-  <si>
-    <t>grid link -66.0 km- way/183945016-220;way/40946790-220</t>
-  </si>
-  <si>
-    <t>grid link -93.0 km- PL46-220;way/336990960-220</t>
-  </si>
-  <si>
-    <t>grid link -92.0 km- PL18-400;way/39428977-400</t>
-  </si>
-  <si>
-    <t>grid link -45.0 km- way/165763717-220;way/39428977-400</t>
-  </si>
-  <si>
-    <t>grid link -208.0 km- way/32036484-220;way/39428977-400</t>
-  </si>
-  <si>
-    <t>grid link -82.0 km- way/166838338-400;way/191038569-220</t>
-  </si>
-  <si>
-    <t>grid link -96.0 km- way/191038569-220;way/199098053-220</t>
-  </si>
-  <si>
-    <t>grid link -86.0 km- way/191038569-220;way/215282393-400</t>
-  </si>
-  <si>
-    <t>grid link -182.0 km- way/101915790-220;way/245964556-220</t>
-  </si>
-  <si>
-    <t>grid link -61.0 km- PL36-400;way/79033485-400</t>
-  </si>
-  <si>
-    <t>grid link -60.0 km- way/173613665-220;way/194903381-400</t>
-  </si>
-  <si>
-    <t>grid link -66.0 km- way/158232924-220;way/180535363-220</t>
+    <t>grid link -49.0 km- way/40946790-220;way/44389929-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -98.0 km- PL34-400;way/111615226-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -89.0 km- way/111615226-220;way/180535363-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -107.0 km- way/111615226-220;way/158232924-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -106.0 km- PL15-400;way/112614319-400 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -74.0 km- PL15-400;way/46092396-400 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -70.0 km- PL15-400;PL7-400 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -83.0 km- PL15-400;way/32036484-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -82.0 km- way/199098050-220;way/216060722-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -78.0 km- way/170316833-220;way/216060722-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -53.0 km- way/112614319-400;way/86494356-400 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -90.0 km- way/112614319-400;way/46092396-400 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -137.0 km- way/101915790-220;way/112614319-400 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -34.0 km- way/293489607-400;way/40946790-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -91.0 km- PL18-400;way/158232924-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -120.0 km- way/46092396-400;way/658600169-400 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -43.0 km- way/216060722-220;way/40946790-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -92.0 km- way/199098050-220;way/40946790-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -85.0 km- way/40946790-220;way/87667718-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -15.0 km- way/183945016-220;way/40946790-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -49.0 km- way/183945016-220;way/336990960-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -110.0 km- way/199098050-220;way/199098053-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -72.0 km- way/199098050-220;way/254235846-400 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -94.0 km- PL15-400;way/255284259-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -78.0 km- way/170316833-220;way/255284259-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -108.0 km- way/255284259-220;way/658600169-400 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -146.0 km- way/255284259-220;way/29115701-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -81.0 km- way/245964556-220;way/255284259-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -122.0 km- way/112614319-400;way/178838661-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -65.0 km- relation/18085709-400;way/178838661-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -188.0 km- way/215282393-400;way/87667718-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -99.0 km- way/191038569-220;way/87667718-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -59.0 km- way/166838338-400;way/215282393-400 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -4.0 km- PL7-400;way/46092396-400 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -64.0 km- PL7-400;way/245964556-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -23.0 km- PL34-400;way/180535363-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -43.0 km- PL34-400;PL46-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -49.0 km- PL34-400;way/79033485-400 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -90.0 km- PL17-400;way/121656686-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -83.0 km- way/121656686-220;way/303870256-400 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -92.0 km- way/121656686-220;way/170259740-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -133.0 km- way/101915790-220;way/121656686-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -35.0 km- way/121656686-220;way/29115701-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -90.0 km- way/180535363-220;way/32036484-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -68.0 km- way/198635989-220;way/199098053-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -61.0 km- way/199098053-220;way/254235846-400 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -94.0 km- PL36-400;way/216060722-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -125.0 km- PL36-400;way/170316833-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -130.0 km- PL36-400;way/171917072-400 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -54.0 km- PL36-400;way/255277953-400 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -121.0 km- way/183945016-220;way/255277953-400 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -78.0 km- way/255277953-400;way/79033485-400 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -78.0 km- way/254235846-400;way/88544449-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -204.0 km- way/170316833-220;way/658600169-400 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -180.0 km- way/170316833-220;way/29115701-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -94.0 km- way/29115701-220;way/658600169-400 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -128.0 km- way/165763717-220;way/178838661-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -140.0 km- PL18-400;way/32036484-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -81.0 km- way/255284259-220;way/32036484-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -113.0 km- way/178838661-220;way/32036484-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -113.0 km- PL36-400;way/32036484-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -66.0 km- way/194903381-400;way/88544449-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -13.0 km- way/121656686-220;way/88544449-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -38.0 km- way/29115701-220;way/88544449-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -79.0 km- way/173613665-220;way/88544449-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -27.0 km- way/171917072-400;way/216060722-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -44.0 km- way/170316833-220;way/171917072-400 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -52.0 km- way/199098053-220;way/215282393-400 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -86.0 km- way/215282393-400;way/88544449-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -88.0 km- relation/18085709-400;way/86494356-400 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -0.0 km- relation/18085709-400;way/255314292 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -48.0 km- way/183945016-220;way/44389929-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -52.0 km- way/183945016-220;way/293489607-400 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -66.0 km- way/183945016-220;way/40946790-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -93.0 km- PL46-220;way/336990960-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -92.0 km- PL18-400;way/39428977-400 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -45.0 km- way/165763717-220;way/39428977-400 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -208.0 km- way/32036484-220;way/39428977-400 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -82.0 km- way/166838338-400;way/191038569-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -96.0 km- way/191038569-220;way/199098053-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -86.0 km- way/191038569-220;way/215282393-400 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -182.0 km- way/101915790-220;way/245964556-220 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -61.0 km- PL36-400;way/79033485-400 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -60.0 km- way/173613665-220;way/194903381-400 (thermal x 0.7 N-1)</t>
+  </si>
+  <si>
+    <t>grid link -66.0 km- way/158232924-220;way/180535363-220 (thermal x 0.7 N-1)</t>
   </si>
   <si>
     <t>~commodity_geo</t>
@@ -1859,7 +1859,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04A9E722-1521-46E6-AE1F-75AF796516AF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{134615C0-C5B4-4889-BAA6-85C2DF1E7B5C}">
   <dimension ref="B3:R102"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5588,7 +5588,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{746E0B5A-BC12-416B-B3C0-3B1400335A17}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02D3F727-7745-4E47-A093-0D41A5699FB7}">
   <dimension ref="B3:L62"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5186AEF9-E7DD-430F-A3EF-13F960ED80A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{51ACD3F9-8F24-4E7A-AF95-4296120C0551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{8C4ADE14-7A6A-42F0-83C4-4EE93DF9CD76}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{D156341E-DB3C-4563-B46B-5646EAC22056}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1859,7 +1859,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{134615C0-C5B4-4889-BAA6-85C2DF1E7B5C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A2B3198-C324-4B3E-8360-92FB636FAE92}">
   <dimension ref="B3:R102"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3918,10 +3918,10 @@
         <v>8</v>
       </c>
       <c r="Q53">
-        <v>14.802766317314759</v>
+        <v>22.486114252755243</v>
       </c>
       <c r="R53">
-        <v>51.535218780041816</v>
+        <v>52.863922335501393</v>
       </c>
     </row>
     <row r="54" spans="2:18" x14ac:dyDescent="0.45">
@@ -3959,10 +3959,10 @@
         <v>8</v>
       </c>
       <c r="Q54">
-        <v>17.419694531519191</v>
+        <v>22.355446487150843</v>
       </c>
       <c r="R54">
-        <v>50.345189363482064</v>
+        <v>54.113341639485057</v>
       </c>
     </row>
     <row r="55" spans="2:18" x14ac:dyDescent="0.45">
@@ -4000,10 +4000,10 @@
         <v>8</v>
       </c>
       <c r="Q55">
-        <v>17.419694531519191</v>
+        <v>22.769487912886849</v>
       </c>
       <c r="R55">
-        <v>51.113688192174173</v>
+        <v>49.699254968261187</v>
       </c>
     </row>
     <row r="56" spans="2:18" x14ac:dyDescent="0.45">
@@ -4041,10 +4041,10 @@
         <v>8</v>
       </c>
       <c r="Q56">
-        <v>14.879031900155717</v>
+        <v>20.330764696968672</v>
       </c>
       <c r="R56">
-        <v>52.593490272793417</v>
+        <v>49.662523715830574</v>
       </c>
     </row>
     <row r="57" spans="2:18" x14ac:dyDescent="0.45">
@@ -4082,10 +4082,10 @@
         <v>8</v>
       </c>
       <c r="Q57">
-        <v>16.921576298661556</v>
+        <v>23.167734279905289</v>
       </c>
       <c r="R57">
-        <v>53.043150454655688</v>
+        <v>51.94391590414488</v>
       </c>
     </row>
     <row r="58" spans="2:18" x14ac:dyDescent="0.45">
@@ -4123,10 +4123,10 @@
         <v>8</v>
       </c>
       <c r="Q58">
-        <v>20.701782962343003</v>
+        <v>23.592994218050087</v>
       </c>
       <c r="R58">
-        <v>54.18832903488137</v>
+        <v>50.345189363482064</v>
       </c>
     </row>
     <row r="59" spans="2:18" x14ac:dyDescent="0.45">
@@ -4164,10 +4164,10 @@
         <v>8</v>
       </c>
       <c r="Q59">
-        <v>17.019284902403875</v>
+        <v>15.018966875646065</v>
       </c>
       <c r="R59">
-        <v>54.223922873901166</v>
+        <v>53.492810636517959</v>
       </c>
     </row>
     <row r="60" spans="2:18" x14ac:dyDescent="0.45">
@@ -4205,10 +4205,10 @@
         <v>8</v>
       </c>
       <c r="Q60">
-        <v>19.124890801214669</v>
+        <v>16.941516115030385</v>
       </c>
       <c r="R60">
-        <v>53.942470818380237</v>
+        <v>53.284115777169447</v>
       </c>
     </row>
     <row r="61" spans="2:18" x14ac:dyDescent="0.45">
@@ -4246,10 +4246,10 @@
         <v>8</v>
       </c>
       <c r="Q61">
-        <v>22.958991065199903</v>
+        <v>18.420682874609959</v>
       </c>
       <c r="R61">
-        <v>52.452026740518932</v>
+        <v>53.000181755301838</v>
       </c>
     </row>
     <row r="62" spans="2:18" x14ac:dyDescent="0.45">
@@ -4287,10 +4287,10 @@
         <v>8</v>
       </c>
       <c r="Q62">
-        <v>22.192834290615568</v>
+        <v>20.701782962343</v>
       </c>
       <c r="R62">
-        <v>54.314299403909786</v>
+        <v>54.18832903488137</v>
       </c>
     </row>
     <row r="63" spans="2:18" x14ac:dyDescent="0.45">
@@ -4328,10 +4328,10 @@
         <v>8</v>
       </c>
       <c r="Q63">
-        <v>22.648597650181891</v>
+        <v>19.124890801214669</v>
       </c>
       <c r="R63">
-        <v>53.434480489186768</v>
+        <v>53.94247081838023</v>
       </c>
     </row>
     <row r="64" spans="2:18" x14ac:dyDescent="0.45">
@@ -4369,10 +4369,10 @@
         <v>8</v>
       </c>
       <c r="Q64">
-        <v>22.769487912886849</v>
+        <v>16.733772344126866</v>
       </c>
       <c r="R64">
-        <v>49.699254968261187</v>
+        <v>52.368660181862282</v>
       </c>
     </row>
     <row r="65" spans="2:18" x14ac:dyDescent="0.45">
@@ -4410,10 +4410,10 @@
         <v>8</v>
       </c>
       <c r="Q65">
-        <v>23.518797665713208</v>
+        <v>17.419694531519191</v>
       </c>
       <c r="R65">
-        <v>50.281517317209371</v>
+        <v>51.244509727206605</v>
       </c>
     </row>
     <row r="66" spans="2:18" x14ac:dyDescent="0.45">
@@ -4451,10 +4451,10 @@
         <v>8</v>
       </c>
       <c r="Q66">
-        <v>19.808895899423351</v>
+        <v>15.361927969342226</v>
       </c>
       <c r="R66">
-        <v>49.877840849428637</v>
+        <v>50.794849545344334</v>
       </c>
     </row>
     <row r="67" spans="2:18" x14ac:dyDescent="0.45">
@@ -4492,10 +4492,10 @@
         <v>8</v>
       </c>
       <c r="Q67">
-        <v>18.832255867717425</v>
+        <v>14.877600333640924</v>
       </c>
       <c r="R67">
-        <v>50.208161047601962</v>
+        <v>52.291143302037241</v>
       </c>
     </row>
     <row r="68" spans="2:18" x14ac:dyDescent="0.45">
@@ -4533,10 +4533,10 @@
         <v>8</v>
       </c>
       <c r="Q68">
-        <v>18.264969048585325</v>
+        <v>17.419694531519191</v>
       </c>
       <c r="R68">
-        <v>52.039365767049581</v>
+        <v>50.345189363482064</v>
       </c>
     </row>
     <row r="69" spans="2:18" x14ac:dyDescent="0.45">
@@ -4574,10 +4574,10 @@
         <v>8</v>
       </c>
       <c r="Q69">
-        <v>18.420682874609959</v>
+        <v>19.105207880643142</v>
       </c>
       <c r="R69">
-        <v>53.000181755301838</v>
+        <v>49.977712352369977</v>
       </c>
     </row>
     <row r="70" spans="2:18" x14ac:dyDescent="0.45">
@@ -4615,10 +4615,10 @@
         <v>8</v>
       </c>
       <c r="Q70">
-        <v>21.248115859694053</v>
+        <v>21.146631128021703</v>
       </c>
       <c r="R70">
-        <v>52.500354971622542</v>
+        <v>52.224797256244031</v>
       </c>
     </row>
     <row r="71" spans="2:18" x14ac:dyDescent="0.45">
@@ -4656,10 +4656,10 @@
         <v>8</v>
       </c>
       <c r="Q71">
-        <v>20.515250703668858</v>
+        <v>20.164133104060543</v>
       </c>
       <c r="R71">
-        <v>51.474217933303869</v>
+        <v>51.018998941964419</v>
       </c>
     </row>
     <row r="72" spans="2:18" x14ac:dyDescent="0.45">
@@ -4697,10 +4697,10 @@
         <v>8</v>
       </c>
       <c r="Q72">
-        <v>21.857841551631548</v>
+        <v>18.687733391143109</v>
       </c>
       <c r="R72">
-        <v>51.981070871811788</v>
+        <v>51.673884605679042</v>
       </c>
     </row>
     <row r="73" spans="2:18" x14ac:dyDescent="0.45">
@@ -5148,10 +5148,10 @@
         <v>8</v>
       </c>
       <c r="Q83">
-        <v>20.569491805687608</v>
+        <v>20.578025216197691</v>
       </c>
       <c r="R83">
-        <v>51.945619106835984</v>
+        <v>54.262847574985429</v>
       </c>
     </row>
     <row r="84" spans="2:18" x14ac:dyDescent="0.45">
@@ -5189,10 +5189,10 @@
         <v>8</v>
       </c>
       <c r="Q84">
-        <v>21.251508341202094</v>
+        <v>16.9418209357206</v>
       </c>
       <c r="R84">
-        <v>50.572503835555374</v>
+        <v>53.288039440612657</v>
       </c>
     </row>
     <row r="85" spans="2:18" x14ac:dyDescent="0.45">
@@ -5230,10 +5230,10 @@
         <v>8</v>
       </c>
       <c r="Q85">
-        <v>22.221541482666314</v>
+        <v>18.871863191695702</v>
       </c>
       <c r="R85">
-        <v>52.402780027123931</v>
+        <v>52.975118986600947</v>
       </c>
     </row>
     <row r="86" spans="2:18" x14ac:dyDescent="0.45">
@@ -5271,10 +5271,10 @@
         <v>8</v>
       </c>
       <c r="Q86">
-        <v>23.413558137569936</v>
+        <v>18.606953227893715</v>
       </c>
       <c r="R86">
-        <v>50.221928080120989</v>
+        <v>52.063118080140882</v>
       </c>
     </row>
     <row r="87" spans="2:18" x14ac:dyDescent="0.45">
@@ -5312,10 +5312,10 @@
         <v>8</v>
       </c>
       <c r="Q87">
-        <v>22.593353600809184</v>
+        <v>16.315889173301674</v>
       </c>
       <c r="R87">
-        <v>53.760902274894448</v>
+        <v>51.776071734258643</v>
       </c>
     </row>
     <row r="88" spans="2:18" x14ac:dyDescent="0.45">
@@ -5353,10 +5353,10 @@
         <v>8</v>
       </c>
       <c r="Q88">
-        <v>18.684196405805043</v>
+        <v>15.361927969342226</v>
       </c>
       <c r="R88">
-        <v>52.397385084500648</v>
+        <v>51.244509727206612</v>
       </c>
     </row>
     <row r="89" spans="2:18" x14ac:dyDescent="0.45">
@@ -5394,10 +5394,10 @@
         <v>8</v>
       </c>
       <c r="Q89">
-        <v>20.68150354863176</v>
+        <v>15.026892107180988</v>
       </c>
       <c r="R89">
-        <v>53.14080843144523</v>
+        <v>52.383060462397033</v>
       </c>
     </row>
     <row r="90" spans="2:18" x14ac:dyDescent="0.45">
@@ -5408,10 +5408,10 @@
         <v>8</v>
       </c>
       <c r="Q90">
-        <v>21.103188435801304</v>
+        <v>18.932210981819424</v>
       </c>
       <c r="R90">
-        <v>54.312441674352527</v>
+        <v>50.145875258712522</v>
       </c>
     </row>
     <row r="91" spans="2:18" x14ac:dyDescent="0.45">
@@ -5422,10 +5422,10 @@
         <v>8</v>
       </c>
       <c r="Q91">
-        <v>19.258540287803484</v>
+        <v>17.365475335345355</v>
       </c>
       <c r="R91">
-        <v>53.94247081838023</v>
+        <v>49.895529181619786</v>
       </c>
     </row>
     <row r="92" spans="2:18" x14ac:dyDescent="0.45">
@@ -5436,10 +5436,10 @@
         <v>8</v>
       </c>
       <c r="Q92">
-        <v>16.903251720257263</v>
+        <v>16.047850156734548</v>
       </c>
       <c r="R92">
-        <v>54.161619422062977</v>
+        <v>50.794849545344334</v>
       </c>
     </row>
     <row r="93" spans="2:18" x14ac:dyDescent="0.45">
@@ -5450,10 +5450,10 @@
         <v>8</v>
       </c>
       <c r="Q93">
-        <v>15.361927969342226</v>
+        <v>22.221149843265444</v>
       </c>
       <c r="R93">
-        <v>51.244509727206612</v>
+        <v>49.445868999757522</v>
       </c>
     </row>
     <row r="94" spans="2:18" x14ac:dyDescent="0.45">
@@ -5464,10 +5464,10 @@
         <v>8</v>
       </c>
       <c r="Q94">
-        <v>15.026892107180988</v>
+        <v>21.136931470305012</v>
       </c>
       <c r="R94">
-        <v>52.383060462397033</v>
+        <v>49.735591777639613</v>
       </c>
     </row>
     <row r="95" spans="2:18" x14ac:dyDescent="0.45">
@@ -5478,10 +5478,10 @@
         <v>8</v>
       </c>
       <c r="Q95">
-        <v>16.375814143056594</v>
+        <v>19.327550696596081</v>
       </c>
       <c r="R95">
-        <v>51.541179017177562</v>
+        <v>49.445868999757522</v>
       </c>
     </row>
     <row r="96" spans="2:18" x14ac:dyDescent="0.45">
@@ -5492,10 +5492,10 @@
         <v>8</v>
       </c>
       <c r="Q96">
-        <v>16.859888285978002</v>
+        <v>19.953409684858084</v>
       </c>
       <c r="R96">
-        <v>52.951863842623695</v>
+        <v>49.698508147405903</v>
       </c>
     </row>
     <row r="97" spans="15:18" x14ac:dyDescent="0.45">
@@ -5506,10 +5506,10 @@
         <v>8</v>
       </c>
       <c r="Q97">
-        <v>19.826467717110425</v>
+        <v>21.045096223061503</v>
       </c>
       <c r="R97">
-        <v>49.445868999757508</v>
+        <v>50.710655128353615</v>
       </c>
     </row>
     <row r="98" spans="15:18" x14ac:dyDescent="0.45">
@@ -5520,10 +5520,10 @@
         <v>8</v>
       </c>
       <c r="Q98">
-        <v>22.221149843265444</v>
+        <v>23.592994218050087</v>
       </c>
       <c r="R98">
-        <v>49.445868999757522</v>
+        <v>50.345189363482064</v>
       </c>
     </row>
     <row r="99" spans="15:18" x14ac:dyDescent="0.45">
@@ -5534,10 +5534,10 @@
         <v>8</v>
       </c>
       <c r="Q99">
-        <v>21.136931470305012</v>
+        <v>23.129636354579976</v>
       </c>
       <c r="R99">
-        <v>49.735591777639613</v>
+        <v>51.507256371414606</v>
       </c>
     </row>
     <row r="100" spans="15:18" x14ac:dyDescent="0.45">
@@ -5548,10 +5548,10 @@
         <v>8</v>
       </c>
       <c r="Q100">
-        <v>16.733772344126869</v>
+        <v>21.256272083525616</v>
       </c>
       <c r="R100">
-        <v>50.345189363482064</v>
+        <v>53.023548837825182</v>
       </c>
     </row>
     <row r="101" spans="15:18" x14ac:dyDescent="0.45">
@@ -5562,10 +5562,10 @@
         <v>8</v>
       </c>
       <c r="Q101">
-        <v>19.691296586567169</v>
+        <v>22.857822220602117</v>
       </c>
       <c r="R101">
-        <v>50.177730966847243</v>
+        <v>52.900922470344462</v>
       </c>
     </row>
     <row r="102" spans="15:18" x14ac:dyDescent="0.45">
@@ -5576,10 +5576,10 @@
         <v>8</v>
       </c>
       <c r="Q102">
-        <v>18.59892442917592</v>
+        <v>22.342822704147078</v>
       </c>
       <c r="R102">
-        <v>49.960030388543707</v>
+        <v>54.182329331426978</v>
       </c>
     </row>
   </sheetData>
@@ -5588,7 +5588,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02D3F727-7745-4E47-A093-0D41A5699FB7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DC4CF4D-23B9-462E-8D54-1F805448DFED}">
   <dimension ref="B3:L62"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{51ACD3F9-8F24-4E7A-AF95-4296120C0551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5660DDFA-7329-499F-8F45-BF89CAFADD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{D156341E-DB3C-4563-B46B-5646EAC22056}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{DF8EEEB6-3404-400F-B8C8-2337EC6D22B3}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1859,7 +1859,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A2B3198-C324-4B3E-8360-92FB636FAE92}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{810270D1-44C0-4ED1-8B0D-9F067BEE6BC4}">
   <dimension ref="B3:R102"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5588,7 +5588,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DC4CF4D-23B9-462E-8D54-1F805448DFED}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1042AE4D-5BF6-4933-988F-C109BAD4471B}">
   <dimension ref="B3:L62"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25928"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5660DDFA-7329-499F-8F45-BF89CAFADD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D133278-8F83-449A-AACF-CE9155F96905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{DF8EEEB6-3404-400F-B8C8-2337EC6D22B3}"/>
+    <workbookView xWindow="2573" yWindow="2573" windowWidth="21600" windowHeight="11422" activeTab="1" xr2:uid="{8C11EA35-DE0A-42C5-9429-40BA2C1DD091}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -32,15 +32,12 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1510" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="482">
   <si>
     <t>~tradelinks_dins</t>
   </si>
@@ -898,9 +895,6 @@
   </si>
   <si>
     <t>elc_won_POL_019</t>
-  </si>
-  <si>
-    <t>elc_won_POL_020</t>
   </si>
   <si>
     <t>co2</t>
@@ -1499,7 +1493,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1554,39 +1548,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1638,7 +1632,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1749,6 +1743,13 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -1757,13 +1758,6 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1828,39 +1822,19 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme 2013 - 2022" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{810270D1-44C0-4ED1-8B0D-9F067BEE6BC4}">
-  <dimension ref="B3:R102"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD186334-F32C-4D6A-9165-844FFA079C53}">
+  <dimension ref="B3:R101"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="3" spans="2:18" x14ac:dyDescent="0.45">
@@ -3918,10 +3892,10 @@
         <v>8</v>
       </c>
       <c r="Q53">
-        <v>22.486114252755243</v>
+        <v>22.387884415840912</v>
       </c>
       <c r="R53">
-        <v>52.863922335501393</v>
+        <v>52.797852990301593</v>
       </c>
     </row>
     <row r="54" spans="2:18" x14ac:dyDescent="0.45">
@@ -3959,10 +3933,10 @@
         <v>8</v>
       </c>
       <c r="Q54">
-        <v>22.355446487150843</v>
+        <v>22.436878727454864</v>
       </c>
       <c r="R54">
-        <v>54.113341639485057</v>
+        <v>53.758426235726397</v>
       </c>
     </row>
     <row r="55" spans="2:18" x14ac:dyDescent="0.45">
@@ -4000,10 +3974,10 @@
         <v>8</v>
       </c>
       <c r="Q55">
-        <v>22.769487912886849</v>
+        <v>22.158862912599531</v>
       </c>
       <c r="R55">
-        <v>49.699254968261187</v>
+        <v>49.985302240943966</v>
       </c>
     </row>
     <row r="56" spans="2:18" x14ac:dyDescent="0.45">
@@ -4041,10 +4015,10 @@
         <v>8</v>
       </c>
       <c r="Q56">
-        <v>20.330764696968672</v>
+        <v>20.576363415677669</v>
       </c>
       <c r="R56">
-        <v>49.662523715830574</v>
+        <v>50.179698397399775</v>
       </c>
     </row>
     <row r="57" spans="2:18" x14ac:dyDescent="0.45">
@@ -4082,10 +4056,10 @@
         <v>8</v>
       </c>
       <c r="Q57">
-        <v>23.167734279905289</v>
+        <v>22.647999312422595</v>
       </c>
       <c r="R57">
-        <v>51.94391590414488</v>
+        <v>51.755872298670091</v>
       </c>
     </row>
     <row r="58" spans="2:18" x14ac:dyDescent="0.45">
@@ -4123,10 +4097,10 @@
         <v>8</v>
       </c>
       <c r="Q58">
-        <v>23.592994218050087</v>
+        <v>22.614693947996503</v>
       </c>
       <c r="R58">
-        <v>50.345189363482064</v>
+        <v>50.677937554331706</v>
       </c>
     </row>
     <row r="59" spans="2:18" x14ac:dyDescent="0.45">
@@ -4164,10 +4138,10 @@
         <v>8</v>
       </c>
       <c r="Q59">
-        <v>15.018966875646065</v>
+        <v>15.177025576701782</v>
       </c>
       <c r="R59">
-        <v>53.492810636517959</v>
+        <v>53.385570698209328</v>
       </c>
     </row>
     <row r="60" spans="2:18" x14ac:dyDescent="0.45">
@@ -4205,10 +4179,10 @@
         <v>8</v>
       </c>
       <c r="Q60">
-        <v>16.941516115030385</v>
+        <v>16.851528118709499</v>
       </c>
       <c r="R60">
-        <v>53.284115777169447</v>
+        <v>53.556913702673697</v>
       </c>
     </row>
     <row r="61" spans="2:18" x14ac:dyDescent="0.45">
@@ -4246,10 +4220,10 @@
         <v>8</v>
       </c>
       <c r="Q61">
-        <v>18.420682874609959</v>
+        <v>18.833039725101798</v>
       </c>
       <c r="R61">
-        <v>53.000181755301838</v>
+        <v>52.848472544632912</v>
       </c>
     </row>
     <row r="62" spans="2:18" x14ac:dyDescent="0.45">
@@ -4287,10 +4261,10 @@
         <v>8</v>
       </c>
       <c r="Q62">
-        <v>20.701782962343</v>
+        <v>20.474987843539957</v>
       </c>
       <c r="R62">
-        <v>54.18832903488137</v>
+        <v>53.867432812752376</v>
       </c>
     </row>
     <row r="63" spans="2:18" x14ac:dyDescent="0.45">
@@ -4328,10 +4302,10 @@
         <v>8</v>
       </c>
       <c r="Q63">
-        <v>19.124890801214669</v>
+        <v>18.950202712790809</v>
       </c>
       <c r="R63">
-        <v>53.94247081838023</v>
+        <v>53.834708755581374</v>
       </c>
     </row>
     <row r="64" spans="2:18" x14ac:dyDescent="0.45">
@@ -4369,10 +4343,10 @@
         <v>8</v>
       </c>
       <c r="Q64">
-        <v>16.733772344126866</v>
+        <v>16.541594041004011</v>
       </c>
       <c r="R64">
-        <v>52.368660181862282</v>
+        <v>52.292582195464313</v>
       </c>
     </row>
     <row r="65" spans="2:18" x14ac:dyDescent="0.45">
@@ -4410,10 +4384,10 @@
         <v>8</v>
       </c>
       <c r="Q65">
-        <v>17.419694531519191</v>
+        <v>16.597184145059202</v>
       </c>
       <c r="R65">
-        <v>51.244509727206605</v>
+        <v>51.381036311175727</v>
       </c>
     </row>
     <row r="66" spans="2:18" x14ac:dyDescent="0.45">
@@ -4451,10 +4425,10 @@
         <v>8</v>
       </c>
       <c r="Q66">
-        <v>15.361927969342226</v>
+        <v>15.346251681111026</v>
       </c>
       <c r="R66">
-        <v>50.794849545344334</v>
+        <v>51.202873879217471</v>
       </c>
     </row>
     <row r="67" spans="2:18" x14ac:dyDescent="0.45">
@@ -4492,10 +4466,10 @@
         <v>8</v>
       </c>
       <c r="Q67">
-        <v>14.877600333640924</v>
+        <v>15.145356416678331</v>
       </c>
       <c r="R67">
-        <v>52.291143302037241</v>
+        <v>52.186880964694659</v>
       </c>
     </row>
     <row r="68" spans="2:18" x14ac:dyDescent="0.45">
@@ -4533,10 +4507,10 @@
         <v>8</v>
       </c>
       <c r="Q68">
-        <v>17.419694531519191</v>
+        <v>17.083147938913381</v>
       </c>
       <c r="R68">
-        <v>50.345189363482064</v>
+        <v>50.673345049899048</v>
       </c>
     </row>
     <row r="69" spans="2:18" x14ac:dyDescent="0.45">
@@ -4574,10 +4548,10 @@
         <v>8</v>
       </c>
       <c r="Q69">
-        <v>19.105207880643142</v>
+        <v>18.911500370089843</v>
       </c>
       <c r="R69">
-        <v>49.977712352369977</v>
+        <v>50.08331213626267</v>
       </c>
     </row>
     <row r="70" spans="2:18" x14ac:dyDescent="0.45">
@@ -4615,10 +4589,10 @@
         <v>8</v>
       </c>
       <c r="Q70">
-        <v>21.146631128021703</v>
+        <v>20.781405442235567</v>
       </c>
       <c r="R70">
-        <v>52.224797256244031</v>
+        <v>52.366491870473581</v>
       </c>
     </row>
     <row r="71" spans="2:18" x14ac:dyDescent="0.45">
@@ -4656,10 +4630,10 @@
         <v>8</v>
       </c>
       <c r="Q71">
-        <v>20.164133104060543</v>
+        <v>20.402957702269411</v>
       </c>
       <c r="R71">
-        <v>51.018998941964419</v>
+        <v>51.12109494883768</v>
       </c>
     </row>
     <row r="72" spans="2:18" x14ac:dyDescent="0.45">
@@ -4697,10 +4671,10 @@
         <v>8</v>
       </c>
       <c r="Q72">
-        <v>18.687733391143109</v>
+        <v>18.792464723500991</v>
       </c>
       <c r="R72">
-        <v>51.673884605679042</v>
+        <v>51.330784626906521</v>
       </c>
     </row>
     <row r="73" spans="2:18" x14ac:dyDescent="0.45">
@@ -5148,10 +5122,10 @@
         <v>8</v>
       </c>
       <c r="Q83">
-        <v>20.578025216197691</v>
+        <v>16.384709287577795</v>
       </c>
       <c r="R83">
-        <v>54.262847574985429</v>
+        <v>50.776690615375294</v>
       </c>
     </row>
     <row r="84" spans="2:18" x14ac:dyDescent="0.45">
@@ -5189,10 +5163,10 @@
         <v>8</v>
       </c>
       <c r="Q84">
-        <v>16.9418209357206</v>
+        <v>17.419694531519191</v>
       </c>
       <c r="R84">
-        <v>53.288039440612657</v>
+        <v>49.895529181619793</v>
       </c>
     </row>
     <row r="85" spans="2:18" x14ac:dyDescent="0.45">
@@ -5230,10 +5204,10 @@
         <v>8</v>
       </c>
       <c r="Q85">
-        <v>18.871863191695702</v>
+        <v>15.256062905619441</v>
       </c>
       <c r="R85">
-        <v>52.975118986600947</v>
+        <v>51.98468831119169</v>
       </c>
     </row>
     <row r="86" spans="2:18" x14ac:dyDescent="0.45">
@@ -5271,10 +5245,10 @@
         <v>8</v>
       </c>
       <c r="Q86">
-        <v>18.606953227893715</v>
+        <v>16.80515814440529</v>
       </c>
       <c r="R86">
-        <v>52.063118080140882</v>
+        <v>52.124016263770471</v>
       </c>
     </row>
     <row r="87" spans="2:18" x14ac:dyDescent="0.45">
@@ -5312,10 +5286,10 @@
         <v>8</v>
       </c>
       <c r="Q87">
-        <v>16.315889173301674</v>
+        <v>19.003551538461117</v>
       </c>
       <c r="R87">
-        <v>51.776071734258643</v>
+        <v>53.788484402851722</v>
       </c>
     </row>
     <row r="88" spans="2:18" x14ac:dyDescent="0.45">
@@ -5353,10 +5327,10 @@
         <v>8</v>
       </c>
       <c r="Q88">
-        <v>15.361927969342226</v>
+        <v>15.172985574189886</v>
       </c>
       <c r="R88">
-        <v>51.244509727206612</v>
+        <v>53.270513397783269</v>
       </c>
     </row>
     <row r="89" spans="2:18" x14ac:dyDescent="0.45">
@@ -5394,10 +5368,10 @@
         <v>8</v>
       </c>
       <c r="Q89">
-        <v>15.026892107180988</v>
+        <v>17.551521574400923</v>
       </c>
       <c r="R89">
-        <v>52.383060462397033</v>
+        <v>54.392131000242507</v>
       </c>
     </row>
     <row r="90" spans="2:18" x14ac:dyDescent="0.45">
@@ -5408,10 +5382,10 @@
         <v>8</v>
       </c>
       <c r="Q90">
-        <v>18.932210981819424</v>
+        <v>16.852061394622268</v>
       </c>
       <c r="R90">
-        <v>50.145875258712522</v>
+        <v>53.40601844225278</v>
       </c>
     </row>
     <row r="91" spans="2:18" x14ac:dyDescent="0.45">
@@ -5422,10 +5396,10 @@
         <v>8</v>
       </c>
       <c r="Q91">
-        <v>17.365475335345355</v>
+        <v>22.728951916805229</v>
       </c>
       <c r="R91">
-        <v>49.895529181619786</v>
+        <v>53.629053884575626</v>
       </c>
     </row>
     <row r="92" spans="2:18" x14ac:dyDescent="0.45">
@@ -5436,10 +5410,10 @@
         <v>8</v>
       </c>
       <c r="Q92">
-        <v>16.047850156734548</v>
+        <v>21.016862912105651</v>
       </c>
       <c r="R92">
-        <v>50.794849545344334</v>
+        <v>54.067358273794383</v>
       </c>
     </row>
     <row r="93" spans="2:18" x14ac:dyDescent="0.45">
@@ -5450,10 +5424,10 @@
         <v>8</v>
       </c>
       <c r="Q93">
-        <v>22.221149843265444</v>
+        <v>22.557805508871297</v>
       </c>
       <c r="R93">
-        <v>49.445868999757522</v>
+        <v>52.454344370054137</v>
       </c>
     </row>
     <row r="94" spans="2:18" x14ac:dyDescent="0.45">
@@ -5464,10 +5438,10 @@
         <v>8</v>
       </c>
       <c r="Q94">
-        <v>21.136931470305012</v>
+        <v>20.648531569729403</v>
       </c>
       <c r="R94">
-        <v>49.735591777639613</v>
+        <v>52.768785613368301</v>
       </c>
     </row>
     <row r="95" spans="2:18" x14ac:dyDescent="0.45">
@@ -5478,10 +5452,10 @@
         <v>8</v>
       </c>
       <c r="Q95">
-        <v>19.327550696596081</v>
+        <v>18.369571653809839</v>
       </c>
       <c r="R95">
-        <v>49.445868999757522</v>
+        <v>51.799686803699899</v>
       </c>
     </row>
     <row r="96" spans="2:18" x14ac:dyDescent="0.45">
@@ -5492,10 +5466,10 @@
         <v>8</v>
       </c>
       <c r="Q96">
-        <v>19.953409684858084</v>
+        <v>19.027975647671131</v>
       </c>
       <c r="R96">
-        <v>49.698508147405903</v>
+        <v>52.655496867703171</v>
       </c>
     </row>
     <row r="97" spans="15:18" x14ac:dyDescent="0.45">
@@ -5506,10 +5480,10 @@
         <v>8</v>
       </c>
       <c r="Q97">
-        <v>21.045096223061503</v>
+        <v>19.265584431429922</v>
       </c>
       <c r="R97">
-        <v>50.710655128353615</v>
+        <v>50.628803361963257</v>
       </c>
     </row>
     <row r="98" spans="15:18" x14ac:dyDescent="0.45">
@@ -5520,10 +5494,10 @@
         <v>8</v>
       </c>
       <c r="Q98">
-        <v>23.592994218050087</v>
+        <v>20.044508863733864</v>
       </c>
       <c r="R98">
-        <v>50.345189363482064</v>
+        <v>51.478266767104472</v>
       </c>
     </row>
     <row r="99" spans="15:18" x14ac:dyDescent="0.45">
@@ -5534,10 +5508,10 @@
         <v>8</v>
       </c>
       <c r="Q99">
-        <v>23.129636354579976</v>
+        <v>22.909847640550961</v>
       </c>
       <c r="R99">
-        <v>51.507256371414606</v>
+        <v>50.868423259833534</v>
       </c>
     </row>
     <row r="100" spans="15:18" x14ac:dyDescent="0.45">
@@ -5548,10 +5522,10 @@
         <v>8</v>
       </c>
       <c r="Q100">
-        <v>21.256272083525616</v>
+        <v>22.221487288334288</v>
       </c>
       <c r="R100">
-        <v>53.023548837825182</v>
+        <v>49.853731539665588</v>
       </c>
     </row>
     <row r="101" spans="15:18" x14ac:dyDescent="0.45">
@@ -5562,24 +5536,10 @@
         <v>8</v>
       </c>
       <c r="Q101">
-        <v>22.857822220602117</v>
+        <v>21.524822746291907</v>
       </c>
       <c r="R101">
-        <v>52.900922470344462</v>
-      </c>
-    </row>
-    <row r="102" spans="15:18" x14ac:dyDescent="0.45">
-      <c r="O102" t="s">
-        <v>286</v>
-      </c>
-      <c r="P102" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q102">
-        <v>22.342822704147078</v>
-      </c>
-      <c r="R102">
-        <v>54.182329331426978</v>
+        <v>49.648253092611611</v>
       </c>
     </row>
   </sheetData>
@@ -5588,7 +5548,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1042AE4D-5BF6-4933-988F-C109BAD4471B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BA005D2-884D-439D-A1C3-8082CDECE021}">
   <dimension ref="B3:L62"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5637,25 +5597,25 @@
         <v>8</v>
       </c>
       <c r="D5" t="s">
+        <v>286</v>
+      </c>
+      <c r="E5" t="s">
         <v>287</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>288</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>289</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>290</v>
       </c>
-      <c r="H5" t="s">
-        <v>291</v>
-      </c>
       <c r="K5" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="L5" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.45">
@@ -5666,25 +5626,25 @@
         <v>8</v>
       </c>
       <c r="D6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E6" t="s">
+        <v>291</v>
+      </c>
+      <c r="F6" t="s">
         <v>292</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>293</v>
       </c>
-      <c r="G6" t="s">
-        <v>294</v>
-      </c>
       <c r="H6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="L6" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.45">
@@ -5695,25 +5655,25 @@
         <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E7" t="s">
+        <v>294</v>
+      </c>
+      <c r="F7" t="s">
         <v>295</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>296</v>
       </c>
-      <c r="G7" t="s">
-        <v>297</v>
-      </c>
       <c r="H7" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K7" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="L7" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.45">
@@ -5724,25 +5684,25 @@
         <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E8" t="s">
+        <v>297</v>
+      </c>
+      <c r="F8" t="s">
         <v>298</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>299</v>
       </c>
-      <c r="G8" t="s">
-        <v>300</v>
-      </c>
       <c r="H8" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K8" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="L8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.45">
@@ -5753,25 +5713,25 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E9" t="s">
+        <v>300</v>
+      </c>
+      <c r="F9" t="s">
         <v>301</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>302</v>
       </c>
-      <c r="G9" t="s">
-        <v>303</v>
-      </c>
       <c r="H9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="L9" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.45">
@@ -5782,25 +5742,25 @@
         <v>8</v>
       </c>
       <c r="D10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E10" t="s">
+        <v>303</v>
+      </c>
+      <c r="F10" t="s">
         <v>304</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>305</v>
       </c>
-      <c r="G10" t="s">
-        <v>306</v>
-      </c>
       <c r="H10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K10" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="L10" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.45">
@@ -5811,25 +5771,25 @@
         <v>8</v>
       </c>
       <c r="D11" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E11" t="s">
+        <v>306</v>
+      </c>
+      <c r="F11" t="s">
+        <v>288</v>
+      </c>
+      <c r="G11" t="s">
         <v>307</v>
       </c>
-      <c r="F11" t="s">
-        <v>289</v>
-      </c>
-      <c r="G11" t="s">
-        <v>308</v>
-      </c>
       <c r="H11" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K11" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L11" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.45">
@@ -5840,25 +5800,25 @@
         <v>8</v>
       </c>
       <c r="D12" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E12" t="s">
+        <v>308</v>
+      </c>
+      <c r="F12" t="s">
         <v>309</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>310</v>
       </c>
-      <c r="G12" t="s">
-        <v>311</v>
-      </c>
       <c r="H12" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K12" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="L12" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.45">
@@ -5869,25 +5829,25 @@
         <v>8</v>
       </c>
       <c r="D13" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E13" t="s">
+        <v>311</v>
+      </c>
+      <c r="F13" t="s">
         <v>312</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>313</v>
       </c>
-      <c r="G13" t="s">
-        <v>314</v>
-      </c>
       <c r="H13" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K13" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="L13" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.45">
@@ -5898,25 +5858,25 @@
         <v>8</v>
       </c>
       <c r="D14" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F14" t="s">
+        <v>298</v>
+      </c>
+      <c r="G14" t="s">
         <v>315</v>
       </c>
-      <c r="F14" t="s">
-        <v>299</v>
-      </c>
-      <c r="G14" t="s">
-        <v>316</v>
-      </c>
       <c r="H14" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K14" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="L14" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.45">
@@ -5927,25 +5887,25 @@
         <v>8</v>
       </c>
       <c r="D15" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E15" t="s">
+        <v>316</v>
+      </c>
+      <c r="F15" t="s">
+        <v>312</v>
+      </c>
+      <c r="G15" t="s">
         <v>317</v>
       </c>
-      <c r="F15" t="s">
-        <v>313</v>
-      </c>
-      <c r="G15" t="s">
-        <v>318</v>
-      </c>
       <c r="H15" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K15" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="L15" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.45">
@@ -5956,25 +5916,25 @@
         <v>8</v>
       </c>
       <c r="D16" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E16" t="s">
+        <v>318</v>
+      </c>
+      <c r="F16" t="s">
+        <v>292</v>
+      </c>
+      <c r="G16" t="s">
         <v>319</v>
       </c>
-      <c r="F16" t="s">
-        <v>293</v>
-      </c>
-      <c r="G16" t="s">
-        <v>320</v>
-      </c>
       <c r="H16" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K16" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="L16" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.45">
@@ -5985,25 +5945,25 @@
         <v>8</v>
       </c>
       <c r="D17" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E17" t="s">
+        <v>320</v>
+      </c>
+      <c r="F17" t="s">
+        <v>298</v>
+      </c>
+      <c r="G17" t="s">
         <v>321</v>
       </c>
-      <c r="F17" t="s">
-        <v>299</v>
-      </c>
-      <c r="G17" t="s">
-        <v>322</v>
-      </c>
       <c r="H17" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K17" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="L17" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.45">
@@ -6014,25 +5974,25 @@
         <v>8</v>
       </c>
       <c r="D18" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E18" t="s">
+        <v>322</v>
+      </c>
+      <c r="F18" t="s">
         <v>323</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>324</v>
       </c>
-      <c r="G18" t="s">
-        <v>325</v>
-      </c>
       <c r="H18" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K18" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="L18" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.45">
@@ -6043,25 +6003,25 @@
         <v>8</v>
       </c>
       <c r="D19" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E19" t="s">
+        <v>325</v>
+      </c>
+      <c r="F19" t="s">
         <v>326</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>327</v>
       </c>
-      <c r="G19" t="s">
-        <v>328</v>
-      </c>
       <c r="H19" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K19" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="L19" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.45">
@@ -6072,25 +6032,25 @@
         <v>8</v>
       </c>
       <c r="D20" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E20" t="s">
+        <v>328</v>
+      </c>
+      <c r="F20" t="s">
+        <v>312</v>
+      </c>
+      <c r="G20" t="s">
         <v>329</v>
       </c>
-      <c r="F20" t="s">
-        <v>313</v>
-      </c>
-      <c r="G20" t="s">
-        <v>330</v>
-      </c>
       <c r="H20" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K20" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="L20" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.45">
@@ -6101,25 +6061,25 @@
         <v>8</v>
       </c>
       <c r="D21" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E21" t="s">
+        <v>330</v>
+      </c>
+      <c r="F21" t="s">
         <v>331</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>332</v>
       </c>
-      <c r="G21" t="s">
-        <v>333</v>
-      </c>
       <c r="H21" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K21" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="L21" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.45">
@@ -6130,25 +6090,25 @@
         <v>8</v>
       </c>
       <c r="D22" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E22" t="s">
+        <v>333</v>
+      </c>
+      <c r="F22" t="s">
         <v>334</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>335</v>
       </c>
-      <c r="G22" t="s">
-        <v>336</v>
-      </c>
       <c r="H22" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K22" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="L22" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.45">
@@ -6159,25 +6119,25 @@
         <v>8</v>
       </c>
       <c r="D23" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E23" t="s">
+        <v>336</v>
+      </c>
+      <c r="F23" t="s">
+        <v>326</v>
+      </c>
+      <c r="G23" t="s">
         <v>337</v>
       </c>
-      <c r="F23" t="s">
-        <v>327</v>
-      </c>
-      <c r="G23" t="s">
-        <v>338</v>
-      </c>
       <c r="H23" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K23" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="L23" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.45">
@@ -6188,25 +6148,25 @@
         <v>8</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E24" t="s">
+        <v>338</v>
+      </c>
+      <c r="F24" t="s">
         <v>339</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>340</v>
       </c>
-      <c r="G24" t="s">
-        <v>341</v>
-      </c>
       <c r="H24" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K24" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="L24" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.45">
@@ -6217,25 +6177,25 @@
         <v>8</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E25" t="s">
+        <v>341</v>
+      </c>
+      <c r="F25" t="s">
+        <v>298</v>
+      </c>
+      <c r="G25" t="s">
         <v>342</v>
       </c>
-      <c r="F25" t="s">
-        <v>299</v>
-      </c>
-      <c r="G25" t="s">
-        <v>343</v>
-      </c>
       <c r="H25" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K25" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="L25" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.45">
@@ -6246,25 +6206,25 @@
         <v>8</v>
       </c>
       <c r="D26" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E26" t="s">
+        <v>343</v>
+      </c>
+      <c r="F26" t="s">
         <v>344</v>
       </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>345</v>
       </c>
-      <c r="G26" t="s">
-        <v>346</v>
-      </c>
       <c r="H26" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K26" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="L26" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.45">
@@ -6275,25 +6235,25 @@
         <v>8</v>
       </c>
       <c r="D27" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E27" t="s">
+        <v>346</v>
+      </c>
+      <c r="F27" t="s">
+        <v>344</v>
+      </c>
+      <c r="G27" t="s">
         <v>347</v>
       </c>
-      <c r="F27" t="s">
-        <v>345</v>
-      </c>
-      <c r="G27" t="s">
-        <v>348</v>
-      </c>
       <c r="H27" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K27" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L27" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.45">
@@ -6304,25 +6264,25 @@
         <v>8</v>
       </c>
       <c r="D28" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E28" t="s">
+        <v>348</v>
+      </c>
+      <c r="F28" t="s">
+        <v>326</v>
+      </c>
+      <c r="G28" t="s">
         <v>349</v>
       </c>
-      <c r="F28" t="s">
-        <v>327</v>
-      </c>
-      <c r="G28" t="s">
-        <v>350</v>
-      </c>
       <c r="H28" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K28" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="L28" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.45">
@@ -6333,25 +6293,25 @@
         <v>8</v>
       </c>
       <c r="D29" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E29" t="s">
+        <v>350</v>
+      </c>
+      <c r="F29" t="s">
+        <v>326</v>
+      </c>
+      <c r="G29" t="s">
         <v>351</v>
       </c>
-      <c r="F29" t="s">
-        <v>327</v>
-      </c>
-      <c r="G29" t="s">
-        <v>352</v>
-      </c>
       <c r="H29" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K29" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="L29" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.45">
@@ -6362,25 +6322,25 @@
         <v>8</v>
       </c>
       <c r="D30" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E30" t="s">
+        <v>352</v>
+      </c>
+      <c r="F30" t="s">
+        <v>331</v>
+      </c>
+      <c r="G30" t="s">
         <v>353</v>
       </c>
-      <c r="F30" t="s">
-        <v>332</v>
-      </c>
-      <c r="G30" t="s">
-        <v>354</v>
-      </c>
       <c r="H30" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K30" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L30" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.45">
@@ -6391,25 +6351,25 @@
         <v>8</v>
       </c>
       <c r="D31" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E31" t="s">
+        <v>354</v>
+      </c>
+      <c r="F31" t="s">
+        <v>326</v>
+      </c>
+      <c r="G31" t="s">
         <v>355</v>
       </c>
-      <c r="F31" t="s">
-        <v>327</v>
-      </c>
-      <c r="G31" t="s">
-        <v>356</v>
-      </c>
       <c r="H31" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K31" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="L31" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.45">
@@ -6420,25 +6380,25 @@
         <v>8</v>
       </c>
       <c r="D32" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E32" t="s">
+        <v>356</v>
+      </c>
+      <c r="F32" t="s">
+        <v>326</v>
+      </c>
+      <c r="G32" t="s">
         <v>357</v>
       </c>
-      <c r="F32" t="s">
-        <v>327</v>
-      </c>
-      <c r="G32" t="s">
-        <v>358</v>
-      </c>
       <c r="H32" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K32" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="L32" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.45">
@@ -6449,25 +6409,25 @@
         <v>8</v>
       </c>
       <c r="D33" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E33" t="s">
+        <v>358</v>
+      </c>
+      <c r="F33" t="s">
+        <v>334</v>
+      </c>
+      <c r="G33" t="s">
         <v>359</v>
       </c>
-      <c r="F33" t="s">
-        <v>335</v>
-      </c>
-      <c r="G33" t="s">
-        <v>360</v>
-      </c>
       <c r="H33" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K33" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="L33" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.45">
@@ -6478,25 +6438,25 @@
         <v>8</v>
       </c>
       <c r="D34" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E34" t="s">
+        <v>360</v>
+      </c>
+      <c r="F34" t="s">
         <v>361</v>
       </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
         <v>362</v>
       </c>
-      <c r="G34" t="s">
-        <v>363</v>
-      </c>
       <c r="H34" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K34" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="L34" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.45">
@@ -6507,25 +6467,25 @@
         <v>8</v>
       </c>
       <c r="D35" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E35" t="s">
+        <v>363</v>
+      </c>
+      <c r="F35" t="s">
+        <v>326</v>
+      </c>
+      <c r="G35" t="s">
         <v>364</v>
       </c>
-      <c r="F35" t="s">
-        <v>327</v>
-      </c>
-      <c r="G35" t="s">
-        <v>365</v>
-      </c>
       <c r="H35" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K35" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="L35" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="36" spans="2:12" x14ac:dyDescent="0.45">
@@ -6536,25 +6496,25 @@
         <v>8</v>
       </c>
       <c r="D36" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E36" t="s">
+        <v>365</v>
+      </c>
+      <c r="F36" t="s">
+        <v>301</v>
+      </c>
+      <c r="G36" t="s">
         <v>366</v>
       </c>
-      <c r="F36" t="s">
-        <v>302</v>
-      </c>
-      <c r="G36" t="s">
-        <v>367</v>
-      </c>
       <c r="H36" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K36" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="L36" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="37" spans="2:12" x14ac:dyDescent="0.45">
@@ -6565,25 +6525,25 @@
         <v>8</v>
       </c>
       <c r="D37" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E37" t="s">
+        <v>367</v>
+      </c>
+      <c r="F37" t="s">
         <v>368</v>
       </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
         <v>369</v>
       </c>
-      <c r="G37" t="s">
-        <v>370</v>
-      </c>
       <c r="H37" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K37" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="L37" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="38" spans="2:12" x14ac:dyDescent="0.45">
@@ -6594,25 +6554,25 @@
         <v>8</v>
       </c>
       <c r="D38" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E38" t="s">
+        <v>370</v>
+      </c>
+      <c r="F38" t="s">
+        <v>309</v>
+      </c>
+      <c r="G38" t="s">
         <v>371</v>
       </c>
-      <c r="F38" t="s">
-        <v>310</v>
-      </c>
-      <c r="G38" t="s">
-        <v>372</v>
-      </c>
       <c r="H38" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K38" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="L38" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.45">
@@ -6623,25 +6583,25 @@
         <v>8</v>
       </c>
       <c r="D39" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E39" t="s">
+        <v>372</v>
+      </c>
+      <c r="F39" t="s">
+        <v>326</v>
+      </c>
+      <c r="G39" t="s">
         <v>373</v>
       </c>
-      <c r="F39" t="s">
-        <v>327</v>
-      </c>
-      <c r="G39" t="s">
-        <v>374</v>
-      </c>
       <c r="H39" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K39" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="L39" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.45">
@@ -6652,25 +6612,25 @@
         <v>8</v>
       </c>
       <c r="D40" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E40" t="s">
+        <v>374</v>
+      </c>
+      <c r="F40" t="s">
+        <v>344</v>
+      </c>
+      <c r="G40" t="s">
         <v>375</v>
       </c>
-      <c r="F40" t="s">
-        <v>345</v>
-      </c>
-      <c r="G40" t="s">
-        <v>376</v>
-      </c>
       <c r="H40" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K40" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="L40" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.45">
@@ -6681,25 +6641,25 @@
         <v>8</v>
       </c>
       <c r="D41" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E41" t="s">
+        <v>376</v>
+      </c>
+      <c r="F41" t="s">
+        <v>312</v>
+      </c>
+      <c r="G41" t="s">
         <v>377</v>
       </c>
-      <c r="F41" t="s">
-        <v>313</v>
-      </c>
-      <c r="G41" t="s">
-        <v>378</v>
-      </c>
       <c r="H41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K41" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="L41" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="42" spans="2:12" x14ac:dyDescent="0.45">
@@ -6710,25 +6670,25 @@
         <v>8</v>
       </c>
       <c r="D42" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E42" t="s">
+        <v>378</v>
+      </c>
+      <c r="F42" t="s">
         <v>379</v>
       </c>
-      <c r="F42" t="s">
+      <c r="G42" t="s">
         <v>380</v>
       </c>
-      <c r="G42" t="s">
-        <v>381</v>
-      </c>
       <c r="H42" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K42" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L42" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.45">
@@ -6739,25 +6699,25 @@
         <v>8</v>
       </c>
       <c r="D43" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E43" t="s">
+        <v>381</v>
+      </c>
+      <c r="F43" t="s">
+        <v>344</v>
+      </c>
+      <c r="G43" t="s">
         <v>382</v>
       </c>
-      <c r="F43" t="s">
-        <v>345</v>
-      </c>
-      <c r="G43" t="s">
-        <v>383</v>
-      </c>
       <c r="H43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K43" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="L43" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="44" spans="2:12" x14ac:dyDescent="0.45">
@@ -6768,25 +6728,25 @@
         <v>8</v>
       </c>
       <c r="D44" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E44" t="s">
+        <v>383</v>
+      </c>
+      <c r="F44" t="s">
+        <v>323</v>
+      </c>
+      <c r="G44" t="s">
         <v>384</v>
       </c>
-      <c r="F44" t="s">
-        <v>324</v>
-      </c>
-      <c r="G44" t="s">
-        <v>385</v>
-      </c>
       <c r="H44" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K44" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L44" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.45">
@@ -6797,25 +6757,25 @@
         <v>8</v>
       </c>
       <c r="D45" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E45" t="s">
+        <v>385</v>
+      </c>
+      <c r="F45" t="s">
+        <v>344</v>
+      </c>
+      <c r="G45" t="s">
         <v>386</v>
       </c>
-      <c r="F45" t="s">
-        <v>345</v>
-      </c>
-      <c r="G45" t="s">
-        <v>387</v>
-      </c>
       <c r="H45" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K45" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="L45" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="46" spans="2:12" x14ac:dyDescent="0.45">
@@ -6826,25 +6786,25 @@
         <v>8</v>
       </c>
       <c r="D46" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E46" t="s">
+        <v>387</v>
+      </c>
+      <c r="F46" t="s">
+        <v>344</v>
+      </c>
+      <c r="G46" t="s">
         <v>388</v>
       </c>
-      <c r="F46" t="s">
-        <v>345</v>
-      </c>
-      <c r="G46" t="s">
-        <v>389</v>
-      </c>
       <c r="H46" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K46" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L46" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="47" spans="2:12" x14ac:dyDescent="0.45">
@@ -6855,25 +6815,25 @@
         <v>8</v>
       </c>
       <c r="D47" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E47" t="s">
+        <v>389</v>
+      </c>
+      <c r="F47" t="s">
+        <v>288</v>
+      </c>
+      <c r="G47" t="s">
         <v>390</v>
       </c>
-      <c r="F47" t="s">
-        <v>289</v>
-      </c>
-      <c r="G47" t="s">
-        <v>391</v>
-      </c>
       <c r="H47" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K47" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="L47" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="48" spans="2:12" x14ac:dyDescent="0.45">
@@ -6884,25 +6844,25 @@
         <v>8</v>
       </c>
       <c r="D48" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E48" t="s">
+        <v>391</v>
+      </c>
+      <c r="F48" t="s">
         <v>392</v>
       </c>
-      <c r="F48" t="s">
+      <c r="G48" t="s">
         <v>393</v>
       </c>
-      <c r="G48" t="s">
-        <v>394</v>
-      </c>
       <c r="H48" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K48" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="L48" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="49" spans="2:12" x14ac:dyDescent="0.45">
@@ -6913,25 +6873,25 @@
         <v>8</v>
       </c>
       <c r="D49" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E49" t="s">
+        <v>394</v>
+      </c>
+      <c r="F49" t="s">
         <v>395</v>
       </c>
-      <c r="F49" t="s">
+      <c r="G49" t="s">
         <v>396</v>
       </c>
-      <c r="G49" t="s">
-        <v>397</v>
-      </c>
       <c r="H49" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K49" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="L49" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="50" spans="2:12" x14ac:dyDescent="0.45">
@@ -6942,25 +6902,25 @@
         <v>8</v>
       </c>
       <c r="D50" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E50" t="s">
+        <v>397</v>
+      </c>
+      <c r="F50" t="s">
         <v>398</v>
       </c>
-      <c r="F50" t="s">
+      <c r="G50" t="s">
         <v>399</v>
       </c>
-      <c r="G50" t="s">
-        <v>400</v>
-      </c>
       <c r="H50" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K50" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="L50" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="51" spans="2:12" x14ac:dyDescent="0.45">
@@ -6971,25 +6931,25 @@
         <v>8</v>
       </c>
       <c r="D51" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E51" t="s">
+        <v>400</v>
+      </c>
+      <c r="F51" t="s">
+        <v>344</v>
+      </c>
+      <c r="G51" t="s">
         <v>401</v>
       </c>
-      <c r="F51" t="s">
-        <v>345</v>
-      </c>
-      <c r="G51" t="s">
-        <v>402</v>
-      </c>
       <c r="H51" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K51" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="L51" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="52" spans="2:12" x14ac:dyDescent="0.45">
@@ -7000,25 +6960,25 @@
         <v>8</v>
       </c>
       <c r="D52" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E52" t="s">
+        <v>402</v>
+      </c>
+      <c r="F52" t="s">
+        <v>326</v>
+      </c>
+      <c r="G52" t="s">
         <v>403</v>
       </c>
-      <c r="F52" t="s">
-        <v>327</v>
-      </c>
-      <c r="G52" t="s">
-        <v>404</v>
-      </c>
       <c r="H52" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K52" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="L52" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="53" spans="2:12" x14ac:dyDescent="0.45">
@@ -7029,25 +6989,25 @@
         <v>8</v>
       </c>
       <c r="D53" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E53" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F53" t="s">
+        <v>404</v>
+      </c>
+      <c r="G53" t="s">
         <v>405</v>
       </c>
-      <c r="G53" t="s">
-        <v>406</v>
-      </c>
       <c r="H53" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K53" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="L53" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="54" spans="2:12" x14ac:dyDescent="0.45">
@@ -7058,25 +7018,25 @@
         <v>8</v>
       </c>
       <c r="D54" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E54" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F54" t="s">
+        <v>406</v>
+      </c>
+      <c r="G54" t="s">
         <v>407</v>
       </c>
-      <c r="G54" t="s">
-        <v>408</v>
-      </c>
       <c r="H54" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K54" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="L54" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="55" spans="2:12" x14ac:dyDescent="0.45">
@@ -7087,25 +7047,25 @@
         <v>8</v>
       </c>
       <c r="D55" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E55" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F55" t="s">
+        <v>408</v>
+      </c>
+      <c r="G55" t="s">
         <v>409</v>
       </c>
-      <c r="G55" t="s">
-        <v>410</v>
-      </c>
       <c r="H55" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K55" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="L55" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="56" spans="2:12" x14ac:dyDescent="0.45">
@@ -7116,25 +7076,25 @@
         <v>8</v>
       </c>
       <c r="D56" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F56" t="s">
+        <v>410</v>
+      </c>
+      <c r="G56" t="s">
         <v>411</v>
       </c>
-      <c r="G56" t="s">
-        <v>412</v>
-      </c>
       <c r="H56" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K56" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="L56" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="57" spans="2:12" x14ac:dyDescent="0.45">
@@ -7145,25 +7105,25 @@
         <v>8</v>
       </c>
       <c r="D57" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E57" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F57" t="s">
+        <v>412</v>
+      </c>
+      <c r="G57" t="s">
         <v>413</v>
       </c>
-      <c r="G57" t="s">
-        <v>414</v>
-      </c>
       <c r="H57" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K57" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="L57" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="58" spans="2:12" x14ac:dyDescent="0.45">
@@ -7174,25 +7134,25 @@
         <v>8</v>
       </c>
       <c r="D58" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E58" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F58" t="s">
+        <v>414</v>
+      </c>
+      <c r="G58" t="s">
         <v>415</v>
       </c>
-      <c r="G58" t="s">
-        <v>416</v>
-      </c>
       <c r="H58" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K58" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L58" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="59" spans="2:12" x14ac:dyDescent="0.45">
@@ -7203,25 +7163,25 @@
         <v>8</v>
       </c>
       <c r="D59" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E59" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F59" t="s">
+        <v>416</v>
+      </c>
+      <c r="G59" t="s">
         <v>417</v>
       </c>
-      <c r="G59" t="s">
-        <v>418</v>
-      </c>
       <c r="H59" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K59" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="L59" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="60" spans="2:12" x14ac:dyDescent="0.45">
@@ -7232,25 +7192,25 @@
         <v>8</v>
       </c>
       <c r="D60" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E60" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F60" t="s">
+        <v>418</v>
+      </c>
+      <c r="G60" t="s">
         <v>419</v>
       </c>
-      <c r="G60" t="s">
-        <v>420</v>
-      </c>
       <c r="H60" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K60" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="L60" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="61" spans="2:12" x14ac:dyDescent="0.45">
@@ -7261,25 +7221,25 @@
         <v>8</v>
       </c>
       <c r="D61" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E61" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F61" t="s">
+        <v>420</v>
+      </c>
+      <c r="G61" t="s">
         <v>421</v>
       </c>
-      <c r="G61" t="s">
-        <v>422</v>
-      </c>
       <c r="H61" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K61" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L61" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="62" spans="2:12" x14ac:dyDescent="0.45">
@@ -7290,25 +7250,25 @@
         <v>8</v>
       </c>
       <c r="D62" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E62" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F62" t="s">
+        <v>422</v>
+      </c>
+      <c r="G62" t="s">
         <v>423</v>
       </c>
-      <c r="G62" t="s">
-        <v>424</v>
-      </c>
       <c r="H62" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K62" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="L62" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25928"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D133278-8F83-449A-AACF-CE9155F96905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{06FEA5EE-9F65-4A03-9A44-15DAC35A3B2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2573" yWindow="2573" windowWidth="21600" windowHeight="11422" activeTab="1" xr2:uid="{8C11EA35-DE0A-42C5-9429-40BA2C1DD091}"/>
+    <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675" activeTab="1" xr2:uid="{553D755F-3C19-4748-A8BB-66F3A215FB4D}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -32,12 +32,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1729" uniqueCount="598">
   <si>
     <t>~tradelinks_dins</t>
   </si>
@@ -750,96 +753,357 @@
     <t>lat</t>
   </si>
   <si>
+    <t>shape</t>
+  </si>
+  <si>
     <t>elc_spv_POL_001</t>
   </si>
   <si>
+    <t>POLYGON ((18.448578 52.81832, 17.762656 52.81832, 17.076733 52.81832, 17.076733 53.267981, 17.076733 53.717641, 17.762656 53.717641, 18.448578 53.717641, 18.448578 53.267981, 18.448578 52.81832))</t>
+  </si>
+  <si>
     <t>elc_spv_POL_002</t>
   </si>
   <si>
+    <t>POLYGON ((22.564111 53.267981, 22.564111 53.717641, 23.250033 53.717641, 23.250033 54.167301, 23.935955 54.167301, 23.935955 53.717641, 23.935955 53.267981, 23.935955 52.81832, 23.935955 52.36866, 23.250033 52.36866, 23.250033 51.919, 22.564111 51.919, 22.564111 52.36866, 22.564111 52.81832, 22.564111 53.267981))</t>
+  </si>
+  <si>
     <t>elc_spv_POL_003</t>
   </si>
   <si>
+    <t>POLYGON ((15.018967 52.81832, 15.018967 53.267981, 15.018967 53.717641, 15.704889 53.717641, 15.704889 53.267981, 15.704889 52.81832, 15.704889 52.36866, 15.018967 52.36866, 14.333045 52.36866, 14.333045 52.81832, 15.018967 52.81832))</t>
+  </si>
+  <si>
     <t>elc_spv_POL_004</t>
   </si>
   <si>
+    <t>POLYGON ((15.704889 51.46934, 16.390811 51.46934, 16.390811 51.919, 17.076733 51.919, 17.076733 51.46934, 17.076733 51.01968, 16.390811 51.01968, 16.390811 50.570019, 15.704889 50.570019, 15.704889 51.01968, 15.704889 51.46934))</t>
+  </si>
+  <si>
     <t>elc_spv_POL_005</t>
   </si>
   <si>
+    <t>MULTIPOLYGON (((17.076733 51.01968, 17.762656 51.01968, 17.762656 50.570019, 17.076733 50.570019, 17.076733 51.01968)), ((17.762656 51.46934, 18.448578 51.46934, 18.448578 51.01968, 17.762656 51.01968, 17.762656 51.46934)))</t>
+  </si>
+  <si>
     <t>elc_spv_POL_006</t>
   </si>
   <si>
+    <t>POLYGON ((17.076733 49.670699, 16.390811 49.670699, 16.390811 50.120359, 15.704889 50.120359, 15.704889 50.570019, 16.390811 50.570019, 16.390811 51.01968, 17.076733 51.01968, 17.076733 50.570019, 17.076733 50.120359, 17.076733 49.670699))</t>
+  </si>
+  <si>
     <t>elc_spv_POL_007</t>
   </si>
   <si>
+    <t>POLYGON ((19.1345 53.267981, 19.1345 53.717641, 19.820422 53.717641, 19.820422 53.267981, 19.1345 53.267981))</t>
+  </si>
+  <si>
     <t>elc_spv_POL_008</t>
   </si>
   <si>
+    <t>POLYGON ((17.076733 54.167301, 17.076733 54.616961, 17.762656 54.616961, 17.762656 54.167301, 17.076733 54.167301))</t>
+  </si>
+  <si>
     <t>elc_spv_POL_009</t>
   </si>
   <si>
+    <t>POLYGON ((19.820422 54.167301, 19.820422 54.616961, 20.506344 54.616961, 21.192267 54.616961, 21.192267 54.167301, 21.192267 53.717641, 21.192267 53.267981, 20.506344 53.267981, 19.820422 53.267981, 19.820422 53.717641, 19.820422 54.167301))</t>
+  </si>
+  <si>
     <t>elc_spv_POL_010</t>
   </si>
   <si>
+    <t>POLYGON ((15.704889 50.570019, 15.018967 50.570019, 14.333045 50.570019, 14.333045 51.01968, 14.333045 51.46934, 15.018967 51.46934, 15.704889 51.46934, 15.704889 51.01968, 15.704889 50.570019))</t>
+  </si>
+  <si>
     <t>elc_spv_POL_011</t>
   </si>
   <si>
+    <t>POLYGON ((18.448578 54.167301, 18.448578 54.616961, 19.1345 54.616961, 19.820422 54.616961, 19.820422 54.167301, 19.1345 54.167301, 19.1345 53.717641, 18.448578 53.717641, 17.762656 53.717641, 17.762656 54.167301, 18.448578 54.167301))</t>
+  </si>
+  <si>
     <t>elc_spv_POL_012</t>
   </si>
   <si>
+    <t>POLYGON ((22.564111 52.36866, 21.878189 52.36866, 21.192267 52.36866, 21.192267 52.81832, 20.506344 52.81832, 20.506344 53.267981, 21.192267 53.267981, 21.192267 53.717641, 21.878189 53.717641, 21.878189 53.267981, 22.564111 53.267981, 22.564111 52.81832, 22.564111 52.36866))</t>
+  </si>
+  <si>
     <t>elc_spv_POL_013</t>
   </si>
   <si>
+    <t>POLYGON ((15.704889 51.46934, 15.018967 51.46934, 14.333045 51.46934, 14.333045 51.919, 14.333045 52.36866, 15.018967 52.36866, 15.704889 52.36866, 15.704889 51.919, 15.704889 51.46934))</t>
+  </si>
+  <si>
     <t>elc_spv_POL_014</t>
   </si>
   <si>
+    <t>POLYGON ((14.333045 53.717641, 14.333045 54.167301, 15.018967 54.167301, 15.704889 54.167301, 15.704889 53.717641, 15.018967 53.717641, 15.018967 53.267981, 14.333045 53.267981, 14.333045 53.717641))</t>
+  </si>
+  <si>
     <t>elc_spv_POL_015</t>
   </si>
   <si>
+    <t>POLYGON ((22.564111 49.670699, 23.250033 49.670699, 23.250033 49.221039, 22.564111 49.221039, 21.878189 49.221039, 21.192267 49.221039, 21.192267 49.670699, 21.192267 50.120359, 21.878189 50.120359, 21.878189 49.670699, 22.564111 49.670699))</t>
+  </si>
+  <si>
     <t>elc_spv_POL_016</t>
   </si>
   <si>
+    <t>POLYGON ((23.250033 53.717641, 22.564111 53.717641, 21.878189 53.717641, 21.878189 54.167301, 21.878189 54.616961, 22.564111 54.616961, 23.250033 54.616961, 23.935955 54.616961, 23.935955 54.167301, 23.250033 54.167301, 23.250033 53.717641))</t>
+  </si>
+  <si>
     <t>elc_spv_POL_017</t>
   </si>
   <si>
+    <t>POLYGON ((19.1345 51.46934, 19.1345 51.919, 19.820422 51.919, 20.506344 51.919, 20.506344 51.46934, 19.820422 51.46934, 19.820422 51.01968, 19.1345 51.01968, 19.1345 51.46934))</t>
+  </si>
+  <si>
     <t>elc_spv_POL_018</t>
   </si>
   <si>
+    <t>POLYGON ((18.448578 51.46934, 18.448578 51.919, 19.1345 51.919, 19.1345 51.46934, 19.1345 51.01968, 18.448578 51.01968, 18.448578 51.46934))</t>
+  </si>
+  <si>
     <t>elc_spv_POL_019</t>
   </si>
   <si>
+    <t>POLYGON ((22.564111 50.570019, 22.564111 51.01968, 23.250033 51.01968, 23.935955 51.01968, 23.935955 50.570019, 23.935955 50.120359, 23.935955 49.670699, 23.250033 49.670699, 22.564111 49.670699, 22.564111 50.120359, 22.564111 50.570019))</t>
+  </si>
+  <si>
     <t>elc_spv_POL_020</t>
   </si>
   <si>
+    <t>POLYGON ((15.704889 54.167301, 15.704889 54.616961, 16.390811 54.616961, 16.390811 54.167301, 17.076733 54.167301, 17.762656 54.167301, 17.762656 53.717641, 17.076733 53.717641, 17.076733 53.267981, 16.390811 53.267981, 15.704889 53.267981, 15.704889 53.717641, 15.704889 54.167301))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_021</t>
+  </si>
+  <si>
+    <t>POLYGON ((15.704889 51.919, 15.704889 52.36866, 16.390811 52.36866, 16.390811 51.919, 16.390811 51.46934, 15.704889 51.46934, 15.704889 51.919))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_022</t>
+  </si>
+  <si>
+    <t>POLYGON ((18.448578 49.670699, 18.448578 50.120359, 19.1345 50.120359, 19.1345 49.670699, 18.448578 49.670699))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_023</t>
+  </si>
+  <si>
+    <t>POLYGON ((20.506344 49.670699, 20.506344 50.120359, 20.506344 50.570019, 21.192267 50.570019, 21.192267 50.120359, 21.192267 49.670699, 21.192267 49.221039, 20.506344 49.221039, 20.506344 49.670699))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_024</t>
+  </si>
+  <si>
+    <t>POLYGON ((23.935955 51.01968, 23.250033 51.01968, 22.564111 51.01968, 22.564111 51.46934, 22.564111 51.919, 23.250033 51.919, 23.250033 52.36866, 23.935955 52.36866, 23.935955 51.919, 23.935955 51.46934, 23.935955 51.01968))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_025</t>
+  </si>
+  <si>
+    <t>POLYGON ((21.878189 49.670699, 21.878189 50.120359, 22.564111 50.120359, 22.564111 49.670699, 21.878189 49.670699))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_026</t>
+  </si>
+  <si>
+    <t>POLYGON ((21.192267 50.570019, 20.506344 50.570019, 19.820422 50.570019, 19.820422 51.01968, 19.820422 51.46934, 20.506344 51.46934, 21.192267 51.46934, 21.192267 51.01968, 21.192267 50.570019))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_027</t>
+  </si>
+  <si>
+    <t>POLYGON ((21.192267 50.120359, 21.192267 50.570019, 21.878189 50.570019, 21.878189 50.120359, 21.192267 50.120359))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_028</t>
+  </si>
+  <si>
+    <t>POLYGON ((21.878189 50.570019, 21.878189 51.01968, 22.564111 51.01968, 22.564111 50.570019, 22.564111 50.120359, 21.878189 50.120359, 21.878189 50.570019))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_029</t>
+  </si>
+  <si>
+    <t>POLYGON ((18.448578 51.01968, 19.1345 51.01968, 19.820422 51.01968, 19.820422 50.570019, 19.1345 50.570019, 18.448578 50.570019, 18.448578 51.01968))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_030</t>
+  </si>
+  <si>
+    <t>POLYGON ((18.448578 52.81832, 18.448578 53.267981, 19.1345 53.267981, 19.1345 52.81832, 19.1345 52.36866, 18.448578 52.36866, 18.448578 52.81832))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_031</t>
+  </si>
+  <si>
+    <t>POLYGON ((21.192267 51.01968, 21.192267 51.46934, 21.878189 51.46934, 21.878189 51.01968, 21.878189 50.570019, 21.192267 50.570019, 21.192267 51.01968))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_032</t>
+  </si>
+  <si>
+    <t>POLYGON ((17.076733 50.120359, 17.076733 50.570019, 17.762656 50.570019, 17.762656 50.120359, 17.076733 50.120359))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_033</t>
+  </si>
+  <si>
+    <t>POLYGON ((17.762656 52.36866, 17.762656 52.81832, 18.448578 52.81832, 18.448578 52.36866, 19.1345 52.36866, 19.1345 51.919, 18.448578 51.919, 18.448578 51.46934, 17.762656 51.46934, 17.762656 51.919, 17.762656 52.36866))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_034</t>
+  </si>
+  <si>
+    <t>POLYGON ((16.390811 54.167301, 16.390811 54.616961, 17.076733 54.616961, 17.076733 54.167301, 16.390811 54.167301))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_035</t>
+  </si>
+  <si>
+    <t>POLYGON ((20.506344 52.36866, 20.506344 52.81832, 21.192267 52.81832, 21.192267 52.36866, 21.878189 52.36866, 21.878189 51.919, 21.192267 51.919, 21.192267 51.46934, 20.506344 51.46934, 20.506344 51.919, 20.506344 52.36866))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_036</t>
+  </si>
+  <si>
+    <t>POLYGON ((18.448578 50.120359, 18.448578 50.570019, 19.1345 50.570019, 19.1345 50.120359, 18.448578 50.120359))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_037</t>
+  </si>
+  <si>
+    <t>MULTIPOLYGON (((21.878189 53.717641, 22.564111 53.717641, 22.564111 53.267981, 21.878189 53.267981, 21.878189 53.717641)), ((21.192267 54.616961, 21.878189 54.616961, 21.878189 54.167301, 21.878189 53.717641, 21.192267 53.717641, 21.192267 54.167301, 21.192267 54.616961)))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_038</t>
+  </si>
+  <si>
+    <t>POLYGON ((17.762656 51.919, 17.076733 51.919, 16.390811 51.919, 16.390811 52.36866, 15.704889 52.36866, 15.704889 52.81832, 15.704889 53.267981, 16.390811 53.267981, 17.076733 53.267981, 17.076733 52.81832, 17.762656 52.81832, 17.762656 52.36866, 17.762656 51.919))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_039</t>
+  </si>
+  <si>
+    <t>POLYGON ((17.762656 50.120359, 17.762656 50.570019, 17.762656 51.01968, 18.448578 51.01968, 18.448578 50.570019, 18.448578 50.120359, 18.448578 49.670699, 17.762656 49.670699, 17.076733 49.670699, 17.076733 50.120359, 17.762656 50.120359))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_040</t>
+  </si>
+  <si>
+    <t>POLYGON ((14.333045 52.81832, 14.333045 53.267981, 15.018967 53.267981, 15.018967 52.81832, 14.333045 52.81832))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_041</t>
+  </si>
+  <si>
+    <t>POLYGON ((19.1345 50.120359, 19.1345 50.570019, 19.820422 50.570019, 19.820422 50.120359, 19.1345 50.120359))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_042</t>
+  </si>
+  <si>
+    <t>POLYGON ((18.448578 49.670699, 19.1345 49.670699, 19.1345 50.120359, 19.820422 50.120359, 19.820422 49.670699, 19.820422 49.221039, 19.1345 49.221039, 18.448578 49.221039, 18.448578 49.670699))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_043</t>
+  </si>
+  <si>
+    <t>MULTIPOLYGON (((18.448578 53.717641, 19.1345 53.717641, 19.1345 53.267981, 18.448578 53.267981, 18.448578 53.717641)), ((19.1345 54.167301, 19.820422 54.167301, 19.820422 53.717641, 19.1345 53.717641, 19.1345 54.167301)))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_044</t>
+  </si>
+  <si>
+    <t>POLYGON ((19.1345 52.81832, 19.1345 53.267981, 19.820422 53.267981, 20.506344 53.267981, 20.506344 52.81832, 20.506344 52.36866, 20.506344 51.919, 19.820422 51.919, 19.1345 51.919, 19.1345 52.36866, 19.1345 52.81832))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_045</t>
+  </si>
+  <si>
+    <t>POLYGON ((17.076733 51.46934, 17.076733 51.919, 17.762656 51.919, 17.762656 51.46934, 17.762656 51.01968, 17.076733 51.01968, 17.076733 51.46934))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_046</t>
+  </si>
+  <si>
+    <t>POLYGON ((17.762656 54.167301, 17.762656 54.616961, 18.448578 54.616961, 18.448578 54.167301, 17.762656 54.167301))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_047</t>
+  </si>
+  <si>
+    <t>POLYGON ((19.820422 49.670699, 19.820422 50.120359, 19.820422 50.570019, 20.506344 50.570019, 20.506344 50.120359, 20.506344 49.670699, 20.506344 49.221039, 19.820422 49.221039, 19.820422 49.670699))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_048</t>
+  </si>
+  <si>
+    <t>POLYGON ((22.564111 51.01968, 21.878189 51.01968, 21.878189 51.46934, 21.192267 51.46934, 21.192267 51.919, 21.878189 51.919, 21.878189 52.36866, 22.564111 52.36866, 22.564111 51.919, 22.564111 51.46934, 22.564111 51.01968))</t>
+  </si>
+  <si>
     <t>elc_wof_POL_001</t>
   </si>
   <si>
+    <t>POLYGON ((18.448578 54.485273, 19.1345 54.485273, 19.820422 54.485273, 19.820422 54.035613, 19.1345 54.035613, 18.448578 54.035613, 18.448578 54.485273))</t>
+  </si>
+  <si>
     <t>elc_wof_POL_002</t>
   </si>
   <si>
+    <t>POLYGON ((18.448578 54.934934, 19.1345 54.934934, 19.1345 55.384594, 19.820422 55.384594, 19.820422 54.934934, 19.820422 54.485273, 19.1345 54.485273, 18.448578 54.485273, 18.448578 54.934934))</t>
+  </si>
+  <si>
     <t>elc_wof_POL_003</t>
   </si>
   <si>
+    <t>POLYGON ((14.333045 54.934934, 15.018967 54.934934, 15.704889 54.934934, 15.704889 54.485273, 15.018967 54.485273, 14.333045 54.485273, 14.333045 54.934934))</t>
+  </si>
+  <si>
     <t>elc_wof_POL_004</t>
   </si>
   <si>
+    <t>POLYGON ((15.018967 54.035613, 15.018967 54.485273, 15.704889 54.485273, 15.704889 54.035613, 15.018967 54.035613))</t>
+  </si>
+  <si>
     <t>elc_wof_POL_005</t>
   </si>
   <si>
+    <t>POLYGON ((15.704889 54.035613, 15.704889 54.485273, 16.390811 54.485273, 16.390811 54.035613, 15.704889 54.035613))</t>
+  </si>
+  <si>
     <t>elc_wof_POL_006</t>
   </si>
   <si>
+    <t>POLYGON ((15.704889 55.384594, 16.390811 55.384594, 16.390811 55.834254, 17.076733 55.834254, 17.076733 55.384594, 17.076733 54.934934, 16.390811 54.934934, 15.704889 54.934934, 15.704889 55.384594))</t>
+  </si>
+  <si>
     <t>elc_wof_POL_007</t>
   </si>
   <si>
+    <t>POLYGON ((15.704889 54.485273, 15.704889 54.934934, 16.390811 54.934934, 16.390811 54.485273, 15.704889 54.485273))</t>
+  </si>
+  <si>
     <t>elc_wof_POL_008</t>
   </si>
   <si>
+    <t>POLYGON ((17.076733 55.384594, 17.076733 55.834254, 17.762656 55.834254, 17.762656 55.384594, 17.762656 54.934934, 17.076733 54.934934, 17.076733 55.384594))</t>
+  </si>
+  <si>
     <t>elc_wof_POL_009</t>
   </si>
   <si>
+    <t>POLYGON ((17.762656 55.834254, 18.448578 55.834254, 19.1345 55.834254, 19.1345 55.384594, 18.448578 55.384594, 17.762656 55.384594, 17.762656 55.834254))</t>
+  </si>
+  <si>
     <t>elc_wof_POL_010</t>
   </si>
   <si>
+    <t>POLYGON ((17.762656 55.384594, 18.448578 55.384594, 19.1345 55.384594, 19.1345 54.934934, 18.448578 54.934934, 17.762656 54.934934, 17.762656 55.384594))</t>
+  </si>
+  <si>
     <t>elc_won_POL_001</t>
   </si>
   <si>
@@ -895,6 +1159,93 @@
   </si>
   <si>
     <t>elc_won_POL_019</t>
+  </si>
+  <si>
+    <t>elc_won_POL_020</t>
+  </si>
+  <si>
+    <t>elc_won_POL_021</t>
+  </si>
+  <si>
+    <t>elc_won_POL_022</t>
+  </si>
+  <si>
+    <t>elc_won_POL_023</t>
+  </si>
+  <si>
+    <t>elc_won_POL_024</t>
+  </si>
+  <si>
+    <t>elc_won_POL_025</t>
+  </si>
+  <si>
+    <t>elc_won_POL_026</t>
+  </si>
+  <si>
+    <t>elc_won_POL_027</t>
+  </si>
+  <si>
+    <t>elc_won_POL_028</t>
+  </si>
+  <si>
+    <t>elc_won_POL_029</t>
+  </si>
+  <si>
+    <t>elc_won_POL_030</t>
+  </si>
+  <si>
+    <t>elc_won_POL_031</t>
+  </si>
+  <si>
+    <t>elc_won_POL_032</t>
+  </si>
+  <si>
+    <t>elc_won_POL_033</t>
+  </si>
+  <si>
+    <t>elc_won_POL_034</t>
+  </si>
+  <si>
+    <t>elc_won_POL_035</t>
+  </si>
+  <si>
+    <t>elc_won_POL_036</t>
+  </si>
+  <si>
+    <t>elc_won_POL_037</t>
+  </si>
+  <si>
+    <t>elc_won_POL_038</t>
+  </si>
+  <si>
+    <t>elc_won_POL_039</t>
+  </si>
+  <si>
+    <t>elc_won_POL_040</t>
+  </si>
+  <si>
+    <t>elc_won_POL_041</t>
+  </si>
+  <si>
+    <t>elc_won_POL_042</t>
+  </si>
+  <si>
+    <t>elc_won_POL_043</t>
+  </si>
+  <si>
+    <t>elc_won_POL_044</t>
+  </si>
+  <si>
+    <t>elc_won_POL_045</t>
+  </si>
+  <si>
+    <t>elc_won_POL_046</t>
+  </si>
+  <si>
+    <t>elc_won_POL_047</t>
+  </si>
+  <si>
+    <t>elc_won_POL_048</t>
   </si>
   <si>
     <t>co2</t>
@@ -1493,7 +1844,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1548,39 +1899,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1632,7 +1983,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1743,13 +2094,6 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -1758,6 +2102,13 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1822,22 +2173,42 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme 2013 - 2022" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD186334-F32C-4D6A-9165-844FFA079C53}">
-  <dimension ref="B3:R101"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE1B498B-64CF-4794-BDEA-CB5C495F4AF9}">
+  <dimension ref="B3:S158"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="3" spans="2:18" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
         <v>0</v>
       </c>
@@ -1848,7 +2219,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="4" spans="2:18" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
         <v>1</v>
       </c>
@@ -1888,8 +2259,11 @@
       <c r="R4" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="S4" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="5" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
         <v>8</v>
       </c>
@@ -1930,7 +2304,7 @@
         <v>52.934591495109792</v>
       </c>
     </row>
-    <row r="6" spans="2:18" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
         <v>8</v>
       </c>
@@ -1971,7 +2345,7 @@
         <v>49.84240724566758</v>
       </c>
     </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
         <v>8</v>
       </c>
@@ -2012,7 +2386,7 @@
         <v>51.092587962369954</v>
       </c>
     </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
         <v>8</v>
       </c>
@@ -2053,7 +2427,7 @@
         <v>53.09476020715347</v>
       </c>
     </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
         <v>8</v>
       </c>
@@ -2094,7 +2468,7 @@
         <v>51.15840073090456</v>
       </c>
     </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
         <v>8</v>
       </c>
@@ -2135,7 +2509,7 @@
         <v>50.832052960395522</v>
       </c>
     </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
         <v>8</v>
       </c>
@@ -2176,7 +2550,7 @@
         <v>49.994080927127975</v>
       </c>
     </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
         <v>8</v>
       </c>
@@ -2217,7 +2591,7 @@
         <v>53.757586946292747</v>
       </c>
     </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
         <v>8</v>
       </c>
@@ -2258,7 +2632,7 @@
         <v>54.338650185173492</v>
       </c>
     </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
         <v>8</v>
       </c>
@@ -2299,7 +2673,7 @@
         <v>54.718832956325642</v>
       </c>
     </row>
-    <row r="15" spans="2:18" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
         <v>8</v>
       </c>
@@ -2340,7 +2714,7 @@
         <v>50.365380141626972</v>
       </c>
     </row>
-    <row r="16" spans="2:18" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
         <v>8</v>
       </c>
@@ -3693,7 +4067,7 @@
         <v>52.214439540966467</v>
       </c>
     </row>
-    <row r="49" spans="2:18" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B49" t="s">
         <v>8</v>
       </c>
@@ -3734,7 +4108,7 @@
         <v>52.714665383017554</v>
       </c>
     </row>
-    <row r="50" spans="2:18" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B50" t="s">
         <v>8</v>
       </c>
@@ -3775,7 +4149,7 @@
         <v>51.213751122843391</v>
       </c>
     </row>
-    <row r="51" spans="2:18" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B51" t="s">
         <v>8</v>
       </c>
@@ -3816,7 +4190,7 @@
         <v>50.716735959213132</v>
       </c>
     </row>
-    <row r="52" spans="2:18" x14ac:dyDescent="0.45">
+    <row r="52" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B52" t="s">
         <v>8</v>
       </c>
@@ -3857,7 +4231,7 @@
         <v>51.988382273984612</v>
       </c>
     </row>
-    <row r="53" spans="2:18" x14ac:dyDescent="0.45">
+    <row r="53" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B53" t="s">
         <v>8</v>
       </c>
@@ -3886,19 +4260,22 @@
         <v>195</v>
       </c>
       <c r="O53" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P53" t="s">
         <v>8</v>
       </c>
       <c r="Q53">
-        <v>22.387884415840912</v>
+        <v>17.547809697404155</v>
       </c>
       <c r="R53">
-        <v>52.797852990301593</v>
-      </c>
-    </row>
-    <row r="54" spans="2:18" x14ac:dyDescent="0.45">
+        <v>53.043150454655695</v>
+      </c>
+      <c r="S53" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="54" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B54" t="s">
         <v>8</v>
       </c>
@@ -3927,19 +4304,22 @@
         <v>196</v>
       </c>
       <c r="O54" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="P54" t="s">
         <v>8</v>
       </c>
       <c r="Q54">
-        <v>22.436878727454864</v>
+        <v>23.133301060688336</v>
       </c>
       <c r="R54">
-        <v>53.758426235726397</v>
-      </c>
-    </row>
-    <row r="55" spans="2:18" x14ac:dyDescent="0.45">
+        <v>53.187251027326219</v>
+      </c>
+      <c r="S54" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="55" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B55" t="s">
         <v>8</v>
       </c>
@@ -3968,19 +4348,22 @@
         <v>197</v>
       </c>
       <c r="O55" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="P55" t="s">
         <v>8</v>
       </c>
       <c r="Q55">
-        <v>22.158862912599531</v>
+        <v>14.879031900155717</v>
       </c>
       <c r="R55">
-        <v>49.985302240943966</v>
-      </c>
-    </row>
-    <row r="56" spans="2:18" x14ac:dyDescent="0.45">
+        <v>52.593490272793417</v>
+      </c>
+      <c r="S55" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="56" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B56" t="s">
         <v>8</v>
       </c>
@@ -4009,19 +4392,22 @@
         <v>198</v>
       </c>
       <c r="O56" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="P56" t="s">
         <v>8</v>
       </c>
       <c r="Q56">
-        <v>20.576363415677669</v>
+        <v>16.047850156734548</v>
       </c>
       <c r="R56">
-        <v>50.179698397399775</v>
-      </c>
-    </row>
-    <row r="57" spans="2:18" x14ac:dyDescent="0.45">
+        <v>50.794849545344334</v>
+      </c>
+      <c r="S56" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="57" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B57" t="s">
         <v>8</v>
       </c>
@@ -4050,19 +4436,22 @@
         <v>199</v>
       </c>
       <c r="O57" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="P57" t="s">
         <v>8</v>
       </c>
       <c r="Q57">
-        <v>22.647999312422595</v>
+        <v>17.419694531519191</v>
       </c>
       <c r="R57">
-        <v>51.755872298670091</v>
-      </c>
-    </row>
-    <row r="58" spans="2:18" x14ac:dyDescent="0.45">
+        <v>50.794849545344334</v>
+      </c>
+      <c r="S57" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="58" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B58" t="s">
         <v>8</v>
       </c>
@@ -4091,19 +4480,22 @@
         <v>200</v>
       </c>
       <c r="O58" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="P58" t="s">
         <v>8</v>
       </c>
       <c r="Q58">
-        <v>22.614693947996503</v>
+        <v>16.700680826967581</v>
       </c>
       <c r="R58">
-        <v>50.677937554331706</v>
-      </c>
-    </row>
-    <row r="59" spans="2:18" x14ac:dyDescent="0.45">
+        <v>50.20437696578923</v>
+      </c>
+      <c r="S58" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="59" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B59" t="s">
         <v>8</v>
       </c>
@@ -4132,19 +4524,22 @@
         <v>201</v>
       </c>
       <c r="O59" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="P59" t="s">
         <v>8</v>
       </c>
       <c r="Q59">
-        <v>15.177025576701782</v>
+        <v>19.477461093696157</v>
       </c>
       <c r="R59">
-        <v>53.385570698209328</v>
-      </c>
-    </row>
-    <row r="60" spans="2:18" x14ac:dyDescent="0.45">
+        <v>53.492810636517952</v>
+      </c>
+      <c r="S59" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="60" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B60" t="s">
         <v>8</v>
       </c>
@@ -4173,19 +4568,22 @@
         <v>202</v>
       </c>
       <c r="O60" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="P60" t="s">
         <v>8</v>
       </c>
       <c r="Q60">
-        <v>16.851528118709499</v>
+        <v>17.419694531519191</v>
       </c>
       <c r="R60">
-        <v>53.556913702673697</v>
-      </c>
-    </row>
-    <row r="61" spans="2:18" x14ac:dyDescent="0.45">
+        <v>54.3921310002425</v>
+      </c>
+      <c r="S60" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="61" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B61" t="s">
         <v>8</v>
       </c>
@@ -4214,19 +4612,22 @@
         <v>203</v>
       </c>
       <c r="O61" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="P61" t="s">
         <v>8</v>
       </c>
       <c r="Q61">
-        <v>18.833039725101798</v>
+        <v>20.701782962343</v>
       </c>
       <c r="R61">
-        <v>52.848472544632912</v>
-      </c>
-    </row>
-    <row r="62" spans="2:18" x14ac:dyDescent="0.45">
+        <v>54.18832903488137</v>
+      </c>
+      <c r="S61" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="62" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B62" t="s">
         <v>8</v>
       </c>
@@ -4255,19 +4656,22 @@
         <v>204</v>
       </c>
       <c r="O62" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="P62" t="s">
         <v>8</v>
       </c>
       <c r="Q62">
-        <v>20.474987843539957</v>
+        <v>15.361927969342226</v>
       </c>
       <c r="R62">
-        <v>53.867432812752376</v>
-      </c>
-    </row>
-    <row r="63" spans="2:18" x14ac:dyDescent="0.45">
+        <v>50.794849545344334</v>
+      </c>
+      <c r="S62" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="63" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B63" t="s">
         <v>8</v>
       </c>
@@ -4296,19 +4700,22 @@
         <v>205</v>
       </c>
       <c r="O63" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="P63" t="s">
         <v>8</v>
       </c>
       <c r="Q63">
-        <v>18.950202712790809</v>
+        <v>18.782950053433741</v>
       </c>
       <c r="R63">
-        <v>53.834708755581374</v>
-      </c>
-    </row>
-    <row r="64" spans="2:18" x14ac:dyDescent="0.45">
+        <v>53.942470818380237</v>
+      </c>
+      <c r="S63" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="64" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B64" t="s">
         <v>8</v>
       </c>
@@ -4337,19 +4744,22 @@
         <v>206</v>
       </c>
       <c r="O64" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="P64" t="s">
         <v>8</v>
       </c>
       <c r="Q64">
-        <v>16.541594041004011</v>
+        <v>21.887953266623537</v>
       </c>
       <c r="R64">
-        <v>52.292582195464313</v>
-      </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.45">
+        <v>53.014105550648793</v>
+      </c>
+      <c r="S64" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B65" t="s">
         <v>8</v>
       </c>
@@ -4378,19 +4788,22 @@
         <v>207</v>
       </c>
       <c r="O65" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="P65" t="s">
         <v>8</v>
       </c>
       <c r="Q65">
-        <v>16.597184145059202</v>
+        <v>14.875712340153196</v>
       </c>
       <c r="R65">
-        <v>51.381036311175727</v>
-      </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.45">
+        <v>51.892398915433461</v>
+      </c>
+      <c r="S65" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B66" t="s">
         <v>8</v>
       </c>
@@ -4419,19 +4832,22 @@
         <v>208</v>
       </c>
       <c r="O66" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="P66" t="s">
         <v>8</v>
       </c>
       <c r="Q66">
-        <v>15.346251681111026</v>
+        <v>14.904646511080676</v>
       </c>
       <c r="R66">
-        <v>51.202873879217471</v>
-      </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.45">
+        <v>53.792584091092806</v>
+      </c>
+      <c r="S66" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B67" t="s">
         <v>8</v>
       </c>
@@ -4460,19 +4876,22 @@
         <v>209</v>
       </c>
       <c r="O67" t="s">
-        <v>251</v>
+        <v>266</v>
       </c>
       <c r="P67" t="s">
         <v>8</v>
       </c>
       <c r="Q67">
-        <v>15.145356416678331</v>
+        <v>22.221149843265444</v>
       </c>
       <c r="R67">
-        <v>52.186880964694659</v>
-      </c>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.45">
+        <v>49.445868999757522</v>
+      </c>
+      <c r="S67" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B68" t="s">
         <v>8</v>
       </c>
@@ -4501,19 +4920,22 @@
         <v>210</v>
       </c>
       <c r="O68" t="s">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="P68" t="s">
         <v>8</v>
       </c>
       <c r="Q68">
-        <v>17.083147938913381</v>
+        <v>22.603515833460445</v>
       </c>
       <c r="R68">
-        <v>50.673345049899048</v>
-      </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.45">
+        <v>54.312064653523798</v>
+      </c>
+      <c r="S68" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B69" t="s">
         <v>8</v>
       </c>
@@ -4542,19 +4964,22 @@
         <v>211</v>
       </c>
       <c r="O69" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
       <c r="P69" t="s">
         <v>8</v>
       </c>
       <c r="Q69">
-        <v>18.911500370089843</v>
+        <v>19.477461093696157</v>
       </c>
       <c r="R69">
-        <v>50.08331213626267</v>
-      </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.45">
+        <v>51.244509727206612</v>
+      </c>
+      <c r="S69" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B70" t="s">
         <v>8</v>
       </c>
@@ -4583,19 +5008,22 @@
         <v>212</v>
       </c>
       <c r="O70" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="P70" t="s">
         <v>8</v>
       </c>
       <c r="Q70">
-        <v>20.781405442235567</v>
+        <v>18.791538906303831</v>
       </c>
       <c r="R70">
-        <v>52.366491870473581</v>
-      </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.45">
+        <v>51.690437204601821</v>
+      </c>
+      <c r="S70" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B71" t="s">
         <v>8</v>
       </c>
@@ -4624,19 +5052,22 @@
         <v>213</v>
       </c>
       <c r="O71" t="s">
-        <v>255</v>
+        <v>274</v>
       </c>
       <c r="P71" t="s">
         <v>8</v>
       </c>
       <c r="Q71">
-        <v>20.402957702269411</v>
+        <v>23.592994218050087</v>
       </c>
       <c r="R71">
-        <v>51.12109494883768</v>
-      </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.45">
+        <v>50.345189363482064</v>
+      </c>
+      <c r="S71" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B72" t="s">
         <v>8</v>
       </c>
@@ -4665,19 +5096,22 @@
         <v>214</v>
       </c>
       <c r="O72" t="s">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="P72" t="s">
         <v>8</v>
       </c>
       <c r="Q72">
-        <v>18.792464723500991</v>
+        <v>16.349304708128344</v>
       </c>
       <c r="R72">
-        <v>51.330784626906521</v>
-      </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.45">
+        <v>53.94247081838023</v>
+      </c>
+      <c r="S72" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B73" t="s">
         <v>8</v>
       </c>
@@ -4706,19 +5140,22 @@
         <v>215</v>
       </c>
       <c r="O73" t="s">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="P73" t="s">
         <v>8</v>
       </c>
       <c r="Q73">
-        <v>19.270410803611803</v>
+        <v>16.047850156734548</v>
       </c>
       <c r="R73">
-        <v>54.260516439232255</v>
-      </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.45">
+        <v>51.919000000000011</v>
+      </c>
+      <c r="S73" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B74" t="s">
         <v>8</v>
       </c>
@@ -4747,19 +5184,22 @@
         <v>216</v>
       </c>
       <c r="O74" t="s">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="P74" t="s">
         <v>8</v>
       </c>
       <c r="Q74">
-        <v>19.132199145306835</v>
+        <v>18.791538906303831</v>
       </c>
       <c r="R74">
-        <v>55.159813342891759</v>
-      </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.45">
+        <v>49.895529181619793</v>
+      </c>
+      <c r="S74" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B75" t="s">
         <v>8</v>
       </c>
@@ -4788,19 +5228,22 @@
         <v>217</v>
       </c>
       <c r="O75" t="s">
-        <v>259</v>
+        <v>282</v>
       </c>
       <c r="P75" t="s">
         <v>8</v>
       </c>
       <c r="Q75">
-        <v>19.209580353300481</v>
+        <v>20.8493054684808</v>
       </c>
       <c r="R75">
-        <v>54.710164987068232</v>
-      </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.45">
+        <v>49.8599303133334</v>
+      </c>
+      <c r="S75" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B76" t="s">
         <v>8</v>
       </c>
@@ -4829,19 +5272,22 @@
         <v>218</v>
       </c>
       <c r="O76" t="s">
-        <v>260</v>
+        <v>284</v>
       </c>
       <c r="P76" t="s">
         <v>8</v>
       </c>
       <c r="Q76">
-        <v>16.941376551896891</v>
+        <v>23.486875120767376</v>
       </c>
       <c r="R76">
-        <v>55.60946078087305</v>
-      </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.45">
+        <v>51.710185794668313</v>
+      </c>
+      <c r="S76" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B77" t="s">
         <v>8</v>
       </c>
@@ -4870,19 +5316,22 @@
         <v>219</v>
       </c>
       <c r="O77" t="s">
-        <v>261</v>
+        <v>286</v>
       </c>
       <c r="P77" t="s">
         <v>8</v>
       </c>
       <c r="Q77">
-        <v>18.450551982707839</v>
+        <v>22.221149843265444</v>
       </c>
       <c r="R77">
-        <v>55.609461280132123</v>
-      </c>
-    </row>
-    <row r="78" spans="2:18" x14ac:dyDescent="0.45">
+        <v>49.895529181619793</v>
+      </c>
+      <c r="S77" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="78" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B78" t="s">
         <v>8</v>
       </c>
@@ -4911,19 +5360,22 @@
         <v>220</v>
       </c>
       <c r="O78" t="s">
-        <v>262</v>
+        <v>288</v>
       </c>
       <c r="P78" t="s">
         <v>8</v>
       </c>
       <c r="Q78">
-        <v>17.878286085105412</v>
+        <v>20.164133104060543</v>
       </c>
       <c r="R78">
-        <v>55.159812876695007</v>
-      </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.45">
+        <v>51.018998941964419</v>
+      </c>
+      <c r="S78" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B79" t="s">
         <v>8</v>
       </c>
@@ -4952,19 +5404,22 @@
         <v>221</v>
       </c>
       <c r="O79" t="s">
-        <v>263</v>
+        <v>290</v>
       </c>
       <c r="P79" t="s">
         <v>8</v>
       </c>
       <c r="Q79">
-        <v>15.47382532166216</v>
+        <v>21.535227655873118</v>
       </c>
       <c r="R79">
-        <v>54.260515174922851</v>
-      </c>
-    </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.45">
+        <v>50.345189363482064</v>
+      </c>
+      <c r="S79" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="80" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B80" t="s">
         <v>8</v>
       </c>
@@ -4993,19 +5448,22 @@
         <v>222</v>
       </c>
       <c r="O80" t="s">
-        <v>264</v>
+        <v>292</v>
       </c>
       <c r="P80" t="s">
         <v>8</v>
       </c>
       <c r="Q80">
-        <v>15.28816677077992</v>
+        <v>22.221149843265444</v>
       </c>
       <c r="R80">
-        <v>54.710163723178738</v>
-      </c>
-    </row>
-    <row r="81" spans="2:18" x14ac:dyDescent="0.45">
+        <v>50.345189363482064</v>
+      </c>
+      <c r="S80" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="81" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B81" t="s">
         <v>8</v>
       </c>
@@ -5034,19 +5492,22 @@
         <v>223</v>
       </c>
       <c r="O81" t="s">
-        <v>265</v>
+        <v>294</v>
       </c>
       <c r="P81" t="s">
         <v>8</v>
       </c>
       <c r="Q81">
-        <v>16.268392183867956</v>
+        <v>19.477461093696157</v>
       </c>
       <c r="R81">
-        <v>55.159812379291822</v>
-      </c>
-    </row>
-    <row r="82" spans="2:18" x14ac:dyDescent="0.45">
+        <v>50.794849545344334</v>
+      </c>
+      <c r="S81" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="82" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B82" t="s">
         <v>8</v>
       </c>
@@ -5075,19 +5536,22 @@
         <v>224</v>
       </c>
       <c r="O82" t="s">
-        <v>266</v>
+        <v>296</v>
       </c>
       <c r="P82" t="s">
         <v>8</v>
       </c>
       <c r="Q82">
-        <v>16.047809605897839</v>
+        <v>18.791538906303831</v>
       </c>
       <c r="R82">
-        <v>54.710163913347117</v>
-      </c>
-    </row>
-    <row r="83" spans="2:18" x14ac:dyDescent="0.45">
+        <v>53.043150454655688</v>
+      </c>
+      <c r="S82" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="83" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B83" t="s">
         <v>8</v>
       </c>
@@ -5116,19 +5580,22 @@
         <v>225</v>
       </c>
       <c r="O83" t="s">
-        <v>267</v>
+        <v>298</v>
       </c>
       <c r="P83" t="s">
         <v>8</v>
       </c>
       <c r="Q83">
-        <v>16.384709287577795</v>
+        <v>21.535227655873118</v>
       </c>
       <c r="R83">
-        <v>50.776690615375294</v>
-      </c>
-    </row>
-    <row r="84" spans="2:18" x14ac:dyDescent="0.45">
+        <v>50.794849545344334</v>
+      </c>
+      <c r="S83" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="84" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B84" t="s">
         <v>8</v>
       </c>
@@ -5157,7 +5624,7 @@
         <v>226</v>
       </c>
       <c r="O84" t="s">
-        <v>268</v>
+        <v>300</v>
       </c>
       <c r="P84" t="s">
         <v>8</v>
@@ -5166,10 +5633,13 @@
         <v>17.419694531519191</v>
       </c>
       <c r="R84">
-        <v>49.895529181619793</v>
-      </c>
-    </row>
-    <row r="85" spans="2:18" x14ac:dyDescent="0.45">
+        <v>50.345189363482064</v>
+      </c>
+      <c r="S84" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="85" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B85" t="s">
         <v>8</v>
       </c>
@@ -5198,19 +5668,22 @@
         <v>227</v>
       </c>
       <c r="O85" t="s">
-        <v>269</v>
+        <v>302</v>
       </c>
       <c r="P85" t="s">
         <v>8</v>
       </c>
       <c r="Q85">
-        <v>15.256062905619441</v>
+        <v>18.105616718911509</v>
       </c>
       <c r="R85">
-        <v>51.98468831119169</v>
-      </c>
-    </row>
-    <row r="86" spans="2:18" x14ac:dyDescent="0.45">
+        <v>52.143830090931147</v>
+      </c>
+      <c r="S85" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="86" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B86" t="s">
         <v>8</v>
       </c>
@@ -5239,19 +5712,22 @@
         <v>228</v>
       </c>
       <c r="O86" t="s">
-        <v>270</v>
+        <v>304</v>
       </c>
       <c r="P86" t="s">
         <v>8</v>
       </c>
       <c r="Q86">
-        <v>16.80515814440529</v>
+        <v>16.733772344126869</v>
       </c>
       <c r="R86">
-        <v>52.124016263770471</v>
-      </c>
-    </row>
-    <row r="87" spans="2:18" x14ac:dyDescent="0.45">
+        <v>54.3921310002425</v>
+      </c>
+      <c r="S86" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="87" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B87" t="s">
         <v>8</v>
       </c>
@@ -5280,19 +5756,22 @@
         <v>229</v>
       </c>
       <c r="O87" t="s">
-        <v>271</v>
+        <v>306</v>
       </c>
       <c r="P87" t="s">
         <v>8</v>
       </c>
       <c r="Q87">
-        <v>19.003551538461117</v>
+        <v>21.135688356956784</v>
       </c>
       <c r="R87">
-        <v>53.788484402851722</v>
-      </c>
-    </row>
-    <row r="88" spans="2:18" x14ac:dyDescent="0.45">
+        <v>52.239739576014692</v>
+      </c>
+      <c r="S87" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="88" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B88" t="s">
         <v>8</v>
       </c>
@@ -5321,19 +5800,22 @@
         <v>230</v>
       </c>
       <c r="O88" t="s">
-        <v>272</v>
+        <v>308</v>
       </c>
       <c r="P88" t="s">
         <v>8</v>
       </c>
       <c r="Q88">
-        <v>15.172985574189886</v>
+        <v>18.791538906303831</v>
       </c>
       <c r="R88">
-        <v>53.270513397783269</v>
-      </c>
-    </row>
-    <row r="89" spans="2:18" x14ac:dyDescent="0.45">
+        <v>50.345189363482064</v>
+      </c>
+      <c r="S88" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="89" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B89" t="s">
         <v>8</v>
       </c>
@@ -5362,184 +5844,1192 @@
         <v>231</v>
       </c>
       <c r="O89" t="s">
+        <v>310</v>
+      </c>
+      <c r="P89" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q89">
+        <v>21.708559845867718</v>
+      </c>
+      <c r="R89">
+        <v>54.126240919490058</v>
+      </c>
+      <c r="S89" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="90" spans="2:19" x14ac:dyDescent="0.45">
+      <c r="O90" t="s">
+        <v>312</v>
+      </c>
+      <c r="P90" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q90">
+        <v>16.559716621285517</v>
+      </c>
+      <c r="R90">
+        <v>53.043150454655688</v>
+      </c>
+      <c r="S90" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="91" spans="2:19" x14ac:dyDescent="0.45">
+      <c r="O91" t="s">
+        <v>314</v>
+      </c>
+      <c r="P91" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q91">
+        <v>18.105616718911509</v>
+      </c>
+      <c r="R91">
+        <v>50.345189363482064</v>
+      </c>
+      <c r="S91" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="92" spans="2:19" x14ac:dyDescent="0.45">
+      <c r="O92" t="s">
+        <v>316</v>
+      </c>
+      <c r="P92" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q92">
+        <v>14.676005781949902</v>
+      </c>
+      <c r="R92">
+        <v>53.043150454655688</v>
+      </c>
+      <c r="S92" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="93" spans="2:19" x14ac:dyDescent="0.45">
+      <c r="O93" t="s">
+        <v>318</v>
+      </c>
+      <c r="P93" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q93">
+        <v>19.477461093696157</v>
+      </c>
+      <c r="R93">
+        <v>50.345189363482064</v>
+      </c>
+      <c r="S93" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="94" spans="2:19" x14ac:dyDescent="0.45">
+      <c r="O94" t="s">
+        <v>320</v>
+      </c>
+      <c r="P94" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q94">
+        <v>19.439611648373191</v>
+      </c>
+      <c r="R94">
+        <v>49.720309400782064</v>
+      </c>
+      <c r="S94" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="95" spans="2:19" x14ac:dyDescent="0.45">
+      <c r="O95" t="s">
+        <v>322</v>
+      </c>
+      <c r="P95" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q95">
+        <v>19.477461093696157</v>
+      </c>
+      <c r="R95">
+        <v>53.942470818380237</v>
+      </c>
+      <c r="S95" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="96" spans="2:19" x14ac:dyDescent="0.45">
+      <c r="O96" t="s">
+        <v>324</v>
+      </c>
+      <c r="P96" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q96">
+        <v>19.477461093696157</v>
+      </c>
+      <c r="R96">
+        <v>52.593490272793417</v>
+      </c>
+      <c r="S96" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="97" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O97" t="s">
+        <v>326</v>
+      </c>
+      <c r="P97" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q97">
+        <v>17.419694531519191</v>
+      </c>
+      <c r="R97">
+        <v>51.244509727206605</v>
+      </c>
+      <c r="S97" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="98" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O98" t="s">
+        <v>328</v>
+      </c>
+      <c r="P98" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q98">
+        <v>18.105616718911509</v>
+      </c>
+      <c r="R98">
+        <v>54.3921310002425</v>
+      </c>
+      <c r="S98" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="99" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O99" t="s">
+        <v>330</v>
+      </c>
+      <c r="P99" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q99">
+        <v>20.163383281088475</v>
+      </c>
+      <c r="R99">
+        <v>49.598802215787757</v>
+      </c>
+      <c r="S99" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="100" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O100" t="s">
+        <v>332</v>
+      </c>
+      <c r="P100" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q100">
+        <v>22.178267215011683</v>
+      </c>
+      <c r="R100">
+        <v>51.90882588090858</v>
+      </c>
+      <c r="S100" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="101" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O101" t="s">
+        <v>334</v>
+      </c>
+      <c r="P101" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q101">
+        <v>19.270410803611803</v>
+      </c>
+      <c r="R101">
+        <v>54.260516439232255</v>
+      </c>
+      <c r="S101" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="102" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O102" t="s">
+        <v>336</v>
+      </c>
+      <c r="P102" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q102">
+        <v>19.336482428831868</v>
+      </c>
+      <c r="R102">
+        <v>54.923226170318472</v>
+      </c>
+      <c r="S102" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="103" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O103" t="s">
+        <v>338</v>
+      </c>
+      <c r="P103" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q103">
+        <v>15.28816677077992</v>
+      </c>
+      <c r="R103">
+        <v>54.710163723178738</v>
+      </c>
+      <c r="S103" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="104" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O104" t="s">
+        <v>340</v>
+      </c>
+      <c r="P104" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q104">
+        <v>15.361892353269836</v>
+      </c>
+      <c r="R104">
+        <v>54.26051514610343</v>
+      </c>
+      <c r="S104" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="105" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O105" t="s">
+        <v>342</v>
+      </c>
+      <c r="P105" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q105">
+        <v>16.047809989056592</v>
+      </c>
+      <c r="R105">
+        <v>54.260515322706873</v>
+      </c>
+      <c r="S105" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="106" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O106" t="s">
+        <v>344</v>
+      </c>
+      <c r="P106" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q106">
+        <v>16.360336631261571</v>
+      </c>
+      <c r="R106">
+        <v>55.248657504176741</v>
+      </c>
+      <c r="S106" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="107" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O107" t="s">
+        <v>346</v>
+      </c>
+      <c r="P107" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q107">
+        <v>16.047809605897839</v>
+      </c>
+      <c r="R107">
+        <v>54.710163913347117</v>
+      </c>
+      <c r="S107" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="108" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O108" t="s">
+        <v>348</v>
+      </c>
+      <c r="P108" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q108">
+        <v>17.419644121917074</v>
+      </c>
+      <c r="R108">
+        <v>55.329041014058205</v>
+      </c>
+      <c r="S108" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="109" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O109" t="s">
+        <v>350</v>
+      </c>
+      <c r="P109" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q109">
+        <v>18.450551982707839</v>
+      </c>
+      <c r="R109">
+        <v>55.609461280132123</v>
+      </c>
+      <c r="S109" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="110" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O110" t="s">
+        <v>352</v>
+      </c>
+      <c r="P110" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q110">
+        <v>18.559290016941631</v>
+      </c>
+      <c r="R110">
+        <v>55.159813121219983</v>
+      </c>
+      <c r="S110" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="111" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O111" t="s">
+        <v>354</v>
+      </c>
+      <c r="P111" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q111">
+        <v>17.527280239724924</v>
+      </c>
+      <c r="R111">
+        <v>53.043150454655688</v>
+      </c>
+      <c r="S111" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="112" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O112" t="s">
+        <v>355</v>
+      </c>
+      <c r="P112" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q112">
+        <v>23.129035583947079</v>
+      </c>
+      <c r="R112">
+        <v>53.220134909443168</v>
+      </c>
+      <c r="S112" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="113" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O113" t="s">
+        <v>356</v>
+      </c>
+      <c r="P113" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q113">
+        <v>15.16673080647341</v>
+      </c>
+      <c r="R113">
+        <v>52.645003231161056</v>
+      </c>
+      <c r="S113" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="114" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O114" t="s">
+        <v>357</v>
+      </c>
+      <c r="P114" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q114">
+        <v>16.109615043411317</v>
+      </c>
+      <c r="R114">
+        <v>50.927035346571493</v>
+      </c>
+      <c r="S114" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="115" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O115" t="s">
+        <v>358</v>
+      </c>
+      <c r="P115" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q115">
+        <v>17.419694531519191</v>
+      </c>
+      <c r="R115">
+        <v>50.794849545344334</v>
+      </c>
+      <c r="S115" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="116" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O116" t="s">
+        <v>359</v>
+      </c>
+      <c r="P116" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q116">
+        <v>16.658975418762132</v>
+      </c>
+      <c r="R116">
+        <v>50.279268599866718</v>
+      </c>
+      <c r="S116" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="117" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O117" t="s">
+        <v>360</v>
+      </c>
+      <c r="P117" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q117">
+        <v>19.477461093696157</v>
+      </c>
+      <c r="R117">
+        <v>53.492810636517952</v>
+      </c>
+      <c r="S117" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="118" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O118" t="s">
+        <v>361</v>
+      </c>
+      <c r="P118" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q118">
+        <v>17.419694531519191</v>
+      </c>
+      <c r="R118">
+        <v>54.3921310002425</v>
+      </c>
+      <c r="S118" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="119" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O119" t="s">
+        <v>362</v>
+      </c>
+      <c r="P119" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q119">
+        <v>20.6609465803446</v>
+      </c>
+      <c r="R119">
+        <v>54.215908666282239</v>
+      </c>
+      <c r="S119" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="120" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O120" t="s">
+        <v>363</v>
+      </c>
+      <c r="P120" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q120">
+        <v>15.361927969342226</v>
+      </c>
+      <c r="R120">
+        <v>50.794849545344334</v>
+      </c>
+      <c r="S120" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="121" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O121" t="s">
+        <v>364</v>
+      </c>
+      <c r="P121" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q121">
+        <v>18.791538906303831</v>
+      </c>
+      <c r="R121">
+        <v>53.942470818380237</v>
+      </c>
+      <c r="S121" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="122" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O122" t="s">
+        <v>365</v>
+      </c>
+      <c r="P122" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q122">
+        <v>21.814778267800516</v>
+      </c>
+      <c r="R122">
+        <v>53.031656729647359</v>
+      </c>
+      <c r="S122" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="123" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O123" t="s">
+        <v>366</v>
+      </c>
+      <c r="P123" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q123">
+        <v>14.819703456589529</v>
+      </c>
+      <c r="R123">
+        <v>51.922744864982697</v>
+      </c>
+      <c r="S123" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="124" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O124" t="s">
+        <v>367</v>
+      </c>
+      <c r="P124" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q124">
+        <v>14.904646511080676</v>
+      </c>
+      <c r="R124">
+        <v>53.792584091092806</v>
+      </c>
+      <c r="S124" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="125" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O125" t="s">
+        <v>368</v>
+      </c>
+      <c r="P125" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q125">
+        <v>22.608798223120601</v>
+      </c>
+      <c r="R125">
+        <v>49.490542406443481</v>
+      </c>
+      <c r="S125" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="126" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O126" t="s">
+        <v>369</v>
+      </c>
+      <c r="P126" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q126">
+        <v>22.581041961268149</v>
+      </c>
+      <c r="R126">
+        <v>54.334057528005133</v>
+      </c>
+      <c r="S126" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="127" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O127" t="s">
+        <v>370</v>
+      </c>
+      <c r="P127" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q127">
+        <v>19.484239146008623</v>
+      </c>
+      <c r="R127">
+        <v>51.248953117858669</v>
+      </c>
+      <c r="S127" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="128" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O128" t="s">
+        <v>371</v>
+      </c>
+      <c r="P128" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q128">
+        <v>18.791538906303831</v>
+      </c>
+      <c r="R128">
+        <v>51.694169909068883</v>
+      </c>
+      <c r="S128" t="s">
         <v>273</v>
       </c>
-      <c r="P89" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q89">
-        <v>17.551521574400923</v>
-      </c>
-      <c r="R89">
-        <v>54.392131000242507</v>
-      </c>
-    </row>
-    <row r="90" spans="2:18" x14ac:dyDescent="0.45">
-      <c r="O90" t="s">
-        <v>274</v>
-      </c>
-      <c r="P90" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q90">
-        <v>16.852061394622268</v>
-      </c>
-      <c r="R90">
-        <v>53.40601844225278</v>
-      </c>
-    </row>
-    <row r="91" spans="2:18" x14ac:dyDescent="0.45">
-      <c r="O91" t="s">
+    </row>
+    <row r="129" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O129" t="s">
+        <v>372</v>
+      </c>
+      <c r="P129" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q129">
+        <v>23.592994218050087</v>
+      </c>
+      <c r="R129">
+        <v>50.345189363482064</v>
+      </c>
+      <c r="S129" t="s">
         <v>275</v>
       </c>
-      <c r="P91" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q91">
-        <v>22.728951916805229</v>
-      </c>
-      <c r="R91">
-        <v>53.629053884575626</v>
-      </c>
-    </row>
-    <row r="92" spans="2:18" x14ac:dyDescent="0.45">
-      <c r="O92" t="s">
-        <v>276</v>
-      </c>
-      <c r="P92" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q92">
-        <v>21.016862912105651</v>
-      </c>
-      <c r="R92">
-        <v>54.067358273794383</v>
-      </c>
-    </row>
-    <row r="93" spans="2:18" x14ac:dyDescent="0.45">
-      <c r="O93" t="s">
+    </row>
+    <row r="130" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O130" t="s">
+        <v>373</v>
+      </c>
+      <c r="P130" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q130">
+        <v>16.171652634518797</v>
+      </c>
+      <c r="R130">
+        <v>53.832005977672566</v>
+      </c>
+      <c r="S130" t="s">
         <v>277</v>
       </c>
-      <c r="P93" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q93">
-        <v>22.557805508871297</v>
-      </c>
-      <c r="R93">
-        <v>52.454344370054137</v>
-      </c>
-    </row>
-    <row r="94" spans="2:18" x14ac:dyDescent="0.45">
-      <c r="O94" t="s">
-        <v>278</v>
-      </c>
-      <c r="P94" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q94">
-        <v>20.648531569729403</v>
-      </c>
-      <c r="R94">
-        <v>52.768785613368301</v>
-      </c>
-    </row>
-    <row r="95" spans="2:18" x14ac:dyDescent="0.45">
-      <c r="O95" t="s">
+    </row>
+    <row r="131" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O131" t="s">
+        <v>374</v>
+      </c>
+      <c r="P131" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q131">
+        <v>16.047850156734548</v>
+      </c>
+      <c r="R131">
+        <v>51.861260822850973</v>
+      </c>
+      <c r="S131" t="s">
         <v>279</v>
       </c>
-      <c r="P95" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q95">
-        <v>18.369571653809839</v>
-      </c>
-      <c r="R95">
-        <v>51.799686803699899</v>
-      </c>
-    </row>
-    <row r="96" spans="2:18" x14ac:dyDescent="0.45">
-      <c r="O96" t="s">
-        <v>280</v>
-      </c>
-      <c r="P96" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q96">
-        <v>19.027975647671131</v>
-      </c>
-      <c r="R96">
-        <v>52.655496867703171</v>
-      </c>
-    </row>
-    <row r="97" spans="15:18" x14ac:dyDescent="0.45">
-      <c r="O97" t="s">
+    </row>
+    <row r="132" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O132" t="s">
+        <v>375</v>
+      </c>
+      <c r="P132" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q132">
+        <v>18.791538906303831</v>
+      </c>
+      <c r="R132">
+        <v>49.895529181619793</v>
+      </c>
+      <c r="S132" t="s">
         <v>281</v>
       </c>
-      <c r="P97" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q97">
-        <v>19.265584431429922</v>
-      </c>
-      <c r="R97">
-        <v>50.628803361963257</v>
-      </c>
-    </row>
-    <row r="98" spans="15:18" x14ac:dyDescent="0.45">
-      <c r="O98" t="s">
-        <v>282</v>
-      </c>
-      <c r="P98" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q98">
-        <v>20.044508863733864</v>
-      </c>
-      <c r="R98">
-        <v>51.478266767104472</v>
-      </c>
-    </row>
-    <row r="99" spans="15:18" x14ac:dyDescent="0.45">
-      <c r="O99" t="s">
+    </row>
+    <row r="133" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O133" t="s">
+        <v>376</v>
+      </c>
+      <c r="P133" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q133">
+        <v>20.8493054684808</v>
+      </c>
+      <c r="R133">
+        <v>49.91077177331681</v>
+      </c>
+      <c r="S133" t="s">
         <v>283</v>
       </c>
-      <c r="P99" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q99">
-        <v>22.909847640550961</v>
-      </c>
-      <c r="R99">
-        <v>50.868423259833534</v>
-      </c>
-    </row>
-    <row r="100" spans="15:18" x14ac:dyDescent="0.45">
-      <c r="O100" t="s">
-        <v>284</v>
-      </c>
-      <c r="P100" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q100">
-        <v>22.221487288334288</v>
-      </c>
-      <c r="R100">
-        <v>49.853731539665588</v>
-      </c>
-    </row>
-    <row r="101" spans="15:18" x14ac:dyDescent="0.45">
-      <c r="O101" t="s">
+    </row>
+    <row r="134" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O134" t="s">
+        <v>377</v>
+      </c>
+      <c r="P134" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q134">
+        <v>23.508838878966412</v>
+      </c>
+      <c r="R134">
+        <v>51.694088645539807</v>
+      </c>
+      <c r="S134" t="s">
         <v>285</v>
       </c>
-      <c r="P101" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q101">
-        <v>21.524822746291907</v>
-      </c>
-      <c r="R101">
-        <v>49.648253092611611</v>
+    </row>
+    <row r="135" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O135" t="s">
+        <v>378</v>
+      </c>
+      <c r="P135" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q135">
+        <v>22.221149843265444</v>
+      </c>
+      <c r="R135">
+        <v>49.895529181619793</v>
+      </c>
+      <c r="S135" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="136" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O136" t="s">
+        <v>379</v>
+      </c>
+      <c r="P136" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q136">
+        <v>20.409532233050189</v>
+      </c>
+      <c r="R136">
+        <v>50.93087347353012</v>
+      </c>
+      <c r="S136" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="137" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O137" t="s">
+        <v>380</v>
+      </c>
+      <c r="P137" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q137">
+        <v>21.535227655873118</v>
+      </c>
+      <c r="R137">
+        <v>50.345189363482064</v>
+      </c>
+      <c r="S137" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="138" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O138" t="s">
+        <v>381</v>
+      </c>
+      <c r="P138" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q138">
+        <v>22.221149843265444</v>
+      </c>
+      <c r="R138">
+        <v>50.408257221982232</v>
+      </c>
+      <c r="S138" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="139" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O139" t="s">
+        <v>382</v>
+      </c>
+      <c r="P139" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q139">
+        <v>19.266410025240862</v>
+      </c>
+      <c r="R139">
+        <v>50.794849545344334</v>
+      </c>
+      <c r="S139" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="140" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O140" t="s">
+        <v>383</v>
+      </c>
+      <c r="P140" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q140">
+        <v>18.791538906303831</v>
+      </c>
+      <c r="R140">
+        <v>53.043150454655681</v>
+      </c>
+      <c r="S140" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="141" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O141" t="s">
+        <v>384</v>
+      </c>
+      <c r="P141" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q141">
+        <v>21.535227655873118</v>
+      </c>
+      <c r="R141">
+        <v>50.888635183462817</v>
+      </c>
+      <c r="S141" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="142" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O142" t="s">
+        <v>385</v>
+      </c>
+      <c r="P142" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q142">
+        <v>17.419694531519191</v>
+      </c>
+      <c r="R142">
+        <v>50.345189363482064</v>
+      </c>
+      <c r="S142" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="143" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O143" t="s">
+        <v>386</v>
+      </c>
+      <c r="P143" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q143">
+        <v>18.41752059971844</v>
+      </c>
+      <c r="R143">
+        <v>52.143830090931147</v>
+      </c>
+      <c r="S143" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="144" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O144" t="s">
+        <v>387</v>
+      </c>
+      <c r="P144" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q144">
+        <v>16.733772344126869</v>
+      </c>
+      <c r="R144">
+        <v>54.3921310002425</v>
+      </c>
+      <c r="S144" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="145" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O145" t="s">
+        <v>388</v>
+      </c>
+      <c r="P145" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q145">
+        <v>21.182327215095697</v>
+      </c>
+      <c r="R145">
+        <v>52.208865366630896</v>
+      </c>
+      <c r="S145" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="146" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O146" t="s">
+        <v>389</v>
+      </c>
+      <c r="P146" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q146">
+        <v>18.791538906303831</v>
+      </c>
+      <c r="R146">
+        <v>50.345189363482064</v>
+      </c>
+      <c r="S146" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="147" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O147" t="s">
+        <v>390</v>
+      </c>
+      <c r="P147" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q147">
+        <v>21.703352022374737</v>
+      </c>
+      <c r="R147">
+        <v>54.13287173739576</v>
+      </c>
+      <c r="S147" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="148" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O148" t="s">
+        <v>391</v>
+      </c>
+      <c r="P148" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q148">
+        <v>16.588549565253906</v>
+      </c>
+      <c r="R148">
+        <v>53.010781572357352</v>
+      </c>
+      <c r="S148" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="149" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O149" t="s">
+        <v>392</v>
+      </c>
+      <c r="P149" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q149">
+        <v>18.105616718911509</v>
+      </c>
+      <c r="R149">
+        <v>50.345189363482064</v>
+      </c>
+      <c r="S149" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="150" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O150" t="s">
+        <v>393</v>
+      </c>
+      <c r="P150" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q150">
+        <v>14.676005781949904</v>
+      </c>
+      <c r="R150">
+        <v>53.043150454655688</v>
+      </c>
+      <c r="S150" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="151" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O151" t="s">
+        <v>394</v>
+      </c>
+      <c r="P151" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q151">
+        <v>19.477461093696157</v>
+      </c>
+      <c r="R151">
+        <v>50.345189363482064</v>
+      </c>
+      <c r="S151" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="152" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O152" t="s">
+        <v>395</v>
+      </c>
+      <c r="P152" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q152">
+        <v>19.403780261531288</v>
+      </c>
+      <c r="R152">
+        <v>49.674521586203319</v>
+      </c>
+      <c r="S152" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="153" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O153" t="s">
+        <v>396</v>
+      </c>
+      <c r="P153" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q153">
+        <v>19.477461093696157</v>
+      </c>
+      <c r="R153">
+        <v>53.942470818380237</v>
+      </c>
+      <c r="S153" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="154" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O154" t="s">
+        <v>397</v>
+      </c>
+      <c r="P154" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q154">
+        <v>19.869295209633083</v>
+      </c>
+      <c r="R154">
+        <v>52.66680063954901</v>
+      </c>
+      <c r="S154" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="155" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O155" t="s">
+        <v>398</v>
+      </c>
+      <c r="P155" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q155">
+        <v>17.419694531519191</v>
+      </c>
+      <c r="R155">
+        <v>51.244509727206612</v>
+      </c>
+      <c r="S155" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="156" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O156" t="s">
+        <v>399</v>
+      </c>
+      <c r="P156" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q156">
+        <v>18.105616718911509</v>
+      </c>
+      <c r="R156">
+        <v>54.3921310002425</v>
+      </c>
+      <c r="S156" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="157" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O157" t="s">
+        <v>400</v>
+      </c>
+      <c r="P157" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q157">
+        <v>20.163383281088478</v>
+      </c>
+      <c r="R157">
+        <v>49.63609311948067</v>
+      </c>
+      <c r="S157" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="158" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O158" t="s">
+        <v>401</v>
+      </c>
+      <c r="P158" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q158">
+        <v>22.196099857010601</v>
+      </c>
+      <c r="R158">
+        <v>51.918163705689693</v>
+      </c>
+      <c r="S158" t="s">
+        <v>333</v>
       </c>
     </row>
   </sheetData>
@@ -5548,7 +7038,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BA005D2-884D-439D-A1C3-8082CDECE021}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10FD80F3-C1F0-45AC-A912-54D2BBE5DE53}">
   <dimension ref="B3:L62"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5597,25 +7087,25 @@
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E5" t="s">
-        <v>287</v>
+        <v>403</v>
       </c>
       <c r="F5" t="s">
-        <v>288</v>
+        <v>404</v>
       </c>
       <c r="G5" t="s">
-        <v>289</v>
+        <v>405</v>
       </c>
       <c r="H5" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K5" t="s">
-        <v>289</v>
+        <v>405</v>
       </c>
       <c r="L5" t="s">
-        <v>424</v>
+        <v>540</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.45">
@@ -5626,25 +7116,25 @@
         <v>8</v>
       </c>
       <c r="D6" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E6" t="s">
-        <v>291</v>
+        <v>407</v>
       </c>
       <c r="F6" t="s">
-        <v>292</v>
+        <v>408</v>
       </c>
       <c r="G6" t="s">
-        <v>293</v>
+        <v>409</v>
       </c>
       <c r="H6" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K6" t="s">
-        <v>293</v>
+        <v>409</v>
       </c>
       <c r="L6" t="s">
-        <v>425</v>
+        <v>541</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.45">
@@ -5655,25 +7145,25 @@
         <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E7" t="s">
-        <v>294</v>
+        <v>410</v>
       </c>
       <c r="F7" t="s">
-        <v>295</v>
+        <v>411</v>
       </c>
       <c r="G7" t="s">
-        <v>296</v>
+        <v>412</v>
       </c>
       <c r="H7" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K7" t="s">
-        <v>296</v>
+        <v>412</v>
       </c>
       <c r="L7" t="s">
-        <v>426</v>
+        <v>542</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.45">
@@ -5684,25 +7174,25 @@
         <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E8" t="s">
-        <v>297</v>
+        <v>413</v>
       </c>
       <c r="F8" t="s">
-        <v>298</v>
+        <v>414</v>
       </c>
       <c r="G8" t="s">
-        <v>299</v>
+        <v>415</v>
       </c>
       <c r="H8" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K8" t="s">
-        <v>299</v>
+        <v>415</v>
       </c>
       <c r="L8" t="s">
-        <v>427</v>
+        <v>543</v>
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.45">
@@ -5713,25 +7203,25 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E9" t="s">
-        <v>300</v>
+        <v>416</v>
       </c>
       <c r="F9" t="s">
-        <v>301</v>
+        <v>417</v>
       </c>
       <c r="G9" t="s">
-        <v>302</v>
+        <v>418</v>
       </c>
       <c r="H9" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K9" t="s">
-        <v>302</v>
+        <v>418</v>
       </c>
       <c r="L9" t="s">
-        <v>428</v>
+        <v>544</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.45">
@@ -5742,25 +7232,25 @@
         <v>8</v>
       </c>
       <c r="D10" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E10" t="s">
-        <v>303</v>
+        <v>419</v>
       </c>
       <c r="F10" t="s">
-        <v>304</v>
+        <v>420</v>
       </c>
       <c r="G10" t="s">
-        <v>305</v>
+        <v>421</v>
       </c>
       <c r="H10" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K10" t="s">
-        <v>305</v>
+        <v>421</v>
       </c>
       <c r="L10" t="s">
-        <v>429</v>
+        <v>545</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.45">
@@ -5771,25 +7261,25 @@
         <v>8</v>
       </c>
       <c r="D11" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E11" t="s">
-        <v>306</v>
+        <v>422</v>
       </c>
       <c r="F11" t="s">
-        <v>288</v>
+        <v>404</v>
       </c>
       <c r="G11" t="s">
-        <v>307</v>
+        <v>423</v>
       </c>
       <c r="H11" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K11" t="s">
-        <v>307</v>
+        <v>423</v>
       </c>
       <c r="L11" t="s">
-        <v>430</v>
+        <v>546</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.45">
@@ -5800,25 +7290,25 @@
         <v>8</v>
       </c>
       <c r="D12" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E12" t="s">
-        <v>308</v>
+        <v>424</v>
       </c>
       <c r="F12" t="s">
-        <v>309</v>
+        <v>425</v>
       </c>
       <c r="G12" t="s">
-        <v>310</v>
+        <v>426</v>
       </c>
       <c r="H12" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K12" t="s">
-        <v>310</v>
+        <v>426</v>
       </c>
       <c r="L12" t="s">
-        <v>431</v>
+        <v>547</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.45">
@@ -5829,25 +7319,25 @@
         <v>8</v>
       </c>
       <c r="D13" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E13" t="s">
-        <v>311</v>
+        <v>427</v>
       </c>
       <c r="F13" t="s">
-        <v>312</v>
+        <v>428</v>
       </c>
       <c r="G13" t="s">
-        <v>313</v>
+        <v>429</v>
       </c>
       <c r="H13" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K13" t="s">
-        <v>313</v>
+        <v>429</v>
       </c>
       <c r="L13" t="s">
-        <v>432</v>
+        <v>548</v>
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.45">
@@ -5858,25 +7348,25 @@
         <v>8</v>
       </c>
       <c r="D14" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E14" t="s">
-        <v>314</v>
+        <v>430</v>
       </c>
       <c r="F14" t="s">
-        <v>298</v>
+        <v>414</v>
       </c>
       <c r="G14" t="s">
-        <v>315</v>
+        <v>431</v>
       </c>
       <c r="H14" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K14" t="s">
-        <v>315</v>
+        <v>431</v>
       </c>
       <c r="L14" t="s">
-        <v>433</v>
+        <v>549</v>
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.45">
@@ -5887,25 +7377,25 @@
         <v>8</v>
       </c>
       <c r="D15" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E15" t="s">
-        <v>316</v>
+        <v>432</v>
       </c>
       <c r="F15" t="s">
-        <v>312</v>
+        <v>428</v>
       </c>
       <c r="G15" t="s">
-        <v>317</v>
+        <v>433</v>
       </c>
       <c r="H15" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K15" t="s">
-        <v>317</v>
+        <v>433</v>
       </c>
       <c r="L15" t="s">
-        <v>434</v>
+        <v>550</v>
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.45">
@@ -5916,25 +7406,25 @@
         <v>8</v>
       </c>
       <c r="D16" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E16" t="s">
-        <v>318</v>
+        <v>434</v>
       </c>
       <c r="F16" t="s">
-        <v>292</v>
+        <v>408</v>
       </c>
       <c r="G16" t="s">
-        <v>319</v>
+        <v>435</v>
       </c>
       <c r="H16" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K16" t="s">
-        <v>319</v>
+        <v>435</v>
       </c>
       <c r="L16" t="s">
-        <v>435</v>
+        <v>551</v>
       </c>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.45">
@@ -5945,25 +7435,25 @@
         <v>8</v>
       </c>
       <c r="D17" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E17" t="s">
-        <v>320</v>
+        <v>436</v>
       </c>
       <c r="F17" t="s">
-        <v>298</v>
+        <v>414</v>
       </c>
       <c r="G17" t="s">
-        <v>321</v>
+        <v>437</v>
       </c>
       <c r="H17" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K17" t="s">
-        <v>321</v>
+        <v>437</v>
       </c>
       <c r="L17" t="s">
-        <v>436</v>
+        <v>552</v>
       </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.45">
@@ -5974,25 +7464,25 @@
         <v>8</v>
       </c>
       <c r="D18" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E18" t="s">
-        <v>322</v>
+        <v>438</v>
       </c>
       <c r="F18" t="s">
-        <v>323</v>
+        <v>439</v>
       </c>
       <c r="G18" t="s">
-        <v>324</v>
+        <v>440</v>
       </c>
       <c r="H18" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K18" t="s">
-        <v>324</v>
+        <v>440</v>
       </c>
       <c r="L18" t="s">
-        <v>437</v>
+        <v>553</v>
       </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.45">
@@ -6003,25 +7493,25 @@
         <v>8</v>
       </c>
       <c r="D19" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E19" t="s">
-        <v>325</v>
+        <v>441</v>
       </c>
       <c r="F19" t="s">
-        <v>326</v>
+        <v>442</v>
       </c>
       <c r="G19" t="s">
-        <v>327</v>
+        <v>443</v>
       </c>
       <c r="H19" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K19" t="s">
-        <v>327</v>
+        <v>443</v>
       </c>
       <c r="L19" t="s">
-        <v>438</v>
+        <v>554</v>
       </c>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.45">
@@ -6032,25 +7522,25 @@
         <v>8</v>
       </c>
       <c r="D20" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E20" t="s">
-        <v>328</v>
+        <v>444</v>
       </c>
       <c r="F20" t="s">
-        <v>312</v>
+        <v>428</v>
       </c>
       <c r="G20" t="s">
-        <v>329</v>
+        <v>445</v>
       </c>
       <c r="H20" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K20" t="s">
-        <v>329</v>
+        <v>445</v>
       </c>
       <c r="L20" t="s">
-        <v>439</v>
+        <v>555</v>
       </c>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.45">
@@ -6061,25 +7551,25 @@
         <v>8</v>
       </c>
       <c r="D21" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E21" t="s">
-        <v>330</v>
+        <v>446</v>
       </c>
       <c r="F21" t="s">
-        <v>331</v>
+        <v>447</v>
       </c>
       <c r="G21" t="s">
-        <v>332</v>
+        <v>448</v>
       </c>
       <c r="H21" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K21" t="s">
-        <v>332</v>
+        <v>448</v>
       </c>
       <c r="L21" t="s">
-        <v>440</v>
+        <v>556</v>
       </c>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.45">
@@ -6090,25 +7580,25 @@
         <v>8</v>
       </c>
       <c r="D22" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E22" t="s">
-        <v>333</v>
+        <v>449</v>
       </c>
       <c r="F22" t="s">
-        <v>334</v>
+        <v>450</v>
       </c>
       <c r="G22" t="s">
-        <v>335</v>
+        <v>451</v>
       </c>
       <c r="H22" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K22" t="s">
-        <v>335</v>
+        <v>451</v>
       </c>
       <c r="L22" t="s">
-        <v>441</v>
+        <v>557</v>
       </c>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.45">
@@ -6119,25 +7609,25 @@
         <v>8</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E23" t="s">
-        <v>336</v>
+        <v>452</v>
       </c>
       <c r="F23" t="s">
-        <v>326</v>
+        <v>442</v>
       </c>
       <c r="G23" t="s">
-        <v>337</v>
+        <v>453</v>
       </c>
       <c r="H23" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K23" t="s">
-        <v>337</v>
+        <v>453</v>
       </c>
       <c r="L23" t="s">
-        <v>442</v>
+        <v>558</v>
       </c>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.45">
@@ -6148,25 +7638,25 @@
         <v>8</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E24" t="s">
-        <v>338</v>
+        <v>454</v>
       </c>
       <c r="F24" t="s">
-        <v>339</v>
+        <v>455</v>
       </c>
       <c r="G24" t="s">
-        <v>340</v>
+        <v>456</v>
       </c>
       <c r="H24" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K24" t="s">
-        <v>340</v>
+        <v>456</v>
       </c>
       <c r="L24" t="s">
-        <v>443</v>
+        <v>559</v>
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.45">
@@ -6177,25 +7667,25 @@
         <v>8</v>
       </c>
       <c r="D25" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E25" t="s">
-        <v>341</v>
+        <v>457</v>
       </c>
       <c r="F25" t="s">
-        <v>298</v>
+        <v>414</v>
       </c>
       <c r="G25" t="s">
-        <v>342</v>
+        <v>458</v>
       </c>
       <c r="H25" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K25" t="s">
-        <v>342</v>
+        <v>458</v>
       </c>
       <c r="L25" t="s">
-        <v>444</v>
+        <v>560</v>
       </c>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.45">
@@ -6206,25 +7696,25 @@
         <v>8</v>
       </c>
       <c r="D26" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E26" t="s">
-        <v>343</v>
+        <v>459</v>
       </c>
       <c r="F26" t="s">
-        <v>344</v>
+        <v>460</v>
       </c>
       <c r="G26" t="s">
-        <v>345</v>
+        <v>461</v>
       </c>
       <c r="H26" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K26" t="s">
-        <v>345</v>
+        <v>461</v>
       </c>
       <c r="L26" t="s">
-        <v>445</v>
+        <v>561</v>
       </c>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.45">
@@ -6235,25 +7725,25 @@
         <v>8</v>
       </c>
       <c r="D27" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E27" t="s">
-        <v>346</v>
+        <v>462</v>
       </c>
       <c r="F27" t="s">
-        <v>344</v>
+        <v>460</v>
       </c>
       <c r="G27" t="s">
-        <v>347</v>
+        <v>463</v>
       </c>
       <c r="H27" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K27" t="s">
-        <v>347</v>
+        <v>463</v>
       </c>
       <c r="L27" t="s">
-        <v>446</v>
+        <v>562</v>
       </c>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.45">
@@ -6264,25 +7754,25 @@
         <v>8</v>
       </c>
       <c r="D28" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E28" t="s">
-        <v>348</v>
+        <v>464</v>
       </c>
       <c r="F28" t="s">
-        <v>326</v>
+        <v>442</v>
       </c>
       <c r="G28" t="s">
-        <v>349</v>
+        <v>465</v>
       </c>
       <c r="H28" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K28" t="s">
-        <v>349</v>
+        <v>465</v>
       </c>
       <c r="L28" t="s">
-        <v>447</v>
+        <v>563</v>
       </c>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.45">
@@ -6293,25 +7783,25 @@
         <v>8</v>
       </c>
       <c r="D29" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E29" t="s">
-        <v>350</v>
+        <v>466</v>
       </c>
       <c r="F29" t="s">
-        <v>326</v>
+        <v>442</v>
       </c>
       <c r="G29" t="s">
-        <v>351</v>
+        <v>467</v>
       </c>
       <c r="H29" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K29" t="s">
-        <v>351</v>
+        <v>467</v>
       </c>
       <c r="L29" t="s">
-        <v>448</v>
+        <v>564</v>
       </c>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.45">
@@ -6322,25 +7812,25 @@
         <v>8</v>
       </c>
       <c r="D30" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E30" t="s">
-        <v>352</v>
+        <v>468</v>
       </c>
       <c r="F30" t="s">
-        <v>331</v>
+        <v>447</v>
       </c>
       <c r="G30" t="s">
-        <v>353</v>
+        <v>469</v>
       </c>
       <c r="H30" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K30" t="s">
-        <v>353</v>
+        <v>469</v>
       </c>
       <c r="L30" t="s">
-        <v>449</v>
+        <v>565</v>
       </c>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.45">
@@ -6351,25 +7841,25 @@
         <v>8</v>
       </c>
       <c r="D31" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E31" t="s">
-        <v>354</v>
+        <v>470</v>
       </c>
       <c r="F31" t="s">
-        <v>326</v>
+        <v>442</v>
       </c>
       <c r="G31" t="s">
-        <v>355</v>
+        <v>471</v>
       </c>
       <c r="H31" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K31" t="s">
-        <v>355</v>
+        <v>471</v>
       </c>
       <c r="L31" t="s">
-        <v>450</v>
+        <v>566</v>
       </c>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.45">
@@ -6380,25 +7870,25 @@
         <v>8</v>
       </c>
       <c r="D32" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E32" t="s">
-        <v>356</v>
+        <v>472</v>
       </c>
       <c r="F32" t="s">
-        <v>326</v>
+        <v>442</v>
       </c>
       <c r="G32" t="s">
-        <v>357</v>
+        <v>473</v>
       </c>
       <c r="H32" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K32" t="s">
-        <v>357</v>
+        <v>473</v>
       </c>
       <c r="L32" t="s">
-        <v>451</v>
+        <v>567</v>
       </c>
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.45">
@@ -6409,25 +7899,25 @@
         <v>8</v>
       </c>
       <c r="D33" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E33" t="s">
-        <v>358</v>
+        <v>474</v>
       </c>
       <c r="F33" t="s">
-        <v>334</v>
+        <v>450</v>
       </c>
       <c r="G33" t="s">
-        <v>359</v>
+        <v>475</v>
       </c>
       <c r="H33" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K33" t="s">
-        <v>359</v>
+        <v>475</v>
       </c>
       <c r="L33" t="s">
-        <v>452</v>
+        <v>568</v>
       </c>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.45">
@@ -6438,25 +7928,25 @@
         <v>8</v>
       </c>
       <c r="D34" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E34" t="s">
-        <v>360</v>
+        <v>476</v>
       </c>
       <c r="F34" t="s">
-        <v>361</v>
+        <v>477</v>
       </c>
       <c r="G34" t="s">
-        <v>362</v>
+        <v>478</v>
       </c>
       <c r="H34" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K34" t="s">
-        <v>362</v>
+        <v>478</v>
       </c>
       <c r="L34" t="s">
-        <v>453</v>
+        <v>569</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.45">
@@ -6467,25 +7957,25 @@
         <v>8</v>
       </c>
       <c r="D35" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E35" t="s">
-        <v>363</v>
+        <v>479</v>
       </c>
       <c r="F35" t="s">
-        <v>326</v>
+        <v>442</v>
       </c>
       <c r="G35" t="s">
-        <v>364</v>
+        <v>480</v>
       </c>
       <c r="H35" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K35" t="s">
-        <v>364</v>
+        <v>480</v>
       </c>
       <c r="L35" t="s">
-        <v>454</v>
+        <v>570</v>
       </c>
     </row>
     <row r="36" spans="2:12" x14ac:dyDescent="0.45">
@@ -6496,25 +7986,25 @@
         <v>8</v>
       </c>
       <c r="D36" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E36" t="s">
-        <v>365</v>
+        <v>481</v>
       </c>
       <c r="F36" t="s">
-        <v>301</v>
+        <v>417</v>
       </c>
       <c r="G36" t="s">
-        <v>366</v>
+        <v>482</v>
       </c>
       <c r="H36" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K36" t="s">
-        <v>366</v>
+        <v>482</v>
       </c>
       <c r="L36" t="s">
-        <v>455</v>
+        <v>571</v>
       </c>
     </row>
     <row r="37" spans="2:12" x14ac:dyDescent="0.45">
@@ -6525,25 +8015,25 @@
         <v>8</v>
       </c>
       <c r="D37" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E37" t="s">
-        <v>367</v>
+        <v>483</v>
       </c>
       <c r="F37" t="s">
-        <v>368</v>
+        <v>484</v>
       </c>
       <c r="G37" t="s">
-        <v>369</v>
+        <v>485</v>
       </c>
       <c r="H37" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K37" t="s">
-        <v>369</v>
+        <v>485</v>
       </c>
       <c r="L37" t="s">
-        <v>456</v>
+        <v>572</v>
       </c>
     </row>
     <row r="38" spans="2:12" x14ac:dyDescent="0.45">
@@ -6554,25 +8044,25 @@
         <v>8</v>
       </c>
       <c r="D38" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E38" t="s">
-        <v>370</v>
+        <v>486</v>
       </c>
       <c r="F38" t="s">
-        <v>309</v>
+        <v>425</v>
       </c>
       <c r="G38" t="s">
-        <v>371</v>
+        <v>487</v>
       </c>
       <c r="H38" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K38" t="s">
-        <v>371</v>
+        <v>487</v>
       </c>
       <c r="L38" t="s">
-        <v>457</v>
+        <v>573</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.45">
@@ -6583,25 +8073,25 @@
         <v>8</v>
       </c>
       <c r="D39" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E39" t="s">
-        <v>372</v>
+        <v>488</v>
       </c>
       <c r="F39" t="s">
-        <v>326</v>
+        <v>442</v>
       </c>
       <c r="G39" t="s">
-        <v>373</v>
+        <v>489</v>
       </c>
       <c r="H39" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K39" t="s">
-        <v>373</v>
+        <v>489</v>
       </c>
       <c r="L39" t="s">
-        <v>458</v>
+        <v>574</v>
       </c>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.45">
@@ -6612,25 +8102,25 @@
         <v>8</v>
       </c>
       <c r="D40" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E40" t="s">
-        <v>374</v>
+        <v>490</v>
       </c>
       <c r="F40" t="s">
-        <v>344</v>
+        <v>460</v>
       </c>
       <c r="G40" t="s">
-        <v>375</v>
+        <v>491</v>
       </c>
       <c r="H40" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K40" t="s">
-        <v>375</v>
+        <v>491</v>
       </c>
       <c r="L40" t="s">
-        <v>459</v>
+        <v>575</v>
       </c>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.45">
@@ -6641,25 +8131,25 @@
         <v>8</v>
       </c>
       <c r="D41" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E41" t="s">
-        <v>376</v>
+        <v>492</v>
       </c>
       <c r="F41" t="s">
-        <v>312</v>
+        <v>428</v>
       </c>
       <c r="G41" t="s">
-        <v>377</v>
+        <v>493</v>
       </c>
       <c r="H41" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K41" t="s">
-        <v>377</v>
+        <v>493</v>
       </c>
       <c r="L41" t="s">
-        <v>460</v>
+        <v>576</v>
       </c>
     </row>
     <row r="42" spans="2:12" x14ac:dyDescent="0.45">
@@ -6670,25 +8160,25 @@
         <v>8</v>
       </c>
       <c r="D42" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E42" t="s">
-        <v>378</v>
+        <v>494</v>
       </c>
       <c r="F42" t="s">
-        <v>379</v>
+        <v>495</v>
       </c>
       <c r="G42" t="s">
-        <v>380</v>
+        <v>496</v>
       </c>
       <c r="H42" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K42" t="s">
-        <v>380</v>
+        <v>496</v>
       </c>
       <c r="L42" t="s">
-        <v>461</v>
+        <v>577</v>
       </c>
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.45">
@@ -6699,25 +8189,25 @@
         <v>8</v>
       </c>
       <c r="D43" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E43" t="s">
-        <v>381</v>
+        <v>497</v>
       </c>
       <c r="F43" t="s">
-        <v>344</v>
+        <v>460</v>
       </c>
       <c r="G43" t="s">
-        <v>382</v>
+        <v>498</v>
       </c>
       <c r="H43" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K43" t="s">
-        <v>382</v>
+        <v>498</v>
       </c>
       <c r="L43" t="s">
-        <v>462</v>
+        <v>578</v>
       </c>
     </row>
     <row r="44" spans="2:12" x14ac:dyDescent="0.45">
@@ -6728,25 +8218,25 @@
         <v>8</v>
       </c>
       <c r="D44" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E44" t="s">
-        <v>383</v>
+        <v>499</v>
       </c>
       <c r="F44" t="s">
-        <v>323</v>
+        <v>439</v>
       </c>
       <c r="G44" t="s">
-        <v>384</v>
+        <v>500</v>
       </c>
       <c r="H44" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K44" t="s">
-        <v>384</v>
+        <v>500</v>
       </c>
       <c r="L44" t="s">
-        <v>463</v>
+        <v>579</v>
       </c>
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.45">
@@ -6757,25 +8247,25 @@
         <v>8</v>
       </c>
       <c r="D45" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E45" t="s">
-        <v>385</v>
+        <v>501</v>
       </c>
       <c r="F45" t="s">
-        <v>344</v>
+        <v>460</v>
       </c>
       <c r="G45" t="s">
-        <v>386</v>
+        <v>502</v>
       </c>
       <c r="H45" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K45" t="s">
-        <v>386</v>
+        <v>502</v>
       </c>
       <c r="L45" t="s">
-        <v>464</v>
+        <v>580</v>
       </c>
     </row>
     <row r="46" spans="2:12" x14ac:dyDescent="0.45">
@@ -6786,25 +8276,25 @@
         <v>8</v>
       </c>
       <c r="D46" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E46" t="s">
-        <v>387</v>
+        <v>503</v>
       </c>
       <c r="F46" t="s">
-        <v>344</v>
+        <v>460</v>
       </c>
       <c r="G46" t="s">
-        <v>388</v>
+        <v>504</v>
       </c>
       <c r="H46" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K46" t="s">
-        <v>388</v>
+        <v>504</v>
       </c>
       <c r="L46" t="s">
-        <v>465</v>
+        <v>581</v>
       </c>
     </row>
     <row r="47" spans="2:12" x14ac:dyDescent="0.45">
@@ -6815,25 +8305,25 @@
         <v>8</v>
       </c>
       <c r="D47" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E47" t="s">
-        <v>389</v>
+        <v>505</v>
       </c>
       <c r="F47" t="s">
-        <v>288</v>
+        <v>404</v>
       </c>
       <c r="G47" t="s">
-        <v>390</v>
+        <v>506</v>
       </c>
       <c r="H47" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K47" t="s">
-        <v>390</v>
+        <v>506</v>
       </c>
       <c r="L47" t="s">
-        <v>466</v>
+        <v>582</v>
       </c>
     </row>
     <row r="48" spans="2:12" x14ac:dyDescent="0.45">
@@ -6844,25 +8334,25 @@
         <v>8</v>
       </c>
       <c r="D48" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E48" t="s">
-        <v>391</v>
+        <v>507</v>
       </c>
       <c r="F48" t="s">
-        <v>392</v>
+        <v>508</v>
       </c>
       <c r="G48" t="s">
-        <v>393</v>
+        <v>509</v>
       </c>
       <c r="H48" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K48" t="s">
-        <v>393</v>
+        <v>509</v>
       </c>
       <c r="L48" t="s">
-        <v>467</v>
+        <v>583</v>
       </c>
     </row>
     <row r="49" spans="2:12" x14ac:dyDescent="0.45">
@@ -6873,25 +8363,25 @@
         <v>8</v>
       </c>
       <c r="D49" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E49" t="s">
-        <v>394</v>
+        <v>510</v>
       </c>
       <c r="F49" t="s">
-        <v>395</v>
+        <v>511</v>
       </c>
       <c r="G49" t="s">
-        <v>396</v>
+        <v>512</v>
       </c>
       <c r="H49" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K49" t="s">
-        <v>396</v>
+        <v>512</v>
       </c>
       <c r="L49" t="s">
-        <v>468</v>
+        <v>584</v>
       </c>
     </row>
     <row r="50" spans="2:12" x14ac:dyDescent="0.45">
@@ -6902,25 +8392,25 @@
         <v>8</v>
       </c>
       <c r="D50" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E50" t="s">
-        <v>397</v>
+        <v>513</v>
       </c>
       <c r="F50" t="s">
-        <v>398</v>
+        <v>514</v>
       </c>
       <c r="G50" t="s">
-        <v>399</v>
+        <v>515</v>
       </c>
       <c r="H50" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K50" t="s">
-        <v>399</v>
+        <v>515</v>
       </c>
       <c r="L50" t="s">
-        <v>469</v>
+        <v>585</v>
       </c>
     </row>
     <row r="51" spans="2:12" x14ac:dyDescent="0.45">
@@ -6931,25 +8421,25 @@
         <v>8</v>
       </c>
       <c r="D51" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E51" t="s">
-        <v>400</v>
+        <v>516</v>
       </c>
       <c r="F51" t="s">
-        <v>344</v>
+        <v>460</v>
       </c>
       <c r="G51" t="s">
-        <v>401</v>
+        <v>517</v>
       </c>
       <c r="H51" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K51" t="s">
-        <v>401</v>
+        <v>517</v>
       </c>
       <c r="L51" t="s">
-        <v>470</v>
+        <v>586</v>
       </c>
     </row>
     <row r="52" spans="2:12" x14ac:dyDescent="0.45">
@@ -6960,25 +8450,25 @@
         <v>8</v>
       </c>
       <c r="D52" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E52" t="s">
-        <v>402</v>
+        <v>518</v>
       </c>
       <c r="F52" t="s">
-        <v>326</v>
+        <v>442</v>
       </c>
       <c r="G52" t="s">
-        <v>403</v>
+        <v>519</v>
       </c>
       <c r="H52" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K52" t="s">
-        <v>403</v>
+        <v>519</v>
       </c>
       <c r="L52" t="s">
-        <v>471</v>
+        <v>587</v>
       </c>
     </row>
     <row r="53" spans="2:12" x14ac:dyDescent="0.45">
@@ -6989,25 +8479,25 @@
         <v>8</v>
       </c>
       <c r="D53" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E53" t="s">
-        <v>391</v>
+        <v>507</v>
       </c>
       <c r="F53" t="s">
-        <v>404</v>
+        <v>520</v>
       </c>
       <c r="G53" t="s">
-        <v>405</v>
+        <v>521</v>
       </c>
       <c r="H53" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K53" t="s">
-        <v>405</v>
+        <v>521</v>
       </c>
       <c r="L53" t="s">
-        <v>472</v>
+        <v>588</v>
       </c>
     </row>
     <row r="54" spans="2:12" x14ac:dyDescent="0.45">
@@ -7018,25 +8508,25 @@
         <v>8</v>
       </c>
       <c r="D54" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E54" t="s">
-        <v>391</v>
+        <v>507</v>
       </c>
       <c r="F54" t="s">
+        <v>522</v>
+      </c>
+      <c r="G54" t="s">
+        <v>523</v>
+      </c>
+      <c r="H54" t="s">
         <v>406</v>
       </c>
-      <c r="G54" t="s">
-        <v>407</v>
-      </c>
-      <c r="H54" t="s">
-        <v>290</v>
-      </c>
       <c r="K54" t="s">
-        <v>407</v>
+        <v>523</v>
       </c>
       <c r="L54" t="s">
-        <v>473</v>
+        <v>589</v>
       </c>
     </row>
     <row r="55" spans="2:12" x14ac:dyDescent="0.45">
@@ -7047,25 +8537,25 @@
         <v>8</v>
       </c>
       <c r="D55" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E55" t="s">
-        <v>391</v>
+        <v>507</v>
       </c>
       <c r="F55" t="s">
-        <v>408</v>
+        <v>524</v>
       </c>
       <c r="G55" t="s">
-        <v>409</v>
+        <v>525</v>
       </c>
       <c r="H55" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K55" t="s">
-        <v>409</v>
+        <v>525</v>
       </c>
       <c r="L55" t="s">
-        <v>474</v>
+        <v>590</v>
       </c>
     </row>
     <row r="56" spans="2:12" x14ac:dyDescent="0.45">
@@ -7076,25 +8566,25 @@
         <v>8</v>
       </c>
       <c r="D56" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E56" t="s">
-        <v>360</v>
+        <v>476</v>
       </c>
       <c r="F56" t="s">
-        <v>410</v>
+        <v>526</v>
       </c>
       <c r="G56" t="s">
-        <v>411</v>
+        <v>527</v>
       </c>
       <c r="H56" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K56" t="s">
-        <v>411</v>
+        <v>527</v>
       </c>
       <c r="L56" t="s">
-        <v>475</v>
+        <v>591</v>
       </c>
     </row>
     <row r="57" spans="2:12" x14ac:dyDescent="0.45">
@@ -7105,25 +8595,25 @@
         <v>8</v>
       </c>
       <c r="D57" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E57" t="s">
-        <v>367</v>
+        <v>483</v>
       </c>
       <c r="F57" t="s">
-        <v>412</v>
+        <v>528</v>
       </c>
       <c r="G57" t="s">
-        <v>413</v>
+        <v>529</v>
       </c>
       <c r="H57" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K57" t="s">
-        <v>413</v>
+        <v>529</v>
       </c>
       <c r="L57" t="s">
-        <v>476</v>
+        <v>592</v>
       </c>
     </row>
     <row r="58" spans="2:12" x14ac:dyDescent="0.45">
@@ -7134,25 +8624,25 @@
         <v>8</v>
       </c>
       <c r="D58" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E58" t="s">
-        <v>322</v>
+        <v>438</v>
       </c>
       <c r="F58" t="s">
-        <v>414</v>
+        <v>530</v>
       </c>
       <c r="G58" t="s">
-        <v>415</v>
+        <v>531</v>
       </c>
       <c r="H58" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K58" t="s">
-        <v>415</v>
+        <v>531</v>
       </c>
       <c r="L58" t="s">
-        <v>477</v>
+        <v>593</v>
       </c>
     </row>
     <row r="59" spans="2:12" x14ac:dyDescent="0.45">
@@ -7163,25 +8653,25 @@
         <v>8</v>
       </c>
       <c r="D59" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E59" t="s">
-        <v>322</v>
+        <v>438</v>
       </c>
       <c r="F59" t="s">
-        <v>416</v>
+        <v>532</v>
       </c>
       <c r="G59" t="s">
-        <v>417</v>
+        <v>533</v>
       </c>
       <c r="H59" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K59" t="s">
-        <v>417</v>
+        <v>533</v>
       </c>
       <c r="L59" t="s">
-        <v>478</v>
+        <v>594</v>
       </c>
     </row>
     <row r="60" spans="2:12" x14ac:dyDescent="0.45">
@@ -7192,25 +8682,25 @@
         <v>8</v>
       </c>
       <c r="D60" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E60" t="s">
-        <v>330</v>
+        <v>446</v>
       </c>
       <c r="F60" t="s">
-        <v>418</v>
+        <v>534</v>
       </c>
       <c r="G60" t="s">
-        <v>419</v>
+        <v>535</v>
       </c>
       <c r="H60" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K60" t="s">
-        <v>419</v>
+        <v>535</v>
       </c>
       <c r="L60" t="s">
-        <v>479</v>
+        <v>595</v>
       </c>
     </row>
     <row r="61" spans="2:12" x14ac:dyDescent="0.45">
@@ -7221,25 +8711,25 @@
         <v>8</v>
       </c>
       <c r="D61" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E61" t="s">
-        <v>322</v>
+        <v>438</v>
       </c>
       <c r="F61" t="s">
-        <v>420</v>
+        <v>536</v>
       </c>
       <c r="G61" t="s">
-        <v>421</v>
+        <v>537</v>
       </c>
       <c r="H61" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K61" t="s">
-        <v>421</v>
+        <v>537</v>
       </c>
       <c r="L61" t="s">
-        <v>480</v>
+        <v>596</v>
       </c>
     </row>
     <row r="62" spans="2:12" x14ac:dyDescent="0.45">
@@ -7250,25 +8740,25 @@
         <v>8</v>
       </c>
       <c r="D62" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E62" t="s">
-        <v>372</v>
+        <v>488</v>
       </c>
       <c r="F62" t="s">
-        <v>422</v>
+        <v>538</v>
       </c>
       <c r="G62" t="s">
-        <v>423</v>
+        <v>539</v>
       </c>
       <c r="H62" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="K62" t="s">
-        <v>423</v>
+        <v>539</v>
       </c>
       <c r="L62" t="s">
-        <v>481</v>
+        <v>597</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25928"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{06FEA5EE-9F65-4A03-9A44-15DAC35A3B2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FE16354E-6D73-4095-AFD4-129D6E01D0D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675" activeTab="1" xr2:uid="{553D755F-3C19-4748-A8BB-66F3A215FB4D}"/>
+    <workbookView xWindow="2573" yWindow="2573" windowWidth="21600" windowHeight="11422" activeTab="1" xr2:uid="{905D0BE9-63A2-4257-BCF9-CEA42253A243}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -32,15 +32,12 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1729" uniqueCount="598">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1558" uniqueCount="532">
   <si>
     <t>~tradelinks_dins</t>
   </si>
@@ -759,289 +756,121 @@
     <t>elc_spv_POL_001</t>
   </si>
   <si>
-    <t>POLYGON ((18.448578 52.81832, 17.762656 52.81832, 17.076733 52.81832, 17.076733 53.267981, 17.076733 53.717641, 17.762656 53.717641, 18.448578 53.717641, 18.448578 53.267981, 18.448578 52.81832))</t>
+    <t>POLYGON ((23.935955 52.36866, 23.250033 52.36866, 22.564111 52.36866, 21.878189 52.36866, 21.192267 52.36866, 21.192267 52.81832, 21.192267 53.267981, 21.878189 53.267981, 22.564111 53.267981, 23.250033 53.267981, 23.935955 53.267981, 23.935955 52.81832, 23.935955 52.36866))</t>
   </si>
   <si>
     <t>elc_spv_POL_002</t>
   </si>
   <si>
-    <t>POLYGON ((22.564111 53.267981, 22.564111 53.717641, 23.250033 53.717641, 23.250033 54.167301, 23.935955 54.167301, 23.935955 53.717641, 23.935955 53.267981, 23.935955 52.81832, 23.935955 52.36866, 23.250033 52.36866, 23.250033 51.919, 22.564111 51.919, 22.564111 52.36866, 22.564111 52.81832, 22.564111 53.267981))</t>
+    <t>POLYGON ((21.192267 54.616961, 21.878189 54.616961, 22.564111 54.616961, 23.250033 54.616961, 23.935955 54.616961, 23.935955 54.167301, 23.935955 53.717641, 23.935955 53.267981, 23.250033 53.267981, 22.564111 53.267981, 21.878189 53.267981, 21.192267 53.267981, 21.192267 53.717641, 21.192267 54.167301, 21.192267 54.616961))</t>
   </si>
   <si>
     <t>elc_spv_POL_003</t>
   </si>
   <si>
-    <t>POLYGON ((15.018967 52.81832, 15.018967 53.267981, 15.018967 53.717641, 15.704889 53.717641, 15.704889 53.267981, 15.704889 52.81832, 15.704889 52.36866, 15.018967 52.36866, 14.333045 52.36866, 14.333045 52.81832, 15.018967 52.81832))</t>
+    <t>POLYGON ((23.250033 49.221039, 22.564111 49.221039, 21.878189 49.221039, 21.192267 49.221039, 21.192267 49.670699, 21.192267 50.120359, 21.192267 50.570019, 21.878189 50.570019, 21.878189 50.120359, 22.564111 50.120359, 23.250033 50.120359, 23.250033 49.670699, 23.250033 49.221039))</t>
   </si>
   <si>
     <t>elc_spv_POL_004</t>
   </si>
   <si>
-    <t>POLYGON ((15.704889 51.46934, 16.390811 51.46934, 16.390811 51.919, 17.076733 51.919, 17.076733 51.46934, 17.076733 51.01968, 16.390811 51.01968, 16.390811 50.570019, 15.704889 50.570019, 15.704889 51.01968, 15.704889 51.46934))</t>
+    <t>POLYGON ((19.820422 50.120359, 19.820422 50.570019, 20.506344 50.570019, 21.192267 50.570019, 21.192267 50.120359, 21.192267 49.670699, 21.192267 49.221039, 20.506344 49.221039, 19.820422 49.221039, 19.820422 49.670699, 19.820422 50.120359))</t>
   </si>
   <si>
     <t>elc_spv_POL_005</t>
   </si>
   <si>
-    <t>MULTIPOLYGON (((17.076733 51.01968, 17.762656 51.01968, 17.762656 50.570019, 17.076733 50.570019, 17.076733 51.01968)), ((17.762656 51.46934, 18.448578 51.46934, 18.448578 51.01968, 17.762656 51.01968, 17.762656 51.46934)))</t>
+    <t>POLYGON ((22.564111 51.01968, 21.878189 51.01968, 21.878189 51.46934, 21.878189 51.919, 21.878189 52.36866, 22.564111 52.36866, 23.250033 52.36866, 23.935955 52.36866, 23.935955 51.919, 23.935955 51.46934, 23.250033 51.46934, 23.250033 51.01968, 22.564111 51.01968))</t>
   </si>
   <si>
     <t>elc_spv_POL_006</t>
   </si>
   <si>
-    <t>POLYGON ((17.076733 49.670699, 16.390811 49.670699, 16.390811 50.120359, 15.704889 50.120359, 15.704889 50.570019, 16.390811 50.570019, 16.390811 51.01968, 17.076733 51.01968, 17.076733 50.570019, 17.076733 50.120359, 17.076733 49.670699))</t>
+    <t>POLYGON ((23.250033 49.670699, 23.250033 50.120359, 22.564111 50.120359, 21.878189 50.120359, 21.878189 50.570019, 21.192267 50.570019, 21.192267 51.01968, 21.192267 51.46934, 21.878189 51.46934, 21.878189 51.01968, 22.564111 51.01968, 23.250033 51.01968, 23.250033 51.46934, 23.935955 51.46934, 23.935955 51.01968, 23.935955 50.570019, 23.935955 50.120359, 23.935955 49.670699, 23.250033 49.670699))</t>
   </si>
   <si>
     <t>elc_spv_POL_007</t>
   </si>
   <si>
-    <t>POLYGON ((19.1345 53.267981, 19.1345 53.717641, 19.820422 53.717641, 19.820422 53.267981, 19.1345 53.267981))</t>
+    <t>POLYGON ((14.333045 53.717641, 14.333045 54.167301, 15.018967 54.167301, 15.704889 54.167301, 15.704889 53.717641, 15.704889 53.267981, 15.704889 52.81832, 15.018967 52.81832, 14.333045 52.81832, 14.333045 53.267981, 14.333045 53.717641))</t>
   </si>
   <si>
     <t>elc_spv_POL_008</t>
   </si>
   <si>
-    <t>POLYGON ((17.076733 54.167301, 17.076733 54.616961, 17.762656 54.616961, 17.762656 54.167301, 17.076733 54.167301))</t>
+    <t>POLYGON ((15.704889 54.167301, 15.704889 54.616961, 16.390811 54.616961, 17.076733 54.616961, 17.762656 54.616961, 17.762656 54.167301, 17.762656 53.717641, 17.762656 53.267981, 17.762656 52.81832, 17.076733 52.81832, 16.390811 52.81832, 15.704889 52.81832, 15.704889 53.267981, 15.704889 53.717641, 15.704889 54.167301))</t>
   </si>
   <si>
     <t>elc_spv_POL_009</t>
   </si>
   <si>
+    <t>POLYGON ((19.820422 52.36866, 19.1345 52.36866, 18.448578 52.36866, 17.762656 52.36866, 17.762656 52.81832, 17.762656 53.267981, 18.448578 53.267981, 19.1345 53.267981, 19.820422 53.267981, 19.820422 52.81832, 19.820422 52.36866))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_010</t>
+  </si>
+  <si>
     <t>POLYGON ((19.820422 54.167301, 19.820422 54.616961, 20.506344 54.616961, 21.192267 54.616961, 21.192267 54.167301, 21.192267 53.717641, 21.192267 53.267981, 20.506344 53.267981, 19.820422 53.267981, 19.820422 53.717641, 19.820422 54.167301))</t>
   </si>
   <si>
-    <t>elc_spv_POL_010</t>
+    <t>elc_spv_POL_011</t>
+  </si>
+  <si>
+    <t>POLYGON ((19.820422 53.267981, 19.1345 53.267981, 18.448578 53.267981, 17.762656 53.267981, 17.762656 53.717641, 17.762656 54.167301, 17.762656 54.616961, 18.448578 54.616961, 19.1345 54.616961, 19.820422 54.616961, 19.820422 54.167301, 19.820422 53.717641, 19.820422 53.267981))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_012</t>
+  </si>
+  <si>
+    <t>POLYGON ((17.762656 51.919, 17.076733 51.919, 16.390811 51.919, 15.704889 51.919, 15.704889 52.36866, 15.704889 52.81832, 16.390811 52.81832, 17.076733 52.81832, 17.762656 52.81832, 17.762656 52.36866, 17.762656 51.919))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_013</t>
+  </si>
+  <si>
+    <t>POLYGON ((17.762656 51.01968, 17.076733 51.01968, 16.390811 51.01968, 15.704889 51.01968, 15.704889 51.46934, 15.704889 51.919, 16.390811 51.919, 17.076733 51.919, 17.762656 51.919, 17.762656 51.46934, 17.762656 51.01968))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_014</t>
   </si>
   <si>
     <t>POLYGON ((15.704889 50.570019, 15.018967 50.570019, 14.333045 50.570019, 14.333045 51.01968, 14.333045 51.46934, 15.018967 51.46934, 15.704889 51.46934, 15.704889 51.01968, 15.704889 50.570019))</t>
   </si>
   <si>
-    <t>elc_spv_POL_011</t>
-  </si>
-  <si>
-    <t>POLYGON ((18.448578 54.167301, 18.448578 54.616961, 19.1345 54.616961, 19.820422 54.616961, 19.820422 54.167301, 19.1345 54.167301, 19.1345 53.717641, 18.448578 53.717641, 17.762656 53.717641, 17.762656 54.167301, 18.448578 54.167301))</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_012</t>
-  </si>
-  <si>
-    <t>POLYGON ((22.564111 52.36866, 21.878189 52.36866, 21.192267 52.36866, 21.192267 52.81832, 20.506344 52.81832, 20.506344 53.267981, 21.192267 53.267981, 21.192267 53.717641, 21.878189 53.717641, 21.878189 53.267981, 22.564111 53.267981, 22.564111 52.81832, 22.564111 52.36866))</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_013</t>
-  </si>
-  <si>
-    <t>POLYGON ((15.704889 51.46934, 15.018967 51.46934, 14.333045 51.46934, 14.333045 51.919, 14.333045 52.36866, 15.018967 52.36866, 15.704889 52.36866, 15.704889 51.919, 15.704889 51.46934))</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_014</t>
-  </si>
-  <si>
-    <t>POLYGON ((14.333045 53.717641, 14.333045 54.167301, 15.018967 54.167301, 15.704889 54.167301, 15.704889 53.717641, 15.018967 53.717641, 15.018967 53.267981, 14.333045 53.267981, 14.333045 53.717641))</t>
-  </si>
-  <si>
     <t>elc_spv_POL_015</t>
   </si>
   <si>
-    <t>POLYGON ((22.564111 49.670699, 23.250033 49.670699, 23.250033 49.221039, 22.564111 49.221039, 21.878189 49.221039, 21.192267 49.221039, 21.192267 49.670699, 21.192267 50.120359, 21.878189 50.120359, 21.878189 49.670699, 22.564111 49.670699))</t>
+    <t>POLYGON ((14.333045 52.36866, 14.333045 52.81832, 15.018967 52.81832, 15.704889 52.81832, 15.704889 52.36866, 15.704889 51.919, 15.704889 51.46934, 15.018967 51.46934, 14.333045 51.46934, 14.333045 51.919, 14.333045 52.36866))</t>
   </si>
   <si>
     <t>elc_spv_POL_016</t>
   </si>
   <si>
-    <t>POLYGON ((23.250033 53.717641, 22.564111 53.717641, 21.878189 53.717641, 21.878189 54.167301, 21.878189 54.616961, 22.564111 54.616961, 23.250033 54.616961, 23.935955 54.616961, 23.935955 54.167301, 23.250033 54.167301, 23.250033 53.717641))</t>
+    <t>POLYGON ((17.762656 49.670699, 17.076733 49.670699, 16.390811 49.670699, 16.390811 50.120359, 15.704889 50.120359, 15.704889 50.570019, 15.704889 51.01968, 16.390811 51.01968, 17.076733 51.01968, 17.762656 51.01968, 17.762656 50.570019, 17.762656 50.120359, 17.762656 49.670699))</t>
   </si>
   <si>
     <t>elc_spv_POL_017</t>
   </si>
   <si>
-    <t>POLYGON ((19.1345 51.46934, 19.1345 51.919, 19.820422 51.919, 20.506344 51.919, 20.506344 51.46934, 19.820422 51.46934, 19.820422 51.01968, 19.1345 51.01968, 19.1345 51.46934))</t>
+    <t>POLYGON ((19.820422 49.221039, 19.1345 49.221039, 18.448578 49.221039, 18.448578 49.670699, 17.762656 49.670699, 17.762656 50.120359, 17.762656 50.570019, 18.448578 50.570019, 19.1345 50.570019, 19.820422 50.570019, 19.820422 50.120359, 19.820422 49.670699, 19.820422 49.221039))</t>
   </si>
   <si>
     <t>elc_spv_POL_018</t>
   </si>
   <si>
-    <t>POLYGON ((18.448578 51.46934, 18.448578 51.919, 19.1345 51.919, 19.1345 51.46934, 19.1345 51.01968, 18.448578 51.01968, 18.448578 51.46934))</t>
+    <t>POLYGON ((21.878189 51.46934, 21.192267 51.46934, 20.506344 51.46934, 20.506344 51.919, 19.820422 51.919, 19.820422 52.36866, 19.820422 52.81832, 19.820422 53.267981, 20.506344 53.267981, 21.192267 53.267981, 21.192267 52.81832, 21.192267 52.36866, 21.878189 52.36866, 21.878189 51.919, 21.878189 51.46934))</t>
   </si>
   <si>
     <t>elc_spv_POL_019</t>
   </si>
   <si>
-    <t>POLYGON ((22.564111 50.570019, 22.564111 51.01968, 23.250033 51.01968, 23.935955 51.01968, 23.935955 50.570019, 23.935955 50.120359, 23.935955 49.670699, 23.250033 49.670699, 22.564111 49.670699, 22.564111 50.120359, 22.564111 50.570019))</t>
+    <t>POLYGON ((21.192267 50.570019, 20.506344 50.570019, 19.820422 50.570019, 19.820422 51.01968, 19.820422 51.46934, 19.820422 51.919, 20.506344 51.919, 20.506344 51.46934, 21.192267 51.46934, 21.192267 51.01968, 21.192267 50.570019))</t>
   </si>
   <si>
     <t>elc_spv_POL_020</t>
   </si>
   <si>
-    <t>POLYGON ((15.704889 54.167301, 15.704889 54.616961, 16.390811 54.616961, 16.390811 54.167301, 17.076733 54.167301, 17.762656 54.167301, 17.762656 53.717641, 17.076733 53.717641, 17.076733 53.267981, 16.390811 53.267981, 15.704889 53.267981, 15.704889 53.717641, 15.704889 54.167301))</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_021</t>
-  </si>
-  <si>
-    <t>POLYGON ((15.704889 51.919, 15.704889 52.36866, 16.390811 52.36866, 16.390811 51.919, 16.390811 51.46934, 15.704889 51.46934, 15.704889 51.919))</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_022</t>
-  </si>
-  <si>
-    <t>POLYGON ((18.448578 49.670699, 18.448578 50.120359, 19.1345 50.120359, 19.1345 49.670699, 18.448578 49.670699))</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_023</t>
-  </si>
-  <si>
-    <t>POLYGON ((20.506344 49.670699, 20.506344 50.120359, 20.506344 50.570019, 21.192267 50.570019, 21.192267 50.120359, 21.192267 49.670699, 21.192267 49.221039, 20.506344 49.221039, 20.506344 49.670699))</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_024</t>
-  </si>
-  <si>
-    <t>POLYGON ((23.935955 51.01968, 23.250033 51.01968, 22.564111 51.01968, 22.564111 51.46934, 22.564111 51.919, 23.250033 51.919, 23.250033 52.36866, 23.935955 52.36866, 23.935955 51.919, 23.935955 51.46934, 23.935955 51.01968))</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_025</t>
-  </si>
-  <si>
-    <t>POLYGON ((21.878189 49.670699, 21.878189 50.120359, 22.564111 50.120359, 22.564111 49.670699, 21.878189 49.670699))</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_026</t>
-  </si>
-  <si>
-    <t>POLYGON ((21.192267 50.570019, 20.506344 50.570019, 19.820422 50.570019, 19.820422 51.01968, 19.820422 51.46934, 20.506344 51.46934, 21.192267 51.46934, 21.192267 51.01968, 21.192267 50.570019))</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_027</t>
-  </si>
-  <si>
-    <t>POLYGON ((21.192267 50.120359, 21.192267 50.570019, 21.878189 50.570019, 21.878189 50.120359, 21.192267 50.120359))</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_028</t>
-  </si>
-  <si>
-    <t>POLYGON ((21.878189 50.570019, 21.878189 51.01968, 22.564111 51.01968, 22.564111 50.570019, 22.564111 50.120359, 21.878189 50.120359, 21.878189 50.570019))</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_029</t>
-  </si>
-  <si>
-    <t>POLYGON ((18.448578 51.01968, 19.1345 51.01968, 19.820422 51.01968, 19.820422 50.570019, 19.1345 50.570019, 18.448578 50.570019, 18.448578 51.01968))</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_030</t>
-  </si>
-  <si>
-    <t>POLYGON ((18.448578 52.81832, 18.448578 53.267981, 19.1345 53.267981, 19.1345 52.81832, 19.1345 52.36866, 18.448578 52.36866, 18.448578 52.81832))</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_031</t>
-  </si>
-  <si>
-    <t>POLYGON ((21.192267 51.01968, 21.192267 51.46934, 21.878189 51.46934, 21.878189 51.01968, 21.878189 50.570019, 21.192267 50.570019, 21.192267 51.01968))</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_032</t>
-  </si>
-  <si>
-    <t>POLYGON ((17.076733 50.120359, 17.076733 50.570019, 17.762656 50.570019, 17.762656 50.120359, 17.076733 50.120359))</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_033</t>
-  </si>
-  <si>
-    <t>POLYGON ((17.762656 52.36866, 17.762656 52.81832, 18.448578 52.81832, 18.448578 52.36866, 19.1345 52.36866, 19.1345 51.919, 18.448578 51.919, 18.448578 51.46934, 17.762656 51.46934, 17.762656 51.919, 17.762656 52.36866))</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_034</t>
-  </si>
-  <si>
-    <t>POLYGON ((16.390811 54.167301, 16.390811 54.616961, 17.076733 54.616961, 17.076733 54.167301, 16.390811 54.167301))</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_035</t>
-  </si>
-  <si>
-    <t>POLYGON ((20.506344 52.36866, 20.506344 52.81832, 21.192267 52.81832, 21.192267 52.36866, 21.878189 52.36866, 21.878189 51.919, 21.192267 51.919, 21.192267 51.46934, 20.506344 51.46934, 20.506344 51.919, 20.506344 52.36866))</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_036</t>
-  </si>
-  <si>
-    <t>POLYGON ((18.448578 50.120359, 18.448578 50.570019, 19.1345 50.570019, 19.1345 50.120359, 18.448578 50.120359))</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_037</t>
-  </si>
-  <si>
-    <t>MULTIPOLYGON (((21.878189 53.717641, 22.564111 53.717641, 22.564111 53.267981, 21.878189 53.267981, 21.878189 53.717641)), ((21.192267 54.616961, 21.878189 54.616961, 21.878189 54.167301, 21.878189 53.717641, 21.192267 53.717641, 21.192267 54.167301, 21.192267 54.616961)))</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_038</t>
-  </si>
-  <si>
-    <t>POLYGON ((17.762656 51.919, 17.076733 51.919, 16.390811 51.919, 16.390811 52.36866, 15.704889 52.36866, 15.704889 52.81832, 15.704889 53.267981, 16.390811 53.267981, 17.076733 53.267981, 17.076733 52.81832, 17.762656 52.81832, 17.762656 52.36866, 17.762656 51.919))</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_039</t>
-  </si>
-  <si>
-    <t>POLYGON ((17.762656 50.120359, 17.762656 50.570019, 17.762656 51.01968, 18.448578 51.01968, 18.448578 50.570019, 18.448578 50.120359, 18.448578 49.670699, 17.762656 49.670699, 17.076733 49.670699, 17.076733 50.120359, 17.762656 50.120359))</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_040</t>
-  </si>
-  <si>
-    <t>POLYGON ((14.333045 52.81832, 14.333045 53.267981, 15.018967 53.267981, 15.018967 52.81832, 14.333045 52.81832))</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_041</t>
-  </si>
-  <si>
-    <t>POLYGON ((19.1345 50.120359, 19.1345 50.570019, 19.820422 50.570019, 19.820422 50.120359, 19.1345 50.120359))</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_042</t>
-  </si>
-  <si>
-    <t>POLYGON ((18.448578 49.670699, 19.1345 49.670699, 19.1345 50.120359, 19.820422 50.120359, 19.820422 49.670699, 19.820422 49.221039, 19.1345 49.221039, 18.448578 49.221039, 18.448578 49.670699))</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_043</t>
-  </si>
-  <si>
-    <t>MULTIPOLYGON (((18.448578 53.717641, 19.1345 53.717641, 19.1345 53.267981, 18.448578 53.267981, 18.448578 53.717641)), ((19.1345 54.167301, 19.820422 54.167301, 19.820422 53.717641, 19.1345 53.717641, 19.1345 54.167301)))</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_044</t>
-  </si>
-  <si>
-    <t>POLYGON ((19.1345 52.81832, 19.1345 53.267981, 19.820422 53.267981, 20.506344 53.267981, 20.506344 52.81832, 20.506344 52.36866, 20.506344 51.919, 19.820422 51.919, 19.1345 51.919, 19.1345 52.36866, 19.1345 52.81832))</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_045</t>
-  </si>
-  <si>
-    <t>POLYGON ((17.076733 51.46934, 17.076733 51.919, 17.762656 51.919, 17.762656 51.46934, 17.762656 51.01968, 17.076733 51.01968, 17.076733 51.46934))</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_046</t>
-  </si>
-  <si>
-    <t>POLYGON ((17.762656 54.167301, 17.762656 54.616961, 18.448578 54.616961, 18.448578 54.167301, 17.762656 54.167301))</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_047</t>
-  </si>
-  <si>
-    <t>POLYGON ((19.820422 49.670699, 19.820422 50.120359, 19.820422 50.570019, 20.506344 50.570019, 20.506344 50.120359, 20.506344 49.670699, 20.506344 49.221039, 19.820422 49.221039, 19.820422 49.670699))</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_048</t>
-  </si>
-  <si>
-    <t>POLYGON ((22.564111 51.01968, 21.878189 51.01968, 21.878189 51.46934, 21.192267 51.46934, 21.192267 51.919, 21.878189 51.919, 21.878189 52.36866, 22.564111 52.36866, 22.564111 51.919, 22.564111 51.46934, 22.564111 51.01968))</t>
+    <t>POLYGON ((17.762656 51.919, 17.762656 52.36866, 18.448578 52.36866, 19.1345 52.36866, 19.820422 52.36866, 19.820422 51.919, 19.820422 51.46934, 19.820422 51.01968, 19.820422 50.570019, 19.1345 50.570019, 18.448578 50.570019, 17.762656 50.570019, 17.762656 51.01968, 17.762656 51.46934, 17.762656 51.919))</t>
   </si>
   <si>
     <t>elc_wof_POL_001</t>
@@ -1053,199 +882,169 @@
     <t>elc_wof_POL_002</t>
   </si>
   <si>
-    <t>POLYGON ((18.448578 54.934934, 19.1345 54.934934, 19.1345 55.384594, 19.820422 55.384594, 19.820422 54.934934, 19.820422 54.485273, 19.1345 54.485273, 18.448578 54.485273, 18.448578 54.934934))</t>
+    <t>POLYGON ((18.448578 55.384594, 19.1345 55.384594, 19.820422 55.384594, 19.820422 54.934934, 19.1345 54.934934, 18.448578 54.934934, 18.448578 55.384594))</t>
   </si>
   <si>
     <t>elc_wof_POL_003</t>
   </si>
   <si>
+    <t>POLYGON ((18.448578 54.934934, 19.1345 54.934934, 19.820422 54.934934, 19.820422 54.485273, 19.1345 54.485273, 18.448578 54.485273, 18.448578 54.934934))</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_004</t>
+  </si>
+  <si>
+    <t>POLYGON ((16.390811 55.834254, 17.076733 55.834254, 17.762656 55.834254, 17.762656 55.384594, 17.076733 55.384594, 16.390811 55.384594, 16.390811 55.834254))</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_005</t>
+  </si>
+  <si>
+    <t>POLYGON ((17.762656 55.834254, 18.448578 55.834254, 19.1345 55.834254, 19.1345 55.384594, 18.448578 55.384594, 17.762656 55.384594, 17.762656 55.834254))</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_006</t>
+  </si>
+  <si>
+    <t>POLYGON ((17.076733 55.384594, 17.762656 55.384594, 18.448578 55.384594, 18.448578 54.934934, 17.762656 54.934934, 17.076733 54.934934, 17.076733 55.384594))</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_007</t>
+  </si>
+  <si>
+    <t>POLYGON ((15.018967 54.485273, 15.704889 54.485273, 16.390811 54.485273, 16.390811 54.035613, 15.704889 54.035613, 15.018967 54.035613, 15.018967 54.485273))</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_008</t>
+  </si>
+  <si>
     <t>POLYGON ((14.333045 54.934934, 15.018967 54.934934, 15.704889 54.934934, 15.704889 54.485273, 15.018967 54.485273, 14.333045 54.485273, 14.333045 54.934934))</t>
   </si>
   <si>
-    <t>elc_wof_POL_004</t>
-  </si>
-  <si>
-    <t>POLYGON ((15.018967 54.035613, 15.018967 54.485273, 15.704889 54.485273, 15.704889 54.035613, 15.018967 54.035613))</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_005</t>
-  </si>
-  <si>
-    <t>POLYGON ((15.704889 54.035613, 15.704889 54.485273, 16.390811 54.485273, 16.390811 54.035613, 15.704889 54.035613))</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_006</t>
-  </si>
-  <si>
-    <t>POLYGON ((15.704889 55.384594, 16.390811 55.384594, 16.390811 55.834254, 17.076733 55.834254, 17.076733 55.384594, 17.076733 54.934934, 16.390811 54.934934, 15.704889 54.934934, 15.704889 55.384594))</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_007</t>
+    <t>elc_wof_POL_009</t>
+  </si>
+  <si>
+    <t>POLYGON ((15.704889 55.384594, 16.390811 55.384594, 17.076733 55.384594, 17.076733 54.934934, 16.390811 54.934934, 15.704889 54.934934, 15.704889 55.384594))</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_010</t>
   </si>
   <si>
     <t>POLYGON ((15.704889 54.485273, 15.704889 54.934934, 16.390811 54.934934, 16.390811 54.485273, 15.704889 54.485273))</t>
   </si>
   <si>
-    <t>elc_wof_POL_008</t>
-  </si>
-  <si>
-    <t>POLYGON ((17.076733 55.384594, 17.076733 55.834254, 17.762656 55.834254, 17.762656 55.384594, 17.762656 54.934934, 17.076733 54.934934, 17.076733 55.384594))</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_009</t>
-  </si>
-  <si>
-    <t>POLYGON ((17.762656 55.834254, 18.448578 55.834254, 19.1345 55.834254, 19.1345 55.384594, 18.448578 55.384594, 17.762656 55.384594, 17.762656 55.834254))</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_010</t>
-  </si>
-  <si>
-    <t>POLYGON ((17.762656 55.384594, 18.448578 55.384594, 19.1345 55.384594, 19.1345 54.934934, 18.448578 54.934934, 17.762656 54.934934, 17.762656 55.384594))</t>
-  </si>
-  <si>
     <t>elc_won_POL_001</t>
   </si>
   <si>
+    <t>POLYGON ((17.076733 50.120359, 16.390811 50.120359, 16.390811 50.570019, 15.704889 50.570019, 15.018967 50.570019, 14.333045 50.570019, 14.333045 51.01968, 15.018967 51.01968, 15.704889 51.01968, 16.390811 51.01968, 17.076733 51.01968, 17.076733 50.570019, 17.076733 50.120359))</t>
+  </si>
+  <si>
     <t>elc_won_POL_002</t>
   </si>
   <si>
+    <t>POLYGON ((17.076733 49.670699, 17.076733 50.120359, 17.762656 50.120359, 17.762656 49.670699, 17.076733 49.670699))</t>
+  </si>
+  <si>
     <t>elc_won_POL_003</t>
   </si>
   <si>
+    <t>POLYGON ((15.704889 51.01968, 15.018967 51.01968, 15.018967 51.46934, 14.333045 51.46934, 14.333045 51.919, 14.333045 52.36866, 15.018967 52.36866, 15.704889 52.36866, 15.704889 51.919, 15.704889 51.46934, 15.704889 51.01968))</t>
+  </si>
+  <si>
     <t>elc_won_POL_004</t>
   </si>
   <si>
+    <t>POLYGON ((15.704889 52.36866, 15.704889 52.81832, 16.390811 52.81832, 17.076733 52.81832, 17.762656 52.81832, 17.762656 52.36866, 17.762656 51.919, 17.762656 51.46934, 17.762656 51.01968, 17.076733 51.01968, 16.390811 51.01968, 15.704889 51.01968, 15.704889 51.46934, 15.704889 51.919, 15.704889 52.36866))</t>
+  </si>
+  <si>
     <t>elc_won_POL_005</t>
   </si>
   <si>
+    <t>POLYGON ((19.820422 53.267981, 19.1345 53.267981, 18.448578 53.267981, 18.448578 52.81832, 17.762656 52.81832, 17.762656 53.267981, 17.762656 53.717641, 17.762656 54.167301, 18.448578 54.167301, 18.448578 54.616961, 19.1345 54.616961, 19.820422 54.616961, 19.820422 54.167301, 19.820422 53.717641, 19.820422 53.267981))</t>
+  </si>
+  <si>
     <t>elc_won_POL_006</t>
   </si>
   <si>
+    <t>POLYGON ((15.018967 52.36866, 14.333045 52.36866, 14.333045 52.81832, 14.333045 53.267981, 14.333045 53.717641, 14.333045 54.167301, 15.018967 54.167301, 15.704889 54.167301, 15.704889 53.717641, 15.704889 53.267981, 15.704889 52.81832, 15.704889 52.36866, 15.018967 52.36866))</t>
+  </si>
+  <si>
     <t>elc_won_POL_007</t>
   </si>
   <si>
+    <t>POLYGON ((16.390811 54.616961, 17.076733 54.616961, 17.762656 54.616961, 18.448578 54.616961, 18.448578 54.167301, 17.762656 54.167301, 17.076733 54.167301, 16.390811 54.167301, 15.704889 54.167301, 15.704889 54.616961, 16.390811 54.616961))</t>
+  </si>
+  <si>
     <t>elc_won_POL_008</t>
   </si>
   <si>
+    <t>POLYGON ((17.762656 52.81832, 17.076733 52.81832, 16.390811 52.81832, 15.704889 52.81832, 15.704889 53.267981, 15.704889 53.717641, 15.704889 54.167301, 16.390811 54.167301, 17.076733 54.167301, 17.762656 54.167301, 17.762656 53.717641, 17.762656 53.267981, 17.762656 52.81832))</t>
+  </si>
+  <si>
     <t>elc_won_POL_009</t>
   </si>
   <si>
+    <t>POLYGON ((23.250033 52.81832, 23.250033 53.267981, 22.564111 53.267981, 21.878189 53.267981, 21.878189 53.717641, 21.878189 54.167301, 22.564111 54.167301, 23.250033 54.167301, 23.250033 54.616961, 23.935955 54.616961, 23.935955 54.167301, 23.935955 53.717641, 23.935955 53.267981, 23.935955 52.81832, 23.250033 52.81832))</t>
+  </si>
+  <si>
     <t>elc_won_POL_010</t>
   </si>
   <si>
+    <t>POLYGON ((21.878189 53.717641, 21.192267 53.717641, 20.506344 53.717641, 19.820422 53.717641, 19.820422 54.167301, 19.820422 54.616961, 20.506344 54.616961, 21.192267 54.616961, 21.878189 54.616961, 22.564111 54.616961, 23.250033 54.616961, 23.250033 54.167301, 22.564111 54.167301, 21.878189 54.167301, 21.878189 53.717641))</t>
+  </si>
+  <si>
     <t>elc_won_POL_011</t>
   </si>
   <si>
+    <t>POLYGON ((21.878189 52.81832, 21.878189 53.267981, 22.564111 53.267981, 23.250033 53.267981, 23.250033 52.81832, 23.935955 52.81832, 23.935955 52.36866, 23.935955 51.919, 23.935955 51.46934, 23.935955 51.01968, 23.250033 51.01968, 23.250033 51.46934, 22.564111 51.46934, 21.878189 51.46934, 21.878189 51.919, 21.878189 52.36866, 21.878189 52.81832))</t>
+  </si>
+  <si>
     <t>elc_won_POL_012</t>
   </si>
   <si>
+    <t>POLYGON ((19.820422 53.267981, 19.820422 53.717641, 20.506344 53.717641, 21.192267 53.717641, 21.878189 53.717641, 21.878189 53.267981, 21.878189 52.81832, 21.878189 52.36866, 21.878189 51.919, 21.192267 51.919, 20.506344 51.919, 19.820422 51.919, 19.820422 52.36866, 19.820422 52.81832, 19.820422 53.267981))</t>
+  </si>
+  <si>
     <t>elc_won_POL_013</t>
   </si>
   <si>
+    <t>POLYGON ((19.1345 51.01968, 18.448578 51.01968, 17.762656 51.01968, 17.762656 51.46934, 17.762656 51.919, 17.762656 52.36866, 18.448578 52.36866, 18.448578 51.919, 19.1345 51.919, 19.1345 51.46934, 19.1345 51.01968))</t>
+  </si>
+  <si>
     <t>elc_won_POL_014</t>
   </si>
   <si>
+    <t>POLYGON ((19.820422 51.919, 19.1345 51.919, 18.448578 51.919, 18.448578 52.36866, 17.762656 52.36866, 17.762656 52.81832, 18.448578 52.81832, 18.448578 53.267981, 19.1345 53.267981, 19.820422 53.267981, 19.820422 52.81832, 19.820422 52.36866, 19.820422 51.919))</t>
+  </si>
+  <si>
     <t>elc_won_POL_015</t>
   </si>
   <si>
+    <t>POLYGON ((19.820422 50.120359, 19.1345 50.120359, 18.448578 50.120359, 17.762656 50.120359, 17.762656 50.570019, 17.762656 51.01968, 18.448578 51.01968, 19.1345 51.01968, 19.820422 51.01968, 19.820422 50.570019, 19.820422 50.120359))</t>
+  </si>
+  <si>
     <t>elc_won_POL_016</t>
   </si>
   <si>
+    <t>POLYGON ((20.506344 50.120359, 19.820422 50.120359, 19.820422 50.570019, 19.820422 51.01968, 19.1345 51.01968, 19.1345 51.46934, 19.1345 51.919, 19.820422 51.919, 20.506344 51.919, 21.192267 51.919, 21.192267 51.46934, 21.192267 51.01968, 21.192267 50.570019, 21.192267 50.120359, 20.506344 50.120359))</t>
+  </si>
+  <si>
     <t>elc_won_POL_017</t>
   </si>
   <si>
+    <t>POLYGON ((21.192267 51.46934, 21.192267 51.919, 21.878189 51.919, 21.878189 51.46934, 22.564111 51.46934, 23.250033 51.46934, 23.250033 51.01968, 23.935955 51.01968, 23.935955 50.570019, 23.935955 50.120359, 23.250033 50.120359, 23.250033 49.670699, 22.564111 49.670699, 22.564111 50.120359, 21.878189 50.120359, 21.192267 50.120359, 21.192267 50.570019, 21.192267 51.01968, 21.192267 51.46934))</t>
+  </si>
+  <si>
     <t>elc_won_POL_018</t>
   </si>
   <si>
+    <t>POLYGON ((21.878189 49.670699, 21.878189 50.120359, 22.564111 50.120359, 22.564111 49.670699, 23.250033 49.670699, 23.250033 49.221039, 22.564111 49.221039, 21.878189 49.221039, 21.878189 49.670699))</t>
+  </si>
+  <si>
     <t>elc_won_POL_019</t>
   </si>
   <si>
-    <t>elc_won_POL_020</t>
-  </si>
-  <si>
-    <t>elc_won_POL_021</t>
-  </si>
-  <si>
-    <t>elc_won_POL_022</t>
-  </si>
-  <si>
-    <t>elc_won_POL_023</t>
-  </si>
-  <si>
-    <t>elc_won_POL_024</t>
-  </si>
-  <si>
-    <t>elc_won_POL_025</t>
-  </si>
-  <si>
-    <t>elc_won_POL_026</t>
-  </si>
-  <si>
-    <t>elc_won_POL_027</t>
-  </si>
-  <si>
-    <t>elc_won_POL_028</t>
-  </si>
-  <si>
-    <t>elc_won_POL_029</t>
-  </si>
-  <si>
-    <t>elc_won_POL_030</t>
-  </si>
-  <si>
-    <t>elc_won_POL_031</t>
-  </si>
-  <si>
-    <t>elc_won_POL_032</t>
-  </si>
-  <si>
-    <t>elc_won_POL_033</t>
-  </si>
-  <si>
-    <t>elc_won_POL_034</t>
-  </si>
-  <si>
-    <t>elc_won_POL_035</t>
-  </si>
-  <si>
-    <t>elc_won_POL_036</t>
-  </si>
-  <si>
-    <t>elc_won_POL_037</t>
-  </si>
-  <si>
-    <t>elc_won_POL_038</t>
-  </si>
-  <si>
-    <t>elc_won_POL_039</t>
-  </si>
-  <si>
-    <t>elc_won_POL_040</t>
-  </si>
-  <si>
-    <t>elc_won_POL_041</t>
-  </si>
-  <si>
-    <t>elc_won_POL_042</t>
-  </si>
-  <si>
-    <t>elc_won_POL_043</t>
-  </si>
-  <si>
-    <t>elc_won_POL_044</t>
-  </si>
-  <si>
-    <t>elc_won_POL_045</t>
-  </si>
-  <si>
-    <t>elc_won_POL_046</t>
-  </si>
-  <si>
-    <t>elc_won_POL_047</t>
-  </si>
-  <si>
-    <t>elc_won_POL_048</t>
+    <t>POLYGON ((21.878189 49.221039, 21.192267 49.221039, 20.506344 49.221039, 20.506344 49.670699, 20.506344 50.120359, 21.192267 50.120359, 21.878189 50.120359, 21.878189 49.670699, 21.878189 49.221039))</t>
   </si>
   <si>
     <t>co2</t>
@@ -1844,7 +1643,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1899,39 +1698,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1983,7 +1782,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -2094,6 +1893,13 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -2102,13 +1908,6 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -2173,39 +1972,19 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme 2013 - 2022" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE1B498B-64CF-4794-BDEA-CB5C495F4AF9}">
-  <dimension ref="B3:S158"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E09F76B-E4F8-4DEB-A8DA-5AE451F73EAE}">
+  <dimension ref="B3:S101"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="3" spans="2:19" x14ac:dyDescent="0.45">
@@ -4266,10 +4045,10 @@
         <v>8</v>
       </c>
       <c r="Q53">
-        <v>17.547809697404155</v>
+        <v>22.387884415840912</v>
       </c>
       <c r="R53">
-        <v>53.043150454655695</v>
+        <v>52.797852990301593</v>
       </c>
       <c r="S53" t="s">
         <v>239</v>
@@ -4310,10 +4089,10 @@
         <v>8</v>
       </c>
       <c r="Q54">
-        <v>23.133301060688336</v>
+        <v>22.436878727454864</v>
       </c>
       <c r="R54">
-        <v>53.187251027326219</v>
+        <v>53.758426235726397</v>
       </c>
       <c r="S54" t="s">
         <v>241</v>
@@ -4354,10 +4133,10 @@
         <v>8</v>
       </c>
       <c r="Q55">
-        <v>14.879031900155717</v>
+        <v>22.158862912599531</v>
       </c>
       <c r="R55">
-        <v>52.593490272793417</v>
+        <v>49.985302240943966</v>
       </c>
       <c r="S55" t="s">
         <v>243</v>
@@ -4398,10 +4177,10 @@
         <v>8</v>
       </c>
       <c r="Q56">
-        <v>16.047850156734548</v>
+        <v>20.576363415677669</v>
       </c>
       <c r="R56">
-        <v>50.794849545344334</v>
+        <v>50.179698397399775</v>
       </c>
       <c r="S56" t="s">
         <v>245</v>
@@ -4442,10 +4221,10 @@
         <v>8</v>
       </c>
       <c r="Q57">
-        <v>17.419694531519191</v>
+        <v>22.647999312422595</v>
       </c>
       <c r="R57">
-        <v>50.794849545344334</v>
+        <v>51.755872298670091</v>
       </c>
       <c r="S57" t="s">
         <v>247</v>
@@ -4486,10 +4265,10 @@
         <v>8</v>
       </c>
       <c r="Q58">
-        <v>16.700680826967581</v>
+        <v>22.614693947996503</v>
       </c>
       <c r="R58">
-        <v>50.20437696578923</v>
+        <v>50.677937554331706</v>
       </c>
       <c r="S58" t="s">
         <v>249</v>
@@ -4530,10 +4309,10 @@
         <v>8</v>
       </c>
       <c r="Q59">
-        <v>19.477461093696157</v>
+        <v>15.177025576701782</v>
       </c>
       <c r="R59">
-        <v>53.492810636517952</v>
+        <v>53.385570698209328</v>
       </c>
       <c r="S59" t="s">
         <v>251</v>
@@ -4574,10 +4353,10 @@
         <v>8</v>
       </c>
       <c r="Q60">
-        <v>17.419694531519191</v>
+        <v>16.851528118709499</v>
       </c>
       <c r="R60">
-        <v>54.3921310002425</v>
+        <v>53.556913702673697</v>
       </c>
       <c r="S60" t="s">
         <v>253</v>
@@ -4618,10 +4397,10 @@
         <v>8</v>
       </c>
       <c r="Q61">
-        <v>20.701782962343</v>
+        <v>18.833039725101798</v>
       </c>
       <c r="R61">
-        <v>54.18832903488137</v>
+        <v>52.848472544632912</v>
       </c>
       <c r="S61" t="s">
         <v>255</v>
@@ -4662,10 +4441,10 @@
         <v>8</v>
       </c>
       <c r="Q62">
-        <v>15.361927969342226</v>
+        <v>20.474987843539957</v>
       </c>
       <c r="R62">
-        <v>50.794849545344334</v>
+        <v>53.867432812752376</v>
       </c>
       <c r="S62" t="s">
         <v>257</v>
@@ -4706,10 +4485,10 @@
         <v>8</v>
       </c>
       <c r="Q63">
-        <v>18.782950053433741</v>
+        <v>18.950202712790809</v>
       </c>
       <c r="R63">
-        <v>53.942470818380237</v>
+        <v>53.834708755581374</v>
       </c>
       <c r="S63" t="s">
         <v>259</v>
@@ -4750,10 +4529,10 @@
         <v>8</v>
       </c>
       <c r="Q64">
-        <v>21.887953266623537</v>
+        <v>16.541594041004011</v>
       </c>
       <c r="R64">
-        <v>53.014105550648793</v>
+        <v>52.292582195464313</v>
       </c>
       <c r="S64" t="s">
         <v>261</v>
@@ -4794,10 +4573,10 @@
         <v>8</v>
       </c>
       <c r="Q65">
-        <v>14.875712340153196</v>
+        <v>16.597184145059202</v>
       </c>
       <c r="R65">
-        <v>51.892398915433461</v>
+        <v>51.381036311175727</v>
       </c>
       <c r="S65" t="s">
         <v>263</v>
@@ -4838,10 +4617,10 @@
         <v>8</v>
       </c>
       <c r="Q66">
-        <v>14.904646511080676</v>
+        <v>15.346251681111026</v>
       </c>
       <c r="R66">
-        <v>53.792584091092806</v>
+        <v>51.202873879217471</v>
       </c>
       <c r="S66" t="s">
         <v>265</v>
@@ -4882,10 +4661,10 @@
         <v>8</v>
       </c>
       <c r="Q67">
-        <v>22.221149843265444</v>
+        <v>15.145356416678331</v>
       </c>
       <c r="R67">
-        <v>49.445868999757522</v>
+        <v>52.186880964694659</v>
       </c>
       <c r="S67" t="s">
         <v>267</v>
@@ -4926,10 +4705,10 @@
         <v>8</v>
       </c>
       <c r="Q68">
-        <v>22.603515833460445</v>
+        <v>17.083147938913381</v>
       </c>
       <c r="R68">
-        <v>54.312064653523798</v>
+        <v>50.673345049899048</v>
       </c>
       <c r="S68" t="s">
         <v>269</v>
@@ -4970,10 +4749,10 @@
         <v>8</v>
       </c>
       <c r="Q69">
-        <v>19.477461093696157</v>
+        <v>18.911500370089843</v>
       </c>
       <c r="R69">
-        <v>51.244509727206612</v>
+        <v>50.08331213626267</v>
       </c>
       <c r="S69" t="s">
         <v>271</v>
@@ -5014,10 +4793,10 @@
         <v>8</v>
       </c>
       <c r="Q70">
-        <v>18.791538906303831</v>
+        <v>20.781405442235567</v>
       </c>
       <c r="R70">
-        <v>51.690437204601821</v>
+        <v>52.366491870473581</v>
       </c>
       <c r="S70" t="s">
         <v>273</v>
@@ -5058,10 +4837,10 @@
         <v>8</v>
       </c>
       <c r="Q71">
-        <v>23.592994218050087</v>
+        <v>20.402957702269411</v>
       </c>
       <c r="R71">
-        <v>50.345189363482064</v>
+        <v>51.12109494883768</v>
       </c>
       <c r="S71" t="s">
         <v>275</v>
@@ -5102,10 +4881,10 @@
         <v>8</v>
       </c>
       <c r="Q72">
-        <v>16.349304708128344</v>
+        <v>18.792464723500991</v>
       </c>
       <c r="R72">
-        <v>53.94247081838023</v>
+        <v>51.330784626906521</v>
       </c>
       <c r="S72" t="s">
         <v>277</v>
@@ -5146,10 +4925,10 @@
         <v>8</v>
       </c>
       <c r="Q73">
-        <v>16.047850156734548</v>
+        <v>19.270410803611803</v>
       </c>
       <c r="R73">
-        <v>51.919000000000011</v>
+        <v>54.260516439232255</v>
       </c>
       <c r="S73" t="s">
         <v>279</v>
@@ -5190,10 +4969,10 @@
         <v>8</v>
       </c>
       <c r="Q74">
-        <v>18.791538906303831</v>
+        <v>19.132199145306835</v>
       </c>
       <c r="R74">
-        <v>49.895529181619793</v>
+        <v>55.159813342891759</v>
       </c>
       <c r="S74" t="s">
         <v>281</v>
@@ -5234,10 +5013,10 @@
         <v>8</v>
       </c>
       <c r="Q75">
-        <v>20.8493054684808</v>
+        <v>19.209580353300481</v>
       </c>
       <c r="R75">
-        <v>49.8599303133334</v>
+        <v>54.710164987068232</v>
       </c>
       <c r="S75" t="s">
         <v>283</v>
@@ -5278,10 +5057,10 @@
         <v>8</v>
       </c>
       <c r="Q76">
-        <v>23.486875120767376</v>
+        <v>16.941376551896891</v>
       </c>
       <c r="R76">
-        <v>51.710185794668313</v>
+        <v>55.60946078087305</v>
       </c>
       <c r="S76" t="s">
         <v>285</v>
@@ -5322,10 +5101,10 @@
         <v>8</v>
       </c>
       <c r="Q77">
-        <v>22.221149843265444</v>
+        <v>18.450551982707839</v>
       </c>
       <c r="R77">
-        <v>49.895529181619793</v>
+        <v>55.609461280132123</v>
       </c>
       <c r="S77" t="s">
         <v>287</v>
@@ -5366,10 +5145,10 @@
         <v>8</v>
       </c>
       <c r="Q78">
-        <v>20.164133104060543</v>
+        <v>17.878286085105412</v>
       </c>
       <c r="R78">
-        <v>51.018998941964419</v>
+        <v>55.159812876695007</v>
       </c>
       <c r="S78" t="s">
         <v>289</v>
@@ -5410,10 +5189,10 @@
         <v>8</v>
       </c>
       <c r="Q79">
-        <v>21.535227655873118</v>
+        <v>15.47382532166216</v>
       </c>
       <c r="R79">
-        <v>50.345189363482064</v>
+        <v>54.260515174922851</v>
       </c>
       <c r="S79" t="s">
         <v>291</v>
@@ -5454,10 +5233,10 @@
         <v>8</v>
       </c>
       <c r="Q80">
-        <v>22.221149843265444</v>
+        <v>15.28816677077992</v>
       </c>
       <c r="R80">
-        <v>50.345189363482064</v>
+        <v>54.710163723178738</v>
       </c>
       <c r="S80" t="s">
         <v>293</v>
@@ -5498,10 +5277,10 @@
         <v>8</v>
       </c>
       <c r="Q81">
-        <v>19.477461093696157</v>
+        <v>16.268392183867956</v>
       </c>
       <c r="R81">
-        <v>50.794849545344334</v>
+        <v>55.159812379291822</v>
       </c>
       <c r="S81" t="s">
         <v>295</v>
@@ -5542,10 +5321,10 @@
         <v>8</v>
       </c>
       <c r="Q82">
-        <v>18.791538906303831</v>
+        <v>16.047809605897839</v>
       </c>
       <c r="R82">
-        <v>53.043150454655688</v>
+        <v>54.710163913347117</v>
       </c>
       <c r="S82" t="s">
         <v>297</v>
@@ -5586,10 +5365,10 @@
         <v>8</v>
       </c>
       <c r="Q83">
-        <v>21.535227655873118</v>
+        <v>16.384709287577795</v>
       </c>
       <c r="R83">
-        <v>50.794849545344334</v>
+        <v>50.776690615375294</v>
       </c>
       <c r="S83" t="s">
         <v>299</v>
@@ -5633,7 +5412,7 @@
         <v>17.419694531519191</v>
       </c>
       <c r="R84">
-        <v>50.345189363482064</v>
+        <v>49.895529181619793</v>
       </c>
       <c r="S84" t="s">
         <v>301</v>
@@ -5674,10 +5453,10 @@
         <v>8</v>
       </c>
       <c r="Q85">
-        <v>18.105616718911509</v>
+        <v>15.256062905619441</v>
       </c>
       <c r="R85">
-        <v>52.143830090931147</v>
+        <v>51.98468831119169</v>
       </c>
       <c r="S85" t="s">
         <v>303</v>
@@ -5718,10 +5497,10 @@
         <v>8</v>
       </c>
       <c r="Q86">
-        <v>16.733772344126869</v>
+        <v>16.80515814440529</v>
       </c>
       <c r="R86">
-        <v>54.3921310002425</v>
+        <v>52.124016263770471</v>
       </c>
       <c r="S86" t="s">
         <v>305</v>
@@ -5762,10 +5541,10 @@
         <v>8</v>
       </c>
       <c r="Q87">
-        <v>21.135688356956784</v>
+        <v>19.003551538461117</v>
       </c>
       <c r="R87">
-        <v>52.239739576014692</v>
+        <v>53.788484402851722</v>
       </c>
       <c r="S87" t="s">
         <v>307</v>
@@ -5806,10 +5585,10 @@
         <v>8</v>
       </c>
       <c r="Q88">
-        <v>18.791538906303831</v>
+        <v>15.172985574189886</v>
       </c>
       <c r="R88">
-        <v>50.345189363482064</v>
+        <v>53.270513397783269</v>
       </c>
       <c r="S88" t="s">
         <v>309</v>
@@ -5850,10 +5629,10 @@
         <v>8</v>
       </c>
       <c r="Q89">
-        <v>21.708559845867718</v>
+        <v>17.551521574400923</v>
       </c>
       <c r="R89">
-        <v>54.126240919490058</v>
+        <v>54.392131000242507</v>
       </c>
       <c r="S89" t="s">
         <v>311</v>
@@ -5867,10 +5646,10 @@
         <v>8</v>
       </c>
       <c r="Q90">
-        <v>16.559716621285517</v>
+        <v>16.852061394622268</v>
       </c>
       <c r="R90">
-        <v>53.043150454655688</v>
+        <v>53.40601844225278</v>
       </c>
       <c r="S90" t="s">
         <v>313</v>
@@ -5884,10 +5663,10 @@
         <v>8</v>
       </c>
       <c r="Q91">
-        <v>18.105616718911509</v>
+        <v>22.728951916805229</v>
       </c>
       <c r="R91">
-        <v>50.345189363482064</v>
+        <v>53.629053884575626</v>
       </c>
       <c r="S91" t="s">
         <v>315</v>
@@ -5901,10 +5680,10 @@
         <v>8</v>
       </c>
       <c r="Q92">
-        <v>14.676005781949902</v>
+        <v>21.016862912105651</v>
       </c>
       <c r="R92">
-        <v>53.043150454655688</v>
+        <v>54.067358273794383</v>
       </c>
       <c r="S92" t="s">
         <v>317</v>
@@ -5918,10 +5697,10 @@
         <v>8</v>
       </c>
       <c r="Q93">
-        <v>19.477461093696157</v>
+        <v>22.557805508871297</v>
       </c>
       <c r="R93">
-        <v>50.345189363482064</v>
+        <v>52.454344370054137</v>
       </c>
       <c r="S93" t="s">
         <v>319</v>
@@ -5935,10 +5714,10 @@
         <v>8</v>
       </c>
       <c r="Q94">
-        <v>19.439611648373191</v>
+        <v>20.648531569729403</v>
       </c>
       <c r="R94">
-        <v>49.720309400782064</v>
+        <v>52.768785613368301</v>
       </c>
       <c r="S94" t="s">
         <v>321</v>
@@ -5952,10 +5731,10 @@
         <v>8</v>
       </c>
       <c r="Q95">
-        <v>19.477461093696157</v>
+        <v>18.369571653809839</v>
       </c>
       <c r="R95">
-        <v>53.942470818380237</v>
+        <v>51.799686803699899</v>
       </c>
       <c r="S95" t="s">
         <v>323</v>
@@ -5969,10 +5748,10 @@
         <v>8</v>
       </c>
       <c r="Q96">
-        <v>19.477461093696157</v>
+        <v>19.027975647671131</v>
       </c>
       <c r="R96">
-        <v>52.593490272793417</v>
+        <v>52.655496867703171</v>
       </c>
       <c r="S96" t="s">
         <v>325</v>
@@ -5986,10 +5765,10 @@
         <v>8</v>
       </c>
       <c r="Q97">
-        <v>17.419694531519191</v>
+        <v>19.265584431429922</v>
       </c>
       <c r="R97">
-        <v>51.244509727206605</v>
+        <v>50.628803361963257</v>
       </c>
       <c r="S97" t="s">
         <v>327</v>
@@ -6003,10 +5782,10 @@
         <v>8</v>
       </c>
       <c r="Q98">
-        <v>18.105616718911509</v>
+        <v>20.044508863733864</v>
       </c>
       <c r="R98">
-        <v>54.3921310002425</v>
+        <v>51.478266767104472</v>
       </c>
       <c r="S98" t="s">
         <v>329</v>
@@ -6020,10 +5799,10 @@
         <v>8</v>
       </c>
       <c r="Q99">
-        <v>20.163383281088475</v>
+        <v>22.909847640550961</v>
       </c>
       <c r="R99">
-        <v>49.598802215787757</v>
+        <v>50.868423259833534</v>
       </c>
       <c r="S99" t="s">
         <v>331</v>
@@ -6037,10 +5816,10 @@
         <v>8</v>
       </c>
       <c r="Q100">
-        <v>22.178267215011683</v>
+        <v>22.221487288334288</v>
       </c>
       <c r="R100">
-        <v>51.90882588090858</v>
+        <v>49.853731539665588</v>
       </c>
       <c r="S100" t="s">
         <v>333</v>
@@ -6054,982 +5833,13 @@
         <v>8</v>
       </c>
       <c r="Q101">
-        <v>19.270410803611803</v>
+        <v>21.524822746291907</v>
       </c>
       <c r="R101">
-        <v>54.260516439232255</v>
+        <v>49.648253092611611</v>
       </c>
       <c r="S101" t="s">
         <v>335</v>
-      </c>
-    </row>
-    <row r="102" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O102" t="s">
-        <v>336</v>
-      </c>
-      <c r="P102" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q102">
-        <v>19.336482428831868</v>
-      </c>
-      <c r="R102">
-        <v>54.923226170318472</v>
-      </c>
-      <c r="S102" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="103" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O103" t="s">
-        <v>338</v>
-      </c>
-      <c r="P103" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q103">
-        <v>15.28816677077992</v>
-      </c>
-      <c r="R103">
-        <v>54.710163723178738</v>
-      </c>
-      <c r="S103" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="104" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O104" t="s">
-        <v>340</v>
-      </c>
-      <c r="P104" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q104">
-        <v>15.361892353269836</v>
-      </c>
-      <c r="R104">
-        <v>54.26051514610343</v>
-      </c>
-      <c r="S104" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="105" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O105" t="s">
-        <v>342</v>
-      </c>
-      <c r="P105" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q105">
-        <v>16.047809989056592</v>
-      </c>
-      <c r="R105">
-        <v>54.260515322706873</v>
-      </c>
-      <c r="S105" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="106" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O106" t="s">
-        <v>344</v>
-      </c>
-      <c r="P106" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q106">
-        <v>16.360336631261571</v>
-      </c>
-      <c r="R106">
-        <v>55.248657504176741</v>
-      </c>
-      <c r="S106" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="107" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O107" t="s">
-        <v>346</v>
-      </c>
-      <c r="P107" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q107">
-        <v>16.047809605897839</v>
-      </c>
-      <c r="R107">
-        <v>54.710163913347117</v>
-      </c>
-      <c r="S107" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="108" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O108" t="s">
-        <v>348</v>
-      </c>
-      <c r="P108" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q108">
-        <v>17.419644121917074</v>
-      </c>
-      <c r="R108">
-        <v>55.329041014058205</v>
-      </c>
-      <c r="S108" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="109" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O109" t="s">
-        <v>350</v>
-      </c>
-      <c r="P109" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q109">
-        <v>18.450551982707839</v>
-      </c>
-      <c r="R109">
-        <v>55.609461280132123</v>
-      </c>
-      <c r="S109" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="110" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O110" t="s">
-        <v>352</v>
-      </c>
-      <c r="P110" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q110">
-        <v>18.559290016941631</v>
-      </c>
-      <c r="R110">
-        <v>55.159813121219983</v>
-      </c>
-      <c r="S110" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="111" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O111" t="s">
-        <v>354</v>
-      </c>
-      <c r="P111" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q111">
-        <v>17.527280239724924</v>
-      </c>
-      <c r="R111">
-        <v>53.043150454655688</v>
-      </c>
-      <c r="S111" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="112" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O112" t="s">
-        <v>355</v>
-      </c>
-      <c r="P112" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q112">
-        <v>23.129035583947079</v>
-      </c>
-      <c r="R112">
-        <v>53.220134909443168</v>
-      </c>
-      <c r="S112" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="113" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O113" t="s">
-        <v>356</v>
-      </c>
-      <c r="P113" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q113">
-        <v>15.16673080647341</v>
-      </c>
-      <c r="R113">
-        <v>52.645003231161056</v>
-      </c>
-      <c r="S113" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="114" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O114" t="s">
-        <v>357</v>
-      </c>
-      <c r="P114" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q114">
-        <v>16.109615043411317</v>
-      </c>
-      <c r="R114">
-        <v>50.927035346571493</v>
-      </c>
-      <c r="S114" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="115" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O115" t="s">
-        <v>358</v>
-      </c>
-      <c r="P115" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q115">
-        <v>17.419694531519191</v>
-      </c>
-      <c r="R115">
-        <v>50.794849545344334</v>
-      </c>
-      <c r="S115" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="116" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O116" t="s">
-        <v>359</v>
-      </c>
-      <c r="P116" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q116">
-        <v>16.658975418762132</v>
-      </c>
-      <c r="R116">
-        <v>50.279268599866718</v>
-      </c>
-      <c r="S116" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="117" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O117" t="s">
-        <v>360</v>
-      </c>
-      <c r="P117" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q117">
-        <v>19.477461093696157</v>
-      </c>
-      <c r="R117">
-        <v>53.492810636517952</v>
-      </c>
-      <c r="S117" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="118" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O118" t="s">
-        <v>361</v>
-      </c>
-      <c r="P118" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q118">
-        <v>17.419694531519191</v>
-      </c>
-      <c r="R118">
-        <v>54.3921310002425</v>
-      </c>
-      <c r="S118" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="119" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O119" t="s">
-        <v>362</v>
-      </c>
-      <c r="P119" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q119">
-        <v>20.6609465803446</v>
-      </c>
-      <c r="R119">
-        <v>54.215908666282239</v>
-      </c>
-      <c r="S119" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="120" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O120" t="s">
-        <v>363</v>
-      </c>
-      <c r="P120" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q120">
-        <v>15.361927969342226</v>
-      </c>
-      <c r="R120">
-        <v>50.794849545344334</v>
-      </c>
-      <c r="S120" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="121" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O121" t="s">
-        <v>364</v>
-      </c>
-      <c r="P121" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q121">
-        <v>18.791538906303831</v>
-      </c>
-      <c r="R121">
-        <v>53.942470818380237</v>
-      </c>
-      <c r="S121" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="122" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O122" t="s">
-        <v>365</v>
-      </c>
-      <c r="P122" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q122">
-        <v>21.814778267800516</v>
-      </c>
-      <c r="R122">
-        <v>53.031656729647359</v>
-      </c>
-      <c r="S122" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="123" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O123" t="s">
-        <v>366</v>
-      </c>
-      <c r="P123" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q123">
-        <v>14.819703456589529</v>
-      </c>
-      <c r="R123">
-        <v>51.922744864982697</v>
-      </c>
-      <c r="S123" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="124" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O124" t="s">
-        <v>367</v>
-      </c>
-      <c r="P124" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q124">
-        <v>14.904646511080676</v>
-      </c>
-      <c r="R124">
-        <v>53.792584091092806</v>
-      </c>
-      <c r="S124" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="125" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O125" t="s">
-        <v>368</v>
-      </c>
-      <c r="P125" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q125">
-        <v>22.608798223120601</v>
-      </c>
-      <c r="R125">
-        <v>49.490542406443481</v>
-      </c>
-      <c r="S125" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="126" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O126" t="s">
-        <v>369</v>
-      </c>
-      <c r="P126" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q126">
-        <v>22.581041961268149</v>
-      </c>
-      <c r="R126">
-        <v>54.334057528005133</v>
-      </c>
-      <c r="S126" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="127" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O127" t="s">
-        <v>370</v>
-      </c>
-      <c r="P127" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q127">
-        <v>19.484239146008623</v>
-      </c>
-      <c r="R127">
-        <v>51.248953117858669</v>
-      </c>
-      <c r="S127" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="128" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O128" t="s">
-        <v>371</v>
-      </c>
-      <c r="P128" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q128">
-        <v>18.791538906303831</v>
-      </c>
-      <c r="R128">
-        <v>51.694169909068883</v>
-      </c>
-      <c r="S128" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="129" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O129" t="s">
-        <v>372</v>
-      </c>
-      <c r="P129" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q129">
-        <v>23.592994218050087</v>
-      </c>
-      <c r="R129">
-        <v>50.345189363482064</v>
-      </c>
-      <c r="S129" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="130" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O130" t="s">
-        <v>373</v>
-      </c>
-      <c r="P130" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q130">
-        <v>16.171652634518797</v>
-      </c>
-      <c r="R130">
-        <v>53.832005977672566</v>
-      </c>
-      <c r="S130" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="131" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O131" t="s">
-        <v>374</v>
-      </c>
-      <c r="P131" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q131">
-        <v>16.047850156734548</v>
-      </c>
-      <c r="R131">
-        <v>51.861260822850973</v>
-      </c>
-      <c r="S131" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="132" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O132" t="s">
-        <v>375</v>
-      </c>
-      <c r="P132" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q132">
-        <v>18.791538906303831</v>
-      </c>
-      <c r="R132">
-        <v>49.895529181619793</v>
-      </c>
-      <c r="S132" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="133" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O133" t="s">
-        <v>376</v>
-      </c>
-      <c r="P133" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q133">
-        <v>20.8493054684808</v>
-      </c>
-      <c r="R133">
-        <v>49.91077177331681</v>
-      </c>
-      <c r="S133" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="134" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O134" t="s">
-        <v>377</v>
-      </c>
-      <c r="P134" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q134">
-        <v>23.508838878966412</v>
-      </c>
-      <c r="R134">
-        <v>51.694088645539807</v>
-      </c>
-      <c r="S134" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="135" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O135" t="s">
-        <v>378</v>
-      </c>
-      <c r="P135" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q135">
-        <v>22.221149843265444</v>
-      </c>
-      <c r="R135">
-        <v>49.895529181619793</v>
-      </c>
-      <c r="S135" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="136" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O136" t="s">
-        <v>379</v>
-      </c>
-      <c r="P136" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q136">
-        <v>20.409532233050189</v>
-      </c>
-      <c r="R136">
-        <v>50.93087347353012</v>
-      </c>
-      <c r="S136" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="137" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O137" t="s">
-        <v>380</v>
-      </c>
-      <c r="P137" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q137">
-        <v>21.535227655873118</v>
-      </c>
-      <c r="R137">
-        <v>50.345189363482064</v>
-      </c>
-      <c r="S137" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="138" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O138" t="s">
-        <v>381</v>
-      </c>
-      <c r="P138" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q138">
-        <v>22.221149843265444</v>
-      </c>
-      <c r="R138">
-        <v>50.408257221982232</v>
-      </c>
-      <c r="S138" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="139" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O139" t="s">
-        <v>382</v>
-      </c>
-      <c r="P139" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q139">
-        <v>19.266410025240862</v>
-      </c>
-      <c r="R139">
-        <v>50.794849545344334</v>
-      </c>
-      <c r="S139" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="140" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O140" t="s">
-        <v>383</v>
-      </c>
-      <c r="P140" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q140">
-        <v>18.791538906303831</v>
-      </c>
-      <c r="R140">
-        <v>53.043150454655681</v>
-      </c>
-      <c r="S140" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="141" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O141" t="s">
-        <v>384</v>
-      </c>
-      <c r="P141" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q141">
-        <v>21.535227655873118</v>
-      </c>
-      <c r="R141">
-        <v>50.888635183462817</v>
-      </c>
-      <c r="S141" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="142" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O142" t="s">
-        <v>385</v>
-      </c>
-      <c r="P142" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q142">
-        <v>17.419694531519191</v>
-      </c>
-      <c r="R142">
-        <v>50.345189363482064</v>
-      </c>
-      <c r="S142" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="143" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O143" t="s">
-        <v>386</v>
-      </c>
-      <c r="P143" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q143">
-        <v>18.41752059971844</v>
-      </c>
-      <c r="R143">
-        <v>52.143830090931147</v>
-      </c>
-      <c r="S143" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="144" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O144" t="s">
-        <v>387</v>
-      </c>
-      <c r="P144" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q144">
-        <v>16.733772344126869</v>
-      </c>
-      <c r="R144">
-        <v>54.3921310002425</v>
-      </c>
-      <c r="S144" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="145" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O145" t="s">
-        <v>388</v>
-      </c>
-      <c r="P145" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q145">
-        <v>21.182327215095697</v>
-      </c>
-      <c r="R145">
-        <v>52.208865366630896</v>
-      </c>
-      <c r="S145" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="146" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O146" t="s">
-        <v>389</v>
-      </c>
-      <c r="P146" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q146">
-        <v>18.791538906303831</v>
-      </c>
-      <c r="R146">
-        <v>50.345189363482064</v>
-      </c>
-      <c r="S146" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="147" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O147" t="s">
-        <v>390</v>
-      </c>
-      <c r="P147" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q147">
-        <v>21.703352022374737</v>
-      </c>
-      <c r="R147">
-        <v>54.13287173739576</v>
-      </c>
-      <c r="S147" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="148" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O148" t="s">
-        <v>391</v>
-      </c>
-      <c r="P148" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q148">
-        <v>16.588549565253906</v>
-      </c>
-      <c r="R148">
-        <v>53.010781572357352</v>
-      </c>
-      <c r="S148" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="149" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O149" t="s">
-        <v>392</v>
-      </c>
-      <c r="P149" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q149">
-        <v>18.105616718911509</v>
-      </c>
-      <c r="R149">
-        <v>50.345189363482064</v>
-      </c>
-      <c r="S149" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="150" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O150" t="s">
-        <v>393</v>
-      </c>
-      <c r="P150" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q150">
-        <v>14.676005781949904</v>
-      </c>
-      <c r="R150">
-        <v>53.043150454655688</v>
-      </c>
-      <c r="S150" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="151" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O151" t="s">
-        <v>394</v>
-      </c>
-      <c r="P151" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q151">
-        <v>19.477461093696157</v>
-      </c>
-      <c r="R151">
-        <v>50.345189363482064</v>
-      </c>
-      <c r="S151" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="152" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O152" t="s">
-        <v>395</v>
-      </c>
-      <c r="P152" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q152">
-        <v>19.403780261531288</v>
-      </c>
-      <c r="R152">
-        <v>49.674521586203319</v>
-      </c>
-      <c r="S152" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="153" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O153" t="s">
-        <v>396</v>
-      </c>
-      <c r="P153" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q153">
-        <v>19.477461093696157</v>
-      </c>
-      <c r="R153">
-        <v>53.942470818380237</v>
-      </c>
-      <c r="S153" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="154" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O154" t="s">
-        <v>397</v>
-      </c>
-      <c r="P154" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q154">
-        <v>19.869295209633083</v>
-      </c>
-      <c r="R154">
-        <v>52.66680063954901</v>
-      </c>
-      <c r="S154" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="155" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O155" t="s">
-        <v>398</v>
-      </c>
-      <c r="P155" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q155">
-        <v>17.419694531519191</v>
-      </c>
-      <c r="R155">
-        <v>51.244509727206612</v>
-      </c>
-      <c r="S155" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="156" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O156" t="s">
-        <v>399</v>
-      </c>
-      <c r="P156" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q156">
-        <v>18.105616718911509</v>
-      </c>
-      <c r="R156">
-        <v>54.3921310002425</v>
-      </c>
-      <c r="S156" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="157" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O157" t="s">
-        <v>400</v>
-      </c>
-      <c r="P157" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q157">
-        <v>20.163383281088478</v>
-      </c>
-      <c r="R157">
-        <v>49.63609311948067</v>
-      </c>
-      <c r="S157" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="158" spans="15:19" x14ac:dyDescent="0.45">
-      <c r="O158" t="s">
-        <v>401</v>
-      </c>
-      <c r="P158" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q158">
-        <v>22.196099857010601</v>
-      </c>
-      <c r="R158">
-        <v>51.918163705689693</v>
-      </c>
-      <c r="S158" t="s">
-        <v>333</v>
       </c>
     </row>
   </sheetData>
@@ -7038,7 +5848,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10FD80F3-C1F0-45AC-A912-54D2BBE5DE53}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2099808-1E00-490F-92CF-6F939CD2F271}">
   <dimension ref="B3:L62"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -7087,25 +5897,25 @@
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E5" t="s">
-        <v>403</v>
+        <v>337</v>
       </c>
       <c r="F5" t="s">
-        <v>404</v>
+        <v>338</v>
       </c>
       <c r="G5" t="s">
-        <v>405</v>
+        <v>339</v>
       </c>
       <c r="H5" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K5" t="s">
-        <v>405</v>
+        <v>339</v>
       </c>
       <c r="L5" t="s">
-        <v>540</v>
+        <v>474</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.45">
@@ -7116,25 +5926,25 @@
         <v>8</v>
       </c>
       <c r="D6" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E6" t="s">
-        <v>407</v>
+        <v>341</v>
       </c>
       <c r="F6" t="s">
-        <v>408</v>
+        <v>342</v>
       </c>
       <c r="G6" t="s">
-        <v>409</v>
+        <v>343</v>
       </c>
       <c r="H6" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K6" t="s">
-        <v>409</v>
+        <v>343</v>
       </c>
       <c r="L6" t="s">
-        <v>541</v>
+        <v>475</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.45">
@@ -7145,25 +5955,25 @@
         <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E7" t="s">
-        <v>410</v>
+        <v>344</v>
       </c>
       <c r="F7" t="s">
-        <v>411</v>
+        <v>345</v>
       </c>
       <c r="G7" t="s">
-        <v>412</v>
+        <v>346</v>
       </c>
       <c r="H7" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K7" t="s">
-        <v>412</v>
+        <v>346</v>
       </c>
       <c r="L7" t="s">
-        <v>542</v>
+        <v>476</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.45">
@@ -7174,25 +5984,25 @@
         <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E8" t="s">
-        <v>413</v>
+        <v>347</v>
       </c>
       <c r="F8" t="s">
-        <v>414</v>
+        <v>348</v>
       </c>
       <c r="G8" t="s">
-        <v>415</v>
+        <v>349</v>
       </c>
       <c r="H8" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K8" t="s">
-        <v>415</v>
+        <v>349</v>
       </c>
       <c r="L8" t="s">
-        <v>543</v>
+        <v>477</v>
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.45">
@@ -7203,25 +6013,25 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E9" t="s">
-        <v>416</v>
+        <v>350</v>
       </c>
       <c r="F9" t="s">
-        <v>417</v>
+        <v>351</v>
       </c>
       <c r="G9" t="s">
-        <v>418</v>
+        <v>352</v>
       </c>
       <c r="H9" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K9" t="s">
-        <v>418</v>
+        <v>352</v>
       </c>
       <c r="L9" t="s">
-        <v>544</v>
+        <v>478</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.45">
@@ -7232,25 +6042,25 @@
         <v>8</v>
       </c>
       <c r="D10" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E10" t="s">
-        <v>419</v>
+        <v>353</v>
       </c>
       <c r="F10" t="s">
-        <v>420</v>
+        <v>354</v>
       </c>
       <c r="G10" t="s">
-        <v>421</v>
+        <v>355</v>
       </c>
       <c r="H10" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K10" t="s">
-        <v>421</v>
+        <v>355</v>
       </c>
       <c r="L10" t="s">
-        <v>545</v>
+        <v>479</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.45">
@@ -7261,25 +6071,25 @@
         <v>8</v>
       </c>
       <c r="D11" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E11" t="s">
-        <v>422</v>
+        <v>356</v>
       </c>
       <c r="F11" t="s">
-        <v>404</v>
+        <v>338</v>
       </c>
       <c r="G11" t="s">
-        <v>423</v>
+        <v>357</v>
       </c>
       <c r="H11" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K11" t="s">
-        <v>423</v>
+        <v>357</v>
       </c>
       <c r="L11" t="s">
-        <v>546</v>
+        <v>480</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.45">
@@ -7290,25 +6100,25 @@
         <v>8</v>
       </c>
       <c r="D12" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E12" t="s">
-        <v>424</v>
+        <v>358</v>
       </c>
       <c r="F12" t="s">
-        <v>425</v>
+        <v>359</v>
       </c>
       <c r="G12" t="s">
-        <v>426</v>
+        <v>360</v>
       </c>
       <c r="H12" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K12" t="s">
-        <v>426</v>
+        <v>360</v>
       </c>
       <c r="L12" t="s">
-        <v>547</v>
+        <v>481</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.45">
@@ -7319,25 +6129,25 @@
         <v>8</v>
       </c>
       <c r="D13" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E13" t="s">
-        <v>427</v>
+        <v>361</v>
       </c>
       <c r="F13" t="s">
-        <v>428</v>
+        <v>362</v>
       </c>
       <c r="G13" t="s">
-        <v>429</v>
+        <v>363</v>
       </c>
       <c r="H13" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K13" t="s">
-        <v>429</v>
+        <v>363</v>
       </c>
       <c r="L13" t="s">
-        <v>548</v>
+        <v>482</v>
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.45">
@@ -7348,25 +6158,25 @@
         <v>8</v>
       </c>
       <c r="D14" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E14" t="s">
-        <v>430</v>
+        <v>364</v>
       </c>
       <c r="F14" t="s">
-        <v>414</v>
+        <v>348</v>
       </c>
       <c r="G14" t="s">
-        <v>431</v>
+        <v>365</v>
       </c>
       <c r="H14" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K14" t="s">
-        <v>431</v>
+        <v>365</v>
       </c>
       <c r="L14" t="s">
-        <v>549</v>
+        <v>483</v>
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.45">
@@ -7377,25 +6187,25 @@
         <v>8</v>
       </c>
       <c r="D15" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E15" t="s">
-        <v>432</v>
+        <v>366</v>
       </c>
       <c r="F15" t="s">
-        <v>428</v>
+        <v>362</v>
       </c>
       <c r="G15" t="s">
-        <v>433</v>
+        <v>367</v>
       </c>
       <c r="H15" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K15" t="s">
-        <v>433</v>
+        <v>367</v>
       </c>
       <c r="L15" t="s">
-        <v>550</v>
+        <v>484</v>
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.45">
@@ -7406,25 +6216,25 @@
         <v>8</v>
       </c>
       <c r="D16" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E16" t="s">
-        <v>434</v>
+        <v>368</v>
       </c>
       <c r="F16" t="s">
-        <v>408</v>
+        <v>342</v>
       </c>
       <c r="G16" t="s">
-        <v>435</v>
+        <v>369</v>
       </c>
       <c r="H16" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K16" t="s">
-        <v>435</v>
+        <v>369</v>
       </c>
       <c r="L16" t="s">
-        <v>551</v>
+        <v>485</v>
       </c>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.45">
@@ -7435,25 +6245,25 @@
         <v>8</v>
       </c>
       <c r="D17" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E17" t="s">
-        <v>436</v>
+        <v>370</v>
       </c>
       <c r="F17" t="s">
-        <v>414</v>
+        <v>348</v>
       </c>
       <c r="G17" t="s">
-        <v>437</v>
+        <v>371</v>
       </c>
       <c r="H17" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K17" t="s">
-        <v>437</v>
+        <v>371</v>
       </c>
       <c r="L17" t="s">
-        <v>552</v>
+        <v>486</v>
       </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.45">
@@ -7464,25 +6274,25 @@
         <v>8</v>
       </c>
       <c r="D18" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E18" t="s">
-        <v>438</v>
+        <v>372</v>
       </c>
       <c r="F18" t="s">
-        <v>439</v>
+        <v>373</v>
       </c>
       <c r="G18" t="s">
-        <v>440</v>
+        <v>374</v>
       </c>
       <c r="H18" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K18" t="s">
-        <v>440</v>
+        <v>374</v>
       </c>
       <c r="L18" t="s">
-        <v>553</v>
+        <v>487</v>
       </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.45">
@@ -7493,25 +6303,25 @@
         <v>8</v>
       </c>
       <c r="D19" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E19" t="s">
-        <v>441</v>
+        <v>375</v>
       </c>
       <c r="F19" t="s">
-        <v>442</v>
+        <v>376</v>
       </c>
       <c r="G19" t="s">
-        <v>443</v>
+        <v>377</v>
       </c>
       <c r="H19" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K19" t="s">
-        <v>443</v>
+        <v>377</v>
       </c>
       <c r="L19" t="s">
-        <v>554</v>
+        <v>488</v>
       </c>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.45">
@@ -7522,25 +6332,25 @@
         <v>8</v>
       </c>
       <c r="D20" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E20" t="s">
-        <v>444</v>
+        <v>378</v>
       </c>
       <c r="F20" t="s">
-        <v>428</v>
+        <v>362</v>
       </c>
       <c r="G20" t="s">
-        <v>445</v>
+        <v>379</v>
       </c>
       <c r="H20" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K20" t="s">
-        <v>445</v>
+        <v>379</v>
       </c>
       <c r="L20" t="s">
-        <v>555</v>
+        <v>489</v>
       </c>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.45">
@@ -7551,25 +6361,25 @@
         <v>8</v>
       </c>
       <c r="D21" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E21" t="s">
-        <v>446</v>
+        <v>380</v>
       </c>
       <c r="F21" t="s">
-        <v>447</v>
+        <v>381</v>
       </c>
       <c r="G21" t="s">
-        <v>448</v>
+        <v>382</v>
       </c>
       <c r="H21" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K21" t="s">
-        <v>448</v>
+        <v>382</v>
       </c>
       <c r="L21" t="s">
-        <v>556</v>
+        <v>490</v>
       </c>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.45">
@@ -7580,25 +6390,25 @@
         <v>8</v>
       </c>
       <c r="D22" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E22" t="s">
-        <v>449</v>
+        <v>383</v>
       </c>
       <c r="F22" t="s">
-        <v>450</v>
+        <v>384</v>
       </c>
       <c r="G22" t="s">
-        <v>451</v>
+        <v>385</v>
       </c>
       <c r="H22" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K22" t="s">
-        <v>451</v>
+        <v>385</v>
       </c>
       <c r="L22" t="s">
-        <v>557</v>
+        <v>491</v>
       </c>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.45">
@@ -7609,25 +6419,25 @@
         <v>8</v>
       </c>
       <c r="D23" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E23" t="s">
-        <v>452</v>
+        <v>386</v>
       </c>
       <c r="F23" t="s">
-        <v>442</v>
+        <v>376</v>
       </c>
       <c r="G23" t="s">
-        <v>453</v>
+        <v>387</v>
       </c>
       <c r="H23" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K23" t="s">
-        <v>453</v>
+        <v>387</v>
       </c>
       <c r="L23" t="s">
-        <v>558</v>
+        <v>492</v>
       </c>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.45">
@@ -7638,25 +6448,25 @@
         <v>8</v>
       </c>
       <c r="D24" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E24" t="s">
-        <v>454</v>
+        <v>388</v>
       </c>
       <c r="F24" t="s">
-        <v>455</v>
+        <v>389</v>
       </c>
       <c r="G24" t="s">
-        <v>456</v>
+        <v>390</v>
       </c>
       <c r="H24" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K24" t="s">
-        <v>456</v>
+        <v>390</v>
       </c>
       <c r="L24" t="s">
-        <v>559</v>
+        <v>493</v>
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.45">
@@ -7667,25 +6477,25 @@
         <v>8</v>
       </c>
       <c r="D25" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E25" t="s">
-        <v>457</v>
+        <v>391</v>
       </c>
       <c r="F25" t="s">
-        <v>414</v>
+        <v>348</v>
       </c>
       <c r="G25" t="s">
-        <v>458</v>
+        <v>392</v>
       </c>
       <c r="H25" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K25" t="s">
-        <v>458</v>
+        <v>392</v>
       </c>
       <c r="L25" t="s">
-        <v>560</v>
+        <v>494</v>
       </c>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.45">
@@ -7696,25 +6506,25 @@
         <v>8</v>
       </c>
       <c r="D26" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E26" t="s">
-        <v>459</v>
+        <v>393</v>
       </c>
       <c r="F26" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="G26" t="s">
-        <v>461</v>
+        <v>395</v>
       </c>
       <c r="H26" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K26" t="s">
-        <v>461</v>
+        <v>395</v>
       </c>
       <c r="L26" t="s">
-        <v>561</v>
+        <v>495</v>
       </c>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.45">
@@ -7725,25 +6535,25 @@
         <v>8</v>
       </c>
       <c r="D27" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E27" t="s">
-        <v>462</v>
+        <v>396</v>
       </c>
       <c r="F27" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="G27" t="s">
-        <v>463</v>
+        <v>397</v>
       </c>
       <c r="H27" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K27" t="s">
-        <v>463</v>
+        <v>397</v>
       </c>
       <c r="L27" t="s">
-        <v>562</v>
+        <v>496</v>
       </c>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.45">
@@ -7754,25 +6564,25 @@
         <v>8</v>
       </c>
       <c r="D28" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E28" t="s">
-        <v>464</v>
+        <v>398</v>
       </c>
       <c r="F28" t="s">
-        <v>442</v>
+        <v>376</v>
       </c>
       <c r="G28" t="s">
-        <v>465</v>
+        <v>399</v>
       </c>
       <c r="H28" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K28" t="s">
-        <v>465</v>
+        <v>399</v>
       </c>
       <c r="L28" t="s">
-        <v>563</v>
+        <v>497</v>
       </c>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.45">
@@ -7783,25 +6593,25 @@
         <v>8</v>
       </c>
       <c r="D29" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E29" t="s">
-        <v>466</v>
+        <v>400</v>
       </c>
       <c r="F29" t="s">
-        <v>442</v>
+        <v>376</v>
       </c>
       <c r="G29" t="s">
-        <v>467</v>
+        <v>401</v>
       </c>
       <c r="H29" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K29" t="s">
-        <v>467</v>
+        <v>401</v>
       </c>
       <c r="L29" t="s">
-        <v>564</v>
+        <v>498</v>
       </c>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.45">
@@ -7812,25 +6622,25 @@
         <v>8</v>
       </c>
       <c r="D30" t="s">
+        <v>336</v>
+      </c>
+      <c r="E30" t="s">
         <v>402</v>
       </c>
-      <c r="E30" t="s">
-        <v>468</v>
-      </c>
       <c r="F30" t="s">
-        <v>447</v>
+        <v>381</v>
       </c>
       <c r="G30" t="s">
-        <v>469</v>
+        <v>403</v>
       </c>
       <c r="H30" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K30" t="s">
-        <v>469</v>
+        <v>403</v>
       </c>
       <c r="L30" t="s">
-        <v>565</v>
+        <v>499</v>
       </c>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.45">
@@ -7841,25 +6651,25 @@
         <v>8</v>
       </c>
       <c r="D31" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E31" t="s">
-        <v>470</v>
+        <v>404</v>
       </c>
       <c r="F31" t="s">
-        <v>442</v>
+        <v>376</v>
       </c>
       <c r="G31" t="s">
-        <v>471</v>
+        <v>405</v>
       </c>
       <c r="H31" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K31" t="s">
-        <v>471</v>
+        <v>405</v>
       </c>
       <c r="L31" t="s">
-        <v>566</v>
+        <v>500</v>
       </c>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.45">
@@ -7870,25 +6680,25 @@
         <v>8</v>
       </c>
       <c r="D32" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E32" t="s">
-        <v>472</v>
+        <v>406</v>
       </c>
       <c r="F32" t="s">
-        <v>442</v>
+        <v>376</v>
       </c>
       <c r="G32" t="s">
-        <v>473</v>
+        <v>407</v>
       </c>
       <c r="H32" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K32" t="s">
-        <v>473</v>
+        <v>407</v>
       </c>
       <c r="L32" t="s">
-        <v>567</v>
+        <v>501</v>
       </c>
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.45">
@@ -7899,25 +6709,25 @@
         <v>8</v>
       </c>
       <c r="D33" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E33" t="s">
-        <v>474</v>
+        <v>408</v>
       </c>
       <c r="F33" t="s">
-        <v>450</v>
+        <v>384</v>
       </c>
       <c r="G33" t="s">
-        <v>475</v>
+        <v>409</v>
       </c>
       <c r="H33" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K33" t="s">
-        <v>475</v>
+        <v>409</v>
       </c>
       <c r="L33" t="s">
-        <v>568</v>
+        <v>502</v>
       </c>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.45">
@@ -7928,25 +6738,25 @@
         <v>8</v>
       </c>
       <c r="D34" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E34" t="s">
-        <v>476</v>
+        <v>410</v>
       </c>
       <c r="F34" t="s">
-        <v>477</v>
+        <v>411</v>
       </c>
       <c r="G34" t="s">
-        <v>478</v>
+        <v>412</v>
       </c>
       <c r="H34" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K34" t="s">
-        <v>478</v>
+        <v>412</v>
       </c>
       <c r="L34" t="s">
-        <v>569</v>
+        <v>503</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.45">
@@ -7957,25 +6767,25 @@
         <v>8</v>
       </c>
       <c r="D35" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E35" t="s">
-        <v>479</v>
+        <v>413</v>
       </c>
       <c r="F35" t="s">
-        <v>442</v>
+        <v>376</v>
       </c>
       <c r="G35" t="s">
-        <v>480</v>
+        <v>414</v>
       </c>
       <c r="H35" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K35" t="s">
-        <v>480</v>
+        <v>414</v>
       </c>
       <c r="L35" t="s">
-        <v>570</v>
+        <v>504</v>
       </c>
     </row>
     <row r="36" spans="2:12" x14ac:dyDescent="0.45">
@@ -7986,25 +6796,25 @@
         <v>8</v>
       </c>
       <c r="D36" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E36" t="s">
-        <v>481</v>
+        <v>415</v>
       </c>
       <c r="F36" t="s">
-        <v>417</v>
+        <v>351</v>
       </c>
       <c r="G36" t="s">
-        <v>482</v>
+        <v>416</v>
       </c>
       <c r="H36" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K36" t="s">
-        <v>482</v>
+        <v>416</v>
       </c>
       <c r="L36" t="s">
-        <v>571</v>
+        <v>505</v>
       </c>
     </row>
     <row r="37" spans="2:12" x14ac:dyDescent="0.45">
@@ -8015,25 +6825,25 @@
         <v>8</v>
       </c>
       <c r="D37" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E37" t="s">
-        <v>483</v>
+        <v>417</v>
       </c>
       <c r="F37" t="s">
-        <v>484</v>
+        <v>418</v>
       </c>
       <c r="G37" t="s">
-        <v>485</v>
+        <v>419</v>
       </c>
       <c r="H37" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K37" t="s">
-        <v>485</v>
+        <v>419</v>
       </c>
       <c r="L37" t="s">
-        <v>572</v>
+        <v>506</v>
       </c>
     </row>
     <row r="38" spans="2:12" x14ac:dyDescent="0.45">
@@ -8044,25 +6854,25 @@
         <v>8</v>
       </c>
       <c r="D38" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E38" t="s">
-        <v>486</v>
+        <v>420</v>
       </c>
       <c r="F38" t="s">
-        <v>425</v>
+        <v>359</v>
       </c>
       <c r="G38" t="s">
-        <v>487</v>
+        <v>421</v>
       </c>
       <c r="H38" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K38" t="s">
-        <v>487</v>
+        <v>421</v>
       </c>
       <c r="L38" t="s">
-        <v>573</v>
+        <v>507</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.45">
@@ -8073,25 +6883,25 @@
         <v>8</v>
       </c>
       <c r="D39" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E39" t="s">
-        <v>488</v>
+        <v>422</v>
       </c>
       <c r="F39" t="s">
-        <v>442</v>
+        <v>376</v>
       </c>
       <c r="G39" t="s">
-        <v>489</v>
+        <v>423</v>
       </c>
       <c r="H39" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K39" t="s">
-        <v>489</v>
+        <v>423</v>
       </c>
       <c r="L39" t="s">
-        <v>574</v>
+        <v>508</v>
       </c>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.45">
@@ -8102,25 +6912,25 @@
         <v>8</v>
       </c>
       <c r="D40" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E40" t="s">
-        <v>490</v>
+        <v>424</v>
       </c>
       <c r="F40" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="G40" t="s">
-        <v>491</v>
+        <v>425</v>
       </c>
       <c r="H40" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K40" t="s">
-        <v>491</v>
+        <v>425</v>
       </c>
       <c r="L40" t="s">
-        <v>575</v>
+        <v>509</v>
       </c>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.45">
@@ -8131,25 +6941,25 @@
         <v>8</v>
       </c>
       <c r="D41" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E41" t="s">
-        <v>492</v>
+        <v>426</v>
       </c>
       <c r="F41" t="s">
-        <v>428</v>
+        <v>362</v>
       </c>
       <c r="G41" t="s">
-        <v>493</v>
+        <v>427</v>
       </c>
       <c r="H41" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K41" t="s">
-        <v>493</v>
+        <v>427</v>
       </c>
       <c r="L41" t="s">
-        <v>576</v>
+        <v>510</v>
       </c>
     </row>
     <row r="42" spans="2:12" x14ac:dyDescent="0.45">
@@ -8160,25 +6970,25 @@
         <v>8</v>
       </c>
       <c r="D42" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E42" t="s">
-        <v>494</v>
+        <v>428</v>
       </c>
       <c r="F42" t="s">
-        <v>495</v>
+        <v>429</v>
       </c>
       <c r="G42" t="s">
-        <v>496</v>
+        <v>430</v>
       </c>
       <c r="H42" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K42" t="s">
-        <v>496</v>
+        <v>430</v>
       </c>
       <c r="L42" t="s">
-        <v>577</v>
+        <v>511</v>
       </c>
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.45">
@@ -8189,25 +6999,25 @@
         <v>8</v>
       </c>
       <c r="D43" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E43" t="s">
-        <v>497</v>
+        <v>431</v>
       </c>
       <c r="F43" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="G43" t="s">
-        <v>498</v>
+        <v>432</v>
       </c>
       <c r="H43" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K43" t="s">
-        <v>498</v>
+        <v>432</v>
       </c>
       <c r="L43" t="s">
-        <v>578</v>
+        <v>512</v>
       </c>
     </row>
     <row r="44" spans="2:12" x14ac:dyDescent="0.45">
@@ -8218,25 +7028,25 @@
         <v>8</v>
       </c>
       <c r="D44" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E44" t="s">
-        <v>499</v>
+        <v>433</v>
       </c>
       <c r="F44" t="s">
-        <v>439</v>
+        <v>373</v>
       </c>
       <c r="G44" t="s">
-        <v>500</v>
+        <v>434</v>
       </c>
       <c r="H44" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K44" t="s">
-        <v>500</v>
+        <v>434</v>
       </c>
       <c r="L44" t="s">
-        <v>579</v>
+        <v>513</v>
       </c>
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.45">
@@ -8247,25 +7057,25 @@
         <v>8</v>
       </c>
       <c r="D45" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E45" t="s">
-        <v>501</v>
+        <v>435</v>
       </c>
       <c r="F45" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="G45" t="s">
-        <v>502</v>
+        <v>436</v>
       </c>
       <c r="H45" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K45" t="s">
-        <v>502</v>
+        <v>436</v>
       </c>
       <c r="L45" t="s">
-        <v>580</v>
+        <v>514</v>
       </c>
     </row>
     <row r="46" spans="2:12" x14ac:dyDescent="0.45">
@@ -8276,25 +7086,25 @@
         <v>8</v>
       </c>
       <c r="D46" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E46" t="s">
-        <v>503</v>
+        <v>437</v>
       </c>
       <c r="F46" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="G46" t="s">
-        <v>504</v>
+        <v>438</v>
       </c>
       <c r="H46" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K46" t="s">
-        <v>504</v>
+        <v>438</v>
       </c>
       <c r="L46" t="s">
-        <v>581</v>
+        <v>515</v>
       </c>
     </row>
     <row r="47" spans="2:12" x14ac:dyDescent="0.45">
@@ -8305,25 +7115,25 @@
         <v>8</v>
       </c>
       <c r="D47" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E47" t="s">
-        <v>505</v>
+        <v>439</v>
       </c>
       <c r="F47" t="s">
-        <v>404</v>
+        <v>338</v>
       </c>
       <c r="G47" t="s">
-        <v>506</v>
+        <v>440</v>
       </c>
       <c r="H47" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K47" t="s">
-        <v>506</v>
+        <v>440</v>
       </c>
       <c r="L47" t="s">
-        <v>582</v>
+        <v>516</v>
       </c>
     </row>
     <row r="48" spans="2:12" x14ac:dyDescent="0.45">
@@ -8334,25 +7144,25 @@
         <v>8</v>
       </c>
       <c r="D48" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E48" t="s">
-        <v>507</v>
+        <v>441</v>
       </c>
       <c r="F48" t="s">
-        <v>508</v>
+        <v>442</v>
       </c>
       <c r="G48" t="s">
-        <v>509</v>
+        <v>443</v>
       </c>
       <c r="H48" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K48" t="s">
-        <v>509</v>
+        <v>443</v>
       </c>
       <c r="L48" t="s">
-        <v>583</v>
+        <v>517</v>
       </c>
     </row>
     <row r="49" spans="2:12" x14ac:dyDescent="0.45">
@@ -8363,25 +7173,25 @@
         <v>8</v>
       </c>
       <c r="D49" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E49" t="s">
-        <v>510</v>
+        <v>444</v>
       </c>
       <c r="F49" t="s">
-        <v>511</v>
+        <v>445</v>
       </c>
       <c r="G49" t="s">
-        <v>512</v>
+        <v>446</v>
       </c>
       <c r="H49" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K49" t="s">
-        <v>512</v>
+        <v>446</v>
       </c>
       <c r="L49" t="s">
-        <v>584</v>
+        <v>518</v>
       </c>
     </row>
     <row r="50" spans="2:12" x14ac:dyDescent="0.45">
@@ -8392,25 +7202,25 @@
         <v>8</v>
       </c>
       <c r="D50" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E50" t="s">
-        <v>513</v>
+        <v>447</v>
       </c>
       <c r="F50" t="s">
-        <v>514</v>
+        <v>448</v>
       </c>
       <c r="G50" t="s">
-        <v>515</v>
+        <v>449</v>
       </c>
       <c r="H50" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K50" t="s">
-        <v>515</v>
+        <v>449</v>
       </c>
       <c r="L50" t="s">
-        <v>585</v>
+        <v>519</v>
       </c>
     </row>
     <row r="51" spans="2:12" x14ac:dyDescent="0.45">
@@ -8421,25 +7231,25 @@
         <v>8</v>
       </c>
       <c r="D51" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E51" t="s">
-        <v>516</v>
+        <v>450</v>
       </c>
       <c r="F51" t="s">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="G51" t="s">
-        <v>517</v>
+        <v>451</v>
       </c>
       <c r="H51" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K51" t="s">
-        <v>517</v>
+        <v>451</v>
       </c>
       <c r="L51" t="s">
-        <v>586</v>
+        <v>520</v>
       </c>
     </row>
     <row r="52" spans="2:12" x14ac:dyDescent="0.45">
@@ -8450,25 +7260,25 @@
         <v>8</v>
       </c>
       <c r="D52" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E52" t="s">
-        <v>518</v>
+        <v>452</v>
       </c>
       <c r="F52" t="s">
-        <v>442</v>
+        <v>376</v>
       </c>
       <c r="G52" t="s">
-        <v>519</v>
+        <v>453</v>
       </c>
       <c r="H52" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K52" t="s">
-        <v>519</v>
+        <v>453</v>
       </c>
       <c r="L52" t="s">
-        <v>587</v>
+        <v>521</v>
       </c>
     </row>
     <row r="53" spans="2:12" x14ac:dyDescent="0.45">
@@ -8479,25 +7289,25 @@
         <v>8</v>
       </c>
       <c r="D53" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E53" t="s">
-        <v>507</v>
+        <v>441</v>
       </c>
       <c r="F53" t="s">
-        <v>520</v>
+        <v>454</v>
       </c>
       <c r="G53" t="s">
-        <v>521</v>
+        <v>455</v>
       </c>
       <c r="H53" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K53" t="s">
-        <v>521</v>
+        <v>455</v>
       </c>
       <c r="L53" t="s">
-        <v>588</v>
+        <v>522</v>
       </c>
     </row>
     <row r="54" spans="2:12" x14ac:dyDescent="0.45">
@@ -8508,25 +7318,25 @@
         <v>8</v>
       </c>
       <c r="D54" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E54" t="s">
-        <v>507</v>
+        <v>441</v>
       </c>
       <c r="F54" t="s">
-        <v>522</v>
+        <v>456</v>
       </c>
       <c r="G54" t="s">
+        <v>457</v>
+      </c>
+      <c r="H54" t="s">
+        <v>340</v>
+      </c>
+      <c r="K54" t="s">
+        <v>457</v>
+      </c>
+      <c r="L54" t="s">
         <v>523</v>
-      </c>
-      <c r="H54" t="s">
-        <v>406</v>
-      </c>
-      <c r="K54" t="s">
-        <v>523</v>
-      </c>
-      <c r="L54" t="s">
-        <v>589</v>
       </c>
     </row>
     <row r="55" spans="2:12" x14ac:dyDescent="0.45">
@@ -8537,25 +7347,25 @@
         <v>8</v>
       </c>
       <c r="D55" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E55" t="s">
-        <v>507</v>
+        <v>441</v>
       </c>
       <c r="F55" t="s">
+        <v>458</v>
+      </c>
+      <c r="G55" t="s">
+        <v>459</v>
+      </c>
+      <c r="H55" t="s">
+        <v>340</v>
+      </c>
+      <c r="K55" t="s">
+        <v>459</v>
+      </c>
+      <c r="L55" t="s">
         <v>524</v>
-      </c>
-      <c r="G55" t="s">
-        <v>525</v>
-      </c>
-      <c r="H55" t="s">
-        <v>406</v>
-      </c>
-      <c r="K55" t="s">
-        <v>525</v>
-      </c>
-      <c r="L55" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="56" spans="2:12" x14ac:dyDescent="0.45">
@@ -8566,25 +7376,25 @@
         <v>8</v>
       </c>
       <c r="D56" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E56" t="s">
-        <v>476</v>
+        <v>410</v>
       </c>
       <c r="F56" t="s">
-        <v>526</v>
+        <v>460</v>
       </c>
       <c r="G56" t="s">
-        <v>527</v>
+        <v>461</v>
       </c>
       <c r="H56" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K56" t="s">
-        <v>527</v>
+        <v>461</v>
       </c>
       <c r="L56" t="s">
-        <v>591</v>
+        <v>525</v>
       </c>
     </row>
     <row r="57" spans="2:12" x14ac:dyDescent="0.45">
@@ -8595,25 +7405,25 @@
         <v>8</v>
       </c>
       <c r="D57" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E57" t="s">
-        <v>483</v>
+        <v>417</v>
       </c>
       <c r="F57" t="s">
-        <v>528</v>
+        <v>462</v>
       </c>
       <c r="G57" t="s">
-        <v>529</v>
+        <v>463</v>
       </c>
       <c r="H57" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K57" t="s">
-        <v>529</v>
+        <v>463</v>
       </c>
       <c r="L57" t="s">
-        <v>592</v>
+        <v>526</v>
       </c>
     </row>
     <row r="58" spans="2:12" x14ac:dyDescent="0.45">
@@ -8624,25 +7434,25 @@
         <v>8</v>
       </c>
       <c r="D58" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E58" t="s">
-        <v>438</v>
+        <v>372</v>
       </c>
       <c r="F58" t="s">
-        <v>530</v>
+        <v>464</v>
       </c>
       <c r="G58" t="s">
-        <v>531</v>
+        <v>465</v>
       </c>
       <c r="H58" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K58" t="s">
-        <v>531</v>
+        <v>465</v>
       </c>
       <c r="L58" t="s">
-        <v>593</v>
+        <v>527</v>
       </c>
     </row>
     <row r="59" spans="2:12" x14ac:dyDescent="0.45">
@@ -8653,25 +7463,25 @@
         <v>8</v>
       </c>
       <c r="D59" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E59" t="s">
-        <v>438</v>
+        <v>372</v>
       </c>
       <c r="F59" t="s">
-        <v>532</v>
+        <v>466</v>
       </c>
       <c r="G59" t="s">
-        <v>533</v>
+        <v>467</v>
       </c>
       <c r="H59" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K59" t="s">
-        <v>533</v>
+        <v>467</v>
       </c>
       <c r="L59" t="s">
-        <v>594</v>
+        <v>528</v>
       </c>
     </row>
     <row r="60" spans="2:12" x14ac:dyDescent="0.45">
@@ -8682,25 +7492,25 @@
         <v>8</v>
       </c>
       <c r="D60" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E60" t="s">
-        <v>446</v>
+        <v>380</v>
       </c>
       <c r="F60" t="s">
-        <v>534</v>
+        <v>468</v>
       </c>
       <c r="G60" t="s">
-        <v>535</v>
+        <v>469</v>
       </c>
       <c r="H60" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K60" t="s">
-        <v>535</v>
+        <v>469</v>
       </c>
       <c r="L60" t="s">
-        <v>595</v>
+        <v>529</v>
       </c>
     </row>
     <row r="61" spans="2:12" x14ac:dyDescent="0.45">
@@ -8711,25 +7521,25 @@
         <v>8</v>
       </c>
       <c r="D61" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E61" t="s">
-        <v>438</v>
+        <v>372</v>
       </c>
       <c r="F61" t="s">
-        <v>536</v>
+        <v>470</v>
       </c>
       <c r="G61" t="s">
-        <v>537</v>
+        <v>471</v>
       </c>
       <c r="H61" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K61" t="s">
-        <v>537</v>
+        <v>471</v>
       </c>
       <c r="L61" t="s">
-        <v>596</v>
+        <v>530</v>
       </c>
     </row>
     <row r="62" spans="2:12" x14ac:dyDescent="0.45">
@@ -8740,25 +7550,25 @@
         <v>8</v>
       </c>
       <c r="D62" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="E62" t="s">
-        <v>488</v>
+        <v>422</v>
       </c>
       <c r="F62" t="s">
-        <v>538</v>
+        <v>472</v>
       </c>
       <c r="G62" t="s">
-        <v>539</v>
+        <v>473</v>
       </c>
       <c r="H62" t="s">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K62" t="s">
-        <v>539</v>
+        <v>473</v>
       </c>
       <c r="L62" t="s">
-        <v>597</v>
+        <v>531</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FE16354E-6D73-4095-AFD4-129D6E01D0D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC4745F5-BA4E-4AA7-A7A0-2B3282D29505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2573" yWindow="2573" windowWidth="21600" windowHeight="11422" activeTab="1" xr2:uid="{905D0BE9-63A2-4257-BCF9-CEA42253A243}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="12772" activeTab="1" xr2:uid="{9A54E98D-23AE-4D31-9BE3-10F31EF7061F}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1558" uniqueCount="532">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1720" uniqueCount="601">
   <si>
     <t>~tradelinks_dins</t>
   </si>
@@ -756,121 +756,289 @@
     <t>elc_spv_POL_001</t>
   </si>
   <si>
-    <t>POLYGON ((23.935955 52.36866, 23.250033 52.36866, 22.564111 52.36866, 21.878189 52.36866, 21.192267 52.36866, 21.192267 52.81832, 21.192267 53.267981, 21.878189 53.267981, 22.564111 53.267981, 23.250033 53.267981, 23.935955 53.267981, 23.935955 52.81832, 23.935955 52.36866))</t>
+    <t>POLYGON ((18.448578 52.81832, 17.762656 52.81832, 17.076733 52.81832, 17.076733 53.267981, 17.076733 53.717641, 17.762656 53.717641, 18.448578 53.717641, 18.448578 53.267981, 18.448578 52.81832))</t>
   </si>
   <si>
     <t>elc_spv_POL_002</t>
   </si>
   <si>
-    <t>POLYGON ((21.192267 54.616961, 21.878189 54.616961, 22.564111 54.616961, 23.250033 54.616961, 23.935955 54.616961, 23.935955 54.167301, 23.935955 53.717641, 23.935955 53.267981, 23.250033 53.267981, 22.564111 53.267981, 21.878189 53.267981, 21.192267 53.267981, 21.192267 53.717641, 21.192267 54.167301, 21.192267 54.616961))</t>
+    <t>POLYGON ((22.564111 53.267981, 22.564111 53.717641, 23.250033 53.717641, 23.250033 54.167301, 23.935955 54.167301, 23.935955 53.717641, 23.935955 53.267981, 23.935955 52.81832, 23.935955 52.36866, 23.250033 52.36866, 23.250033 51.919, 22.564111 51.919, 22.564111 52.36866, 22.564111 52.81832, 22.564111 53.267981))</t>
   </si>
   <si>
     <t>elc_spv_POL_003</t>
   </si>
   <si>
-    <t>POLYGON ((23.250033 49.221039, 22.564111 49.221039, 21.878189 49.221039, 21.192267 49.221039, 21.192267 49.670699, 21.192267 50.120359, 21.192267 50.570019, 21.878189 50.570019, 21.878189 50.120359, 22.564111 50.120359, 23.250033 50.120359, 23.250033 49.670699, 23.250033 49.221039))</t>
+    <t>POLYGON ((15.018967 52.81832, 15.018967 53.267981, 15.018967 53.717641, 15.704889 53.717641, 15.704889 53.267981, 15.704889 52.81832, 15.704889 52.36866, 15.018967 52.36866, 14.333045 52.36866, 14.333045 52.81832, 15.018967 52.81832))</t>
   </si>
   <si>
     <t>elc_spv_POL_004</t>
   </si>
   <si>
-    <t>POLYGON ((19.820422 50.120359, 19.820422 50.570019, 20.506344 50.570019, 21.192267 50.570019, 21.192267 50.120359, 21.192267 49.670699, 21.192267 49.221039, 20.506344 49.221039, 19.820422 49.221039, 19.820422 49.670699, 19.820422 50.120359))</t>
+    <t>POLYGON ((15.704889 51.46934, 16.390811 51.46934, 16.390811 51.919, 17.076733 51.919, 17.076733 51.46934, 17.076733 51.01968, 16.390811 51.01968, 16.390811 50.570019, 15.704889 50.570019, 15.704889 51.01968, 15.704889 51.46934))</t>
   </si>
   <si>
     <t>elc_spv_POL_005</t>
   </si>
   <si>
-    <t>POLYGON ((22.564111 51.01968, 21.878189 51.01968, 21.878189 51.46934, 21.878189 51.919, 21.878189 52.36866, 22.564111 52.36866, 23.250033 52.36866, 23.935955 52.36866, 23.935955 51.919, 23.935955 51.46934, 23.250033 51.46934, 23.250033 51.01968, 22.564111 51.01968))</t>
+    <t>MULTIPOLYGON (((17.076733 51.01968, 17.762656 51.01968, 17.762656 50.570019, 17.076733 50.570019, 17.076733 51.01968)), ((17.762656 51.46934, 18.448578 51.46934, 18.448578 51.01968, 17.762656 51.01968, 17.762656 51.46934)))</t>
   </si>
   <si>
     <t>elc_spv_POL_006</t>
   </si>
   <si>
-    <t>POLYGON ((23.250033 49.670699, 23.250033 50.120359, 22.564111 50.120359, 21.878189 50.120359, 21.878189 50.570019, 21.192267 50.570019, 21.192267 51.01968, 21.192267 51.46934, 21.878189 51.46934, 21.878189 51.01968, 22.564111 51.01968, 23.250033 51.01968, 23.250033 51.46934, 23.935955 51.46934, 23.935955 51.01968, 23.935955 50.570019, 23.935955 50.120359, 23.935955 49.670699, 23.250033 49.670699))</t>
+    <t>POLYGON ((17.076733 49.670699, 16.390811 49.670699, 16.390811 50.120359, 15.704889 50.120359, 15.704889 50.570019, 16.390811 50.570019, 16.390811 51.01968, 17.076733 51.01968, 17.076733 50.570019, 17.076733 50.120359, 17.076733 49.670699))</t>
   </si>
   <si>
     <t>elc_spv_POL_007</t>
   </si>
   <si>
-    <t>POLYGON ((14.333045 53.717641, 14.333045 54.167301, 15.018967 54.167301, 15.704889 54.167301, 15.704889 53.717641, 15.704889 53.267981, 15.704889 52.81832, 15.018967 52.81832, 14.333045 52.81832, 14.333045 53.267981, 14.333045 53.717641))</t>
+    <t>POLYGON ((19.1345 53.267981, 19.1345 53.717641, 19.820422 53.717641, 19.820422 53.267981, 19.1345 53.267981))</t>
   </si>
   <si>
     <t>elc_spv_POL_008</t>
   </si>
   <si>
-    <t>POLYGON ((15.704889 54.167301, 15.704889 54.616961, 16.390811 54.616961, 17.076733 54.616961, 17.762656 54.616961, 17.762656 54.167301, 17.762656 53.717641, 17.762656 53.267981, 17.762656 52.81832, 17.076733 52.81832, 16.390811 52.81832, 15.704889 52.81832, 15.704889 53.267981, 15.704889 53.717641, 15.704889 54.167301))</t>
+    <t>POLYGON ((17.076733 54.167301, 17.076733 54.616961, 17.762656 54.616961, 17.762656 54.167301, 17.076733 54.167301))</t>
   </si>
   <si>
     <t>elc_spv_POL_009</t>
   </si>
   <si>
-    <t>POLYGON ((19.820422 52.36866, 19.1345 52.36866, 18.448578 52.36866, 17.762656 52.36866, 17.762656 52.81832, 17.762656 53.267981, 18.448578 53.267981, 19.1345 53.267981, 19.820422 53.267981, 19.820422 52.81832, 19.820422 52.36866))</t>
+    <t>POLYGON ((19.820422 54.167301, 19.820422 54.616961, 20.506344 54.616961, 21.192267 54.616961, 21.192267 54.167301, 21.192267 53.717641, 21.192267 53.267981, 20.506344 53.267981, 19.820422 53.267981, 19.820422 53.717641, 19.820422 54.167301))</t>
   </si>
   <si>
     <t>elc_spv_POL_010</t>
   </si>
   <si>
-    <t>POLYGON ((19.820422 54.167301, 19.820422 54.616961, 20.506344 54.616961, 21.192267 54.616961, 21.192267 54.167301, 21.192267 53.717641, 21.192267 53.267981, 20.506344 53.267981, 19.820422 53.267981, 19.820422 53.717641, 19.820422 54.167301))</t>
+    <t>POLYGON ((15.704889 50.570019, 15.018967 50.570019, 14.333045 50.570019, 14.333045 51.01968, 14.333045 51.46934, 15.018967 51.46934, 15.704889 51.46934, 15.704889 51.01968, 15.704889 50.570019))</t>
   </si>
   <si>
     <t>elc_spv_POL_011</t>
   </si>
   <si>
-    <t>POLYGON ((19.820422 53.267981, 19.1345 53.267981, 18.448578 53.267981, 17.762656 53.267981, 17.762656 53.717641, 17.762656 54.167301, 17.762656 54.616961, 18.448578 54.616961, 19.1345 54.616961, 19.820422 54.616961, 19.820422 54.167301, 19.820422 53.717641, 19.820422 53.267981))</t>
+    <t>POLYGON ((18.448578 54.167301, 18.448578 54.616961, 19.1345 54.616961, 19.820422 54.616961, 19.820422 54.167301, 19.1345 54.167301, 19.1345 53.717641, 18.448578 53.717641, 17.762656 53.717641, 17.762656 54.167301, 18.448578 54.167301))</t>
   </si>
   <si>
     <t>elc_spv_POL_012</t>
   </si>
   <si>
-    <t>POLYGON ((17.762656 51.919, 17.076733 51.919, 16.390811 51.919, 15.704889 51.919, 15.704889 52.36866, 15.704889 52.81832, 16.390811 52.81832, 17.076733 52.81832, 17.762656 52.81832, 17.762656 52.36866, 17.762656 51.919))</t>
+    <t>POLYGON ((22.564111 52.36866, 21.878189 52.36866, 21.192267 52.36866, 21.192267 52.81832, 20.506344 52.81832, 20.506344 53.267981, 21.192267 53.267981, 21.192267 53.717641, 21.878189 53.717641, 21.878189 53.267981, 22.564111 53.267981, 22.564111 52.81832, 22.564111 52.36866))</t>
   </si>
   <si>
     <t>elc_spv_POL_013</t>
   </si>
   <si>
-    <t>POLYGON ((17.762656 51.01968, 17.076733 51.01968, 16.390811 51.01968, 15.704889 51.01968, 15.704889 51.46934, 15.704889 51.919, 16.390811 51.919, 17.076733 51.919, 17.762656 51.919, 17.762656 51.46934, 17.762656 51.01968))</t>
+    <t>POLYGON ((15.704889 51.46934, 15.018967 51.46934, 14.333045 51.46934, 14.333045 51.919, 14.333045 52.36866, 15.018967 52.36866, 15.704889 52.36866, 15.704889 51.919, 15.704889 51.46934))</t>
   </si>
   <si>
     <t>elc_spv_POL_014</t>
   </si>
   <si>
-    <t>POLYGON ((15.704889 50.570019, 15.018967 50.570019, 14.333045 50.570019, 14.333045 51.01968, 14.333045 51.46934, 15.018967 51.46934, 15.704889 51.46934, 15.704889 51.01968, 15.704889 50.570019))</t>
+    <t>POLYGON ((14.333045 53.717641, 14.333045 54.167301, 15.018967 54.167301, 15.704889 54.167301, 15.704889 53.717641, 15.018967 53.717641, 15.018967 53.267981, 14.333045 53.267981, 14.333045 53.717641))</t>
   </si>
   <si>
     <t>elc_spv_POL_015</t>
   </si>
   <si>
-    <t>POLYGON ((14.333045 52.36866, 14.333045 52.81832, 15.018967 52.81832, 15.704889 52.81832, 15.704889 52.36866, 15.704889 51.919, 15.704889 51.46934, 15.018967 51.46934, 14.333045 51.46934, 14.333045 51.919, 14.333045 52.36866))</t>
+    <t>POLYGON ((22.564111 49.670699, 23.250033 49.670699, 23.250033 49.221039, 22.564111 49.221039, 21.878189 49.221039, 21.192267 49.221039, 21.192267 49.670699, 21.192267 50.120359, 21.878189 50.120359, 21.878189 49.670699, 22.564111 49.670699))</t>
   </si>
   <si>
     <t>elc_spv_POL_016</t>
   </si>
   <si>
-    <t>POLYGON ((17.762656 49.670699, 17.076733 49.670699, 16.390811 49.670699, 16.390811 50.120359, 15.704889 50.120359, 15.704889 50.570019, 15.704889 51.01968, 16.390811 51.01968, 17.076733 51.01968, 17.762656 51.01968, 17.762656 50.570019, 17.762656 50.120359, 17.762656 49.670699))</t>
+    <t>POLYGON ((23.250033 53.717641, 22.564111 53.717641, 21.878189 53.717641, 21.878189 54.167301, 21.878189 54.616961, 22.564111 54.616961, 23.250033 54.616961, 23.935955 54.616961, 23.935955 54.167301, 23.250033 54.167301, 23.250033 53.717641))</t>
   </si>
   <si>
     <t>elc_spv_POL_017</t>
   </si>
   <si>
-    <t>POLYGON ((19.820422 49.221039, 19.1345 49.221039, 18.448578 49.221039, 18.448578 49.670699, 17.762656 49.670699, 17.762656 50.120359, 17.762656 50.570019, 18.448578 50.570019, 19.1345 50.570019, 19.820422 50.570019, 19.820422 50.120359, 19.820422 49.670699, 19.820422 49.221039))</t>
+    <t>POLYGON ((19.1345 51.46934, 19.1345 51.919, 19.820422 51.919, 20.506344 51.919, 20.506344 51.46934, 19.820422 51.46934, 19.820422 51.01968, 19.1345 51.01968, 19.1345 51.46934))</t>
   </si>
   <si>
     <t>elc_spv_POL_018</t>
   </si>
   <si>
-    <t>POLYGON ((21.878189 51.46934, 21.192267 51.46934, 20.506344 51.46934, 20.506344 51.919, 19.820422 51.919, 19.820422 52.36866, 19.820422 52.81832, 19.820422 53.267981, 20.506344 53.267981, 21.192267 53.267981, 21.192267 52.81832, 21.192267 52.36866, 21.878189 52.36866, 21.878189 51.919, 21.878189 51.46934))</t>
+    <t>POLYGON ((18.448578 51.46934, 18.448578 51.919, 19.1345 51.919, 19.1345 51.46934, 19.1345 51.01968, 18.448578 51.01968, 18.448578 51.46934))</t>
   </si>
   <si>
     <t>elc_spv_POL_019</t>
   </si>
   <si>
-    <t>POLYGON ((21.192267 50.570019, 20.506344 50.570019, 19.820422 50.570019, 19.820422 51.01968, 19.820422 51.46934, 19.820422 51.919, 20.506344 51.919, 20.506344 51.46934, 21.192267 51.46934, 21.192267 51.01968, 21.192267 50.570019))</t>
+    <t>POLYGON ((22.564111 50.570019, 22.564111 51.01968, 23.250033 51.01968, 23.935955 51.01968, 23.935955 50.570019, 23.935955 50.120359, 23.935955 49.670699, 23.250033 49.670699, 22.564111 49.670699, 22.564111 50.120359, 22.564111 50.570019))</t>
   </si>
   <si>
     <t>elc_spv_POL_020</t>
   </si>
   <si>
-    <t>POLYGON ((17.762656 51.919, 17.762656 52.36866, 18.448578 52.36866, 19.1345 52.36866, 19.820422 52.36866, 19.820422 51.919, 19.820422 51.46934, 19.820422 51.01968, 19.820422 50.570019, 19.1345 50.570019, 18.448578 50.570019, 17.762656 50.570019, 17.762656 51.01968, 17.762656 51.46934, 17.762656 51.919))</t>
+    <t>POLYGON ((15.704889 54.167301, 15.704889 54.616961, 16.390811 54.616961, 16.390811 54.167301, 17.076733 54.167301, 17.762656 54.167301, 17.762656 53.717641, 17.076733 53.717641, 17.076733 53.267981, 16.390811 53.267981, 15.704889 53.267981, 15.704889 53.717641, 15.704889 54.167301))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_021</t>
+  </si>
+  <si>
+    <t>POLYGON ((15.704889 51.919, 15.704889 52.36866, 16.390811 52.36866, 16.390811 51.919, 16.390811 51.46934, 15.704889 51.46934, 15.704889 51.919))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_022</t>
+  </si>
+  <si>
+    <t>POLYGON ((18.448578 49.670699, 18.448578 50.120359, 19.1345 50.120359, 19.1345 49.670699, 18.448578 49.670699))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_023</t>
+  </si>
+  <si>
+    <t>POLYGON ((20.506344 49.670699, 20.506344 50.120359, 20.506344 50.570019, 21.192267 50.570019, 21.192267 50.120359, 21.192267 49.670699, 21.192267 49.221039, 20.506344 49.221039, 20.506344 49.670699))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_024</t>
+  </si>
+  <si>
+    <t>POLYGON ((23.935955 51.01968, 23.250033 51.01968, 22.564111 51.01968, 22.564111 51.46934, 22.564111 51.919, 23.250033 51.919, 23.250033 52.36866, 23.935955 52.36866, 23.935955 51.919, 23.935955 51.46934, 23.935955 51.01968))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_025</t>
+  </si>
+  <si>
+    <t>POLYGON ((21.878189 49.670699, 21.878189 50.120359, 22.564111 50.120359, 22.564111 49.670699, 21.878189 49.670699))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_026</t>
+  </si>
+  <si>
+    <t>POLYGON ((21.192267 50.570019, 20.506344 50.570019, 19.820422 50.570019, 19.820422 51.01968, 19.820422 51.46934, 20.506344 51.46934, 21.192267 51.46934, 21.192267 51.01968, 21.192267 50.570019))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_027</t>
+  </si>
+  <si>
+    <t>POLYGON ((21.192267 50.120359, 21.192267 50.570019, 21.878189 50.570019, 21.878189 50.120359, 21.192267 50.120359))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_028</t>
+  </si>
+  <si>
+    <t>POLYGON ((21.878189 50.570019, 21.878189 51.01968, 22.564111 51.01968, 22.564111 50.570019, 22.564111 50.120359, 21.878189 50.120359, 21.878189 50.570019))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_029</t>
+  </si>
+  <si>
+    <t>POLYGON ((18.448578 51.01968, 19.1345 51.01968, 19.820422 51.01968, 19.820422 50.570019, 19.1345 50.570019, 18.448578 50.570019, 18.448578 51.01968))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_030</t>
+  </si>
+  <si>
+    <t>POLYGON ((18.448578 52.81832, 18.448578 53.267981, 19.1345 53.267981, 19.1345 52.81832, 19.1345 52.36866, 18.448578 52.36866, 18.448578 52.81832))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_031</t>
+  </si>
+  <si>
+    <t>POLYGON ((21.192267 51.01968, 21.192267 51.46934, 21.878189 51.46934, 21.878189 51.01968, 21.878189 50.570019, 21.192267 50.570019, 21.192267 51.01968))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_032</t>
+  </si>
+  <si>
+    <t>POLYGON ((17.076733 50.120359, 17.076733 50.570019, 17.762656 50.570019, 17.762656 50.120359, 17.076733 50.120359))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_033</t>
+  </si>
+  <si>
+    <t>POLYGON ((17.762656 52.36866, 17.762656 52.81832, 18.448578 52.81832, 18.448578 52.36866, 19.1345 52.36866, 19.1345 51.919, 18.448578 51.919, 18.448578 51.46934, 17.762656 51.46934, 17.762656 51.919, 17.762656 52.36866))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_034</t>
+  </si>
+  <si>
+    <t>POLYGON ((16.390811 54.167301, 16.390811 54.616961, 17.076733 54.616961, 17.076733 54.167301, 16.390811 54.167301))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_035</t>
+  </si>
+  <si>
+    <t>POLYGON ((20.506344 52.36866, 20.506344 52.81832, 21.192267 52.81832, 21.192267 52.36866, 21.878189 52.36866, 21.878189 51.919, 21.192267 51.919, 21.192267 51.46934, 20.506344 51.46934, 20.506344 51.919, 20.506344 52.36866))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_036</t>
+  </si>
+  <si>
+    <t>POLYGON ((18.448578 50.120359, 18.448578 50.570019, 19.1345 50.570019, 19.1345 50.120359, 18.448578 50.120359))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_037</t>
+  </si>
+  <si>
+    <t>MULTIPOLYGON (((21.878189 53.717641, 22.564111 53.717641, 22.564111 53.267981, 21.878189 53.267981, 21.878189 53.717641)), ((21.192267 54.616961, 21.878189 54.616961, 21.878189 54.167301, 21.878189 53.717641, 21.192267 53.717641, 21.192267 54.167301, 21.192267 54.616961)))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_038</t>
+  </si>
+  <si>
+    <t>POLYGON ((17.762656 51.919, 17.076733 51.919, 16.390811 51.919, 16.390811 52.36866, 15.704889 52.36866, 15.704889 52.81832, 15.704889 53.267981, 16.390811 53.267981, 17.076733 53.267981, 17.076733 52.81832, 17.762656 52.81832, 17.762656 52.36866, 17.762656 51.919))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_039</t>
+  </si>
+  <si>
+    <t>POLYGON ((17.762656 50.120359, 17.762656 50.570019, 17.762656 51.01968, 18.448578 51.01968, 18.448578 50.570019, 18.448578 50.120359, 18.448578 49.670699, 17.762656 49.670699, 17.076733 49.670699, 17.076733 50.120359, 17.762656 50.120359))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_040</t>
+  </si>
+  <si>
+    <t>POLYGON ((14.333045 52.81832, 14.333045 53.267981, 15.018967 53.267981, 15.018967 52.81832, 14.333045 52.81832))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_041</t>
+  </si>
+  <si>
+    <t>POLYGON ((19.1345 50.120359, 19.1345 50.570019, 19.820422 50.570019, 19.820422 50.120359, 19.1345 50.120359))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_042</t>
+  </si>
+  <si>
+    <t>POLYGON ((18.448578 49.670699, 19.1345 49.670699, 19.1345 50.120359, 19.820422 50.120359, 19.820422 49.670699, 19.820422 49.221039, 19.1345 49.221039, 18.448578 49.221039, 18.448578 49.670699))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_043</t>
+  </si>
+  <si>
+    <t>MULTIPOLYGON (((18.448578 53.717641, 19.1345 53.717641, 19.1345 53.267981, 18.448578 53.267981, 18.448578 53.717641)), ((19.1345 54.167301, 19.820422 54.167301, 19.820422 53.717641, 19.1345 53.717641, 19.1345 54.167301)))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_044</t>
+  </si>
+  <si>
+    <t>POLYGON ((19.1345 52.81832, 19.1345 53.267981, 19.820422 53.267981, 20.506344 53.267981, 20.506344 52.81832, 20.506344 52.36866, 20.506344 51.919, 19.820422 51.919, 19.1345 51.919, 19.1345 52.36866, 19.1345 52.81832))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_045</t>
+  </si>
+  <si>
+    <t>POLYGON ((17.076733 51.46934, 17.076733 51.919, 17.762656 51.919, 17.762656 51.46934, 17.762656 51.01968, 17.076733 51.01968, 17.076733 51.46934))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_046</t>
+  </si>
+  <si>
+    <t>POLYGON ((17.762656 54.167301, 17.762656 54.616961, 18.448578 54.616961, 18.448578 54.167301, 17.762656 54.167301))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_047</t>
+  </si>
+  <si>
+    <t>POLYGON ((19.820422 49.670699, 19.820422 50.120359, 19.820422 50.570019, 20.506344 50.570019, 20.506344 50.120359, 20.506344 49.670699, 20.506344 49.221039, 19.820422 49.221039, 19.820422 49.670699))</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_048</t>
+  </si>
+  <si>
+    <t>POLYGON ((22.564111 51.01968, 21.878189 51.01968, 21.878189 51.46934, 21.192267 51.46934, 21.192267 51.919, 21.878189 51.919, 21.878189 52.36866, 22.564111 52.36866, 22.564111 51.919, 22.564111 51.46934, 22.564111 51.01968))</t>
   </si>
   <si>
     <t>elc_wof_POL_001</t>
@@ -882,169 +1050,208 @@
     <t>elc_wof_POL_002</t>
   </si>
   <si>
-    <t>POLYGON ((18.448578 55.384594, 19.1345 55.384594, 19.820422 55.384594, 19.820422 54.934934, 19.1345 54.934934, 18.448578 54.934934, 18.448578 55.384594))</t>
+    <t>POLYGON ((18.448578 54.934934, 19.1345 54.934934, 19.1345 55.384594, 19.820422 55.384594, 19.820422 54.934934, 19.820422 54.485273, 19.1345 54.485273, 18.448578 54.485273, 18.448578 54.934934))</t>
   </si>
   <si>
     <t>elc_wof_POL_003</t>
   </si>
   <si>
-    <t>POLYGON ((18.448578 54.934934, 19.1345 54.934934, 19.820422 54.934934, 19.820422 54.485273, 19.1345 54.485273, 18.448578 54.485273, 18.448578 54.934934))</t>
+    <t>POLYGON ((14.333045 54.934934, 15.018967 54.934934, 15.704889 54.934934, 15.704889 54.485273, 15.018967 54.485273, 14.333045 54.485273, 14.333045 54.934934))</t>
   </si>
   <si>
     <t>elc_wof_POL_004</t>
   </si>
   <si>
-    <t>POLYGON ((16.390811 55.834254, 17.076733 55.834254, 17.762656 55.834254, 17.762656 55.384594, 17.076733 55.384594, 16.390811 55.384594, 16.390811 55.834254))</t>
+    <t>POLYGON ((15.018967 54.035613, 15.018967 54.485273, 15.704889 54.485273, 15.704889 54.035613, 15.018967 54.035613))</t>
   </si>
   <si>
     <t>elc_wof_POL_005</t>
   </si>
   <si>
+    <t>POLYGON ((15.704889 54.035613, 15.704889 54.485273, 16.390811 54.485273, 16.390811 54.035613, 15.704889 54.035613))</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_006</t>
+  </si>
+  <si>
+    <t>POLYGON ((15.704889 55.384594, 16.390811 55.384594, 16.390811 55.834254, 17.076733 55.834254, 17.076733 55.384594, 17.076733 54.934934, 16.390811 54.934934, 15.704889 54.934934, 15.704889 55.384594))</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_007</t>
+  </si>
+  <si>
+    <t>POLYGON ((15.704889 54.485273, 15.704889 54.934934, 16.390811 54.934934, 16.390811 54.485273, 15.704889 54.485273))</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_008</t>
+  </si>
+  <si>
+    <t>POLYGON ((17.076733 55.384594, 17.076733 55.834254, 17.762656 55.834254, 17.762656 55.384594, 17.762656 54.934934, 17.076733 54.934934, 17.076733 55.384594))</t>
+  </si>
+  <si>
+    <t>elc_wof_POL_009</t>
+  </si>
+  <si>
     <t>POLYGON ((17.762656 55.834254, 18.448578 55.834254, 19.1345 55.834254, 19.1345 55.384594, 18.448578 55.384594, 17.762656 55.384594, 17.762656 55.834254))</t>
   </si>
   <si>
-    <t>elc_wof_POL_006</t>
-  </si>
-  <si>
-    <t>POLYGON ((17.076733 55.384594, 17.762656 55.384594, 18.448578 55.384594, 18.448578 54.934934, 17.762656 54.934934, 17.076733 54.934934, 17.076733 55.384594))</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_007</t>
-  </si>
-  <si>
-    <t>POLYGON ((15.018967 54.485273, 15.704889 54.485273, 16.390811 54.485273, 16.390811 54.035613, 15.704889 54.035613, 15.018967 54.035613, 15.018967 54.485273))</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_008</t>
-  </si>
-  <si>
-    <t>POLYGON ((14.333045 54.934934, 15.018967 54.934934, 15.704889 54.934934, 15.704889 54.485273, 15.018967 54.485273, 14.333045 54.485273, 14.333045 54.934934))</t>
-  </si>
-  <si>
-    <t>elc_wof_POL_009</t>
-  </si>
-  <si>
-    <t>POLYGON ((15.704889 55.384594, 16.390811 55.384594, 17.076733 55.384594, 17.076733 54.934934, 16.390811 54.934934, 15.704889 54.934934, 15.704889 55.384594))</t>
-  </si>
-  <si>
     <t>elc_wof_POL_010</t>
   </si>
   <si>
-    <t>POLYGON ((15.704889 54.485273, 15.704889 54.934934, 16.390811 54.934934, 16.390811 54.485273, 15.704889 54.485273))</t>
+    <t>POLYGON ((17.762656 55.384594, 18.448578 55.384594, 19.1345 55.384594, 19.1345 54.934934, 18.448578 54.934934, 17.762656 54.934934, 17.762656 55.384594))</t>
   </si>
   <si>
     <t>elc_won_POL_001</t>
   </si>
   <si>
-    <t>POLYGON ((17.076733 50.120359, 16.390811 50.120359, 16.390811 50.570019, 15.704889 50.570019, 15.018967 50.570019, 14.333045 50.570019, 14.333045 51.01968, 15.018967 51.01968, 15.704889 51.01968, 16.390811 51.01968, 17.076733 51.01968, 17.076733 50.570019, 17.076733 50.120359))</t>
-  </si>
-  <si>
     <t>elc_won_POL_002</t>
   </si>
   <si>
-    <t>POLYGON ((17.076733 49.670699, 17.076733 50.120359, 17.762656 50.120359, 17.762656 49.670699, 17.076733 49.670699))</t>
-  </si>
-  <si>
     <t>elc_won_POL_003</t>
   </si>
   <si>
-    <t>POLYGON ((15.704889 51.01968, 15.018967 51.01968, 15.018967 51.46934, 14.333045 51.46934, 14.333045 51.919, 14.333045 52.36866, 15.018967 52.36866, 15.704889 52.36866, 15.704889 51.919, 15.704889 51.46934, 15.704889 51.01968))</t>
-  </si>
-  <si>
     <t>elc_won_POL_004</t>
   </si>
   <si>
-    <t>POLYGON ((15.704889 52.36866, 15.704889 52.81832, 16.390811 52.81832, 17.076733 52.81832, 17.762656 52.81832, 17.762656 52.36866, 17.762656 51.919, 17.762656 51.46934, 17.762656 51.01968, 17.076733 51.01968, 16.390811 51.01968, 15.704889 51.01968, 15.704889 51.46934, 15.704889 51.919, 15.704889 52.36866))</t>
-  </si>
-  <si>
     <t>elc_won_POL_005</t>
   </si>
   <si>
-    <t>POLYGON ((19.820422 53.267981, 19.1345 53.267981, 18.448578 53.267981, 18.448578 52.81832, 17.762656 52.81832, 17.762656 53.267981, 17.762656 53.717641, 17.762656 54.167301, 18.448578 54.167301, 18.448578 54.616961, 19.1345 54.616961, 19.820422 54.616961, 19.820422 54.167301, 19.820422 53.717641, 19.820422 53.267981))</t>
+    <t>POLYGON ((17.762656 51.01968, 17.762656 51.46934, 18.448578 51.46934, 18.448578 51.01968, 17.762656 51.01968))</t>
   </si>
   <si>
     <t>elc_won_POL_006</t>
   </si>
   <si>
-    <t>POLYGON ((15.018967 52.36866, 14.333045 52.36866, 14.333045 52.81832, 14.333045 53.267981, 14.333045 53.717641, 14.333045 54.167301, 15.018967 54.167301, 15.704889 54.167301, 15.704889 53.717641, 15.704889 53.267981, 15.704889 52.81832, 15.704889 52.36866, 15.018967 52.36866))</t>
+    <t>POLYGON ((16.390811 50.570019, 16.390811 51.01968, 17.076733 51.01968, 17.076733 50.570019, 17.076733 50.120359, 16.390811 50.120359, 16.390811 50.570019))</t>
   </si>
   <si>
     <t>elc_won_POL_007</t>
   </si>
   <si>
-    <t>POLYGON ((16.390811 54.616961, 17.076733 54.616961, 17.762656 54.616961, 18.448578 54.616961, 18.448578 54.167301, 17.762656 54.167301, 17.076733 54.167301, 16.390811 54.167301, 15.704889 54.167301, 15.704889 54.616961, 16.390811 54.616961))</t>
-  </si>
-  <si>
     <t>elc_won_POL_008</t>
   </si>
   <si>
-    <t>POLYGON ((17.762656 52.81832, 17.076733 52.81832, 16.390811 52.81832, 15.704889 52.81832, 15.704889 53.267981, 15.704889 53.717641, 15.704889 54.167301, 16.390811 54.167301, 17.076733 54.167301, 17.762656 54.167301, 17.762656 53.717641, 17.762656 53.267981, 17.762656 52.81832))</t>
-  </si>
-  <si>
     <t>elc_won_POL_009</t>
   </si>
   <si>
-    <t>POLYGON ((23.250033 52.81832, 23.250033 53.267981, 22.564111 53.267981, 21.878189 53.267981, 21.878189 53.717641, 21.878189 54.167301, 22.564111 54.167301, 23.250033 54.167301, 23.250033 54.616961, 23.935955 54.616961, 23.935955 54.167301, 23.935955 53.717641, 23.935955 53.267981, 23.935955 52.81832, 23.250033 52.81832))</t>
-  </si>
-  <si>
     <t>elc_won_POL_010</t>
   </si>
   <si>
-    <t>POLYGON ((21.878189 53.717641, 21.192267 53.717641, 20.506344 53.717641, 19.820422 53.717641, 19.820422 54.167301, 19.820422 54.616961, 20.506344 54.616961, 21.192267 54.616961, 21.878189 54.616961, 22.564111 54.616961, 23.250033 54.616961, 23.250033 54.167301, 22.564111 54.167301, 21.878189 54.167301, 21.878189 53.717641))</t>
+    <t>POLYGON ((14.333045 51.01968, 15.018967 51.01968, 15.018967 51.46934, 15.704889 51.46934, 15.704889 51.01968, 15.704889 50.570019, 15.018967 50.570019, 14.333045 50.570019, 14.333045 51.01968))</t>
   </si>
   <si>
     <t>elc_won_POL_011</t>
   </si>
   <si>
-    <t>POLYGON ((21.878189 52.81832, 21.878189 53.267981, 22.564111 53.267981, 23.250033 53.267981, 23.250033 52.81832, 23.935955 52.81832, 23.935955 52.36866, 23.935955 51.919, 23.935955 51.46934, 23.935955 51.01968, 23.250033 51.01968, 23.250033 51.46934, 22.564111 51.46934, 21.878189 51.46934, 21.878189 51.919, 21.878189 52.36866, 21.878189 52.81832))</t>
-  </si>
-  <si>
     <t>elc_won_POL_012</t>
   </si>
   <si>
-    <t>POLYGON ((19.820422 53.267981, 19.820422 53.717641, 20.506344 53.717641, 21.192267 53.717641, 21.878189 53.717641, 21.878189 53.267981, 21.878189 52.81832, 21.878189 52.36866, 21.878189 51.919, 21.192267 51.919, 20.506344 51.919, 19.820422 51.919, 19.820422 52.36866, 19.820422 52.81832, 19.820422 53.267981))</t>
-  </si>
-  <si>
     <t>elc_won_POL_013</t>
   </si>
   <si>
-    <t>POLYGON ((19.1345 51.01968, 18.448578 51.01968, 17.762656 51.01968, 17.762656 51.46934, 17.762656 51.919, 17.762656 52.36866, 18.448578 52.36866, 18.448578 51.919, 19.1345 51.919, 19.1345 51.46934, 19.1345 51.01968))</t>
-  </si>
-  <si>
     <t>elc_won_POL_014</t>
   </si>
   <si>
-    <t>POLYGON ((19.820422 51.919, 19.1345 51.919, 18.448578 51.919, 18.448578 52.36866, 17.762656 52.36866, 17.762656 52.81832, 18.448578 52.81832, 18.448578 53.267981, 19.1345 53.267981, 19.820422 53.267981, 19.820422 52.81832, 19.820422 52.36866, 19.820422 51.919))</t>
-  </si>
-  <si>
     <t>elc_won_POL_015</t>
   </si>
   <si>
-    <t>POLYGON ((19.820422 50.120359, 19.1345 50.120359, 18.448578 50.120359, 17.762656 50.120359, 17.762656 50.570019, 17.762656 51.01968, 18.448578 51.01968, 19.1345 51.01968, 19.820422 51.01968, 19.820422 50.570019, 19.820422 50.120359))</t>
-  </si>
-  <si>
     <t>elc_won_POL_016</t>
   </si>
   <si>
-    <t>POLYGON ((20.506344 50.120359, 19.820422 50.120359, 19.820422 50.570019, 19.820422 51.01968, 19.1345 51.01968, 19.1345 51.46934, 19.1345 51.919, 19.820422 51.919, 20.506344 51.919, 21.192267 51.919, 21.192267 51.46934, 21.192267 51.01968, 21.192267 50.570019, 21.192267 50.120359, 20.506344 50.120359))</t>
-  </si>
-  <si>
     <t>elc_won_POL_017</t>
   </si>
   <si>
-    <t>POLYGON ((21.192267 51.46934, 21.192267 51.919, 21.878189 51.919, 21.878189 51.46934, 22.564111 51.46934, 23.250033 51.46934, 23.250033 51.01968, 23.935955 51.01968, 23.935955 50.570019, 23.935955 50.120359, 23.250033 50.120359, 23.250033 49.670699, 22.564111 49.670699, 22.564111 50.120359, 21.878189 50.120359, 21.192267 50.120359, 21.192267 50.570019, 21.192267 51.01968, 21.192267 51.46934))</t>
-  </si>
-  <si>
     <t>elc_won_POL_018</t>
   </si>
   <si>
-    <t>POLYGON ((21.878189 49.670699, 21.878189 50.120359, 22.564111 50.120359, 22.564111 49.670699, 23.250033 49.670699, 23.250033 49.221039, 22.564111 49.221039, 21.878189 49.221039, 21.878189 49.670699))</t>
-  </si>
-  <si>
     <t>elc_won_POL_019</t>
   </si>
   <si>
-    <t>POLYGON ((21.878189 49.221039, 21.192267 49.221039, 20.506344 49.221039, 20.506344 49.670699, 20.506344 50.120359, 21.192267 50.120359, 21.878189 50.120359, 21.878189 49.670699, 21.878189 49.221039))</t>
+    <t>POLYGON ((22.564111 50.570019, 22.564111 51.01968, 23.250033 51.01968, 23.935955 51.01968, 23.935955 50.570019, 23.935955 50.120359, 23.250033 50.120359, 23.250033 49.670699, 22.564111 49.670699, 22.564111 50.120359, 22.564111 50.570019))</t>
+  </si>
+  <si>
+    <t>elc_won_POL_020</t>
+  </si>
+  <si>
+    <t>elc_won_POL_021</t>
+  </si>
+  <si>
+    <t>elc_won_POL_022</t>
+  </si>
+  <si>
+    <t>elc_won_POL_023</t>
+  </si>
+  <si>
+    <t>elc_won_POL_024</t>
+  </si>
+  <si>
+    <t>elc_won_POL_025</t>
+  </si>
+  <si>
+    <t>elc_won_POL_026</t>
+  </si>
+  <si>
+    <t>elc_won_POL_027</t>
+  </si>
+  <si>
+    <t>elc_won_POL_028</t>
+  </si>
+  <si>
+    <t>elc_won_POL_029</t>
+  </si>
+  <si>
+    <t>elc_won_POL_030</t>
+  </si>
+  <si>
+    <t>elc_won_POL_031</t>
+  </si>
+  <si>
+    <t>elc_won_POL_032</t>
+  </si>
+  <si>
+    <t>elc_won_POL_033</t>
+  </si>
+  <si>
+    <t>elc_won_POL_034</t>
+  </si>
+  <si>
+    <t>elc_won_POL_035</t>
+  </si>
+  <si>
+    <t>elc_won_POL_036</t>
+  </si>
+  <si>
+    <t>elc_won_POL_037</t>
+  </si>
+  <si>
+    <t>MULTIPOLYGON (((17.076733 50.120359, 17.762656 50.120359, 17.762656 49.670699, 17.076733 49.670699, 17.076733 50.120359)), ((17.762656 51.01968, 18.448578 51.01968, 18.448578 50.570019, 18.448578 50.120359, 17.762656 50.120359, 17.762656 50.570019, 17.762656 51.01968)))</t>
+  </si>
+  <si>
+    <t>elc_won_POL_038</t>
+  </si>
+  <si>
+    <t>elc_won_POL_039</t>
+  </si>
+  <si>
+    <t>elc_won_POL_040</t>
+  </si>
+  <si>
+    <t>elc_won_POL_041</t>
+  </si>
+  <si>
+    <t>elc_won_POL_042</t>
+  </si>
+  <si>
+    <t>elc_won_POL_043</t>
+  </si>
+  <si>
+    <t>elc_won_POL_044</t>
+  </si>
+  <si>
+    <t>POLYGON ((19.820422 50.120359, 19.820422 50.570019, 20.506344 50.570019, 20.506344 50.120359, 19.820422 50.120359))</t>
+  </si>
+  <si>
+    <t>elc_won_POL_045</t>
   </si>
   <si>
     <t>co2</t>
@@ -1983,8 +2190,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E09F76B-E4F8-4DEB-A8DA-5AE451F73EAE}">
-  <dimension ref="B3:S101"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09C7407E-6768-42AB-845B-F5FD3722BCC2}">
+  <dimension ref="B3:S155"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="3" spans="2:19" x14ac:dyDescent="0.45">
@@ -4045,10 +4252,10 @@
         <v>8</v>
       </c>
       <c r="Q53">
-        <v>22.387884415840912</v>
+        <v>17.732742320902791</v>
       </c>
       <c r="R53">
-        <v>52.797852990301593</v>
+        <v>53.197615562848213</v>
       </c>
       <c r="S53" t="s">
         <v>239</v>
@@ -4089,10 +4296,10 @@
         <v>8</v>
       </c>
       <c r="Q54">
-        <v>22.436878727454864</v>
+        <v>23.076741255143787</v>
       </c>
       <c r="R54">
-        <v>53.758426235726397</v>
+        <v>52.887133598646692</v>
       </c>
       <c r="S54" t="s">
         <v>241</v>
@@ -4133,10 +4340,10 @@
         <v>8</v>
       </c>
       <c r="Q55">
-        <v>22.158862912599531</v>
+        <v>15.18361928372261</v>
       </c>
       <c r="R55">
-        <v>49.985302240943966</v>
+        <v>52.800197329771187</v>
       </c>
       <c r="S55" t="s">
         <v>243</v>
@@ -4177,10 +4384,10 @@
         <v>8</v>
       </c>
       <c r="Q56">
-        <v>20.576363415677669</v>
+        <v>16.443817708345744</v>
       </c>
       <c r="R56">
-        <v>50.179698397399775</v>
+        <v>51.286279433186863</v>
       </c>
       <c r="S56" t="s">
         <v>245</v>
@@ -4221,10 +4428,10 @@
         <v>8</v>
       </c>
       <c r="Q57">
-        <v>22.647999312422595</v>
+        <v>17.573992401991987</v>
       </c>
       <c r="R57">
-        <v>51.755872298670091</v>
+        <v>50.896000389817708</v>
       </c>
       <c r="S57" t="s">
         <v>247</v>
@@ -4265,10 +4472,10 @@
         <v>8</v>
       </c>
       <c r="Q58">
-        <v>22.614693947996503</v>
+        <v>16.733772344126869</v>
       </c>
       <c r="R58">
-        <v>50.677937554331706</v>
+        <v>50.670886022355177</v>
       </c>
       <c r="S58" t="s">
         <v>249</v>
@@ -4309,10 +4516,10 @@
         <v>8</v>
       </c>
       <c r="Q59">
-        <v>15.177025576701782</v>
+        <v>19.477461093696157</v>
       </c>
       <c r="R59">
-        <v>53.385570698209328</v>
+        <v>53.492810636517952</v>
       </c>
       <c r="S59" t="s">
         <v>251</v>
@@ -4353,10 +4560,10 @@
         <v>8</v>
       </c>
       <c r="Q60">
-        <v>16.851528118709499</v>
+        <v>17.419694531519191</v>
       </c>
       <c r="R60">
-        <v>53.556913702673697</v>
+        <v>54.3921310002425</v>
       </c>
       <c r="S60" t="s">
         <v>253</v>
@@ -4397,10 +4604,10 @@
         <v>8</v>
       </c>
       <c r="Q61">
-        <v>18.833039725101798</v>
+        <v>20.474987843539957</v>
       </c>
       <c r="R61">
-        <v>52.848472544632912</v>
+        <v>53.867432812752376</v>
       </c>
       <c r="S61" t="s">
         <v>255</v>
@@ -4441,10 +4648,10 @@
         <v>8</v>
       </c>
       <c r="Q62">
-        <v>20.474987843539957</v>
+        <v>15.346251681111026</v>
       </c>
       <c r="R62">
-        <v>53.867432812752376</v>
+        <v>51.202873879217471</v>
       </c>
       <c r="S62" t="s">
         <v>257</v>
@@ -4485,10 +4692,10 @@
         <v>8</v>
       </c>
       <c r="Q63">
-        <v>18.950202712790809</v>
+        <v>18.73472341078692</v>
       </c>
       <c r="R63">
-        <v>53.834708755581374</v>
+        <v>54.02228256102228</v>
       </c>
       <c r="S63" t="s">
         <v>259</v>
@@ -4529,10 +4736,10 @@
         <v>8</v>
       </c>
       <c r="Q64">
-        <v>16.541594041004011</v>
+        <v>21.804009726719805</v>
       </c>
       <c r="R64">
-        <v>52.292582195464313</v>
+        <v>52.847999678035883</v>
       </c>
       <c r="S64" t="s">
         <v>261</v>
@@ -4573,10 +4780,10 @@
         <v>8</v>
       </c>
       <c r="Q65">
-        <v>16.597184145059202</v>
+        <v>15.169582070037247</v>
       </c>
       <c r="R65">
-        <v>51.381036311175727</v>
+        <v>51.911584313619549</v>
       </c>
       <c r="S65" t="s">
         <v>263</v>
@@ -4617,10 +4824,10 @@
         <v>8</v>
       </c>
       <c r="Q66">
-        <v>15.346251681111026</v>
+        <v>15.343911278165097</v>
       </c>
       <c r="R66">
-        <v>51.202873879217471</v>
+        <v>53.930659874252505</v>
       </c>
       <c r="S66" t="s">
         <v>265</v>
@@ -4661,10 +4868,10 @@
         <v>8</v>
       </c>
       <c r="Q67">
-        <v>15.145356416678331</v>
+        <v>21.686893606685583</v>
       </c>
       <c r="R67">
-        <v>52.186880964694659</v>
+        <v>49.748425318724088</v>
       </c>
       <c r="S67" t="s">
         <v>267</v>
@@ -4705,10 +4912,10 @@
         <v>8</v>
       </c>
       <c r="Q68">
-        <v>17.083147938913381</v>
+        <v>22.600054496319373</v>
       </c>
       <c r="R68">
-        <v>50.673345049899048</v>
+        <v>54.004982398083385</v>
       </c>
       <c r="S68" t="s">
         <v>269</v>
@@ -4749,10 +4956,10 @@
         <v>8</v>
       </c>
       <c r="Q69">
-        <v>18.911500370089843</v>
+        <v>19.728152585549065</v>
       </c>
       <c r="R69">
-        <v>50.08331213626267</v>
+        <v>51.550412267890401</v>
       </c>
       <c r="S69" t="s">
         <v>271</v>
@@ -4793,10 +5000,10 @@
         <v>8</v>
       </c>
       <c r="Q70">
-        <v>20.781405442235567</v>
+        <v>18.791538906303831</v>
       </c>
       <c r="R70">
-        <v>52.366491870473581</v>
+        <v>51.419955039622174</v>
       </c>
       <c r="S70" t="s">
         <v>273</v>
@@ -4837,10 +5044,10 @@
         <v>8</v>
       </c>
       <c r="Q71">
-        <v>20.402957702269411</v>
+        <v>23.099272843498948</v>
       </c>
       <c r="R71">
-        <v>51.12109494883768</v>
+        <v>50.260453695040219</v>
       </c>
       <c r="S71" t="s">
         <v>275</v>
@@ -4881,10 +5088,10 @@
         <v>8</v>
       </c>
       <c r="Q72">
-        <v>18.792464723500991</v>
+        <v>16.490596872499417</v>
       </c>
       <c r="R72">
-        <v>51.330784626906521</v>
+        <v>53.766733588287018</v>
       </c>
       <c r="S72" t="s">
         <v>277</v>
@@ -4925,10 +5132,10 @@
         <v>8</v>
       </c>
       <c r="Q73">
-        <v>19.270410803611803</v>
+        <v>16.047850156734548</v>
       </c>
       <c r="R73">
-        <v>54.260516439232255</v>
+        <v>51.819832365173717</v>
       </c>
       <c r="S73" t="s">
         <v>279</v>
@@ -4969,10 +5176,10 @@
         <v>8</v>
       </c>
       <c r="Q74">
-        <v>19.132199145306835</v>
+        <v>18.791538906303831</v>
       </c>
       <c r="R74">
-        <v>55.159813342891759</v>
+        <v>49.895529181619793</v>
       </c>
       <c r="S74" t="s">
         <v>281</v>
@@ -5013,10 +5220,10 @@
         <v>8</v>
       </c>
       <c r="Q75">
-        <v>19.209580353300481</v>
+        <v>20.849305468480804</v>
       </c>
       <c r="R75">
-        <v>54.710164987068232</v>
+        <v>50.224675331577139</v>
       </c>
       <c r="S75" t="s">
         <v>283</v>
@@ -5057,10 +5264,10 @@
         <v>8</v>
       </c>
       <c r="Q76">
-        <v>16.941376551896891</v>
+        <v>23.198875657127921</v>
       </c>
       <c r="R76">
-        <v>55.60946078087305</v>
+        <v>51.540282380815263</v>
       </c>
       <c r="S76" t="s">
         <v>285</v>
@@ -5101,10 +5308,10 @@
         <v>8</v>
       </c>
       <c r="Q77">
-        <v>18.450551982707839</v>
+        <v>22.221149843265444</v>
       </c>
       <c r="R77">
-        <v>55.609461280132123</v>
+        <v>49.895529181619793</v>
       </c>
       <c r="S77" t="s">
         <v>287</v>
@@ -5145,10 +5352,10 @@
         <v>8</v>
       </c>
       <c r="Q78">
-        <v>17.878286085105412</v>
+        <v>20.45513220923721</v>
       </c>
       <c r="R78">
-        <v>55.159812876695007</v>
+        <v>50.996290709060048</v>
       </c>
       <c r="S78" t="s">
         <v>289</v>
@@ -5189,10 +5396,10 @@
         <v>8</v>
       </c>
       <c r="Q79">
-        <v>15.47382532166216</v>
+        <v>21.535227655873118</v>
       </c>
       <c r="R79">
-        <v>54.260515174922851</v>
+        <v>50.345189363482064</v>
       </c>
       <c r="S79" t="s">
         <v>291</v>
@@ -5233,10 +5440,10 @@
         <v>8</v>
       </c>
       <c r="Q80">
-        <v>15.28816677077992</v>
+        <v>22.221149843265444</v>
       </c>
       <c r="R80">
-        <v>54.710163723178738</v>
+        <v>50.466416149028909</v>
       </c>
       <c r="S80" t="s">
         <v>293</v>
@@ -5277,10 +5484,10 @@
         <v>8</v>
       </c>
       <c r="Q81">
-        <v>16.268392183867956</v>
+        <v>19.133601934620422</v>
       </c>
       <c r="R81">
-        <v>55.159812379291822</v>
+        <v>50.794849545344327</v>
       </c>
       <c r="S81" t="s">
         <v>295</v>
@@ -5321,10 +5528,10 @@
         <v>8</v>
       </c>
       <c r="Q82">
-        <v>16.047809605897839</v>
+        <v>18.791538906303828</v>
       </c>
       <c r="R82">
-        <v>54.710163913347117</v>
+        <v>52.858257807793557</v>
       </c>
       <c r="S82" t="s">
         <v>297</v>
@@ -5365,10 +5572,10 @@
         <v>8</v>
       </c>
       <c r="Q83">
-        <v>16.384709287577795</v>
+        <v>21.535227655873118</v>
       </c>
       <c r="R83">
-        <v>50.776690615375294</v>
+        <v>51.028817664495243</v>
       </c>
       <c r="S83" t="s">
         <v>299</v>
@@ -5412,7 +5619,7 @@
         <v>17.419694531519191</v>
       </c>
       <c r="R84">
-        <v>49.895529181619793</v>
+        <v>50.345189363482064</v>
       </c>
       <c r="S84" t="s">
         <v>301</v>
@@ -5453,10 +5660,10 @@
         <v>8</v>
       </c>
       <c r="Q85">
-        <v>15.256062905619441</v>
+        <v>18.200403953900462</v>
       </c>
       <c r="R85">
-        <v>51.98468831119169</v>
+        <v>52.169564808191033</v>
       </c>
       <c r="S85" t="s">
         <v>303</v>
@@ -5497,10 +5704,10 @@
         <v>8</v>
       </c>
       <c r="Q86">
-        <v>16.80515814440529</v>
+        <v>16.733772344126869</v>
       </c>
       <c r="R86">
-        <v>52.124016263770471</v>
+        <v>54.3921310002425</v>
       </c>
       <c r="S86" t="s">
         <v>305</v>
@@ -5541,10 +5748,10 @@
         <v>8</v>
       </c>
       <c r="Q87">
-        <v>19.003551538461117</v>
+        <v>21.031789374844319</v>
       </c>
       <c r="R87">
-        <v>53.788484402851722</v>
+        <v>52.28019358068476</v>
       </c>
       <c r="S87" t="s">
         <v>307</v>
@@ -5585,10 +5792,10 @@
         <v>8</v>
       </c>
       <c r="Q88">
-        <v>15.172985574189886</v>
+        <v>18.791538906303831</v>
       </c>
       <c r="R88">
-        <v>53.270513397783269</v>
+        <v>50.345189363482064</v>
       </c>
       <c r="S88" t="s">
         <v>309</v>
@@ -5629,10 +5836,10 @@
         <v>8</v>
       </c>
       <c r="Q89">
-        <v>17.551521574400923</v>
+        <v>21.866802774911854</v>
       </c>
       <c r="R89">
-        <v>54.392131000242507</v>
+        <v>53.775203125121777</v>
       </c>
       <c r="S89" t="s">
         <v>311</v>
@@ -5646,10 +5853,10 @@
         <v>8</v>
       </c>
       <c r="Q90">
-        <v>16.852061394622268</v>
+        <v>16.65132373540435</v>
       </c>
       <c r="R90">
-        <v>53.40601844225278</v>
+        <v>52.707053608818114</v>
       </c>
       <c r="S90" t="s">
         <v>313</v>
@@ -5663,10 +5870,10 @@
         <v>8</v>
       </c>
       <c r="Q91">
-        <v>22.728951916805229</v>
+        <v>18.102430082591109</v>
       </c>
       <c r="R91">
-        <v>53.629053884575626</v>
+        <v>50.368478771061248</v>
       </c>
       <c r="S91" t="s">
         <v>315</v>
@@ -5680,10 +5887,10 @@
         <v>8</v>
       </c>
       <c r="Q92">
-        <v>21.016862912105651</v>
+        <v>14.676005781949902</v>
       </c>
       <c r="R92">
-        <v>54.067358273794383</v>
+        <v>53.043150454655688</v>
       </c>
       <c r="S92" t="s">
         <v>317</v>
@@ -5697,10 +5904,10 @@
         <v>8</v>
       </c>
       <c r="Q93">
-        <v>22.557805508871297</v>
+        <v>19.477461093696157</v>
       </c>
       <c r="R93">
-        <v>52.454344370054137</v>
+        <v>50.345189363482064</v>
       </c>
       <c r="S93" t="s">
         <v>319</v>
@@ -5714,10 +5921,10 @@
         <v>8</v>
       </c>
       <c r="Q94">
-        <v>20.648531569729403</v>
+        <v>19.475481690054949</v>
       </c>
       <c r="R94">
-        <v>52.768785613368301</v>
+        <v>49.872151522293322</v>
       </c>
       <c r="S94" t="s">
         <v>321</v>
@@ -5731,10 +5938,10 @@
         <v>8</v>
       </c>
       <c r="Q95">
-        <v>18.369571653809839</v>
+        <v>19.163221535912964</v>
       </c>
       <c r="R95">
-        <v>51.799686803699899</v>
+        <v>53.736469293282624</v>
       </c>
       <c r="S95" t="s">
         <v>323</v>
@@ -5748,10 +5955,10 @@
         <v>8</v>
       </c>
       <c r="Q96">
-        <v>19.027975647671131</v>
+        <v>19.907650709888724</v>
       </c>
       <c r="R96">
-        <v>52.655496867703171</v>
+        <v>52.581850669181293</v>
       </c>
       <c r="S96" t="s">
         <v>325</v>
@@ -5765,10 +5972,10 @@
         <v>8</v>
       </c>
       <c r="Q97">
-        <v>19.265584431429922</v>
+        <v>17.419694531519191</v>
       </c>
       <c r="R97">
-        <v>50.628803361963257</v>
+        <v>51.351016228937411</v>
       </c>
       <c r="S97" t="s">
         <v>327</v>
@@ -5782,10 +5989,10 @@
         <v>8</v>
       </c>
       <c r="Q98">
-        <v>20.044508863733864</v>
+        <v>18.105616718911509</v>
       </c>
       <c r="R98">
-        <v>51.478266767104472</v>
+        <v>54.3921310002425</v>
       </c>
       <c r="S98" t="s">
         <v>329</v>
@@ -5799,10 +6006,10 @@
         <v>8</v>
       </c>
       <c r="Q99">
-        <v>22.909847640550961</v>
+        <v>20.163383281088478</v>
       </c>
       <c r="R99">
-        <v>50.868423259833534</v>
+        <v>50.11164519658584</v>
       </c>
       <c r="S99" t="s">
         <v>331</v>
@@ -5816,10 +6023,10 @@
         <v>8</v>
       </c>
       <c r="Q100">
-        <v>22.221487288334288</v>
+        <v>22.033984475568818</v>
       </c>
       <c r="R100">
-        <v>49.853731539665588</v>
+        <v>51.717686603776322</v>
       </c>
       <c r="S100" t="s">
         <v>333</v>
@@ -5833,13 +6040,931 @@
         <v>8</v>
       </c>
       <c r="Q101">
-        <v>21.524822746291907</v>
+        <v>19.270410803611803</v>
       </c>
       <c r="R101">
-        <v>49.648253092611611</v>
+        <v>54.260516439232255</v>
       </c>
       <c r="S101" t="s">
         <v>335</v>
+      </c>
+    </row>
+    <row r="102" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O102" t="s">
+        <v>336</v>
+      </c>
+      <c r="P102" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q102">
+        <v>19.336482428831868</v>
+      </c>
+      <c r="R102">
+        <v>54.923226170318472</v>
+      </c>
+      <c r="S102" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="103" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O103" t="s">
+        <v>338</v>
+      </c>
+      <c r="P103" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q103">
+        <v>15.28816677077992</v>
+      </c>
+      <c r="R103">
+        <v>54.710163723178738</v>
+      </c>
+      <c r="S103" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="104" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O104" t="s">
+        <v>340</v>
+      </c>
+      <c r="P104" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q104">
+        <v>15.361892353269836</v>
+      </c>
+      <c r="R104">
+        <v>54.26051514610343</v>
+      </c>
+      <c r="S104" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="105" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O105" t="s">
+        <v>342</v>
+      </c>
+      <c r="P105" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q105">
+        <v>16.047809989056592</v>
+      </c>
+      <c r="R105">
+        <v>54.260515322706873</v>
+      </c>
+      <c r="S105" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="106" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O106" t="s">
+        <v>344</v>
+      </c>
+      <c r="P106" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q106">
+        <v>16.360336631261571</v>
+      </c>
+      <c r="R106">
+        <v>55.248657504176741</v>
+      </c>
+      <c r="S106" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="107" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O107" t="s">
+        <v>346</v>
+      </c>
+      <c r="P107" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q107">
+        <v>16.047809605897839</v>
+      </c>
+      <c r="R107">
+        <v>54.710163913347117</v>
+      </c>
+      <c r="S107" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="108" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O108" t="s">
+        <v>348</v>
+      </c>
+      <c r="P108" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q108">
+        <v>17.419644121917074</v>
+      </c>
+      <c r="R108">
+        <v>55.329041014058205</v>
+      </c>
+      <c r="S108" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="109" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O109" t="s">
+        <v>350</v>
+      </c>
+      <c r="P109" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q109">
+        <v>18.450551982707839</v>
+      </c>
+      <c r="R109">
+        <v>55.609461280132123</v>
+      </c>
+      <c r="S109" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="110" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O110" t="s">
+        <v>352</v>
+      </c>
+      <c r="P110" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q110">
+        <v>18.559290016941631</v>
+      </c>
+      <c r="R110">
+        <v>55.159813121219983</v>
+      </c>
+      <c r="S110" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="111" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O111" t="s">
+        <v>354</v>
+      </c>
+      <c r="P111" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q111">
+        <v>17.581719183715883</v>
+      </c>
+      <c r="R111">
+        <v>53.196775208514168</v>
+      </c>
+      <c r="S111" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="112" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O112" t="s">
+        <v>355</v>
+      </c>
+      <c r="P112" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q112">
+        <v>23.0458728607606</v>
+      </c>
+      <c r="R112">
+        <v>52.968147537812392</v>
+      </c>
+      <c r="S112" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="113" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O113" t="s">
+        <v>356</v>
+      </c>
+      <c r="P113" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q113">
+        <v>15.304593124504157</v>
+      </c>
+      <c r="R113">
+        <v>53.194499256083724</v>
+      </c>
+      <c r="S113" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="114" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O114" t="s">
+        <v>357</v>
+      </c>
+      <c r="P114" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q114">
+        <v>16.472789268249258</v>
+      </c>
+      <c r="R114">
+        <v>51.400799441590003</v>
+      </c>
+      <c r="S114" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="115" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O115" t="s">
+        <v>358</v>
+      </c>
+      <c r="P115" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q115">
+        <v>18.105616718911509</v>
+      </c>
+      <c r="R115">
+        <v>51.244509727206619</v>
+      </c>
+      <c r="S115" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="116" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O116" t="s">
+        <v>360</v>
+      </c>
+      <c r="P116" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q116">
+        <v>16.733772344126869</v>
+      </c>
+      <c r="R116">
+        <v>50.76219887306744</v>
+      </c>
+      <c r="S116" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="117" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O117" t="s">
+        <v>362</v>
+      </c>
+      <c r="P117" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q117">
+        <v>19.477461093696157</v>
+      </c>
+      <c r="R117">
+        <v>53.492810636517952</v>
+      </c>
+      <c r="S117" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="118" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O118" t="s">
+        <v>363</v>
+      </c>
+      <c r="P118" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q118">
+        <v>17.419694531519191</v>
+      </c>
+      <c r="R118">
+        <v>54.392131000242507</v>
+      </c>
+      <c r="S118" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="119" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O119" t="s">
+        <v>364</v>
+      </c>
+      <c r="P119" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q119">
+        <v>20.492161121941823</v>
+      </c>
+      <c r="R119">
+        <v>53.90075879968235</v>
+      </c>
+      <c r="S119" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="120" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O120" t="s">
+        <v>365</v>
+      </c>
+      <c r="P120" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q120">
+        <v>15.198798723531963</v>
+      </c>
+      <c r="R120">
+        <v>51.04618038583336</v>
+      </c>
+      <c r="S120" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="121" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O121" t="s">
+        <v>367</v>
+      </c>
+      <c r="P121" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q121">
+        <v>18.70294226213645</v>
+      </c>
+      <c r="R121">
+        <v>53.953418222130388</v>
+      </c>
+      <c r="S121" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="122" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O122" t="s">
+        <v>368</v>
+      </c>
+      <c r="P122" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q122">
+        <v>21.770857300719211</v>
+      </c>
+      <c r="R122">
+        <v>52.911855600577397</v>
+      </c>
+      <c r="S122" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="123" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O123" t="s">
+        <v>369</v>
+      </c>
+      <c r="P123" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q123">
+        <v>15.234781597502089</v>
+      </c>
+      <c r="R123">
+        <v>52.133481198606368</v>
+      </c>
+      <c r="S123" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="124" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O124" t="s">
+        <v>370</v>
+      </c>
+      <c r="P124" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q124">
+        <v>15.361927969342224</v>
+      </c>
+      <c r="R124">
+        <v>53.942470818380237</v>
+      </c>
+      <c r="S124" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="125" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O125" t="s">
+        <v>371</v>
+      </c>
+      <c r="P125" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q125">
+        <v>21.599995349696041</v>
+      </c>
+      <c r="R125">
+        <v>49.626238205178431</v>
+      </c>
+      <c r="S125" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="126" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O126" t="s">
+        <v>372</v>
+      </c>
+      <c r="P126" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q126">
+        <v>22.534166549818089</v>
+      </c>
+      <c r="R126">
+        <v>54.009104014230232</v>
+      </c>
+      <c r="S126" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="127" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O127" t="s">
+        <v>373</v>
+      </c>
+      <c r="P127" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q127">
+        <v>19.722955756945726</v>
+      </c>
+      <c r="R127">
+        <v>51.606881385274058</v>
+      </c>
+      <c r="S127" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="128" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O128" t="s">
+        <v>374</v>
+      </c>
+      <c r="P128" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q128">
+        <v>18.791538906303831</v>
+      </c>
+      <c r="R128">
+        <v>51.607784085577883</v>
+      </c>
+      <c r="S128" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="129" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O129" t="s">
+        <v>375</v>
+      </c>
+      <c r="P129" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q129">
+        <v>23.418504807003217</v>
+      </c>
+      <c r="R129">
+        <v>50.648789659390587</v>
+      </c>
+      <c r="S129" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="130" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O130" t="s">
+        <v>377</v>
+      </c>
+      <c r="P130" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q130">
+        <v>16.343285359812334</v>
+      </c>
+      <c r="R130">
+        <v>53.711878482127347</v>
+      </c>
+      <c r="S130" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="131" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O131" t="s">
+        <v>378</v>
+      </c>
+      <c r="P131" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q131">
+        <v>16.047850156734544</v>
+      </c>
+      <c r="R131">
+        <v>51.955421759583338</v>
+      </c>
+      <c r="S131" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="132" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O132" t="s">
+        <v>379</v>
+      </c>
+      <c r="P132" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q132">
+        <v>20.849305468480804</v>
+      </c>
+      <c r="R132">
+        <v>49.979847832487074</v>
+      </c>
+      <c r="S132" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="133" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O133" t="s">
+        <v>380</v>
+      </c>
+      <c r="P133" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q133">
+        <v>23.091175379404827</v>
+      </c>
+      <c r="R133">
+        <v>51.490170313293042</v>
+      </c>
+      <c r="S133" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="134" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O134" t="s">
+        <v>381</v>
+      </c>
+      <c r="P134" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q134">
+        <v>22.221149843265444</v>
+      </c>
+      <c r="R134">
+        <v>49.895529181619793</v>
+      </c>
+      <c r="S134" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="135" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O135" t="s">
+        <v>382</v>
+      </c>
+      <c r="P135" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q135">
+        <v>20.723463068828806</v>
+      </c>
+      <c r="R135">
+        <v>51.206608290896526</v>
+      </c>
+      <c r="S135" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="136" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O136" t="s">
+        <v>383</v>
+      </c>
+      <c r="P136" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q136">
+        <v>21.535227655873118</v>
+      </c>
+      <c r="R136">
+        <v>50.345189363482064</v>
+      </c>
+      <c r="S136" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="137" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O137" t="s">
+        <v>384</v>
+      </c>
+      <c r="P137" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q137">
+        <v>22.221149843265444</v>
+      </c>
+      <c r="R137">
+        <v>50.702019523773188</v>
+      </c>
+      <c r="S137" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="138" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O138" t="s">
+        <v>385</v>
+      </c>
+      <c r="P138" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q138">
+        <v>19.141537976370479</v>
+      </c>
+      <c r="R138">
+        <v>50.794849545344341</v>
+      </c>
+      <c r="S138" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="139" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O139" t="s">
+        <v>386</v>
+      </c>
+      <c r="P139" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q139">
+        <v>18.791538906303831</v>
+      </c>
+      <c r="R139">
+        <v>52.866942494850733</v>
+      </c>
+      <c r="S139" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="140" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O140" t="s">
+        <v>387</v>
+      </c>
+      <c r="P140" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q140">
+        <v>21.535227655873118</v>
+      </c>
+      <c r="R140">
+        <v>51.12207241004873</v>
+      </c>
+      <c r="S140" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="141" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O141" t="s">
+        <v>388</v>
+      </c>
+      <c r="P141" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q141">
+        <v>18.443463902914296</v>
+      </c>
+      <c r="R141">
+        <v>52.152617042117903</v>
+      </c>
+      <c r="S141" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="142" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O142" t="s">
+        <v>389</v>
+      </c>
+      <c r="P142" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q142">
+        <v>16.733772344126869</v>
+      </c>
+      <c r="R142">
+        <v>54.3921310002425</v>
+      </c>
+      <c r="S142" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="143" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O143" t="s">
+        <v>390</v>
+      </c>
+      <c r="P143" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q143">
+        <v>21.004381926924367</v>
+      </c>
+      <c r="R143">
+        <v>52.40875253328344</v>
+      </c>
+      <c r="S143" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="144" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O144" t="s">
+        <v>391</v>
+      </c>
+      <c r="P144" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q144">
+        <v>18.791538906303831</v>
+      </c>
+      <c r="R144">
+        <v>50.345189363482064</v>
+      </c>
+      <c r="S144" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="145" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O145" t="s">
+        <v>392</v>
+      </c>
+      <c r="P145" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q145">
+        <v>21.839359413405159</v>
+      </c>
+      <c r="R145">
+        <v>53.798677421956477</v>
+      </c>
+      <c r="S145" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="146" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O146" t="s">
+        <v>393</v>
+      </c>
+      <c r="P146" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q146">
+        <v>16.811054032011597</v>
+      </c>
+      <c r="R146">
+        <v>52.578511324728609</v>
+      </c>
+      <c r="S146" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="147" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O147" t="s">
+        <v>394</v>
+      </c>
+      <c r="P147" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q147">
+        <v>18.105616718911509</v>
+      </c>
+      <c r="R147">
+        <v>50.345189363482064</v>
+      </c>
+      <c r="S147" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="148" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O148" t="s">
+        <v>396</v>
+      </c>
+      <c r="P148" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q148">
+        <v>14.6760057819499</v>
+      </c>
+      <c r="R148">
+        <v>53.043150454655688</v>
+      </c>
+      <c r="S148" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="149" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O149" t="s">
+        <v>397</v>
+      </c>
+      <c r="P149" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q149">
+        <v>19.477461093696157</v>
+      </c>
+      <c r="R149">
+        <v>50.345189363482064</v>
+      </c>
+      <c r="S149" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="150" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O150" t="s">
+        <v>398</v>
+      </c>
+      <c r="P150" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q150">
+        <v>19.306038498498257</v>
+      </c>
+      <c r="R150">
+        <v>53.830093763447763</v>
+      </c>
+      <c r="S150" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="151" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O151" t="s">
+        <v>399</v>
+      </c>
+      <c r="P151" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q151">
+        <v>19.902988727679805</v>
+      </c>
+      <c r="R151">
+        <v>52.628323275925922</v>
+      </c>
+      <c r="S151" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="152" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O152" t="s">
+        <v>400</v>
+      </c>
+      <c r="P152" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q152">
+        <v>17.419694531519191</v>
+      </c>
+      <c r="R152">
+        <v>51.615078540529446</v>
+      </c>
+      <c r="S152" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="153" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O153" t="s">
+        <v>401</v>
+      </c>
+      <c r="P153" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q153">
+        <v>18.105616718911509</v>
+      </c>
+      <c r="R153">
+        <v>54.392131000242507</v>
+      </c>
+      <c r="S153" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="154" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O154" t="s">
+        <v>402</v>
+      </c>
+      <c r="P154" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q154">
+        <v>20.163383281088478</v>
+      </c>
+      <c r="R154">
+        <v>50.345189363482064</v>
+      </c>
+      <c r="S154" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="155" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O155" t="s">
+        <v>404</v>
+      </c>
+      <c r="P155" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q155">
+        <v>22.194399267951567</v>
+      </c>
+      <c r="R155">
+        <v>51.821273485020299</v>
+      </c>
+      <c r="S155" t="s">
+        <v>333</v>
       </c>
     </row>
   </sheetData>
@@ -5848,7 +6973,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2099808-1E00-490F-92CF-6F939CD2F271}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF27E646-DCD4-477B-8725-771F59E2B283}">
   <dimension ref="B3:L62"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5897,25 +7022,25 @@
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E5" t="s">
-        <v>337</v>
+        <v>406</v>
       </c>
       <c r="F5" t="s">
-        <v>338</v>
+        <v>407</v>
       </c>
       <c r="G5" t="s">
-        <v>339</v>
+        <v>408</v>
       </c>
       <c r="H5" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K5" t="s">
-        <v>339</v>
+        <v>408</v>
       </c>
       <c r="L5" t="s">
-        <v>474</v>
+        <v>543</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.45">
@@ -5926,25 +7051,25 @@
         <v>8</v>
       </c>
       <c r="D6" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E6" t="s">
-        <v>341</v>
+        <v>410</v>
       </c>
       <c r="F6" t="s">
-        <v>342</v>
+        <v>411</v>
       </c>
       <c r="G6" t="s">
-        <v>343</v>
+        <v>412</v>
       </c>
       <c r="H6" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K6" t="s">
-        <v>343</v>
+        <v>412</v>
       </c>
       <c r="L6" t="s">
-        <v>475</v>
+        <v>544</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.45">
@@ -5955,25 +7080,25 @@
         <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E7" t="s">
-        <v>344</v>
+        <v>413</v>
       </c>
       <c r="F7" t="s">
-        <v>345</v>
+        <v>414</v>
       </c>
       <c r="G7" t="s">
-        <v>346</v>
+        <v>415</v>
       </c>
       <c r="H7" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K7" t="s">
-        <v>346</v>
+        <v>415</v>
       </c>
       <c r="L7" t="s">
-        <v>476</v>
+        <v>545</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.45">
@@ -5984,25 +7109,25 @@
         <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E8" t="s">
-        <v>347</v>
+        <v>416</v>
       </c>
       <c r="F8" t="s">
-        <v>348</v>
+        <v>417</v>
       </c>
       <c r="G8" t="s">
-        <v>349</v>
+        <v>418</v>
       </c>
       <c r="H8" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K8" t="s">
-        <v>349</v>
+        <v>418</v>
       </c>
       <c r="L8" t="s">
-        <v>477</v>
+        <v>546</v>
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.45">
@@ -6013,25 +7138,25 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E9" t="s">
-        <v>350</v>
+        <v>419</v>
       </c>
       <c r="F9" t="s">
-        <v>351</v>
+        <v>420</v>
       </c>
       <c r="G9" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="H9" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K9" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="L9" t="s">
-        <v>478</v>
+        <v>547</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.45">
@@ -6042,25 +7167,25 @@
         <v>8</v>
       </c>
       <c r="D10" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E10" t="s">
-        <v>353</v>
+        <v>422</v>
       </c>
       <c r="F10" t="s">
-        <v>354</v>
+        <v>423</v>
       </c>
       <c r="G10" t="s">
-        <v>355</v>
+        <v>424</v>
       </c>
       <c r="H10" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K10" t="s">
-        <v>355</v>
+        <v>424</v>
       </c>
       <c r="L10" t="s">
-        <v>479</v>
+        <v>548</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.45">
@@ -6071,25 +7196,25 @@
         <v>8</v>
       </c>
       <c r="D11" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E11" t="s">
-        <v>356</v>
+        <v>425</v>
       </c>
       <c r="F11" t="s">
-        <v>338</v>
+        <v>407</v>
       </c>
       <c r="G11" t="s">
-        <v>357</v>
+        <v>426</v>
       </c>
       <c r="H11" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K11" t="s">
-        <v>357</v>
+        <v>426</v>
       </c>
       <c r="L11" t="s">
-        <v>480</v>
+        <v>549</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.45">
@@ -6100,25 +7225,25 @@
         <v>8</v>
       </c>
       <c r="D12" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E12" t="s">
-        <v>358</v>
+        <v>427</v>
       </c>
       <c r="F12" t="s">
-        <v>359</v>
+        <v>428</v>
       </c>
       <c r="G12" t="s">
-        <v>360</v>
+        <v>429</v>
       </c>
       <c r="H12" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K12" t="s">
-        <v>360</v>
+        <v>429</v>
       </c>
       <c r="L12" t="s">
-        <v>481</v>
+        <v>550</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.45">
@@ -6129,25 +7254,25 @@
         <v>8</v>
       </c>
       <c r="D13" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E13" t="s">
-        <v>361</v>
+        <v>430</v>
       </c>
       <c r="F13" t="s">
-        <v>362</v>
+        <v>431</v>
       </c>
       <c r="G13" t="s">
-        <v>363</v>
+        <v>432</v>
       </c>
       <c r="H13" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K13" t="s">
-        <v>363</v>
+        <v>432</v>
       </c>
       <c r="L13" t="s">
-        <v>482</v>
+        <v>551</v>
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.45">
@@ -6158,25 +7283,25 @@
         <v>8</v>
       </c>
       <c r="D14" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E14" t="s">
-        <v>364</v>
+        <v>433</v>
       </c>
       <c r="F14" t="s">
-        <v>348</v>
+        <v>417</v>
       </c>
       <c r="G14" t="s">
-        <v>365</v>
+        <v>434</v>
       </c>
       <c r="H14" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K14" t="s">
-        <v>365</v>
+        <v>434</v>
       </c>
       <c r="L14" t="s">
-        <v>483</v>
+        <v>552</v>
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.45">
@@ -6187,25 +7312,25 @@
         <v>8</v>
       </c>
       <c r="D15" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E15" t="s">
-        <v>366</v>
+        <v>435</v>
       </c>
       <c r="F15" t="s">
-        <v>362</v>
+        <v>431</v>
       </c>
       <c r="G15" t="s">
-        <v>367</v>
+        <v>436</v>
       </c>
       <c r="H15" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K15" t="s">
-        <v>367</v>
+        <v>436</v>
       </c>
       <c r="L15" t="s">
-        <v>484</v>
+        <v>553</v>
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.45">
@@ -6216,25 +7341,25 @@
         <v>8</v>
       </c>
       <c r="D16" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E16" t="s">
-        <v>368</v>
+        <v>437</v>
       </c>
       <c r="F16" t="s">
-        <v>342</v>
+        <v>411</v>
       </c>
       <c r="G16" t="s">
-        <v>369</v>
+        <v>438</v>
       </c>
       <c r="H16" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K16" t="s">
-        <v>369</v>
+        <v>438</v>
       </c>
       <c r="L16" t="s">
-        <v>485</v>
+        <v>554</v>
       </c>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.45">
@@ -6245,25 +7370,25 @@
         <v>8</v>
       </c>
       <c r="D17" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E17" t="s">
-        <v>370</v>
+        <v>439</v>
       </c>
       <c r="F17" t="s">
-        <v>348</v>
+        <v>417</v>
       </c>
       <c r="G17" t="s">
-        <v>371</v>
+        <v>440</v>
       </c>
       <c r="H17" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K17" t="s">
-        <v>371</v>
+        <v>440</v>
       </c>
       <c r="L17" t="s">
-        <v>486</v>
+        <v>555</v>
       </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.45">
@@ -6274,25 +7399,25 @@
         <v>8</v>
       </c>
       <c r="D18" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E18" t="s">
-        <v>372</v>
+        <v>441</v>
       </c>
       <c r="F18" t="s">
-        <v>373</v>
+        <v>442</v>
       </c>
       <c r="G18" t="s">
-        <v>374</v>
+        <v>443</v>
       </c>
       <c r="H18" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K18" t="s">
-        <v>374</v>
+        <v>443</v>
       </c>
       <c r="L18" t="s">
-        <v>487</v>
+        <v>556</v>
       </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.45">
@@ -6303,25 +7428,25 @@
         <v>8</v>
       </c>
       <c r="D19" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E19" t="s">
-        <v>375</v>
+        <v>444</v>
       </c>
       <c r="F19" t="s">
-        <v>376</v>
+        <v>445</v>
       </c>
       <c r="G19" t="s">
-        <v>377</v>
+        <v>446</v>
       </c>
       <c r="H19" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K19" t="s">
-        <v>377</v>
+        <v>446</v>
       </c>
       <c r="L19" t="s">
-        <v>488</v>
+        <v>557</v>
       </c>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.45">
@@ -6332,25 +7457,25 @@
         <v>8</v>
       </c>
       <c r="D20" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E20" t="s">
-        <v>378</v>
+        <v>447</v>
       </c>
       <c r="F20" t="s">
-        <v>362</v>
+        <v>431</v>
       </c>
       <c r="G20" t="s">
-        <v>379</v>
+        <v>448</v>
       </c>
       <c r="H20" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K20" t="s">
-        <v>379</v>
+        <v>448</v>
       </c>
       <c r="L20" t="s">
-        <v>489</v>
+        <v>558</v>
       </c>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.45">
@@ -6361,25 +7486,25 @@
         <v>8</v>
       </c>
       <c r="D21" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E21" t="s">
-        <v>380</v>
+        <v>449</v>
       </c>
       <c r="F21" t="s">
-        <v>381</v>
+        <v>450</v>
       </c>
       <c r="G21" t="s">
-        <v>382</v>
+        <v>451</v>
       </c>
       <c r="H21" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K21" t="s">
-        <v>382</v>
+        <v>451</v>
       </c>
       <c r="L21" t="s">
-        <v>490</v>
+        <v>559</v>
       </c>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.45">
@@ -6390,25 +7515,25 @@
         <v>8</v>
       </c>
       <c r="D22" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E22" t="s">
-        <v>383</v>
+        <v>452</v>
       </c>
       <c r="F22" t="s">
-        <v>384</v>
+        <v>453</v>
       </c>
       <c r="G22" t="s">
-        <v>385</v>
+        <v>454</v>
       </c>
       <c r="H22" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K22" t="s">
-        <v>385</v>
+        <v>454</v>
       </c>
       <c r="L22" t="s">
-        <v>491</v>
+        <v>560</v>
       </c>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.45">
@@ -6419,25 +7544,25 @@
         <v>8</v>
       </c>
       <c r="D23" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E23" t="s">
-        <v>386</v>
+        <v>455</v>
       </c>
       <c r="F23" t="s">
-        <v>376</v>
+        <v>445</v>
       </c>
       <c r="G23" t="s">
-        <v>387</v>
+        <v>456</v>
       </c>
       <c r="H23" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K23" t="s">
-        <v>387</v>
+        <v>456</v>
       </c>
       <c r="L23" t="s">
-        <v>492</v>
+        <v>561</v>
       </c>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.45">
@@ -6448,25 +7573,25 @@
         <v>8</v>
       </c>
       <c r="D24" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E24" t="s">
-        <v>388</v>
+        <v>457</v>
       </c>
       <c r="F24" t="s">
-        <v>389</v>
+        <v>458</v>
       </c>
       <c r="G24" t="s">
-        <v>390</v>
+        <v>459</v>
       </c>
       <c r="H24" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K24" t="s">
-        <v>390</v>
+        <v>459</v>
       </c>
       <c r="L24" t="s">
-        <v>493</v>
+        <v>562</v>
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.45">
@@ -6477,25 +7602,25 @@
         <v>8</v>
       </c>
       <c r="D25" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E25" t="s">
-        <v>391</v>
+        <v>460</v>
       </c>
       <c r="F25" t="s">
-        <v>348</v>
+        <v>417</v>
       </c>
       <c r="G25" t="s">
-        <v>392</v>
+        <v>461</v>
       </c>
       <c r="H25" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K25" t="s">
-        <v>392</v>
+        <v>461</v>
       </c>
       <c r="L25" t="s">
-        <v>494</v>
+        <v>563</v>
       </c>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.45">
@@ -6506,25 +7631,25 @@
         <v>8</v>
       </c>
       <c r="D26" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E26" t="s">
-        <v>393</v>
+        <v>462</v>
       </c>
       <c r="F26" t="s">
-        <v>394</v>
+        <v>463</v>
       </c>
       <c r="G26" t="s">
-        <v>395</v>
+        <v>464</v>
       </c>
       <c r="H26" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K26" t="s">
-        <v>395</v>
+        <v>464</v>
       </c>
       <c r="L26" t="s">
-        <v>495</v>
+        <v>564</v>
       </c>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.45">
@@ -6535,25 +7660,25 @@
         <v>8</v>
       </c>
       <c r="D27" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E27" t="s">
-        <v>396</v>
+        <v>465</v>
       </c>
       <c r="F27" t="s">
-        <v>394</v>
+        <v>463</v>
       </c>
       <c r="G27" t="s">
-        <v>397</v>
+        <v>466</v>
       </c>
       <c r="H27" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K27" t="s">
-        <v>397</v>
+        <v>466</v>
       </c>
       <c r="L27" t="s">
-        <v>496</v>
+        <v>565</v>
       </c>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.45">
@@ -6564,25 +7689,25 @@
         <v>8</v>
       </c>
       <c r="D28" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E28" t="s">
-        <v>398</v>
+        <v>467</v>
       </c>
       <c r="F28" t="s">
-        <v>376</v>
+        <v>445</v>
       </c>
       <c r="G28" t="s">
-        <v>399</v>
+        <v>468</v>
       </c>
       <c r="H28" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K28" t="s">
-        <v>399</v>
+        <v>468</v>
       </c>
       <c r="L28" t="s">
-        <v>497</v>
+        <v>566</v>
       </c>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.45">
@@ -6593,25 +7718,25 @@
         <v>8</v>
       </c>
       <c r="D29" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E29" t="s">
-        <v>400</v>
+        <v>469</v>
       </c>
       <c r="F29" t="s">
-        <v>376</v>
+        <v>445</v>
       </c>
       <c r="G29" t="s">
-        <v>401</v>
+        <v>470</v>
       </c>
       <c r="H29" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K29" t="s">
-        <v>401</v>
+        <v>470</v>
       </c>
       <c r="L29" t="s">
-        <v>498</v>
+        <v>567</v>
       </c>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.45">
@@ -6622,25 +7747,25 @@
         <v>8</v>
       </c>
       <c r="D30" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E30" t="s">
-        <v>402</v>
+        <v>471</v>
       </c>
       <c r="F30" t="s">
-        <v>381</v>
+        <v>450</v>
       </c>
       <c r="G30" t="s">
-        <v>403</v>
+        <v>472</v>
       </c>
       <c r="H30" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K30" t="s">
-        <v>403</v>
+        <v>472</v>
       </c>
       <c r="L30" t="s">
-        <v>499</v>
+        <v>568</v>
       </c>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.45">
@@ -6651,25 +7776,25 @@
         <v>8</v>
       </c>
       <c r="D31" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E31" t="s">
-        <v>404</v>
+        <v>473</v>
       </c>
       <c r="F31" t="s">
-        <v>376</v>
+        <v>445</v>
       </c>
       <c r="G31" t="s">
-        <v>405</v>
+        <v>474</v>
       </c>
       <c r="H31" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K31" t="s">
-        <v>405</v>
+        <v>474</v>
       </c>
       <c r="L31" t="s">
-        <v>500</v>
+        <v>569</v>
       </c>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.45">
@@ -6680,25 +7805,25 @@
         <v>8</v>
       </c>
       <c r="D32" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E32" t="s">
-        <v>406</v>
+        <v>475</v>
       </c>
       <c r="F32" t="s">
-        <v>376</v>
+        <v>445</v>
       </c>
       <c r="G32" t="s">
-        <v>407</v>
+        <v>476</v>
       </c>
       <c r="H32" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K32" t="s">
-        <v>407</v>
+        <v>476</v>
       </c>
       <c r="L32" t="s">
-        <v>501</v>
+        <v>570</v>
       </c>
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.45">
@@ -6709,25 +7834,25 @@
         <v>8</v>
       </c>
       <c r="D33" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E33" t="s">
-        <v>408</v>
+        <v>477</v>
       </c>
       <c r="F33" t="s">
-        <v>384</v>
+        <v>453</v>
       </c>
       <c r="G33" t="s">
+        <v>478</v>
+      </c>
+      <c r="H33" t="s">
         <v>409</v>
       </c>
-      <c r="H33" t="s">
-        <v>340</v>
-      </c>
       <c r="K33" t="s">
-        <v>409</v>
+        <v>478</v>
       </c>
       <c r="L33" t="s">
-        <v>502</v>
+        <v>571</v>
       </c>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.45">
@@ -6738,25 +7863,25 @@
         <v>8</v>
       </c>
       <c r="D34" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E34" t="s">
-        <v>410</v>
+        <v>479</v>
       </c>
       <c r="F34" t="s">
-        <v>411</v>
+        <v>480</v>
       </c>
       <c r="G34" t="s">
-        <v>412</v>
+        <v>481</v>
       </c>
       <c r="H34" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K34" t="s">
-        <v>412</v>
+        <v>481</v>
       </c>
       <c r="L34" t="s">
-        <v>503</v>
+        <v>572</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.45">
@@ -6767,25 +7892,25 @@
         <v>8</v>
       </c>
       <c r="D35" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E35" t="s">
-        <v>413</v>
+        <v>482</v>
       </c>
       <c r="F35" t="s">
-        <v>376</v>
+        <v>445</v>
       </c>
       <c r="G35" t="s">
-        <v>414</v>
+        <v>483</v>
       </c>
       <c r="H35" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K35" t="s">
-        <v>414</v>
+        <v>483</v>
       </c>
       <c r="L35" t="s">
-        <v>504</v>
+        <v>573</v>
       </c>
     </row>
     <row r="36" spans="2:12" x14ac:dyDescent="0.45">
@@ -6796,25 +7921,25 @@
         <v>8</v>
       </c>
       <c r="D36" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E36" t="s">
-        <v>415</v>
+        <v>484</v>
       </c>
       <c r="F36" t="s">
-        <v>351</v>
+        <v>420</v>
       </c>
       <c r="G36" t="s">
-        <v>416</v>
+        <v>485</v>
       </c>
       <c r="H36" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K36" t="s">
-        <v>416</v>
+        <v>485</v>
       </c>
       <c r="L36" t="s">
-        <v>505</v>
+        <v>574</v>
       </c>
     </row>
     <row r="37" spans="2:12" x14ac:dyDescent="0.45">
@@ -6825,25 +7950,25 @@
         <v>8</v>
       </c>
       <c r="D37" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E37" t="s">
-        <v>417</v>
+        <v>486</v>
       </c>
       <c r="F37" t="s">
-        <v>418</v>
+        <v>487</v>
       </c>
       <c r="G37" t="s">
-        <v>419</v>
+        <v>488</v>
       </c>
       <c r="H37" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K37" t="s">
-        <v>419</v>
+        <v>488</v>
       </c>
       <c r="L37" t="s">
-        <v>506</v>
+        <v>575</v>
       </c>
     </row>
     <row r="38" spans="2:12" x14ac:dyDescent="0.45">
@@ -6854,25 +7979,25 @@
         <v>8</v>
       </c>
       <c r="D38" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E38" t="s">
-        <v>420</v>
+        <v>489</v>
       </c>
       <c r="F38" t="s">
-        <v>359</v>
+        <v>428</v>
       </c>
       <c r="G38" t="s">
-        <v>421</v>
+        <v>490</v>
       </c>
       <c r="H38" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K38" t="s">
-        <v>421</v>
+        <v>490</v>
       </c>
       <c r="L38" t="s">
-        <v>507</v>
+        <v>576</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.45">
@@ -6883,25 +8008,25 @@
         <v>8</v>
       </c>
       <c r="D39" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E39" t="s">
-        <v>422</v>
+        <v>491</v>
       </c>
       <c r="F39" t="s">
-        <v>376</v>
+        <v>445</v>
       </c>
       <c r="G39" t="s">
-        <v>423</v>
+        <v>492</v>
       </c>
       <c r="H39" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K39" t="s">
-        <v>423</v>
+        <v>492</v>
       </c>
       <c r="L39" t="s">
-        <v>508</v>
+        <v>577</v>
       </c>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.45">
@@ -6912,25 +8037,25 @@
         <v>8</v>
       </c>
       <c r="D40" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E40" t="s">
-        <v>424</v>
+        <v>493</v>
       </c>
       <c r="F40" t="s">
-        <v>394</v>
+        <v>463</v>
       </c>
       <c r="G40" t="s">
-        <v>425</v>
+        <v>494</v>
       </c>
       <c r="H40" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K40" t="s">
-        <v>425</v>
+        <v>494</v>
       </c>
       <c r="L40" t="s">
-        <v>509</v>
+        <v>578</v>
       </c>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.45">
@@ -6941,25 +8066,25 @@
         <v>8</v>
       </c>
       <c r="D41" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E41" t="s">
-        <v>426</v>
+        <v>495</v>
       </c>
       <c r="F41" t="s">
-        <v>362</v>
+        <v>431</v>
       </c>
       <c r="G41" t="s">
-        <v>427</v>
+        <v>496</v>
       </c>
       <c r="H41" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K41" t="s">
-        <v>427</v>
+        <v>496</v>
       </c>
       <c r="L41" t="s">
-        <v>510</v>
+        <v>579</v>
       </c>
     </row>
     <row r="42" spans="2:12" x14ac:dyDescent="0.45">
@@ -6970,25 +8095,25 @@
         <v>8</v>
       </c>
       <c r="D42" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E42" t="s">
-        <v>428</v>
+        <v>497</v>
       </c>
       <c r="F42" t="s">
-        <v>429</v>
+        <v>498</v>
       </c>
       <c r="G42" t="s">
-        <v>430</v>
+        <v>499</v>
       </c>
       <c r="H42" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K42" t="s">
-        <v>430</v>
+        <v>499</v>
       </c>
       <c r="L42" t="s">
-        <v>511</v>
+        <v>580</v>
       </c>
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.45">
@@ -6999,25 +8124,25 @@
         <v>8</v>
       </c>
       <c r="D43" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E43" t="s">
-        <v>431</v>
+        <v>500</v>
       </c>
       <c r="F43" t="s">
-        <v>394</v>
+        <v>463</v>
       </c>
       <c r="G43" t="s">
-        <v>432</v>
+        <v>501</v>
       </c>
       <c r="H43" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K43" t="s">
-        <v>432</v>
+        <v>501</v>
       </c>
       <c r="L43" t="s">
-        <v>512</v>
+        <v>581</v>
       </c>
     </row>
     <row r="44" spans="2:12" x14ac:dyDescent="0.45">
@@ -7028,25 +8153,25 @@
         <v>8</v>
       </c>
       <c r="D44" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E44" t="s">
-        <v>433</v>
+        <v>502</v>
       </c>
       <c r="F44" t="s">
-        <v>373</v>
+        <v>442</v>
       </c>
       <c r="G44" t="s">
-        <v>434</v>
+        <v>503</v>
       </c>
       <c r="H44" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K44" t="s">
-        <v>434</v>
+        <v>503</v>
       </c>
       <c r="L44" t="s">
-        <v>513</v>
+        <v>582</v>
       </c>
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.45">
@@ -7057,25 +8182,25 @@
         <v>8</v>
       </c>
       <c r="D45" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E45" t="s">
-        <v>435</v>
+        <v>504</v>
       </c>
       <c r="F45" t="s">
-        <v>394</v>
+        <v>463</v>
       </c>
       <c r="G45" t="s">
-        <v>436</v>
+        <v>505</v>
       </c>
       <c r="H45" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K45" t="s">
-        <v>436</v>
+        <v>505</v>
       </c>
       <c r="L45" t="s">
-        <v>514</v>
+        <v>583</v>
       </c>
     </row>
     <row r="46" spans="2:12" x14ac:dyDescent="0.45">
@@ -7086,25 +8211,25 @@
         <v>8</v>
       </c>
       <c r="D46" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E46" t="s">
-        <v>437</v>
+        <v>506</v>
       </c>
       <c r="F46" t="s">
-        <v>394</v>
+        <v>463</v>
       </c>
       <c r="G46" t="s">
-        <v>438</v>
+        <v>507</v>
       </c>
       <c r="H46" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K46" t="s">
-        <v>438</v>
+        <v>507</v>
       </c>
       <c r="L46" t="s">
-        <v>515</v>
+        <v>584</v>
       </c>
     </row>
     <row r="47" spans="2:12" x14ac:dyDescent="0.45">
@@ -7115,25 +8240,25 @@
         <v>8</v>
       </c>
       <c r="D47" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E47" t="s">
-        <v>439</v>
+        <v>508</v>
       </c>
       <c r="F47" t="s">
-        <v>338</v>
+        <v>407</v>
       </c>
       <c r="G47" t="s">
-        <v>440</v>
+        <v>509</v>
       </c>
       <c r="H47" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K47" t="s">
-        <v>440</v>
+        <v>509</v>
       </c>
       <c r="L47" t="s">
-        <v>516</v>
+        <v>585</v>
       </c>
     </row>
     <row r="48" spans="2:12" x14ac:dyDescent="0.45">
@@ -7144,25 +8269,25 @@
         <v>8</v>
       </c>
       <c r="D48" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E48" t="s">
-        <v>441</v>
+        <v>510</v>
       </c>
       <c r="F48" t="s">
-        <v>442</v>
+        <v>511</v>
       </c>
       <c r="G48" t="s">
-        <v>443</v>
+        <v>512</v>
       </c>
       <c r="H48" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K48" t="s">
-        <v>443</v>
+        <v>512</v>
       </c>
       <c r="L48" t="s">
-        <v>517</v>
+        <v>586</v>
       </c>
     </row>
     <row r="49" spans="2:12" x14ac:dyDescent="0.45">
@@ -7173,25 +8298,25 @@
         <v>8</v>
       </c>
       <c r="D49" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E49" t="s">
-        <v>444</v>
+        <v>513</v>
       </c>
       <c r="F49" t="s">
-        <v>445</v>
+        <v>514</v>
       </c>
       <c r="G49" t="s">
-        <v>446</v>
+        <v>515</v>
       </c>
       <c r="H49" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K49" t="s">
-        <v>446</v>
+        <v>515</v>
       </c>
       <c r="L49" t="s">
-        <v>518</v>
+        <v>587</v>
       </c>
     </row>
     <row r="50" spans="2:12" x14ac:dyDescent="0.45">
@@ -7202,25 +8327,25 @@
         <v>8</v>
       </c>
       <c r="D50" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E50" t="s">
-        <v>447</v>
+        <v>516</v>
       </c>
       <c r="F50" t="s">
-        <v>448</v>
+        <v>517</v>
       </c>
       <c r="G50" t="s">
-        <v>449</v>
+        <v>518</v>
       </c>
       <c r="H50" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K50" t="s">
-        <v>449</v>
+        <v>518</v>
       </c>
       <c r="L50" t="s">
-        <v>519</v>
+        <v>588</v>
       </c>
     </row>
     <row r="51" spans="2:12" x14ac:dyDescent="0.45">
@@ -7231,25 +8356,25 @@
         <v>8</v>
       </c>
       <c r="D51" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E51" t="s">
-        <v>450</v>
+        <v>519</v>
       </c>
       <c r="F51" t="s">
-        <v>394</v>
+        <v>463</v>
       </c>
       <c r="G51" t="s">
-        <v>451</v>
+        <v>520</v>
       </c>
       <c r="H51" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K51" t="s">
-        <v>451</v>
+        <v>520</v>
       </c>
       <c r="L51" t="s">
-        <v>520</v>
+        <v>589</v>
       </c>
     </row>
     <row r="52" spans="2:12" x14ac:dyDescent="0.45">
@@ -7260,25 +8385,25 @@
         <v>8</v>
       </c>
       <c r="D52" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E52" t="s">
-        <v>452</v>
+        <v>521</v>
       </c>
       <c r="F52" t="s">
-        <v>376</v>
+        <v>445</v>
       </c>
       <c r="G52" t="s">
-        <v>453</v>
+        <v>522</v>
       </c>
       <c r="H52" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K52" t="s">
-        <v>453</v>
+        <v>522</v>
       </c>
       <c r="L52" t="s">
-        <v>521</v>
+        <v>590</v>
       </c>
     </row>
     <row r="53" spans="2:12" x14ac:dyDescent="0.45">
@@ -7289,25 +8414,25 @@
         <v>8</v>
       </c>
       <c r="D53" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E53" t="s">
-        <v>441</v>
+        <v>510</v>
       </c>
       <c r="F53" t="s">
-        <v>454</v>
+        <v>523</v>
       </c>
       <c r="G53" t="s">
-        <v>455</v>
+        <v>524</v>
       </c>
       <c r="H53" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K53" t="s">
-        <v>455</v>
+        <v>524</v>
       </c>
       <c r="L53" t="s">
-        <v>522</v>
+        <v>591</v>
       </c>
     </row>
     <row r="54" spans="2:12" x14ac:dyDescent="0.45">
@@ -7318,25 +8443,25 @@
         <v>8</v>
       </c>
       <c r="D54" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E54" t="s">
-        <v>441</v>
+        <v>510</v>
       </c>
       <c r="F54" t="s">
-        <v>456</v>
+        <v>525</v>
       </c>
       <c r="G54" t="s">
-        <v>457</v>
+        <v>526</v>
       </c>
       <c r="H54" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K54" t="s">
-        <v>457</v>
+        <v>526</v>
       </c>
       <c r="L54" t="s">
-        <v>523</v>
+        <v>592</v>
       </c>
     </row>
     <row r="55" spans="2:12" x14ac:dyDescent="0.45">
@@ -7347,25 +8472,25 @@
         <v>8</v>
       </c>
       <c r="D55" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E55" t="s">
-        <v>441</v>
+        <v>510</v>
       </c>
       <c r="F55" t="s">
-        <v>458</v>
+        <v>527</v>
       </c>
       <c r="G55" t="s">
-        <v>459</v>
+        <v>528</v>
       </c>
       <c r="H55" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K55" t="s">
-        <v>459</v>
+        <v>528</v>
       </c>
       <c r="L55" t="s">
-        <v>524</v>
+        <v>593</v>
       </c>
     </row>
     <row r="56" spans="2:12" x14ac:dyDescent="0.45">
@@ -7376,25 +8501,25 @@
         <v>8</v>
       </c>
       <c r="D56" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E56" t="s">
-        <v>410</v>
+        <v>479</v>
       </c>
       <c r="F56" t="s">
-        <v>460</v>
+        <v>529</v>
       </c>
       <c r="G56" t="s">
-        <v>461</v>
+        <v>530</v>
       </c>
       <c r="H56" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K56" t="s">
-        <v>461</v>
+        <v>530</v>
       </c>
       <c r="L56" t="s">
-        <v>525</v>
+        <v>594</v>
       </c>
     </row>
     <row r="57" spans="2:12" x14ac:dyDescent="0.45">
@@ -7405,25 +8530,25 @@
         <v>8</v>
       </c>
       <c r="D57" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E57" t="s">
-        <v>417</v>
+        <v>486</v>
       </c>
       <c r="F57" t="s">
-        <v>462</v>
+        <v>531</v>
       </c>
       <c r="G57" t="s">
-        <v>463</v>
+        <v>532</v>
       </c>
       <c r="H57" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K57" t="s">
-        <v>463</v>
+        <v>532</v>
       </c>
       <c r="L57" t="s">
-        <v>526</v>
+        <v>595</v>
       </c>
     </row>
     <row r="58" spans="2:12" x14ac:dyDescent="0.45">
@@ -7434,25 +8559,25 @@
         <v>8</v>
       </c>
       <c r="D58" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E58" t="s">
-        <v>372</v>
+        <v>441</v>
       </c>
       <c r="F58" t="s">
-        <v>464</v>
+        <v>533</v>
       </c>
       <c r="G58" t="s">
-        <v>465</v>
+        <v>534</v>
       </c>
       <c r="H58" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K58" t="s">
-        <v>465</v>
+        <v>534</v>
       </c>
       <c r="L58" t="s">
-        <v>527</v>
+        <v>596</v>
       </c>
     </row>
     <row r="59" spans="2:12" x14ac:dyDescent="0.45">
@@ -7463,25 +8588,25 @@
         <v>8</v>
       </c>
       <c r="D59" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E59" t="s">
-        <v>372</v>
+        <v>441</v>
       </c>
       <c r="F59" t="s">
-        <v>466</v>
+        <v>535</v>
       </c>
       <c r="G59" t="s">
-        <v>467</v>
+        <v>536</v>
       </c>
       <c r="H59" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K59" t="s">
-        <v>467</v>
+        <v>536</v>
       </c>
       <c r="L59" t="s">
-        <v>528</v>
+        <v>597</v>
       </c>
     </row>
     <row r="60" spans="2:12" x14ac:dyDescent="0.45">
@@ -7492,25 +8617,25 @@
         <v>8</v>
       </c>
       <c r="D60" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E60" t="s">
-        <v>380</v>
+        <v>449</v>
       </c>
       <c r="F60" t="s">
-        <v>468</v>
+        <v>537</v>
       </c>
       <c r="G60" t="s">
-        <v>469</v>
+        <v>538</v>
       </c>
       <c r="H60" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K60" t="s">
-        <v>469</v>
+        <v>538</v>
       </c>
       <c r="L60" t="s">
-        <v>529</v>
+        <v>598</v>
       </c>
     </row>
     <row r="61" spans="2:12" x14ac:dyDescent="0.45">
@@ -7521,25 +8646,25 @@
         <v>8</v>
       </c>
       <c r="D61" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E61" t="s">
-        <v>372</v>
+        <v>441</v>
       </c>
       <c r="F61" t="s">
-        <v>470</v>
+        <v>539</v>
       </c>
       <c r="G61" t="s">
-        <v>471</v>
+        <v>540</v>
       </c>
       <c r="H61" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K61" t="s">
-        <v>471</v>
+        <v>540</v>
       </c>
       <c r="L61" t="s">
-        <v>530</v>
+        <v>599</v>
       </c>
     </row>
     <row r="62" spans="2:12" x14ac:dyDescent="0.45">
@@ -7550,25 +8675,25 @@
         <v>8</v>
       </c>
       <c r="D62" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
       <c r="E62" t="s">
-        <v>422</v>
+        <v>491</v>
       </c>
       <c r="F62" t="s">
-        <v>472</v>
+        <v>541</v>
       </c>
       <c r="G62" t="s">
-        <v>473</v>
+        <v>542</v>
       </c>
       <c r="H62" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="K62" t="s">
-        <v>473</v>
+        <v>542</v>
       </c>
       <c r="L62" t="s">
-        <v>531</v>
+        <v>600</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC4745F5-BA4E-4AA7-A7A0-2B3282D29505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{92B27EBF-F8A0-4451-910B-9D6DC9492626}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="12772" activeTab="1" xr2:uid="{9A54E98D-23AE-4D31-9BE3-10F31EF7061F}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="12772" activeTab="1" xr2:uid="{DB0057FC-08A0-4573-AD6A-33DE9E5EBBA7}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2190,7 +2190,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09C7407E-6768-42AB-845B-F5FD3722BCC2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACF917C8-41ED-474A-8F99-9C8CB2D6B467}">
   <dimension ref="B3:S155"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6973,7 +6973,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF27E646-DCD4-477B-8725-771F59E2B283}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{498974E5-2C79-4E7B-8BC8-95C6C5774924}">
   <dimension ref="B3:L62"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
